--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C00B95-DFE5-46E3-8FD0-EAB2DF77F0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664414AC-3491-47C3-8C12-D7E898FE868F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,6 +883,10 @@
     <xf numFmtId="176" fontId="7" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -898,15 +902,53 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="216">
+  <dxfs count="219">
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3684,13 +3726,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3710,13 +3752,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -3741,7 +3783,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="12">
-        <f t="shared" ref="E6:E24" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
+        <f t="shared" ref="E6:E31" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
         <v>1</v>
       </c>
     </row>
@@ -3926,7 +3968,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="20" t="str">
+      <c r="E17" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3938,7 +3980,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="20" t="str">
+      <c r="E18" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3950,7 +3992,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="20" t="str">
+      <c r="E19" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3962,7 +4004,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="20" t="str">
+      <c r="E20" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3974,7 +4016,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="20" t="str">
+      <c r="E21" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3986,7 +4028,7 @@
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="20" t="str">
+      <c r="E22" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3998,7 +4040,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="20" t="str">
+      <c r="E23" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4010,7 +4052,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="20" t="str">
+      <c r="E24" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4022,9 +4064,9 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="21"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>28</v>
       </c>
@@ -4037,12 +4079,12 @@
       <c r="D26" s="2">
         <v>5</v>
       </c>
-      <c r="E26" s="20">
-        <f t="shared" ref="E26:E31" si="1">IF(AND(C26&lt;&gt;"",D26&lt;&gt;""),D26/C26,"")</f>
+      <c r="E26" s="12">
+        <f t="shared" si="0"/>
         <v>0.45454545454545453</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>29</v>
       </c>
@@ -4055,12 +4097,12 @@
       <c r="D27" s="2">
         <v>15</v>
       </c>
-      <c r="E27" s="20">
-        <f t="shared" si="1"/>
+      <c r="E27" s="12">
+        <f t="shared" si="0"/>
         <v>0.78947368421052633</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>30</v>
       </c>
@@ -4073,12 +4115,12 @@
       <c r="D28" s="2">
         <v>13</v>
       </c>
-      <c r="E28" s="20">
-        <f t="shared" si="1"/>
+      <c r="E28" s="12">
+        <f t="shared" si="0"/>
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>31</v>
       </c>
@@ -4091,32 +4133,32 @@
       <c r="D29" s="2">
         <v>11</v>
       </c>
-      <c r="E29" s="20">
-        <f t="shared" si="1"/>
+      <c r="E29" s="12">
+        <f t="shared" si="0"/>
         <v>0.6470588235294118</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="20" t="str">
-        <f t="shared" si="1"/>
+      <c r="E31" s="12" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -4127,7 +4169,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="21"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
@@ -4136,8 +4178,8 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="20" t="str">
-        <f t="shared" ref="E33:E38" si="2">IF(AND(C33&lt;&gt;"",D33&lt;&gt;""),D33/C33,"")</f>
+      <c r="E33" s="13" t="str">
+        <f t="shared" ref="E33:E38" si="1">IF(AND(C33&lt;&gt;"",D33&lt;&gt;""),D33/C33,"")</f>
         <v/>
       </c>
     </row>
@@ -4148,8 +4190,8 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="E34" s="13" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4160,8 +4202,8 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="E35" s="13" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4172,8 +4214,8 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="E36" s="13" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4184,8 +4226,8 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="E37" s="13" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4196,8 +4238,8 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="E38" s="13" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4220,13 +4262,13 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="17"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
@@ -4245,7 +4287,7 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="str">
-        <f t="shared" ref="E43:E60" si="3">IF(AND(C43&lt;&gt;"",D43&lt;&gt;""),D43/C43,"")</f>
+        <f t="shared" ref="E43:E60" si="2">IF(AND(C43&lt;&gt;"",D43&lt;&gt;""),D43/C43,"")</f>
         <v/>
       </c>
     </row>
@@ -4257,7 +4299,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4269,7 +4311,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4281,7 +4323,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4293,7 +4335,7 @@
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4305,7 +4347,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4317,7 +4359,7 @@
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4329,7 +4371,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4341,7 +4383,7 @@
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4353,7 +4395,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4365,7 +4407,7 @@
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4377,7 +4419,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4389,7 +4431,7 @@
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4401,7 +4443,7 @@
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4413,7 +4455,7 @@
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4425,7 +4467,7 @@
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4437,7 +4479,7 @@
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4449,7 +4491,7 @@
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4472,13 +4514,13 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="15"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="17"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
@@ -4497,7 +4539,7 @@
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2" t="str">
-        <f t="shared" ref="E65:E73" si="4">IF(AND(C65&lt;&gt;"",D65&lt;&gt;""),D65/C65,"")</f>
+        <f t="shared" ref="E65:E73" si="3">IF(AND(C65&lt;&gt;"",D65&lt;&gt;""),D65/C65,"")</f>
         <v/>
       </c>
     </row>
@@ -4509,7 +4551,7 @@
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4521,7 +4563,7 @@
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4533,7 +4575,7 @@
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4545,7 +4587,7 @@
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4557,7 +4599,7 @@
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4569,7 +4611,7 @@
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4581,7 +4623,7 @@
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4593,7 +4635,7 @@
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4614,7 +4656,7 @@
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2" t="str">
-        <f t="shared" ref="E75:E83" si="5">IF(AND(C75&lt;&gt;"",D75&lt;&gt;""),D75/C75,"")</f>
+        <f t="shared" ref="E75:E83" si="4">IF(AND(C75&lt;&gt;"",D75&lt;&gt;""),D75/C75,"")</f>
         <v/>
       </c>
     </row>
@@ -4626,7 +4668,7 @@
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4638,7 +4680,7 @@
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4650,7 +4692,7 @@
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4662,7 +4704,7 @@
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4674,7 +4716,7 @@
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4686,7 +4728,7 @@
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4698,7 +4740,7 @@
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4710,18 +4752,18 @@
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="15"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="17"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
@@ -4898,134 +4940,134 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E16">
-    <cfRule type="cellIs" dxfId="215" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="218" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="217" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17:E24">
-    <cfRule type="cellIs" dxfId="212" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="215" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34:E38">
+    <cfRule type="cellIs" dxfId="209" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="207" priority="84" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="cellIs" dxfId="206" priority="214" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="215" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="216" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E43:E60">
+    <cfRule type="cellIs" dxfId="203" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="99" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64:E73">
+    <cfRule type="cellIs" dxfId="200" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="153" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E76:E83">
+    <cfRule type="cellIs" dxfId="197" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="180" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E85:E88">
+    <cfRule type="cellIs" dxfId="194" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="204" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E91">
+    <cfRule type="cellIs" dxfId="191" priority="223" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="224" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="189" priority="225" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E94">
+    <cfRule type="cellIs" dxfId="188" priority="220" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="221" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="222" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E31">
-    <cfRule type="cellIs" dxfId="209" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="63" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E34:E38">
-    <cfRule type="cellIs" dxfId="206" priority="79" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="81" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="203" priority="211" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="212" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="213" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E43:E60">
-    <cfRule type="cellIs" dxfId="200" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E64:E73">
-    <cfRule type="cellIs" dxfId="197" priority="148" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="149" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="150" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E83">
-    <cfRule type="cellIs" dxfId="194" priority="175" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="176" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="177" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E85:E88">
-    <cfRule type="cellIs" dxfId="191" priority="199" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="200" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="201" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E91">
-    <cfRule type="cellIs" dxfId="188" priority="220" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="221" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="222" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E94">
-    <cfRule type="cellIs" dxfId="185" priority="217" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="218" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="219" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5049,32 +5091,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -5650,146 +5692,146 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E11">
-    <cfRule type="cellIs" dxfId="182" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="185" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="179" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="182" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="176" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="179" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="39" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="173" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="45" operator="lessThan">
+    <cfRule type="cellIs" dxfId="176" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="45" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E28">
-    <cfRule type="cellIs" dxfId="170" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="54" operator="lessThan">
+    <cfRule type="cellIs" dxfId="173" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="53" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="54" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="167" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="170" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="66" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I11">
-    <cfRule type="cellIs" dxfId="164" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="69" operator="lessThan">
+    <cfRule type="cellIs" dxfId="167" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="165" priority="69" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="161" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="87" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="158" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="161" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I23">
-    <cfRule type="cellIs" dxfId="155" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="158" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:I28">
-    <cfRule type="cellIs" dxfId="152" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="cellIs" dxfId="149" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5813,32 +5855,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6744,206 +6786,206 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="146" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="143" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="140" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="143" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="137" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="140" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="134" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="137" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="131" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="134" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E39">
-    <cfRule type="cellIs" dxfId="128" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="3" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="131" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="125" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="128" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="122" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="125" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I8">
-    <cfRule type="cellIs" dxfId="119" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="117" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="117" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I12">
-    <cfRule type="cellIs" dxfId="116" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I19">
-    <cfRule type="cellIs" dxfId="113" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I24">
-    <cfRule type="cellIs" dxfId="110" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I32">
-    <cfRule type="cellIs" dxfId="107" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="110" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I35">
-    <cfRule type="cellIs" dxfId="104" priority="184" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="185" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="186" operator="lessThan">
+    <cfRule type="cellIs" dxfId="107" priority="184" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="185" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="186" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37:I40">
-    <cfRule type="cellIs" dxfId="101" priority="190" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="191" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="192" operator="lessThan">
+    <cfRule type="cellIs" dxfId="104" priority="190" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="191" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="192" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42">
-    <cfRule type="cellIs" dxfId="98" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6967,32 +7009,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -7827,218 +7869,218 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="92" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="89" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="86" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="83" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="80" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="51" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="77" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="74" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="71" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="74" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="68" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="65" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="111" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="111" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="62" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="120" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="120" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="59" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I25">
-    <cfRule type="cellIs" dxfId="56" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I30">
-    <cfRule type="cellIs" dxfId="53" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:I36">
-    <cfRule type="cellIs" dxfId="50" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38:I45">
-    <cfRule type="cellIs" dxfId="47" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="cellIs" dxfId="44" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8062,32 +8104,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -8816,170 +8858,170 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="38" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="35" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="32" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="29" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="26" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="23" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="90" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="90" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="20" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="17" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I20">
-    <cfRule type="cellIs" dxfId="14" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I28">
-    <cfRule type="cellIs" dxfId="11" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I32">
-    <cfRule type="cellIs" dxfId="8" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I39">
-    <cfRule type="cellIs" dxfId="5" priority="160" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="161" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="cellIs" dxfId="2" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664414AC-3491-47C3-8C12-D7E898FE868F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D8D9D1-51AA-419A-8815-DD5A09980CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -906,7 +906,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="219">
+  <dxfs count="225">
     <dxf>
       <font>
         <b/>
@@ -951,7 +951,10 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -962,1376 +965,15 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2381,6 +1023,1420 @@
       <font>
         <b/>
         <sz val="10.5"/>
+        <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF9C0006"/>
         <name val="微软雅黑"/>
       </font>
@@ -2409,6 +2465,34 @@
       <font>
         <b/>
         <sz val="10.5"/>
+        <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF006100"/>
         <name val="微软雅黑"/>
       </font>
@@ -3309,7 +3393,10 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3320,7 +3407,10 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3331,7 +3421,10 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -4940,134 +5033,134 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E16">
-    <cfRule type="cellIs" dxfId="218" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="224" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="222" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17:E24">
-    <cfRule type="cellIs" dxfId="215" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="221" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="220" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="219" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E31">
+    <cfRule type="cellIs" dxfId="218" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="217" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E38">
-    <cfRule type="cellIs" dxfId="209" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="215" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="84" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="206" priority="214" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="215" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="216" operator="lessThan">
+    <cfRule type="cellIs" dxfId="212" priority="214" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="215" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="216" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:E60">
-    <cfRule type="cellIs" dxfId="203" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="209" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="207" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64:E73">
-    <cfRule type="cellIs" dxfId="200" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="206" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E76:E83">
-    <cfRule type="cellIs" dxfId="197" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="203" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85:E88">
-    <cfRule type="cellIs" dxfId="194" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="200" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E91">
-    <cfRule type="cellIs" dxfId="191" priority="223" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="224" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="225" operator="lessThan">
+    <cfRule type="cellIs" dxfId="197" priority="223" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="224" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="225" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E94">
-    <cfRule type="cellIs" dxfId="188" priority="220" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="221" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="222" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E31">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="194" priority="220" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="221" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="222" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5434,16 +5527,22 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2" t="str">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;""),D18/C18,"")</f>
-        <v/>
+      <c r="B18" s="11">
+        <v>609</v>
+      </c>
+      <c r="C18" s="11">
+        <v>72</v>
+      </c>
+      <c r="D18" s="11">
+        <v>51</v>
+      </c>
+      <c r="E18" s="12">
+        <f t="shared" ref="E18:E19" si="2">IF(AND(C18&lt;&gt;"",D18&lt;&gt;""),D18/C18,"")</f>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -5453,15 +5552,15 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2" t="str">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;""),D19/C19,"")</f>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F19" s="9"/>
@@ -5485,15 +5584,15 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2" t="str">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),D21/C21,"")</f>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12" t="str">
+        <f t="shared" ref="E21:E23" si="3">IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),D21/C21,"")</f>
         <v/>
       </c>
       <c r="F21" s="9"/>
@@ -5504,15 +5603,15 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2" t="str">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;""),D22/C22,"")</f>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="F22" s="9"/>
@@ -5523,15 +5622,15 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2" t="str">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;""),D23/C23,"")</f>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="F23" s="9"/>
@@ -5555,15 +5654,15 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="str">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;""),D25/C25,"")</f>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12" t="str">
+        <f t="shared" ref="E25:E27" si="4">IF(AND(C25&lt;&gt;"",D25&lt;&gt;""),D25/C25,"")</f>
         <v/>
       </c>
       <c r="F25" s="9"/>
@@ -5574,15 +5673,15 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="str">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;""),D26/C26,"")</f>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F26" s="9"/>
@@ -5593,15 +5692,15 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2" t="str">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;""),D27/C27,"")</f>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F27" s="9"/>
@@ -5619,15 +5718,15 @@
       <c r="B28" s="8"/>
       <c r="C28" s="8">
         <f>SUM(C5:C27)</f>
-        <v>361</v>
+        <v>433</v>
       </c>
       <c r="D28" s="8">
         <f>SUM(D5:D27)</f>
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="E28" s="8">
         <f>IF(C28&gt;0, D28/C28,"")</f>
-        <v>0.75900277008310246</v>
+        <v>0.75057736720554269</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8">
@@ -5650,15 +5749,15 @@
       <c r="B30" s="5"/>
       <c r="C30" s="5">
         <f>C28+G28</f>
-        <v>361</v>
+        <v>433</v>
       </c>
       <c r="D30" s="5">
         <f>D28+H28</f>
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="E30" s="5">
         <f>IF(C30&gt;0, D30/C30,"")</f>
-        <v>0.75900277008310246</v>
+        <v>0.75057736720554269</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -5692,146 +5791,158 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E11">
-    <cfRule type="cellIs" dxfId="185" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="191" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="189" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="182" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="188" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28">
+    <cfRule type="cellIs" dxfId="179" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="63" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="cellIs" dxfId="176" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="75" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:I11">
+    <cfRule type="cellIs" dxfId="173" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="78" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13:I16">
+    <cfRule type="cellIs" dxfId="170" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18:I19">
+    <cfRule type="cellIs" dxfId="167" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="165" priority="108" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21:I23">
+    <cfRule type="cellIs" dxfId="164" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="114" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25:I28">
+    <cfRule type="cellIs" dxfId="161" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="123" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30">
+    <cfRule type="cellIs" dxfId="158" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="179" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="176" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="45" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E25:E28">
-    <cfRule type="cellIs" dxfId="173" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="170" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="66" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I11">
-    <cfRule type="cellIs" dxfId="167" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="164" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="87" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="161" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="99" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21:I23">
-    <cfRule type="cellIs" dxfId="158" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="105" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25:I28">
-    <cfRule type="cellIs" dxfId="155" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I30">
-    <cfRule type="cellIs" dxfId="152" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="126" operator="lessThan">
+  <conditionalFormatting sqref="E25:E27">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6786,206 +6897,206 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="149" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="146" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="143" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="140" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="137" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="143" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="134" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="140" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E39">
-    <cfRule type="cellIs" dxfId="131" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="3" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="137" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="128" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="134" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="125" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I8">
-    <cfRule type="cellIs" dxfId="122" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="117" operator="lessThan">
+    <cfRule type="cellIs" dxfId="128" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="117" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I12">
-    <cfRule type="cellIs" dxfId="119" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="125" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I19">
-    <cfRule type="cellIs" dxfId="116" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I24">
-    <cfRule type="cellIs" dxfId="113" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I32">
-    <cfRule type="cellIs" dxfId="110" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I35">
-    <cfRule type="cellIs" dxfId="107" priority="184" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="185" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="186" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="184" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="185" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="186" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37:I40">
-    <cfRule type="cellIs" dxfId="104" priority="190" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="191" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="192" operator="lessThan">
+    <cfRule type="cellIs" dxfId="110" priority="190" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="191" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="192" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42">
-    <cfRule type="cellIs" dxfId="101" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="107" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7869,218 +7980,218 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="98" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="104" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="95" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="92" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="89" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="86" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="83" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="51" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="80" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="77" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="74" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="71" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="68" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="111" operator="lessThan">
+    <cfRule type="cellIs" dxfId="74" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="111" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="65" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="120" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="120" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="62" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I25">
-    <cfRule type="cellIs" dxfId="59" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I30">
-    <cfRule type="cellIs" dxfId="56" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:I36">
-    <cfRule type="cellIs" dxfId="53" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38:I45">
-    <cfRule type="cellIs" dxfId="50" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="cellIs" dxfId="47" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8858,170 +8969,170 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="41" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="38" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="35" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="32" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="29" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="26" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="90" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="90" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="23" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="20" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I20">
-    <cfRule type="cellIs" dxfId="17" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I28">
-    <cfRule type="cellIs" dxfId="14" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I32">
-    <cfRule type="cellIs" dxfId="11" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I39">
-    <cfRule type="cellIs" dxfId="8" priority="160" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="161" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="cellIs" dxfId="5" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D8D9D1-51AA-419A-8815-DD5A09980CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C12D7B-A3E8-4CEF-8A67-96D13D4CAE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -887,7 +887,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -896,17 +896,1417 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="225">
+  <dxfs count="219">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -939,6 +2339,34 @@
       <font>
         <b/>
         <sz val="10.5"/>
+        <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF006100"/>
         <name val="微软雅黑"/>
       </font>
@@ -1035,7 +2463,10 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1046,1376 +2477,15 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2465,6 +2535,20 @@
       <font>
         <b/>
         <sz val="10.5"/>
+        <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF9C0006"/>
         <name val="微软雅黑"/>
       </font>
@@ -2505,6 +2589,270 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <sz val="10.5"/>
         <color rgb="FF9C0006"/>
@@ -2621,420 +2969,6 @@
         <sz val="10.5"/>
         <color rgb="FF006100"/>
         <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF9C0006"/>
-        <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF9C6500"/>
-        <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF006100"/>
-        <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF9C0006"/>
-        <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF9C6500"/>
-        <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF006100"/>
-        <name val="微软雅黑"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3845,7 +3779,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="16"/>
@@ -4355,7 +4289,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="21" t="s">
         <v>42</v>
       </c>
       <c r="B41" s="16"/>
@@ -4607,7 +4541,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="21" t="s">
         <v>44</v>
       </c>
       <c r="B63" s="16"/>
@@ -4850,7 +4784,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B84" s="16"/>
@@ -5033,134 +4967,134 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E16">
-    <cfRule type="cellIs" dxfId="224" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="218" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="217" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17:E24">
-    <cfRule type="cellIs" dxfId="221" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="215" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E31">
-    <cfRule type="cellIs" dxfId="218" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="212" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E38">
-    <cfRule type="cellIs" dxfId="215" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="209" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="207" priority="84" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="212" priority="214" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="215" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="216" operator="lessThan">
+    <cfRule type="cellIs" dxfId="206" priority="214" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="215" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="216" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:E60">
-    <cfRule type="cellIs" dxfId="209" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="203" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64:E73">
-    <cfRule type="cellIs" dxfId="206" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="200" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E76:E83">
-    <cfRule type="cellIs" dxfId="203" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="197" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85:E88">
-    <cfRule type="cellIs" dxfId="200" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="194" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E91">
-    <cfRule type="cellIs" dxfId="197" priority="223" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="224" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="225" operator="lessThan">
+    <cfRule type="cellIs" dxfId="191" priority="223" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="224" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="189" priority="225" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E94">
-    <cfRule type="cellIs" dxfId="194" priority="220" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="221" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="222" operator="lessThan">
+    <cfRule type="cellIs" dxfId="188" priority="220" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="221" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="222" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5197,7 +5131,7 @@
       <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B3" s="16"/>
@@ -5205,7 +5139,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="15" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="16"/>
@@ -5556,12 +5490,18 @@
       <c r="A19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="12" t="str">
+      <c r="B19" s="11">
+        <v>610</v>
+      </c>
+      <c r="C19" s="11">
+        <v>61</v>
+      </c>
+      <c r="D19" s="11">
+        <v>46</v>
+      </c>
+      <c r="E19" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.75409836065573765</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -5718,15 +5658,15 @@
       <c r="B28" s="8"/>
       <c r="C28" s="8">
         <f>SUM(C5:C27)</f>
-        <v>433</v>
+        <v>494</v>
       </c>
       <c r="D28" s="8">
         <f>SUM(D5:D27)</f>
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="E28" s="8">
         <f>IF(C28&gt;0, D28/C28,"")</f>
-        <v>0.75057736720554269</v>
+        <v>0.75101214574898789</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8">
@@ -5749,15 +5689,15 @@
       <c r="B30" s="5"/>
       <c r="C30" s="5">
         <f>C28+G28</f>
-        <v>433</v>
+        <v>494</v>
       </c>
       <c r="D30" s="5">
         <f>D28+H28</f>
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="E30" s="5">
         <f>IF(C30&gt;0, D30/C30,"")</f>
-        <v>0.75057736720554269</v>
+        <v>0.75101214574898789</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -5791,158 +5731,158 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E11">
-    <cfRule type="cellIs" dxfId="191" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="185" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="188" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="182" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18:E19">
+    <cfRule type="cellIs" dxfId="179" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E23">
+    <cfRule type="cellIs" dxfId="176" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="6" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:E27">
+    <cfRule type="cellIs" dxfId="173" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="cellIs" dxfId="179" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="170" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="176" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="167" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="165" priority="75" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I11">
-    <cfRule type="cellIs" dxfId="173" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="170" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="161" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="96" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="167" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="158" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I23">
-    <cfRule type="cellIs" dxfId="164" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:I28">
-    <cfRule type="cellIs" dxfId="161" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="cellIs" dxfId="158" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="135" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25:E27">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5979,7 +5919,7 @@
       <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B3" s="16"/>
@@ -5987,7 +5927,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="15" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="16"/>
@@ -6897,206 +6837,206 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="155" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="152" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="143" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="149" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="140" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="146" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="137" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="143" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="134" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="140" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E39">
-    <cfRule type="cellIs" dxfId="137" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="3" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="128" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="134" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="125" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="131" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I8">
-    <cfRule type="cellIs" dxfId="128" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="117" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="117" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I12">
-    <cfRule type="cellIs" dxfId="125" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I19">
-    <cfRule type="cellIs" dxfId="122" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I24">
-    <cfRule type="cellIs" dxfId="119" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="110" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I32">
-    <cfRule type="cellIs" dxfId="116" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="107" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I35">
-    <cfRule type="cellIs" dxfId="113" priority="184" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="185" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="186" operator="lessThan">
+    <cfRule type="cellIs" dxfId="104" priority="184" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="185" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="186" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37:I40">
-    <cfRule type="cellIs" dxfId="110" priority="190" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="191" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="192" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="190" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="191" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="192" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42">
-    <cfRule type="cellIs" dxfId="107" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7133,7 +7073,7 @@
       <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B3" s="16"/>
@@ -7141,7 +7081,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="15" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="16"/>
@@ -7980,218 +7920,218 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="104" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="101" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="98" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="95" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="92" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="89" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="51" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="86" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="83" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="74" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="80" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="77" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="74" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="111" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="111" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="71" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="120" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="120" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="68" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I25">
-    <cfRule type="cellIs" dxfId="65" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I30">
-    <cfRule type="cellIs" dxfId="62" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:I36">
-    <cfRule type="cellIs" dxfId="59" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38:I45">
-    <cfRule type="cellIs" dxfId="56" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="cellIs" dxfId="53" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8228,7 +8168,7 @@
       <c r="I1" s="19"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B3" s="16"/>
@@ -8236,7 +8176,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="17"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="15" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="16"/>
@@ -8969,170 +8909,170 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="47" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="44" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="41" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="38" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="35" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="32" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="90" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="90" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="29" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="26" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I20">
-    <cfRule type="cellIs" dxfId="23" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I28">
-    <cfRule type="cellIs" dxfId="20" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I32">
-    <cfRule type="cellIs" dxfId="17" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I39">
-    <cfRule type="cellIs" dxfId="14" priority="160" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="161" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="cellIs" dxfId="11" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C12D7B-A3E8-4CEF-8A67-96D13D4CAE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CCF2A0-7D9F-43C9-82BE-44ABA3124B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="王道计组" sheetId="3" r:id="rId3"/>
     <sheet name="王道数据结构" sheetId="4" r:id="rId4"/>
     <sheet name="王道计网" sheetId="5" r:id="rId5"/>
+    <sheet name="李林880专题" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -37,32 +38,146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="244">
+  <si>
+    <t>李林880专题 （选择&amp;填空）习题正确率记录</t>
+  </si>
+  <si>
+    <t>基础篇</t>
+  </si>
+  <si>
+    <t>综合篇</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>章节</t>
+  </si>
+  <si>
+    <t>总题数</t>
+  </si>
+  <si>
+    <t>正确数</t>
+  </si>
+  <si>
+    <t>正确率</t>
+  </si>
+  <si>
+    <t>高等数学</t>
+  </si>
+  <si>
+    <t>第一章 函数、极限、连续</t>
+  </si>
+  <si>
+    <t>第二章 一元函数微分学及其应用</t>
+  </si>
+  <si>
+    <t>第三章 一元函数积分学及其应用</t>
+  </si>
+  <si>
+    <t>第四章 空间解析几何</t>
+  </si>
+  <si>
+    <t>第五章 多元函数微分学及其应用</t>
+  </si>
+  <si>
+    <t>第六章 重积分及其应用</t>
+  </si>
+  <si>
+    <t>第七章 微分方程及其应用</t>
+  </si>
+  <si>
+    <t>第八章 无穷级数</t>
+  </si>
+  <si>
+    <t>第九章 曲线积分与曲面积分</t>
+  </si>
+  <si>
+    <t>高等数学 合计</t>
+  </si>
+  <si>
+    <t>线性代数</t>
+  </si>
+  <si>
+    <t>第十章 行列式</t>
+  </si>
+  <si>
+    <t>第十一章 矩阵</t>
+  </si>
+  <si>
+    <t>第十二章 向量</t>
+  </si>
+  <si>
+    <t>第十三章 线性方程组</t>
+  </si>
+  <si>
+    <t>第十四章 相似矩阵</t>
+  </si>
+  <si>
+    <t>第十五章 二次型</t>
+  </si>
+  <si>
+    <t>线性代数 合计</t>
+  </si>
+  <si>
+    <t>概率论与数理统计</t>
+  </si>
+  <si>
+    <t>第十六章 随机事件及其概率</t>
+  </si>
+  <si>
+    <t>第十七章 随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第十八章 多维随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第十九章 随机变量的数字特征</t>
+  </si>
+  <si>
+    <t>第二十章 大数定律与中心极限定理</t>
+  </si>
+  <si>
+    <t>第二十一章 数理统计的基本概念</t>
+  </si>
+  <si>
+    <t>第二十二章 参数估计</t>
+  </si>
+  <si>
+    <t>第二十三章 假设检验</t>
+  </si>
+  <si>
+    <t>概率论与数理统计 合计</t>
+  </si>
+  <si>
+    <t>总 计</t>
+  </si>
+  <si>
+    <t>解答区</t>
+  </si>
+  <si>
+    <t>扩展篇</t>
+  </si>
+  <si>
+    <t>选填+解答总计区</t>
+  </si>
+  <si>
+    <t>选填区</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
   <si>
     <t>张宇1000题 习题册正确率记录</t>
   </si>
   <si>
-    <t>章节</t>
-  </si>
-  <si>
     <t>日期</t>
   </si>
   <si>
     <t>总题目</t>
   </si>
   <si>
-    <t>正确数</t>
-  </si>
-  <si>
-    <t>正确率</t>
-  </si>
-  <si>
-    <t>基础篇</t>
-  </si>
-  <si>
-    <t>高等数学</t>
-  </si>
-  <si>
     <t>零基础</t>
   </si>
   <si>
@@ -120,9 +235,6 @@
     <t>第18章 多元函数积分学</t>
   </si>
   <si>
-    <t>线性代数</t>
-  </si>
-  <si>
     <t>第1章 行列式</t>
   </si>
   <si>
@@ -141,9 +253,6 @@
     <t>第6章 二次型</t>
   </si>
   <si>
-    <t>概率论与数理统计</t>
-  </si>
-  <si>
     <t>第1章 随机事件与概率</t>
   </si>
   <si>
@@ -171,9 +280,6 @@
     <t>强化篇汇总</t>
   </si>
   <si>
-    <t>综合篇</t>
-  </si>
-  <si>
     <t>第2章 余子式和代数余子式的计算</t>
   </si>
   <si>
@@ -328,9 +434,6 @@
   </si>
   <si>
     <t>5.3 磁盘和固态硬盘</t>
-  </si>
-  <si>
-    <t>合计</t>
   </si>
   <si>
     <t>总  计</t>
@@ -676,7 +779,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,8 +841,32 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -782,13 +909,61 @@
         <bgColor rgb="FFEBF5FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC0C0C0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -832,16 +1007,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC0C0C0"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -849,7 +1048,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -877,36 +1076,967 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="219">
+  <dxfs count="330">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3753,43 +4883,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="A1" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3798,7 +4928,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2">
         <v>514</v>
@@ -3810,13 +4940,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="12">
-        <f t="shared" ref="E6:E31" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
+        <f t="shared" ref="E6:E24" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2">
         <v>515</v>
@@ -3834,7 +4964,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2">
         <v>516</v>
@@ -3852,7 +4982,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2">
         <v>517</v>
@@ -3870,7 +5000,7 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2">
         <v>518</v>
@@ -3888,7 +5018,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2">
         <v>520</v>
@@ -3906,7 +5036,7 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2">
         <v>521</v>
@@ -3924,7 +5054,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="11"/>
@@ -3936,7 +5066,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2">
         <v>524</v>
@@ -3954,7 +5084,7 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2">
         <v>526</v>
@@ -3972,7 +5102,7 @@
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2">
         <v>527</v>
@@ -3990,7 +5120,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4002,7 +5132,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4014,7 +5144,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4026,7 +5156,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -4038,7 +5168,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4050,7 +5180,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4062,7 +5192,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4074,7 +5204,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4086,16 +5216,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="14"/>
     </row>
-    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B26" s="2">
         <v>522</v>
@@ -4107,13 +5237,13 @@
         <v>5</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E26:E31" si="1">IF(AND(C26&lt;&gt;"",D26&lt;&gt;""),D26/C26,"")</f>
         <v>0.45454545454545453</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2">
         <v>523</v>
@@ -4125,13 +5255,13 @@
         <v>15</v>
       </c>
       <c r="E27" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.78947368421052633</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2">
         <v>525</v>
@@ -4143,13 +5273,13 @@
         <v>13</v>
       </c>
       <c r="E28" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B29" s="2">
         <v>528</v>
@@ -4161,37 +5291,37 @@
         <v>11</v>
       </c>
       <c r="E29" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.6470588235294118</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -4200,79 +5330,79 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="13" t="str">
-        <f t="shared" ref="E33:E38" si="1">IF(AND(C33&lt;&gt;"",D33&lt;&gt;""),D33/C33,"")</f>
+        <f t="shared" ref="E33:E38" si="2">IF(AND(C33&lt;&gt;"",D33&lt;&gt;""),D33/C33,"")</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3">
@@ -4289,17 +5419,17 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="17"/>
+      <c r="A41" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="35"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -4308,223 +5438,223 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="str">
-        <f t="shared" ref="E43:E60" si="2">IF(AND(C43&lt;&gt;"",D43&lt;&gt;""),D43/C43,"")</f>
+        <f t="shared" ref="E43:E60" si="3">IF(AND(C43&lt;&gt;"",D43&lt;&gt;""),D43/C43,"")</f>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3">
@@ -4541,17 +5671,17 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="17"/>
+      <c r="A63" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="35"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4560,115 +5690,115 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2" t="str">
-        <f t="shared" ref="E65:E73" si="3">IF(AND(C65&lt;&gt;"",D65&lt;&gt;""),D65/C65,"")</f>
+        <f t="shared" ref="E65:E73" si="4">IF(AND(C65&lt;&gt;"",D65&lt;&gt;""),D65/C65,"")</f>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -4677,124 +5807,124 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2" t="str">
-        <f t="shared" ref="E75:E83" si="4">IF(AND(C75&lt;&gt;"",D75&lt;&gt;""),D75/C75,"")</f>
+        <f t="shared" ref="E75:E83" si="5">IF(AND(C75&lt;&gt;"",D75&lt;&gt;""),D75/C75,"")</f>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="17"/>
+      <c r="A84" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="34"/>
+      <c r="C84" s="34"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="35"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4806,7 +5936,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4818,7 +5948,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4830,7 +5960,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4842,7 +5972,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3">
@@ -4860,7 +5990,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5">
@@ -4967,134 +6097,134 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E16">
-    <cfRule type="cellIs" dxfId="218" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="329" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="328" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="327" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17:E24">
-    <cfRule type="cellIs" dxfId="215" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="326" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="325" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="324" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E31">
-    <cfRule type="cellIs" dxfId="212" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="323" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="322" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="321" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E38">
-    <cfRule type="cellIs" dxfId="209" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="320" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="319" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="318" priority="84" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="206" priority="214" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="215" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="216" operator="lessThan">
+    <cfRule type="cellIs" dxfId="317" priority="214" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="316" priority="215" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="315" priority="216" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:E60">
-    <cfRule type="cellIs" dxfId="203" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="314" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="313" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="312" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64:E73">
-    <cfRule type="cellIs" dxfId="200" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="311" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="310" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="309" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E76:E83">
-    <cfRule type="cellIs" dxfId="197" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="308" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="307" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="306" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85:E88">
-    <cfRule type="cellIs" dxfId="194" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="305" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="304" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="303" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E91">
-    <cfRule type="cellIs" dxfId="191" priority="223" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="224" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="225" operator="lessThan">
+    <cfRule type="cellIs" dxfId="302" priority="223" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="301" priority="224" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="300" priority="225" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E94">
-    <cfRule type="cellIs" dxfId="188" priority="220" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="221" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="222" operator="lessThan">
+    <cfRule type="cellIs" dxfId="299" priority="220" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="298" priority="221" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="297" priority="222" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5118,63 +6248,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="A1" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
+      <c r="A3" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="G3" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -5187,7 +6317,7 @@
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="B6" s="11">
         <v>530</v>
@@ -5212,7 +6342,7 @@
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="B7" s="11">
         <v>530</v>
@@ -5237,7 +6367,7 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="B8" s="11">
         <v>530</v>
@@ -5262,7 +6392,7 @@
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="B9" s="11">
         <v>531</v>
@@ -5287,7 +6417,7 @@
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="B10" s="11">
         <v>531</v>
@@ -5312,7 +6442,7 @@
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="B11" s="11">
         <v>531</v>
@@ -5337,7 +6467,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -5350,7 +6480,7 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="B13" s="11">
         <v>601</v>
@@ -5375,7 +6505,7 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B14" s="11">
         <v>602</v>
@@ -5400,7 +6530,7 @@
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="B15" s="11">
         <v>606</v>
@@ -5425,7 +6555,7 @@
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="B16" s="11">
         <v>607</v>
@@ -5450,7 +6580,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -5461,9 +6591,9 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="B18" s="11">
         <v>609</v>
@@ -5475,7 +6605,7 @@
         <v>51</v>
       </c>
       <c r="E18" s="12">
-        <f t="shared" ref="E18:E19" si="2">IF(AND(C18&lt;&gt;"",D18&lt;&gt;""),D18/C18,"")</f>
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;""),D18/C18,"")</f>
         <v>0.70833333333333337</v>
       </c>
       <c r="F18" s="9"/>
@@ -5486,9 +6616,9 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="B19" s="11">
         <v>610</v>
@@ -5500,7 +6630,7 @@
         <v>46</v>
       </c>
       <c r="E19" s="12">
-        <f t="shared" si="2"/>
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;""),D19/C19,"")</f>
         <v>0.75409836065573765</v>
       </c>
       <c r="F19" s="9"/>
@@ -5513,7 +6643,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -5524,16 +6654,22 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12" t="str">
-        <f t="shared" ref="E21:E23" si="3">IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),D21/C21,"")</f>
-        <v/>
+        <v>125</v>
+      </c>
+      <c r="B21" s="11">
+        <v>611</v>
+      </c>
+      <c r="C21" s="11">
+        <v>5</v>
+      </c>
+      <c r="D21" s="11">
+        <v>5</v>
+      </c>
+      <c r="E21" s="12">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),D21/C21,"")</f>
+        <v>1</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -5543,15 +6679,15 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;""),D22/C22,"")</f>
         <v/>
       </c>
       <c r="F22" s="9"/>
@@ -5562,15 +6698,15 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;""),D23/C23,"")</f>
         <v/>
       </c>
       <c r="F23" s="9"/>
@@ -5583,7 +6719,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -5594,15 +6730,15 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="12" t="str">
-        <f t="shared" ref="E25:E27" si="4">IF(AND(C25&lt;&gt;"",D25&lt;&gt;""),D25/C25,"")</f>
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;""),D25/C25,"")</f>
         <v/>
       </c>
       <c r="F25" s="9"/>
@@ -5613,15 +6749,15 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;""),D26/C26,"")</f>
         <v/>
       </c>
       <c r="F26" s="9"/>
@@ -5632,15 +6768,15 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;""),D27/C27,"")</f>
         <v/>
       </c>
       <c r="F27" s="9"/>
@@ -5653,20 +6789,20 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8">
         <f>SUM(C5:C27)</f>
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D28" s="8">
         <f>SUM(D5:D27)</f>
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E28" s="8">
         <f>IF(C28&gt;0, D28/C28,"")</f>
-        <v>0.75101214574898789</v>
+        <v>0.75350701402805609</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8">
@@ -5684,20 +6820,20 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
         <f>C28+G28</f>
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D30" s="5">
         <f>D28+H28</f>
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E30" s="5">
         <f>IF(C30&gt;0, D30/C30,"")</f>
-        <v>0.75101214574898789</v>
+        <v>0.75350701402805609</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -5731,158 +6867,158 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E11">
-    <cfRule type="cellIs" dxfId="185" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="296" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="295" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="294" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="182" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="293" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="292" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="291" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="179" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="290" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="289" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="288" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="176" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="287" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="286" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="285" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E27">
-    <cfRule type="cellIs" dxfId="173" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="284" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="283" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="282" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="cellIs" dxfId="170" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="281" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="280" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="279" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="167" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="278" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="277" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="276" priority="75" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I11">
-    <cfRule type="cellIs" dxfId="164" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="275" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="274" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="273" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="161" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="272" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="271" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="270" priority="96" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="158" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="269" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="268" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="267" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I23">
-    <cfRule type="cellIs" dxfId="155" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="266" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="265" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="264" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:I28">
-    <cfRule type="cellIs" dxfId="152" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="263" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="262" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="261" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="cellIs" dxfId="149" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="260" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="259" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="258" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5906,63 +7042,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="A1" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
+      <c r="A3" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="G3" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -5975,7 +7111,7 @@
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="B6" s="11">
         <v>507</v>
@@ -6000,7 +7136,7 @@
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="B7" s="11">
         <v>507</v>
@@ -6025,7 +7161,7 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="B8" s="11">
         <v>508</v>
@@ -6050,7 +7186,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -6063,7 +7199,7 @@
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="B10" s="11">
         <v>509</v>
@@ -6088,7 +7224,7 @@
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B11" s="11">
         <v>510</v>
@@ -6113,7 +7249,7 @@
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="B12" s="11">
         <v>512</v>
@@ -6138,7 +7274,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -6151,7 +7287,7 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="B14" s="11">
         <v>513</v>
@@ -6176,7 +7312,7 @@
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="B15" s="11">
         <v>514</v>
@@ -6201,7 +7337,7 @@
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="B16" s="11">
         <v>515</v>
@@ -6226,7 +7362,7 @@
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="B17" s="11">
         <v>516</v>
@@ -6251,7 +7387,7 @@
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="B18" s="11">
         <v>516</v>
@@ -6276,7 +7412,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B19" s="11">
         <v>517</v>
@@ -6301,7 +7437,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -6314,7 +7450,7 @@
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="B21" s="11">
         <v>518</v>
@@ -6339,7 +7475,7 @@
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="B22" s="11">
         <v>518</v>
@@ -6364,7 +7500,7 @@
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="B23" s="11">
         <v>519</v>
@@ -6385,7 +7521,7 @@
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="B24" s="11">
         <v>520</v>
@@ -6410,7 +7546,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -6423,7 +7559,7 @@
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="B26" s="11">
         <v>521</v>
@@ -6448,7 +7584,7 @@
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B27" s="11">
         <v>521</v>
@@ -6473,7 +7609,7 @@
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="B28" s="11">
         <v>522</v>
@@ -6498,7 +7634,7 @@
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B29" s="11">
         <v>523</v>
@@ -6523,7 +7659,7 @@
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B30" s="11">
         <v>524</v>
@@ -6548,7 +7684,7 @@
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="B31" s="11">
         <v>525</v>
@@ -6573,7 +7709,7 @@
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="B32" s="11">
         <v>525</v>
@@ -6598,7 +7734,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -6611,7 +7747,7 @@
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B34" s="11">
         <v>526</v>
@@ -6636,7 +7772,7 @@
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="B35" s="11">
         <v>526</v>
@@ -6661,7 +7797,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -6674,7 +7810,7 @@
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="B37" s="11">
         <v>526</v>
@@ -6699,7 +7835,7 @@
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="B38" s="11">
         <v>527</v>
@@ -6724,7 +7860,7 @@
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="B39" s="11">
         <v>528</v>
@@ -6749,7 +7885,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8">
@@ -6780,7 +7916,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
@@ -6837,206 +7973,206 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="146" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="257" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="256" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="255" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="143" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="254" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="253" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="252" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="140" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="251" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="250" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="249" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="137" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="248" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="247" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="246" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="134" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="245" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="244" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="243" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="131" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="242" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="241" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E39">
-    <cfRule type="cellIs" dxfId="128" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="3" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="239" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="238" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="237" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="125" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="236" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="235" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="234" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="122" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="233" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="232" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="231" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I8">
-    <cfRule type="cellIs" dxfId="119" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="117" operator="lessThan">
+    <cfRule type="cellIs" dxfId="230" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="229" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="228" priority="117" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I12">
-    <cfRule type="cellIs" dxfId="116" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="227" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="226" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="225" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I19">
-    <cfRule type="cellIs" dxfId="113" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="224" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="222" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I24">
-    <cfRule type="cellIs" dxfId="110" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="221" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="220" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="219" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I32">
-    <cfRule type="cellIs" dxfId="107" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="218" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="217" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I35">
-    <cfRule type="cellIs" dxfId="104" priority="184" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="185" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="186" operator="lessThan">
+    <cfRule type="cellIs" dxfId="215" priority="184" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="185" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="186" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37:I40">
-    <cfRule type="cellIs" dxfId="101" priority="190" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="191" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="192" operator="lessThan">
+    <cfRule type="cellIs" dxfId="212" priority="190" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="191" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="192" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42">
-    <cfRule type="cellIs" dxfId="98" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="209" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="207" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7060,63 +8196,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="A1" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
+      <c r="A3" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="G3" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -7129,7 +8265,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -7148,7 +8284,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7167,7 +8303,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7180,7 +8316,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -7199,7 +8335,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7218,7 +8354,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7237,7 +8373,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -7250,7 +8386,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -7269,7 +8405,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7288,7 +8424,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7307,7 +8443,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7326,7 +8462,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -7339,7 +8475,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7358,7 +8494,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7377,7 +8513,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -7390,7 +8526,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -7409,7 +8545,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -7428,7 +8564,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -7447,7 +8583,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -7466,7 +8602,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -7485,7 +8621,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -7498,7 +8634,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -7517,7 +8653,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -7536,7 +8672,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -7555,7 +8691,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -7574,7 +8710,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -7587,7 +8723,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -7606,7 +8742,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -7625,7 +8761,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -7644,7 +8780,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -7663,7 +8799,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -7682,7 +8818,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -7695,7 +8831,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -7714,7 +8850,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -7733,7 +8869,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -7752,7 +8888,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -7771,7 +8907,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -7790,7 +8926,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -7809,7 +8945,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -7828,7 +8964,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8">
@@ -7859,7 +8995,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
@@ -7920,218 +9056,218 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="206" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="92" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="203" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="89" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="200" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="86" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="197" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="83" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="194" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="80" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="191" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="189" priority="51" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="77" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="188" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="74" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="185" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="71" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="182" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="68" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="179" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="65" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="111" operator="lessThan">
+    <cfRule type="cellIs" dxfId="176" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="111" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="62" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="120" operator="lessThan">
+    <cfRule type="cellIs" dxfId="173" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="120" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="59" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="170" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I25">
-    <cfRule type="cellIs" dxfId="56" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="167" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="165" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I30">
-    <cfRule type="cellIs" dxfId="53" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:I36">
-    <cfRule type="cellIs" dxfId="50" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="161" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38:I45">
-    <cfRule type="cellIs" dxfId="47" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="158" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="cellIs" dxfId="44" priority="202" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="203" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="204" operator="lessThan">
+    <cfRule type="cellIs" dxfId="155" priority="202" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="203" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8155,63 +9291,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="A1" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
+      <c r="A3" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="G3" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -8224,7 +9360,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -8243,7 +9379,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -8262,7 +9398,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -8275,7 +9411,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -8294,7 +9430,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -8313,7 +9449,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -8332,7 +9468,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -8345,7 +9481,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8364,7 +9500,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -8383,7 +9519,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -8402,7 +9538,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -8421,7 +9557,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -8440,7 +9576,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -8459,7 +9595,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -8478,7 +9614,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8497,7 +9633,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -8510,7 +9646,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -8529,7 +9665,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -8548,7 +9684,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -8567,7 +9703,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -8586,7 +9722,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -8605,7 +9741,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -8624,7 +9760,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -8643,7 +9779,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -8656,7 +9792,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -8675,7 +9811,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -8694,7 +9830,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -8713,7 +9849,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -8726,7 +9862,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -8745,7 +9881,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -8764,7 +9900,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -8783,7 +9919,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -8802,7 +9938,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -8821,7 +9957,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8">
@@ -8852,7 +9988,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
@@ -8909,171 +10045,3974 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="38" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="35" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="32" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="143" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="29" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="140" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="26" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="137" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="23" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="90" operator="lessThan">
+    <cfRule type="cellIs" dxfId="134" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="90" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="20" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="131" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="17" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="128" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I20">
-    <cfRule type="cellIs" dxfId="14" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="125" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I28">
-    <cfRule type="cellIs" dxfId="11" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I32">
-    <cfRule type="cellIs" dxfId="8" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="119" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I39">
-    <cfRule type="cellIs" dxfId="5" priority="160" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="161" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="116" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="cellIs" dxfId="2" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="180" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="113" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="180" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:M112"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="13" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+    </row>
+    <row r="2" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="24"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="24"/>
+      <c r="J3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
+    </row>
+    <row r="6" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="18">
+        <v>15</v>
+      </c>
+      <c r="C6" s="18">
+        <v>12</v>
+      </c>
+      <c r="D6" s="18">
+        <f t="shared" ref="D6:D15" si="0">IF(AND(B6&lt;&gt;"",C6&lt;&gt;""),C6/B6,"")</f>
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="18">
+        <v>22</v>
+      </c>
+      <c r="F6" s="18">
+        <v>14</v>
+      </c>
+      <c r="G6" s="18">
+        <f t="shared" ref="G6:G15" si="1">IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),F6/E6,"")</f>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="H6" s="18">
+        <f t="shared" ref="H6:H14" si="2">B6+E6</f>
+        <v>37</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" ref="I6:I14" si="3">C6+F6</f>
+        <v>26</v>
+      </c>
+      <c r="J6" s="18">
+        <f t="shared" ref="J6:J15" si="4">IF(AND(H6&lt;&gt;"",I6&lt;&gt;""),I6/H6,"")</f>
+        <v>0.70270270270270274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H7" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H11" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H13" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H14" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="20">
+        <f>SUM(B6:B14)</f>
+        <v>15</v>
+      </c>
+      <c r="C15" s="20">
+        <f>SUM(C6:C14)</f>
+        <v>12</v>
+      </c>
+      <c r="D15" s="20">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="E15" s="20">
+        <f>SUM(E6:E14)</f>
+        <v>22</v>
+      </c>
+      <c r="F15" s="20">
+        <f>SUM(F6:F14)</f>
+        <v>14</v>
+      </c>
+      <c r="G15" s="20">
+        <f t="shared" si="1"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="H15" s="20">
+        <f>SUM(H6:H14)</f>
+        <v>37</v>
+      </c>
+      <c r="I15" s="20">
+        <f>SUM(I6:I14)</f>
+        <v>26</v>
+      </c>
+      <c r="J15" s="20">
+        <f t="shared" si="4"/>
+        <v>0.70270270270270274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
+    </row>
+    <row r="18" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18" t="str">
+        <f t="shared" ref="D18:D24" si="5">IF(AND(B18&lt;&gt;"",C18&lt;&gt;""),C18/B18,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18" t="str">
+        <f t="shared" ref="G18:G24" si="6">IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),F18/E18,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="18">
+        <f t="shared" ref="H18:I23" si="7">B18+E18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="18" t="e">
+        <f t="shared" ref="J18:J24" si="8">IF(AND(H18&lt;&gt;"",I18&lt;&gt;""),I18/H18,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H19" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="18" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H20" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="18" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H21" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="18" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H22" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="18" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H23" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="18" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20">
+        <f>SUM(B18:B23)</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="20">
+        <f>SUM(C18:C23)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="20" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E24" s="20">
+        <f>SUM(E18:E23)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="20">
+        <f>SUM(F18:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="20" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H24" s="20">
+        <f>SUM(H18:H23)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="20">
+        <f>SUM(I18:I23)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="20" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18" t="str">
+        <f t="shared" ref="D27:D36" si="9">IF(AND(B27&lt;&gt;"",C27&lt;&gt;""),C27/B27,"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18" t="str">
+        <f t="shared" ref="G27:G36" si="10">IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),F27/E27,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="18">
+        <f t="shared" ref="H27:I34" si="11">B27+E27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="18" t="e">
+        <f t="shared" ref="J27:J36" si="12">IF(AND(H27&lt;&gt;"",I27&lt;&gt;""),I27/H27,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H28" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H29" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H30" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H31" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="18" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="20">
+        <f>SUM(B27:B34)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="20">
+        <f>SUM(C27:C34)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="20" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E35" s="20">
+        <f>SUM(E27:E34)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="20">
+        <f>SUM(F27:F34)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="20" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H35" s="20">
+        <f>SUM(H27:H34)</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="20">
+        <f>SUM(I27:I34)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="20" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="22">
+        <f>B15+B24+B35</f>
+        <v>15</v>
+      </c>
+      <c r="C36" s="22">
+        <f>C15+C24+C35</f>
+        <v>12</v>
+      </c>
+      <c r="D36" s="22">
+        <f t="shared" si="9"/>
+        <v>0.8</v>
+      </c>
+      <c r="E36" s="22">
+        <f>E15+E24+E35</f>
+        <v>22</v>
+      </c>
+      <c r="F36" s="22">
+        <f>F15+F24+F35</f>
+        <v>14</v>
+      </c>
+      <c r="G36" s="22">
+        <f t="shared" si="10"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="H36" s="22">
+        <f>H15+H24+H35</f>
+        <v>37</v>
+      </c>
+      <c r="I36" s="22">
+        <f>I15+I24+I35</f>
+        <v>26</v>
+      </c>
+      <c r="J36" s="22">
+        <f t="shared" si="12"/>
+        <v>0.70270270270270274</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+    </row>
+    <row r="40" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15"/>
+      <c r="B41" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="24"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="24"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="24"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="24"/>
+      <c r="M41" s="25"/>
+    </row>
+    <row r="42" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="29"/>
+    </row>
+    <row r="44" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="18">
+        <v>16</v>
+      </c>
+      <c r="C44" s="18">
+        <v>10</v>
+      </c>
+      <c r="D44" s="18">
+        <f t="shared" ref="D44:D53" si="13">IF(AND(B44&lt;&gt;"",C44&lt;&gt;""),C44/B44,"")</f>
+        <v>0.625</v>
+      </c>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18" t="str">
+        <f t="shared" ref="G44:G53" si="14">IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),F44/E44,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18" t="str">
+        <f t="shared" ref="J44:J53" si="15">IF(AND(H44&lt;&gt;"",I44&lt;&gt;""),I44/H44,"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="18">
+        <f t="shared" ref="K44:K52" si="16">B44+E44+H44</f>
+        <v>16</v>
+      </c>
+      <c r="L44" s="18">
+        <f t="shared" ref="L44:L52" si="17">C44+F44+I44</f>
+        <v>10</v>
+      </c>
+      <c r="M44" s="18">
+        <f t="shared" ref="M44:M53" si="18">IF(AND(K44&lt;&gt;"",L44&lt;&gt;""),L44/K44,"")</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K45" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L45" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K46" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K47" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L47" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K48" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K49" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K50" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K51" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M51" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K52" s="18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M52" s="18" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="20">
+        <f>SUM(B44:B52)</f>
+        <v>16</v>
+      </c>
+      <c r="C53" s="20">
+        <f>SUM(C44:C52)</f>
+        <v>10</v>
+      </c>
+      <c r="D53" s="20">
+        <f t="shared" si="13"/>
+        <v>0.625</v>
+      </c>
+      <c r="E53" s="20">
+        <f>SUM(E44:E52)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="20">
+        <f>SUM(F44:F52)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="20" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H53" s="20">
+        <f>SUM(H44:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="20">
+        <f>SUM(I44:I52)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="20" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K53" s="20">
+        <f>SUM(K44:K52)</f>
+        <v>16</v>
+      </c>
+      <c r="L53" s="20">
+        <f>SUM(L44:L52)</f>
+        <v>10</v>
+      </c>
+      <c r="M53" s="20">
+        <f t="shared" si="18"/>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="29"/>
+    </row>
+    <row r="56" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18" t="str">
+        <f t="shared" ref="D56:D62" si="19">IF(AND(B56&lt;&gt;"",C56&lt;&gt;""),C56/B56,"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18" t="str">
+        <f t="shared" ref="G56:G62" si="20">IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),F56/E56,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18" t="str">
+        <f t="shared" ref="J56:J62" si="21">IF(AND(H56&lt;&gt;"",I56&lt;&gt;""),I56/H56,"")</f>
+        <v/>
+      </c>
+      <c r="K56" s="18">
+        <f t="shared" ref="K56:L61" si="22">B56+E56+H56</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="18" t="e">
+        <f t="shared" ref="M56:M62" si="23">IF(AND(K56&lt;&gt;"",L56&lt;&gt;""),L56/K56,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K57" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="18" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K58" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="18" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K59" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="18" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K60" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M60" s="18" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K61" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M61" s="18" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" s="20">
+        <f>SUM(B56:B61)</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="20">
+        <f>SUM(C56:C61)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="20" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E62" s="20">
+        <f>SUM(E56:E61)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="20">
+        <f>SUM(F56:F61)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="20" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H62" s="20">
+        <f>SUM(H56:H61)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="20">
+        <f>SUM(I56:I61)</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="20" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K62" s="20">
+        <f>SUM(K56:K61)</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="20">
+        <f>SUM(L56:L61)</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="20" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="29"/>
+    </row>
+    <row r="65" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18" t="str">
+        <f t="shared" ref="D65:D74" si="24">IF(AND(B65&lt;&gt;"",C65&lt;&gt;""),C65/B65,"")</f>
+        <v/>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18" t="str">
+        <f t="shared" ref="G65:G74" si="25">IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),F65/E65,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18" t="str">
+        <f t="shared" ref="J65:J74" si="26">IF(AND(H65&lt;&gt;"",I65&lt;&gt;""),I65/H65,"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="18">
+        <f t="shared" ref="K65:L72" si="27">B65+E65+H65</f>
+        <v>0</v>
+      </c>
+      <c r="L65" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M65" s="18" t="e">
+        <f t="shared" ref="M65:M74" si="28">IF(AND(K65&lt;&gt;"",L65&lt;&gt;""),L65/K65,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K66" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M66" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K67" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L67" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M67" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K68" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K69" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K70" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K71" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K72" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="18" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" s="20">
+        <f>SUM(B65:B72)</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="20">
+        <f>SUM(C65:C72)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="20" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E73" s="20">
+        <f>SUM(E65:E72)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="20">
+        <f>SUM(F65:F72)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="20" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H73" s="20">
+        <f>SUM(H65:H72)</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="20">
+        <f>SUM(I65:I72)</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="20" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K73" s="20">
+        <f>SUM(K65:K72)</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="20">
+        <f>SUM(L65:L72)</f>
+        <v>0</v>
+      </c>
+      <c r="M73" s="20" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="22">
+        <f>B53+B62+B73</f>
+        <v>16</v>
+      </c>
+      <c r="C74" s="22">
+        <f>C53+C62+C73</f>
+        <v>10</v>
+      </c>
+      <c r="D74" s="22">
+        <f t="shared" si="24"/>
+        <v>0.625</v>
+      </c>
+      <c r="E74" s="22">
+        <f>E53+E62+E73</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="22">
+        <f>F53+F62+F73</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="22" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H74" s="22">
+        <f>H53+H62+H73</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="22">
+        <f>I53+I62+I73</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="22" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K74" s="22">
+        <f>K53+K62+K73</f>
+        <v>16</v>
+      </c>
+      <c r="L74" s="22">
+        <f>L53+L62+L73</f>
+        <v>10</v>
+      </c>
+      <c r="M74" s="22">
+        <f t="shared" si="28"/>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="24"/>
+    </row>
+    <row r="78" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="15"/>
+      <c r="B79" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="24"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="24"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" s="24"/>
+      <c r="J79" s="25"/>
+    </row>
+    <row r="80" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="28"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="29"/>
+    </row>
+    <row r="82" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="18">
+        <f t="shared" ref="B82:B90" si="29">H6</f>
+        <v>37</v>
+      </c>
+      <c r="C82" s="18">
+        <f t="shared" ref="C82:C90" si="30">I6</f>
+        <v>26</v>
+      </c>
+      <c r="D82" s="18">
+        <f t="shared" ref="D82:D91" si="31">IF(AND(B82&lt;&gt;"",C82&lt;&gt;""),C82/B82,"")</f>
+        <v>0.70270270270270274</v>
+      </c>
+      <c r="E82" s="18">
+        <f t="shared" ref="E82:E90" si="32">K44</f>
+        <v>16</v>
+      </c>
+      <c r="F82" s="18">
+        <f t="shared" ref="F82:F90" si="33">L44</f>
+        <v>10</v>
+      </c>
+      <c r="G82" s="18">
+        <f t="shared" ref="G82:G91" si="34">IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),F82/E82,"")</f>
+        <v>0.625</v>
+      </c>
+      <c r="H82" s="18">
+        <f t="shared" ref="H82:H90" si="35">B82+E82</f>
+        <v>53</v>
+      </c>
+      <c r="I82" s="18">
+        <f t="shared" ref="I82:I90" si="36">C82+F82</f>
+        <v>36</v>
+      </c>
+      <c r="J82" s="18">
+        <f t="shared" ref="J82:J91" si="37">IF(AND(H82&lt;&gt;"",I82&lt;&gt;""),I82/H82,"")</f>
+        <v>0.67924528301886788</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E83" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H83" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E84" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H84" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J84" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E85" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H85" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B86" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E86" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H86" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J86" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E87" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H87" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J87" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E88" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H88" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J88" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D89" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E89" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H89" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J89" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" s="18">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="D90" s="18" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E90" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H90" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J90" s="18" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B91" s="20">
+        <f>SUM(B82:B90)</f>
+        <v>37</v>
+      </c>
+      <c r="C91" s="20">
+        <f>SUM(C82:C90)</f>
+        <v>26</v>
+      </c>
+      <c r="D91" s="20">
+        <f t="shared" si="31"/>
+        <v>0.70270270270270274</v>
+      </c>
+      <c r="E91" s="20">
+        <f>SUM(E82:E90)</f>
+        <v>16</v>
+      </c>
+      <c r="F91" s="20">
+        <f>SUM(F82:F90)</f>
+        <v>10</v>
+      </c>
+      <c r="G91" s="20">
+        <f t="shared" si="34"/>
+        <v>0.625</v>
+      </c>
+      <c r="H91" s="20">
+        <f>SUM(H82:H90)</f>
+        <v>53</v>
+      </c>
+      <c r="I91" s="20">
+        <f>SUM(I82:I90)</f>
+        <v>36</v>
+      </c>
+      <c r="J91" s="20">
+        <f t="shared" si="37"/>
+        <v>0.67924528301886788</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="J93" s="29"/>
+    </row>
+    <row r="94" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" s="18">
+        <f t="shared" ref="B94:C99" si="38">H18</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="D94" s="18" t="e">
+        <f t="shared" ref="D94:D100" si="39">IF(AND(B94&lt;&gt;"",C94&lt;&gt;""),C94/B94,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E94" s="18">
+        <f t="shared" ref="E94:F99" si="40">K56</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="18" t="e">
+        <f t="shared" ref="G94:G100" si="41">IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),F94/E94,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H94" s="18">
+        <f t="shared" ref="H94:I99" si="42">B94+E94</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J94" s="18" t="e">
+        <f t="shared" ref="J94:J100" si="43">IF(AND(H94&lt;&gt;"",I94&lt;&gt;""),I94/H94,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B95" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="18" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E95" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="18" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H95" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J95" s="18" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="D96" s="18" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E96" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G96" s="18" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H96" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="I96" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J96" s="18" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="D97" s="18" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E97" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G97" s="18" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H97" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="I97" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J97" s="18" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="D98" s="18" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E98" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="18" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H98" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J98" s="18" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="C99" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="18" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E99" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="18" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H99" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="I99" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J99" s="18" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" s="20">
+        <f>SUM(B94:B99)</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="20">
+        <f>SUM(C94:C99)</f>
+        <v>0</v>
+      </c>
+      <c r="D100" s="20" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E100" s="20">
+        <f>SUM(E94:E99)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="20">
+        <f>SUM(F94:F99)</f>
+        <v>0</v>
+      </c>
+      <c r="G100" s="20" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H100" s="20">
+        <f>SUM(H94:H99)</f>
+        <v>0</v>
+      </c>
+      <c r="I100" s="20">
+        <f>SUM(I94:I99)</f>
+        <v>0</v>
+      </c>
+      <c r="J100" s="20" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" s="28"/>
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="J102" s="29"/>
+    </row>
+    <row r="103" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" s="18">
+        <f t="shared" ref="B103:C110" si="44">H27</f>
+        <v>0</v>
+      </c>
+      <c r="C103" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D103" s="18" t="e">
+        <f t="shared" ref="D103:D112" si="45">IF(AND(B103&lt;&gt;"",C103&lt;&gt;""),C103/B103,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E103" s="18">
+        <f t="shared" ref="E103:F110" si="46">K65</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G103" s="18" t="e">
+        <f t="shared" ref="G103:G112" si="47">IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),F103/E103,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H103" s="18">
+        <f t="shared" ref="H103:I110" si="48">B103+E103</f>
+        <v>0</v>
+      </c>
+      <c r="I103" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J103" s="18" t="e">
+        <f t="shared" ref="J103:J112" si="49">IF(AND(H103&lt;&gt;"",I103&lt;&gt;""),I103/H103,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C104" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D104" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E104" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G104" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H104" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I104" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J104" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C105" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D105" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E105" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H105" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I105" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J105" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B106" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C106" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D106" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E106" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G106" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H106" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J106" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C107" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D107" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E107" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F107" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G107" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H107" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J107" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B108" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C108" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D108" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E108" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G108" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H108" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I108" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J108" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B109" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C109" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D109" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E109" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F109" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G109" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H109" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J109" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B110" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C110" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="D110" s="18" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E110" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="18">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="G110" s="18" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H110" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="I110" s="18">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J110" s="18" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B111" s="20">
+        <f>SUM(B103:B110)</f>
+        <v>0</v>
+      </c>
+      <c r="C111" s="20">
+        <f>SUM(C103:C110)</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="20" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E111" s="20">
+        <f>SUM(E103:E110)</f>
+        <v>0</v>
+      </c>
+      <c r="F111" s="20">
+        <f>SUM(F103:F110)</f>
+        <v>0</v>
+      </c>
+      <c r="G111" s="20" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H111" s="20">
+        <f>SUM(H103:H110)</f>
+        <v>0</v>
+      </c>
+      <c r="I111" s="20">
+        <f>SUM(I103:I110)</f>
+        <v>0</v>
+      </c>
+      <c r="J111" s="20" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B112" s="22">
+        <f>B91+B100+B111</f>
+        <v>37</v>
+      </c>
+      <c r="C112" s="22">
+        <f>C91+C100+C111</f>
+        <v>26</v>
+      </c>
+      <c r="D112" s="22">
+        <f t="shared" si="45"/>
+        <v>0.70270270270270274</v>
+      </c>
+      <c r="E112" s="22">
+        <f>E91+E100+E111</f>
+        <v>16</v>
+      </c>
+      <c r="F112" s="22">
+        <f>F91+F100+F111</f>
+        <v>10</v>
+      </c>
+      <c r="G112" s="22">
+        <f t="shared" si="47"/>
+        <v>0.625</v>
+      </c>
+      <c r="H112" s="22">
+        <f>H91+H100+H111</f>
+        <v>53</v>
+      </c>
+      <c r="I112" s="22">
+        <f>I91+I100+I111</f>
+        <v>36</v>
+      </c>
+      <c r="J112" s="22">
+        <f t="shared" si="49"/>
+        <v>0.67924528301886788</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A102:J102"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A93:J93"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="A43:M43"/>
+  </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="D6:D15">
+    <cfRule type="cellIs" dxfId="110" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:D24">
+    <cfRule type="cellIs" dxfId="107" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27:D36">
+    <cfRule type="cellIs" dxfId="104" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="21" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D44:D53">
+    <cfRule type="cellIs" dxfId="101" priority="66" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55:D60">
+    <cfRule type="cellIs" dxfId="98" priority="78" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D62:D70">
+    <cfRule type="cellIs" dxfId="95" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D73:D74">
+    <cfRule type="cellIs" dxfId="92" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="126" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D82:D91">
+    <cfRule type="cellIs" dxfId="89" priority="150" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="149" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="148" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D93:D98">
+    <cfRule type="cellIs" dxfId="86" priority="158" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="159" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="157" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D100:D108">
+    <cfRule type="cellIs" dxfId="83" priority="168" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="167" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="166" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D111:D112">
+    <cfRule type="cellIs" dxfId="80" priority="194" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="195" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="193" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G15">
+    <cfRule type="cellIs" dxfId="77" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="6" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18:G24">
+    <cfRule type="cellIs" dxfId="74" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="15" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27:G36">
+    <cfRule type="cellIs" dxfId="71" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="24" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:G53">
+    <cfRule type="cellIs" dxfId="68" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G55:G60">
+    <cfRule type="cellIs" dxfId="65" priority="81" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="79" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G62:G70">
+    <cfRule type="cellIs" dxfId="62" priority="93" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:G74">
+    <cfRule type="cellIs" dxfId="59" priority="128" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="129" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="127" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:G91">
+    <cfRule type="cellIs" dxfId="56" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="153" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G93:G98">
+    <cfRule type="cellIs" dxfId="53" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="162" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G100:G108">
+    <cfRule type="cellIs" dxfId="50" priority="171" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="170" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="169" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G111:G112">
+    <cfRule type="cellIs" dxfId="47" priority="196" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="197" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="198" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J15">
+    <cfRule type="cellIs" dxfId="44" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18:J24">
+    <cfRule type="cellIs" dxfId="41" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27:J36">
+    <cfRule type="cellIs" dxfId="38" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J44:J53">
+    <cfRule type="cellIs" dxfId="35" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="72" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J55:J60">
+    <cfRule type="cellIs" dxfId="32" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="84" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J62:J70">
+    <cfRule type="cellIs" dxfId="29" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J73:J74">
+    <cfRule type="cellIs" dxfId="26" priority="132" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J82:J91">
+    <cfRule type="cellIs" dxfId="23" priority="154" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="155" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="156" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J93:J98">
+    <cfRule type="cellIs" dxfId="20" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="165" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J100:J108">
+    <cfRule type="cellIs" dxfId="17" priority="172" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="173" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="174" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J111:J112">
+    <cfRule type="cellIs" dxfId="14" priority="199" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="200" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="201" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M44:M53">
+    <cfRule type="cellIs" dxfId="11" priority="75" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M55:M60">
+    <cfRule type="cellIs" dxfId="8" priority="87" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M62:M70">
+    <cfRule type="cellIs" dxfId="5" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="99" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M73:M74">
+    <cfRule type="cellIs" dxfId="2" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="135" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601BC7EA-EEAF-4FDC-81F5-4D2692614903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB53537F-D1A4-4727-A8A2-C91102FC54B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -577,214 +577,215 @@
     <t>8.7 外部排序</t>
   </si>
   <si>
+    <t>1.1 计算机发展历程</t>
+  </si>
+  <si>
+    <t>1.2 计算机系统层次结构</t>
+  </si>
+  <si>
+    <t>1.3 计算机的性能指标</t>
+  </si>
+  <si>
+    <t>第2章 数据的表示和运算</t>
+  </si>
+  <si>
+    <t>2.1 数制与编码</t>
+  </si>
+  <si>
+    <t>2.2 运算方法和运算电路</t>
+  </si>
+  <si>
+    <t>2.3 浮点数的表示与运算</t>
+  </si>
+  <si>
+    <t>第3章 存储系统</t>
+  </si>
+  <si>
+    <t>3.1 存储器概述</t>
+  </si>
+  <si>
+    <t>3.2 主存储器</t>
+  </si>
+  <si>
+    <t>3.3 主存储器与CPU的连接</t>
+  </si>
+  <si>
+    <t>3.4 外部存储器</t>
+  </si>
+  <si>
+    <t>3.5 高速缓冲存储器</t>
+  </si>
+  <si>
+    <t>3.6 虚拟存储器</t>
+  </si>
+  <si>
+    <t>第4章 指令系统</t>
+  </si>
+  <si>
+    <t>4.1 指令系统</t>
+  </si>
+  <si>
+    <t>4.2 寻址方式</t>
+  </si>
+  <si>
+    <t>4.3 程序的机器级代码表示</t>
+  </si>
+  <si>
+    <t>4.4 CISC和RISC的基本概念</t>
+  </si>
+  <si>
+    <t>第5章 中央处理器</t>
+  </si>
+  <si>
+    <t>5.1 CPU的功能和基本结构</t>
+  </si>
+  <si>
+    <t>5.2 指令执行过程</t>
+  </si>
+  <si>
+    <t>5.3 数据通路的功能和基本结构</t>
+  </si>
+  <si>
+    <t>5.4 控制器的功能和工作原理</t>
+  </si>
+  <si>
+    <t>5.5 异常和中断机制</t>
+  </si>
+  <si>
+    <t>5.6 指令流水线</t>
+  </si>
+  <si>
+    <t>5.7 多处理器的基本概念</t>
+  </si>
+  <si>
+    <t>第6章 总线</t>
+  </si>
+  <si>
+    <t>6.1 总线概述</t>
+  </si>
+  <si>
+    <t>6.2 总线事务和定时</t>
+  </si>
+  <si>
+    <t>第7章 输入/输出系统</t>
+  </si>
+  <si>
+    <t>7.1 I/O系统基本概念</t>
+  </si>
+  <si>
+    <t>7.2 I/O接口</t>
+  </si>
+  <si>
+    <t>7.3 I/O方式</t>
+  </si>
+  <si>
+    <t>王道计算机网络 课后习题正确率记录</t>
+  </si>
+  <si>
+    <t>第1章 计算机网络体系结构</t>
+  </si>
+  <si>
+    <t>1.1 计算机网络概述</t>
+  </si>
+  <si>
+    <t>1.2 计算机网络体系结构与参考模型</t>
+  </si>
+  <si>
+    <t>第2章 物理层</t>
+  </si>
+  <si>
+    <t>2.1 通信基础</t>
+  </si>
+  <si>
+    <t>2.2 传输介质</t>
+  </si>
+  <si>
+    <t>2.3 物理层设备</t>
+  </si>
+  <si>
+    <t>第3章 数据链路层</t>
+  </si>
+  <si>
+    <t>3.1 数据链路层的功能</t>
+  </si>
+  <si>
+    <t>3.2 组帧</t>
+  </si>
+  <si>
+    <t>3.3 差错控制</t>
+  </si>
+  <si>
+    <t>3.4 流量控制与可靠传输机制</t>
+  </si>
+  <si>
+    <t>3.5 介质访问控制</t>
+  </si>
+  <si>
+    <t>3.6 局域网</t>
+  </si>
+  <si>
+    <t>3.7 广域网</t>
+  </si>
+  <si>
+    <t>3.8 数据链路层设备</t>
+  </si>
+  <si>
+    <t>第4章 网络层</t>
+  </si>
+  <si>
+    <t>4.1 网络层的功能</t>
+  </si>
+  <si>
+    <t>4.2 IPv4</t>
+  </si>
+  <si>
+    <t>4.3 IPv6</t>
+  </si>
+  <si>
+    <t>4.4 路由算法与路由协议</t>
+  </si>
+  <si>
+    <t>4.5 IP多播</t>
+  </si>
+  <si>
+    <t>4.6 移动IP</t>
+  </si>
+  <si>
+    <t>4.7 网络层设备</t>
+  </si>
+  <si>
+    <t>第5章 传输层</t>
+  </si>
+  <si>
+    <t>5.1 传输层提供的服务</t>
+  </si>
+  <si>
+    <t>5.2 UDP</t>
+  </si>
+  <si>
+    <t>5.3 TCP</t>
+  </si>
+  <si>
+    <t>第6章 应用层</t>
+  </si>
+  <si>
+    <t>6.1 网络应用模型</t>
+  </si>
+  <si>
+    <t>6.2 域名系统</t>
+  </si>
+  <si>
+    <t>6.3 文件传输协议</t>
+  </si>
+  <si>
+    <t>6.4 电子邮件</t>
+  </si>
+  <si>
+    <t>6.5 万维网</t>
+  </si>
+  <si>
     <t>王道计算机组成原理 课后习题正确率记录</t>
-  </si>
-  <si>
-    <t>1.1 计算机发展历程</t>
-  </si>
-  <si>
-    <t>1.2 计算机系统层次结构</t>
-  </si>
-  <si>
-    <t>1.3 计算机的性能指标</t>
-  </si>
-  <si>
-    <t>第2章 数据的表示和运算</t>
-  </si>
-  <si>
-    <t>2.1 数制与编码</t>
-  </si>
-  <si>
-    <t>2.2 运算方法和运算电路</t>
-  </si>
-  <si>
-    <t>2.3 浮点数的表示与运算</t>
-  </si>
-  <si>
-    <t>第3章 存储系统</t>
-  </si>
-  <si>
-    <t>3.1 存储器概述</t>
-  </si>
-  <si>
-    <t>3.2 主存储器</t>
-  </si>
-  <si>
-    <t>3.3 主存储器与CPU的连接</t>
-  </si>
-  <si>
-    <t>3.4 外部存储器</t>
-  </si>
-  <si>
-    <t>3.5 高速缓冲存储器</t>
-  </si>
-  <si>
-    <t>3.6 虚拟存储器</t>
-  </si>
-  <si>
-    <t>第4章 指令系统</t>
-  </si>
-  <si>
-    <t>4.1 指令系统</t>
-  </si>
-  <si>
-    <t>4.2 寻址方式</t>
-  </si>
-  <si>
-    <t>4.3 程序的机器级代码表示</t>
-  </si>
-  <si>
-    <t>4.4 CISC和RISC的基本概念</t>
-  </si>
-  <si>
-    <t>第5章 中央处理器</t>
-  </si>
-  <si>
-    <t>5.1 CPU的功能和基本结构</t>
-  </si>
-  <si>
-    <t>5.2 指令执行过程</t>
-  </si>
-  <si>
-    <t>5.3 数据通路的功能和基本结构</t>
-  </si>
-  <si>
-    <t>5.4 控制器的功能和工作原理</t>
-  </si>
-  <si>
-    <t>5.5 异常和中断机制</t>
-  </si>
-  <si>
-    <t>5.6 指令流水线</t>
-  </si>
-  <si>
-    <t>5.7 多处理器的基本概念</t>
-  </si>
-  <si>
-    <t>第6章 总线</t>
-  </si>
-  <si>
-    <t>6.1 总线概述</t>
-  </si>
-  <si>
-    <t>6.2 总线事务和定时</t>
-  </si>
-  <si>
-    <t>第7章 输入/输出系统</t>
-  </si>
-  <si>
-    <t>7.1 I/O系统基本概念</t>
-  </si>
-  <si>
-    <t>7.2 I/O接口</t>
-  </si>
-  <si>
-    <t>7.3 I/O方式</t>
-  </si>
-  <si>
-    <t>王道计算机网络 课后习题正确率记录</t>
-  </si>
-  <si>
-    <t>第1章 计算机网络体系结构</t>
-  </si>
-  <si>
-    <t>1.1 计算机网络概述</t>
-  </si>
-  <si>
-    <t>1.2 计算机网络体系结构与参考模型</t>
-  </si>
-  <si>
-    <t>第2章 物理层</t>
-  </si>
-  <si>
-    <t>2.1 通信基础</t>
-  </si>
-  <si>
-    <t>2.2 传输介质</t>
-  </si>
-  <si>
-    <t>2.3 物理层设备</t>
-  </si>
-  <si>
-    <t>第3章 数据链路层</t>
-  </si>
-  <si>
-    <t>3.1 数据链路层的功能</t>
-  </si>
-  <si>
-    <t>3.2 组帧</t>
-  </si>
-  <si>
-    <t>3.3 差错控制</t>
-  </si>
-  <si>
-    <t>3.4 流量控制与可靠传输机制</t>
-  </si>
-  <si>
-    <t>3.5 介质访问控制</t>
-  </si>
-  <si>
-    <t>3.6 局域网</t>
-  </si>
-  <si>
-    <t>3.7 广域网</t>
-  </si>
-  <si>
-    <t>3.8 数据链路层设备</t>
-  </si>
-  <si>
-    <t>第4章 网络层</t>
-  </si>
-  <si>
-    <t>4.1 网络层的功能</t>
-  </si>
-  <si>
-    <t>4.2 IPv4</t>
-  </si>
-  <si>
-    <t>4.3 IPv6</t>
-  </si>
-  <si>
-    <t>4.4 路由算法与路由协议</t>
-  </si>
-  <si>
-    <t>4.5 IP多播</t>
-  </si>
-  <si>
-    <t>4.6 移动IP</t>
-  </si>
-  <si>
-    <t>4.7 网络层设备</t>
-  </si>
-  <si>
-    <t>第5章 传输层</t>
-  </si>
-  <si>
-    <t>5.1 传输层提供的服务</t>
-  </si>
-  <si>
-    <t>5.2 UDP</t>
-  </si>
-  <si>
-    <t>5.3 TCP</t>
-  </si>
-  <si>
-    <t>第6章 应用层</t>
-  </si>
-  <si>
-    <t>6.1 网络应用模型</t>
-  </si>
-  <si>
-    <t>6.2 域名系统</t>
-  </si>
-  <si>
-    <t>6.3 文件传输协议</t>
-  </si>
-  <si>
-    <t>6.4 电子邮件</t>
-  </si>
-  <si>
-    <t>6.5 万维网</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -794,7 +795,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -895,6 +896,13 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1080,7 +1088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1201,6 +1209,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11588,8 +11599,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>179</v>
+      <c r="A1" s="50" t="s">
+        <v>248</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -11735,7 +11746,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" s="27">
         <v>507</v>
@@ -11801,7 +11812,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="27">
         <v>507</v>
@@ -11867,7 +11878,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="27">
         <v>508</v>
@@ -11933,7 +11944,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -11959,7 +11970,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B10" s="27">
         <v>509</v>
@@ -12025,7 +12036,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B11" s="27">
         <v>510</v>
@@ -12091,7 +12102,7 @@
     </row>
     <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B12" s="27">
         <v>512</v>
@@ -12157,7 +12168,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -12183,7 +12194,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B14" s="27">
         <v>513</v>
@@ -12249,7 +12260,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B15" s="27">
         <v>514</v>
@@ -12315,7 +12326,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B16" s="27">
         <v>515</v>
@@ -12381,7 +12392,7 @@
     </row>
     <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" s="27">
         <v>516</v>
@@ -12447,7 +12458,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B18" s="27">
         <v>516</v>
@@ -12513,7 +12524,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B19" s="27">
         <v>517</v>
@@ -12579,7 +12590,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -12605,7 +12616,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B21" s="27">
         <v>518</v>
@@ -12671,7 +12682,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="27">
         <v>518</v>
@@ -12737,7 +12748,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B23" s="27">
         <v>519</v>
@@ -12799,7 +12810,7 @@
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B24" s="27">
         <v>520</v>
@@ -12865,7 +12876,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -12891,7 +12902,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B26" s="27">
         <v>521</v>
@@ -12957,7 +12968,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B27" s="27">
         <v>521</v>
@@ -13023,7 +13034,7 @@
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B28" s="27">
         <v>522</v>
@@ -13089,7 +13100,7 @@
     </row>
     <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B29" s="27">
         <v>523</v>
@@ -13155,7 +13166,7 @@
     </row>
     <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B30" s="27">
         <v>524</v>
@@ -13221,7 +13232,7 @@
     </row>
     <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B31" s="27">
         <v>525</v>
@@ -13287,7 +13298,7 @@
     </row>
     <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B32" s="27">
         <v>525</v>
@@ -13353,7 +13364,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -13379,7 +13390,7 @@
     </row>
     <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B34" s="27">
         <v>526</v>
@@ -13445,7 +13456,7 @@
     </row>
     <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B35" s="27">
         <v>526</v>
@@ -13511,7 +13522,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -13537,7 +13548,7 @@
     </row>
     <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B37" s="27">
         <v>526</v>
@@ -13603,7 +13614,7 @@
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B38" s="27">
         <v>527</v>
@@ -13669,7 +13680,7 @@
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B39" s="27">
         <v>528</v>
@@ -15701,7 +15712,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -15821,7 +15832,7 @@
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -15847,7 +15858,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -15903,7 +15914,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="27"/>
@@ -15959,7 +15970,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -15985,7 +15996,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="27"/>
@@ -16041,7 +16052,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B10" s="27"/>
       <c r="C10" s="27"/>
@@ -16097,7 +16108,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="27"/>
@@ -16153,7 +16164,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -16179,7 +16190,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
@@ -16235,7 +16246,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="27"/>
       <c r="C14" s="27"/>
@@ -16291,7 +16302,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B15" s="27"/>
       <c r="C15" s="27"/>
@@ -16347,7 +16358,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B16" s="27"/>
       <c r="C16" s="27"/>
@@ -16403,7 +16414,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
@@ -16459,7 +16470,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="27"/>
@@ -16515,7 +16526,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
@@ -16571,7 +16582,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="27"/>
@@ -16627,7 +16638,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -16653,7 +16664,7 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="27"/>
@@ -16709,7 +16720,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B23" s="27"/>
       <c r="C23" s="27"/>
@@ -16765,7 +16776,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="27"/>
@@ -16821,7 +16832,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -16877,7 +16888,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -16933,7 +16944,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B27" s="27"/>
       <c r="C27" s="27"/>
@@ -16989,7 +17000,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
@@ -17045,7 +17056,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -17071,7 +17082,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -17127,7 +17138,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
@@ -17183,7 +17194,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
@@ -17239,7 +17250,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -17265,7 +17276,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -17321,7 +17332,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
@@ -17377,7 +17388,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
@@ -17433,7 +17444,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -17489,7 +17500,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E15F122-35DB-40ED-A4EE-373AB09C0B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BD6B75-302D-43BD-B47F-8D70CB435C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
-    <sheet name="李林880专题" sheetId="2" r:id="rId2"/>
-    <sheet name="王道数据结构" sheetId="3" r:id="rId3"/>
-    <sheet name="王道计组" sheetId="4" r:id="rId4"/>
-    <sheet name="王道操作系统" sheetId="5" r:id="rId5"/>
-    <sheet name="王道计网" sheetId="6" r:id="rId6"/>
+    <sheet name="武忠祥严选题" sheetId="7" r:id="rId2"/>
+    <sheet name="李林880专题" sheetId="2" r:id="rId3"/>
+    <sheet name="王道数据结构" sheetId="3" r:id="rId4"/>
+    <sheet name="王道计组" sheetId="4" r:id="rId5"/>
+    <sheet name="王道操作系统" sheetId="5" r:id="rId6"/>
+    <sheet name="王道计网" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -38,32 +39,149 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="261">
+  <si>
+    <t>李林880专题 （选择&amp;填空）习题正确率记录</t>
+  </si>
+  <si>
+    <t>基础篇</t>
+  </si>
+  <si>
+    <t>综合篇</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>章节</t>
+  </si>
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>总题数</t>
+  </si>
+  <si>
+    <t>正确数</t>
+  </si>
+  <si>
+    <t>正确率</t>
+  </si>
+  <si>
+    <t>高等数学</t>
+  </si>
+  <si>
+    <t>第一章 函数、极限、连续</t>
+  </si>
+  <si>
+    <t>第二章 一元函数微分学及其应用</t>
+  </si>
+  <si>
+    <t>第三章 一元函数积分学及其应用</t>
+  </si>
+  <si>
+    <t>第四章 空间解析几何</t>
+  </si>
+  <si>
+    <t>第五章 多元函数微分学及其应用</t>
+  </si>
+  <si>
+    <t>第六章 重积分及其应用</t>
+  </si>
+  <si>
+    <t>第七章 微分方程及其应用</t>
+  </si>
+  <si>
+    <t>第八章 无穷级数</t>
+  </si>
+  <si>
+    <t>第九章 曲线积分与曲面积分</t>
+  </si>
+  <si>
+    <t>高等数学 合计</t>
+  </si>
+  <si>
+    <t>线性代数</t>
+  </si>
+  <si>
+    <t>第十章 行列式</t>
+  </si>
+  <si>
+    <t>第十一章 矩阵</t>
+  </si>
+  <si>
+    <t>第十二章 向量</t>
+  </si>
+  <si>
+    <t>第十三章 线性方程组</t>
+  </si>
+  <si>
+    <t>第十四章 相似矩阵</t>
+  </si>
+  <si>
+    <t>第十五章 二次型</t>
+  </si>
+  <si>
+    <t>线性代数 合计</t>
+  </si>
+  <si>
+    <t>概率论与数理统计</t>
+  </si>
+  <si>
+    <t>第十六章 随机事件及其概率</t>
+  </si>
+  <si>
+    <t>第十七章 随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第十八章 多维随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第十九章 随机变量的数字特征</t>
+  </si>
+  <si>
+    <t>第二十章 大数定律与中心极限定理</t>
+  </si>
+  <si>
+    <t>第二十一章 数理统计的基本概念</t>
+  </si>
+  <si>
+    <t>第二十二章 参数估计</t>
+  </si>
+  <si>
+    <t>第二十三章 假设检验</t>
+  </si>
+  <si>
+    <t>概率论与数理统计 合计</t>
+  </si>
+  <si>
+    <t>总 计</t>
+  </si>
+  <si>
+    <t>解答区</t>
+  </si>
+  <si>
+    <t>扩展篇</t>
+  </si>
+  <si>
+    <t>选填+解答总计区</t>
+  </si>
+  <si>
+    <t>选填区</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
   <si>
     <t>张宇1000题 习题册正确率记录</t>
   </si>
   <si>
-    <t>章节</t>
-  </si>
-  <si>
     <t>日期</t>
   </si>
   <si>
     <t>总题目</t>
   </si>
   <si>
-    <t>正确数</t>
-  </si>
-  <si>
-    <t>正确率</t>
-  </si>
-  <si>
-    <t>基础篇</t>
-  </si>
-  <si>
-    <t>高等数学</t>
-  </si>
-  <si>
     <t>零基础</t>
   </si>
   <si>
@@ -121,9 +239,6 @@
     <t>第18章 多元函数积分学</t>
   </si>
   <si>
-    <t>线性代数</t>
-  </si>
-  <si>
     <t>第1章 行列式</t>
   </si>
   <si>
@@ -142,9 +257,6 @@
     <t>第6章 二次型</t>
   </si>
   <si>
-    <t>概率论与数理统计</t>
-  </si>
-  <si>
     <t>第1章 随机事件与概率</t>
   </si>
   <si>
@@ -220,9 +332,6 @@
     <t>强化篇合计</t>
   </si>
   <si>
-    <t>综合篇</t>
-  </si>
-  <si>
     <t>综合测试</t>
   </si>
   <si>
@@ -241,114 +350,6 @@
     <t>综合篇合计</t>
   </si>
   <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>李林880专题 （选择&amp;填空）习题正确率记录</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>时间</t>
-  </si>
-  <si>
-    <t>总题数</t>
-  </si>
-  <si>
-    <t>第一章 函数、极限、连续</t>
-  </si>
-  <si>
-    <t>第二章 一元函数微分学及其应用</t>
-  </si>
-  <si>
-    <t>第三章 一元函数积分学及其应用</t>
-  </si>
-  <si>
-    <t>第四章 空间解析几何</t>
-  </si>
-  <si>
-    <t>第五章 多元函数微分学及其应用</t>
-  </si>
-  <si>
-    <t>第六章 重积分及其应用</t>
-  </si>
-  <si>
-    <t>第七章 微分方程及其应用</t>
-  </si>
-  <si>
-    <t>第八章 无穷级数</t>
-  </si>
-  <si>
-    <t>第九章 曲线积分与曲面积分</t>
-  </si>
-  <si>
-    <t>高等数学 合计</t>
-  </si>
-  <si>
-    <t>第十章 行列式</t>
-  </si>
-  <si>
-    <t>第十一章 矩阵</t>
-  </si>
-  <si>
-    <t>第十二章 向量</t>
-  </si>
-  <si>
-    <t>第十三章 线性方程组</t>
-  </si>
-  <si>
-    <t>第十四章 相似矩阵</t>
-  </si>
-  <si>
-    <t>第十五章 二次型</t>
-  </si>
-  <si>
-    <t>线性代数 合计</t>
-  </si>
-  <si>
-    <t>第十六章 随机事件及其概率</t>
-  </si>
-  <si>
-    <t>第十七章 随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第十八章 多维随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第十九章 随机变量的数字特征</t>
-  </si>
-  <si>
-    <t>第二十章 大数定律与中心极限定理</t>
-  </si>
-  <si>
-    <t>第二十一章 数理统计的基本概念</t>
-  </si>
-  <si>
-    <t>第二十二章 参数估计</t>
-  </si>
-  <si>
-    <t>第二十三章 假设检验</t>
-  </si>
-  <si>
-    <t>概率论与数理统计 合计</t>
-  </si>
-  <si>
-    <t>总 计</t>
-  </si>
-  <si>
-    <t>解答区</t>
-  </si>
-  <si>
-    <t>扩展篇</t>
-  </si>
-  <si>
-    <t>选填+解答总计区</t>
-  </si>
-  <si>
-    <t>选填区</t>
-  </si>
-  <si>
     <t>王道数据结构 课后习题正确率记录</t>
   </si>
   <si>
@@ -782,13 +783,52 @@
   </si>
   <si>
     <t>6.5 万维网</t>
+  </si>
+  <si>
+    <t>高等数学辅导讲义严选题 习题正确率记录</t>
+  </si>
+  <si>
+    <t>选择题</t>
+  </si>
+  <si>
+    <t>填空题</t>
+  </si>
+  <si>
+    <t>问答题</t>
+  </si>
+  <si>
+    <t>第一章 函数 极限 连续</t>
+  </si>
+  <si>
+    <t>第二章 一元函数微分学</t>
+  </si>
+  <si>
+    <t>第三章 一元函数积分学</t>
+  </si>
+  <si>
+    <t>第四章 常微分方程</t>
+  </si>
+  <si>
+    <t>第五章 多元函数微分学</t>
+  </si>
+  <si>
+    <t>第六章 二重积分</t>
+  </si>
+  <si>
+    <t>第七章 无穷级数 (仅数学一、三)</t>
+  </si>
+  <si>
+    <t>第八章 向量代数与空间解析几何及多元微分学在几何上的应用 (仅数学一)</t>
+  </si>
+  <si>
+    <t>第九章 多元函数积分学及其应用 (仅数学一)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -882,6 +922,30 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -939,12 +1003,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1016,35 +1095,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1097,77 +1152,305 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="657">
+  <dxfs count="681">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6722,6 +7005,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
   <dimension ref="A1:E91"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6730,44 +7016,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
+      <c r="A1" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="2" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -6776,7 +7062,7 @@
     </row>
     <row r="6" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B6" s="25">
         <v>514</v>
@@ -6794,7 +7080,7 @@
     </row>
     <row r="7" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B7" s="25">
         <v>515</v>
@@ -6812,7 +7098,7 @@
     </row>
     <row r="8" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B8" s="25">
         <v>516</v>
@@ -6830,7 +7116,7 @@
     </row>
     <row r="9" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B9" s="25">
         <v>517</v>
@@ -6848,7 +7134,7 @@
     </row>
     <row r="10" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B10" s="25">
         <v>518</v>
@@ -6866,7 +7152,7 @@
     </row>
     <row r="11" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B11" s="25">
         <v>520</v>
@@ -6884,7 +7170,7 @@
     </row>
     <row r="12" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="B12" s="25">
         <v>521</v>
@@ -6902,7 +7188,7 @@
     </row>
     <row r="13" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -6914,7 +7200,7 @@
     </row>
     <row r="14" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B14" s="25">
         <v>524</v>
@@ -6932,7 +7218,7 @@
     </row>
     <row r="15" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B15" s="25">
         <v>526</v>
@@ -6950,7 +7236,7 @@
     </row>
     <row r="16" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B16" s="25">
         <v>527</v>
@@ -6968,7 +7254,7 @@
     </row>
     <row r="17" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -6980,7 +7266,7 @@
     </row>
     <row r="18" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
@@ -6992,7 +7278,7 @@
     </row>
     <row r="19" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -7004,7 +7290,7 @@
     </row>
     <row r="20" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
@@ -7016,7 +7302,7 @@
     </row>
     <row r="21" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -7028,7 +7314,7 @@
     </row>
     <row r="22" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
@@ -7040,7 +7326,7 @@
     </row>
     <row r="23" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -7052,7 +7338,7 @@
     </row>
     <row r="24" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -7064,7 +7350,7 @@
     </row>
     <row r="25" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -7073,7 +7359,7 @@
     </row>
     <row r="26" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B26" s="25">
         <v>522</v>
@@ -7091,7 +7377,7 @@
     </row>
     <row r="27" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B27" s="25">
         <v>523</v>
@@ -7109,7 +7395,7 @@
     </row>
     <row r="28" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B28" s="25">
         <v>525</v>
@@ -7127,7 +7413,7 @@
     </row>
     <row r="29" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B29" s="25">
         <v>528</v>
@@ -7145,7 +7431,7 @@
     </row>
     <row r="30" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
@@ -7157,7 +7443,7 @@
     </row>
     <row r="31" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -7169,7 +7455,7 @@
     </row>
     <row r="32" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -7178,7 +7464,7 @@
     </row>
     <row r="33" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -7190,7 +7476,7 @@
     </row>
     <row r="34" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
@@ -7202,7 +7488,7 @@
     </row>
     <row r="35" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -7214,7 +7500,7 @@
     </row>
     <row r="36" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
@@ -7226,7 +7512,7 @@
     </row>
     <row r="37" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -7238,7 +7524,7 @@
     </row>
     <row r="38" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
@@ -7250,7 +7536,7 @@
     </row>
     <row r="39" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B39" s="27"/>
       <c r="C39" s="27">
@@ -7268,17 +7554,17 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="33"/>
+      <c r="A41" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="41"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
@@ -7287,7 +7573,7 @@
     </row>
     <row r="43" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -7299,7 +7585,7 @@
     </row>
     <row r="44" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
@@ -7311,7 +7597,7 @@
     </row>
     <row r="45" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="24" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -7323,7 +7609,7 @@
     </row>
     <row r="46" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="25"/>
@@ -7335,7 +7621,7 @@
     </row>
     <row r="47" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -7347,7 +7633,7 @@
     </row>
     <row r="48" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
@@ -7359,7 +7645,7 @@
     </row>
     <row r="49" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -7371,7 +7657,7 @@
     </row>
     <row r="50" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="24" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
@@ -7383,7 +7669,7 @@
     </row>
     <row r="51" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -7395,7 +7681,7 @@
     </row>
     <row r="52" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="25"/>
@@ -7407,7 +7693,7 @@
     </row>
     <row r="53" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -7419,7 +7705,7 @@
     </row>
     <row r="54" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="24" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="25"/>
@@ -7431,7 +7717,7 @@
     </row>
     <row r="55" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -7443,7 +7729,7 @@
     </row>
     <row r="56" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="25"/>
@@ -7455,7 +7741,7 @@
     </row>
     <row r="57" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -7467,7 +7753,7 @@
     </row>
     <row r="58" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -7479,7 +7765,7 @@
     </row>
     <row r="59" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -7491,7 +7777,7 @@
     </row>
     <row r="60" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="25"/>
@@ -7503,7 +7789,7 @@
     </row>
     <row r="61" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -7512,7 +7798,7 @@
     </row>
     <row r="62" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
@@ -7524,7 +7810,7 @@
     </row>
     <row r="63" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -7536,7 +7822,7 @@
     </row>
     <row r="64" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="B64" s="25"/>
       <c r="C64" s="25"/>
@@ -7548,7 +7834,7 @@
     </row>
     <row r="65" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -7560,7 +7846,7 @@
     </row>
     <row r="66" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="B66" s="25"/>
       <c r="C66" s="25"/>
@@ -7572,7 +7858,7 @@
     </row>
     <row r="67" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="24" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -7584,7 +7870,7 @@
     </row>
     <row r="68" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="B68" s="25"/>
       <c r="C68" s="25"/>
@@ -7596,7 +7882,7 @@
     </row>
     <row r="69" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="24" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -7608,7 +7894,7 @@
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="B70" s="25"/>
       <c r="C70" s="25"/>
@@ -7620,7 +7906,7 @@
     </row>
     <row r="71" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B71" s="30"/>
       <c r="C71" s="30"/>
@@ -7629,7 +7915,7 @@
     </row>
     <row r="72" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="B72" s="25"/>
       <c r="C72" s="25"/>
@@ -7641,7 +7927,7 @@
     </row>
     <row r="73" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="24" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -7653,7 +7939,7 @@
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="B74" s="25"/>
       <c r="C74" s="25"/>
@@ -7665,7 +7951,7 @@
     </row>
     <row r="75" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -7677,7 +7963,7 @@
     </row>
     <row r="76" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="B76" s="25"/>
       <c r="C76" s="25"/>
@@ -7689,7 +7975,7 @@
     </row>
     <row r="77" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -7701,7 +7987,7 @@
     </row>
     <row r="78" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="B78" s="25"/>
       <c r="C78" s="25"/>
@@ -7713,7 +7999,7 @@
     </row>
     <row r="79" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="24" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -7725,7 +8011,7 @@
     </row>
     <row r="80" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="B80" s="25"/>
       <c r="C80" s="25"/>
@@ -7737,7 +8023,7 @@
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="27">
@@ -7755,17 +8041,17 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B83" s="32"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
-      <c r="E83" s="33"/>
+      <c r="A83" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" s="40"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="41"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B84" s="30"/>
       <c r="C84" s="30"/>
@@ -7774,7 +8060,7 @@
     </row>
     <row r="85" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="24" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -7786,7 +8072,7 @@
     </row>
     <row r="86" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B86" s="25"/>
       <c r="C86" s="25"/>
@@ -7798,7 +8084,7 @@
     </row>
     <row r="87" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="24" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -7810,7 +8096,7 @@
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B88" s="25"/>
       <c r="C88" s="25"/>
@@ -7822,7 +8108,7 @@
     </row>
     <row r="89" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B89" s="27"/>
       <c r="C89" s="27">
@@ -7841,7 +8127,7 @@
     <row r="90" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="28" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B91" s="29"/>
       <c r="C91" s="29">
@@ -7866,98 +8152,98 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E24">
-    <cfRule type="cellIs" dxfId="656" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="655" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="654" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="680" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="679" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="678" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E31">
-    <cfRule type="cellIs" dxfId="653" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="652" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="651" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="677" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="676" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="675" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E39">
-    <cfRule type="cellIs" dxfId="650" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="649" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="648" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="674" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="673" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="672" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:E60">
-    <cfRule type="cellIs" dxfId="647" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="646" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="645" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="671" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="670" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="669" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E70">
-    <cfRule type="cellIs" dxfId="644" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="643" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="642" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="668" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="667" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="666" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E81">
-    <cfRule type="cellIs" dxfId="641" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="640" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="639" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="665" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="664" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="663" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85:E89">
-    <cfRule type="cellIs" dxfId="638" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="637" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="636" priority="27" operator="lessThan">
+    <cfRule type="cellIs" dxfId="662" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="661" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="660" priority="27" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E91">
-    <cfRule type="cellIs" dxfId="635" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="634" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="633" priority="33" operator="lessThan">
+    <cfRule type="cellIs" dxfId="659" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="658" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="657" priority="33" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7966,6 +8252,631 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="13" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+    </row>
+    <row r="2" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31"/>
+      <c r="B3" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="44"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="I3" s="44"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="44"/>
+      <c r="M3" s="55"/>
+    </row>
+    <row r="4" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34" t="str">
+        <f t="shared" ref="D5:D14" si="0">IF(AND(B5&lt;&gt;"",C5&lt;&gt;""),C5/B5,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34" t="str">
+        <f t="shared" ref="G5:G14" si="1">IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),F5/E5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34" t="str">
+        <f t="shared" ref="J5:J14" si="2">IF(AND(H5&lt;&gt;"",I5&lt;&gt;""),I5/H5,"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="34">
+        <f t="shared" ref="K5:K13" si="3">B5+E5+H5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="34">
+        <f t="shared" ref="L5:L13" si="4">C5+F5+I5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="34" t="e">
+        <f t="shared" ref="M5:M14" si="5">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),L5/K5,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K6" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K7" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K8" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K9" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K10" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K11" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K12" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K13" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="36">
+        <f>SUM(B5:B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="36">
+        <f>SUM(C5:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="36" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E14" s="36">
+        <f>SUM(E5:E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="36">
+        <f>SUM(F5:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="36" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H14" s="36">
+        <f>SUM(H5:H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="36">
+        <f>SUM(I5:I13)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="36" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K14" s="36">
+        <f>SUM(K5:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="36">
+        <f>SUM(L5:L13)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="36" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="38">
+        <f>B14</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="38">
+        <f>C14</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="38" t="e">
+        <f>IF(AND(B16&lt;&gt;"",C16&lt;&gt;""),C16/B16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E16" s="38">
+        <f>E14</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="38">
+        <f>F14</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38" t="e">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),F16/E16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H16" s="38">
+        <f>H14</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="38">
+        <f>I14</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="38" t="e">
+        <f>IF(AND(H16&lt;&gt;"",I16&lt;&gt;""),I16/H16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16" s="38">
+        <f>K14</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="38">
+        <f>L14</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="38" t="e">
+        <f>IF(AND(K16&lt;&gt;"",L16&lt;&gt;""),L16/K16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D5:D14">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G14">
+    <cfRule type="cellIs" dxfId="17" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J14">
+    <cfRule type="cellIs" dxfId="11" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16">
+    <cfRule type="cellIs" dxfId="8" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M14">
+    <cfRule type="cellIs" dxfId="5" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="30" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M16">
+    <cfRule type="cellIs" dxfId="2" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="36" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="4"/>
@@ -7979,93 +8890,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
     </row>
     <row r="2" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
+      <c r="C3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
       <c r="F3" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+        <v>2</v>
+      </c>
+      <c r="G3" s="40"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="40"/>
+      <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="39"/>
+      <c r="A5" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4">
@@ -8103,7 +9014,7 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -8133,7 +9044,7 @@
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -8163,7 +9074,7 @@
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -8193,7 +9104,7 @@
     </row>
     <row r="10" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -8223,7 +9134,7 @@
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -8253,7 +9164,7 @@
     </row>
     <row r="12" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8283,7 +9194,7 @@
     </row>
     <row r="13" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -8313,7 +9224,7 @@
     </row>
     <row r="14" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -8343,7 +9254,7 @@
     </row>
     <row r="15" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7">
@@ -8385,23 +9296,23 @@
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="A17" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -8431,7 +9342,7 @@
     </row>
     <row r="19" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -8461,7 +9372,7 @@
     </row>
     <row r="20" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -8491,7 +9402,7 @@
     </row>
     <row r="21" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -8521,7 +9432,7 @@
     </row>
     <row r="22" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -8551,7 +9462,7 @@
     </row>
     <row r="23" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8581,7 +9492,7 @@
     </row>
     <row r="24" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7">
@@ -8623,23 +9534,23 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="39"/>
+      <c r="A26" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -8669,7 +9580,7 @@
     </row>
     <row r="28" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -8699,7 +9610,7 @@
     </row>
     <row r="29" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -8729,7 +9640,7 @@
     </row>
     <row r="30" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -8759,7 +9670,7 @@
     </row>
     <row r="31" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -8789,7 +9700,7 @@
     </row>
     <row r="32" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -8819,7 +9730,7 @@
     </row>
     <row r="33" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -8849,7 +9760,7 @@
     </row>
     <row r="34" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -8879,7 +9790,7 @@
     </row>
     <row r="35" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="7">
@@ -8921,7 +9832,7 @@
     </row>
     <row r="36" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="10">
@@ -8962,113 +9873,113 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
+      <c r="A39" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="39"/>
+      <c r="C41" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="40"/>
+      <c r="E41" s="41"/>
       <c r="F41" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41" s="38"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="J41" s="38"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="M41" s="38"/>
-      <c r="N41" s="39"/>
+        <v>2</v>
+      </c>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="J41" s="40"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="40"/>
+      <c r="N41" s="41"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="38"/>
-      <c r="M43" s="38"/>
-      <c r="N43" s="39"/>
+      <c r="A43" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="40"/>
+      <c r="N43" s="41"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="B44" s="4">
         <f t="shared" ref="B44:B52" si="13">B6</f>
@@ -9111,7 +10022,7 @@
     </row>
     <row r="45" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="B45" s="4">
         <f t="shared" si="13"/>
@@ -9150,7 +10061,7 @@
     </row>
     <row r="46" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="B46" s="4">
         <f t="shared" si="13"/>
@@ -9189,7 +10100,7 @@
     </row>
     <row r="47" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B47" s="4">
         <f t="shared" si="13"/>
@@ -9228,7 +10139,7 @@
     </row>
     <row r="48" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B48" s="4">
         <f t="shared" si="13"/>
@@ -9267,7 +10178,7 @@
     </row>
     <row r="49" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="B49" s="4">
         <f t="shared" si="13"/>
@@ -9306,7 +10217,7 @@
     </row>
     <row r="50" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B50" s="4">
         <f t="shared" si="13"/>
@@ -9345,7 +10256,7 @@
     </row>
     <row r="51" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" si="13"/>
@@ -9384,7 +10295,7 @@
     </row>
     <row r="52" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="B52" s="4">
         <f t="shared" si="13"/>
@@ -9423,7 +10334,7 @@
     </row>
     <row r="53" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="7">
@@ -9477,26 +10388,26 @@
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="39"/>
+      <c r="A55" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
+      <c r="M55" s="40"/>
+      <c r="N55" s="41"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B56" s="4">
         <f t="shared" ref="B56:B61" si="20">B18</f>
@@ -9535,7 +10446,7 @@
     </row>
     <row r="57" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B57" s="4">
         <f t="shared" si="20"/>
@@ -9574,7 +10485,7 @@
     </row>
     <row r="58" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="B58" s="4">
         <f t="shared" si="20"/>
@@ -9613,7 +10524,7 @@
     </row>
     <row r="59" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="B59" s="4">
         <f t="shared" si="20"/>
@@ -9652,7 +10563,7 @@
     </row>
     <row r="60" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="B60" s="4">
         <f t="shared" si="20"/>
@@ -9691,7 +10602,7 @@
     </row>
     <row r="61" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B61" s="4">
         <f t="shared" si="20"/>
@@ -9730,7 +10641,7 @@
     </row>
     <row r="62" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="7">
@@ -9784,26 +10695,26 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
-      <c r="L64" s="38"/>
-      <c r="M64" s="38"/>
-      <c r="N64" s="39"/>
+      <c r="A64" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="40"/>
+      <c r="L64" s="40"/>
+      <c r="M64" s="40"/>
+      <c r="N64" s="41"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B65" s="4">
         <f t="shared" ref="B65:B72" si="26">B27</f>
@@ -9842,7 +10753,7 @@
     </row>
     <row r="66" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="B66" s="4">
         <f t="shared" si="26"/>
@@ -9881,7 +10792,7 @@
     </row>
     <row r="67" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B67" s="4">
         <f t="shared" si="26"/>
@@ -9920,7 +10831,7 @@
     </row>
     <row r="68" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B68" s="4">
         <f t="shared" si="26"/>
@@ -9959,7 +10870,7 @@
     </row>
     <row r="69" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="B69" s="4">
         <f t="shared" si="26"/>
@@ -9998,7 +10909,7 @@
     </row>
     <row r="70" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="B70" s="4">
         <f t="shared" si="26"/>
@@ -10037,7 +10948,7 @@
     </row>
     <row r="71" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B71" s="4">
         <f t="shared" si="26"/>
@@ -10076,7 +10987,7 @@
     </row>
     <row r="72" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="B72" s="4">
         <f t="shared" si="26"/>
@@ -10115,7 +11026,7 @@
     </row>
     <row r="73" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="7">
@@ -10169,7 +11080,7 @@
     </row>
     <row r="74" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="10">
@@ -10222,93 +11133,93 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B77" s="35"/>
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="35"/>
-      <c r="K77" s="35"/>
+      <c r="A77" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44"/>
+      <c r="I77" s="44"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="44"/>
     </row>
     <row r="78" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D79" s="38"/>
-      <c r="E79" s="39"/>
+      <c r="C79" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79" s="40"/>
+      <c r="E79" s="41"/>
       <c r="F79" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="G79" s="38"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J79" s="38"/>
-      <c r="K79" s="39"/>
+        <v>39</v>
+      </c>
+      <c r="G79" s="40"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J79" s="40"/>
+      <c r="K79" s="41"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="39"/>
+      <c r="A81" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="40"/>
+      <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="B82" s="4">
         <f t="shared" ref="B82:B90" si="32">B6</f>
@@ -10353,7 +11264,7 @@
     </row>
     <row r="83" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="B83" s="4">
         <f t="shared" si="32"/>
@@ -10398,7 +11309,7 @@
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="B84" s="4">
         <f t="shared" si="32"/>
@@ -10443,7 +11354,7 @@
     </row>
     <row r="85" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B85" s="4">
         <f t="shared" si="32"/>
@@ -10488,7 +11399,7 @@
     </row>
     <row r="86" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B86" s="4">
         <f t="shared" si="32"/>
@@ -10533,7 +11444,7 @@
     </row>
     <row r="87" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="B87" s="4">
         <f t="shared" si="32"/>
@@ -10578,7 +11489,7 @@
     </row>
     <row r="88" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="B88" s="4">
         <f t="shared" si="32"/>
@@ -10623,7 +11534,7 @@
     </row>
     <row r="89" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B89" s="4">
         <f t="shared" si="32"/>
@@ -10668,7 +11579,7 @@
     </row>
     <row r="90" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="B90" s="4">
         <f t="shared" si="32"/>
@@ -10713,7 +11624,7 @@
     </row>
     <row r="91" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="7">
@@ -10755,23 +11666,23 @@
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B93" s="38"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
-      <c r="J93" s="38"/>
-      <c r="K93" s="39"/>
+      <c r="A93" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B93" s="40"/>
+      <c r="C93" s="40"/>
+      <c r="D93" s="40"/>
+      <c r="E93" s="40"/>
+      <c r="F93" s="40"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="40"/>
+      <c r="I93" s="40"/>
+      <c r="J93" s="40"/>
+      <c r="K93" s="41"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="B94" s="4">
         <f t="shared" ref="B94:B99" si="42">B18</f>
@@ -10816,7 +11727,7 @@
     </row>
     <row r="95" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B95" s="4">
         <f t="shared" si="42"/>
@@ -10861,7 +11772,7 @@
     </row>
     <row r="96" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="B96" s="4">
         <f t="shared" si="42"/>
@@ -10906,7 +11817,7 @@
     </row>
     <row r="97" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="B97" s="4">
         <f t="shared" si="42"/>
@@ -10951,7 +11862,7 @@
     </row>
     <row r="98" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="B98" s="4">
         <f t="shared" si="42"/>
@@ -10996,7 +11907,7 @@
     </row>
     <row r="99" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B99" s="4">
         <f t="shared" si="42"/>
@@ -11041,7 +11952,7 @@
     </row>
     <row r="100" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="7">
@@ -11083,23 +11994,23 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" s="38"/>
-      <c r="C102" s="38"/>
-      <c r="D102" s="38"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="38"/>
-      <c r="G102" s="38"/>
-      <c r="H102" s="38"/>
-      <c r="I102" s="38"/>
-      <c r="J102" s="38"/>
-      <c r="K102" s="39"/>
+      <c r="A102" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B102" s="40"/>
+      <c r="C102" s="40"/>
+      <c r="D102" s="40"/>
+      <c r="E102" s="40"/>
+      <c r="F102" s="40"/>
+      <c r="G102" s="40"/>
+      <c r="H102" s="40"/>
+      <c r="I102" s="40"/>
+      <c r="J102" s="40"/>
+      <c r="K102" s="41"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B103" s="4">
         <f t="shared" ref="B103:B110" si="49">B27</f>
@@ -11144,7 +12055,7 @@
     </row>
     <row r="104" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="B104" s="4">
         <f t="shared" si="49"/>
@@ -11189,7 +12100,7 @@
     </row>
     <row r="105" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B105" s="4">
         <f t="shared" si="49"/>
@@ -11234,7 +12145,7 @@
     </row>
     <row r="106" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B106" s="4">
         <f t="shared" si="49"/>
@@ -11279,7 +12190,7 @@
     </row>
     <row r="107" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="B107" s="4">
         <f t="shared" si="49"/>
@@ -11324,7 +12235,7 @@
     </row>
     <row r="108" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="B108" s="4">
         <f t="shared" si="49"/>
@@ -11369,7 +12280,7 @@
     </row>
     <row r="109" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B109" s="4">
         <f t="shared" si="49"/>
@@ -11414,7 +12325,7 @@
     </row>
     <row r="110" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="B110" s="4">
         <f t="shared" si="49"/>
@@ -11459,7 +12370,7 @@
     </row>
     <row r="111" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="7">
@@ -11501,7 +12412,7 @@
     </row>
     <row r="112" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B112" s="9"/>
       <c r="C112" s="10">
@@ -11543,14 +12454,7 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A5:K5"/>
@@ -11565,377 +12469,384 @@
     <mergeCell ref="C79:E79"/>
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
-    <cfRule type="cellIs" dxfId="632" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="631" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="630" priority="26" operator="between">
+    <cfRule type="cellIs" dxfId="656" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="655" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="654" priority="26" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E24">
-    <cfRule type="cellIs" dxfId="629" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="628" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="627" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="653" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="652" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="651" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E36">
-    <cfRule type="cellIs" dxfId="626" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="625" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="624" priority="43" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="650" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="649" priority="45" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="648" priority="43" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E44:E53">
-    <cfRule type="cellIs" dxfId="623" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="622" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="621" priority="89" operator="between">
+    <cfRule type="cellIs" dxfId="647" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="646" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="645" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E55:E74">
-    <cfRule type="cellIs" dxfId="620" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="619" priority="3" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="618" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="644" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="643" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="642" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E82:E91">
-    <cfRule type="cellIs" dxfId="617" priority="172" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="616" priority="173" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="615" priority="174" operator="lessThan">
+    <cfRule type="cellIs" dxfId="641" priority="172" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="640" priority="173" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="639" priority="174" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="cellIs" dxfId="614" priority="182" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="613" priority="181" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="612" priority="183" operator="lessThan">
+    <cfRule type="cellIs" dxfId="638" priority="182" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="637" priority="181" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="636" priority="183" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E100:E108">
-    <cfRule type="cellIs" dxfId="611" priority="192" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="610" priority="191" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="609" priority="190" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="635" priority="192" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="634" priority="191" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="633" priority="190" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E112">
-    <cfRule type="cellIs" dxfId="608" priority="217" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="607" priority="218" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="606" priority="219" operator="lessThan">
+    <cfRule type="cellIs" dxfId="632" priority="217" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="631" priority="218" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="630" priority="219" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H15">
-    <cfRule type="cellIs" dxfId="605" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="604" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="603" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="629" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="628" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="627" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H24">
-    <cfRule type="cellIs" dxfId="602" priority="39" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="601" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="600" priority="38" operator="between">
+    <cfRule type="cellIs" dxfId="626" priority="39" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="625" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="624" priority="38" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H36">
-    <cfRule type="cellIs" dxfId="599" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="598" priority="47" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="597" priority="48" operator="lessThan">
+    <cfRule type="cellIs" dxfId="623" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="622" priority="47" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="621" priority="48" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44:H53">
-    <cfRule type="cellIs" dxfId="596" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="595" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="594" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="620" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="619" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="618" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H55:H74">
-    <cfRule type="cellIs" dxfId="593" priority="9" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="592" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="591" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="617" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="616" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="615" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82:H91">
-    <cfRule type="cellIs" dxfId="590" priority="176" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="589" priority="175" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="588" priority="177" operator="lessThan">
+    <cfRule type="cellIs" dxfId="614" priority="176" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="613" priority="175" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="612" priority="177" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H93:H98">
-    <cfRule type="cellIs" dxfId="587" priority="184" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="586" priority="185" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="585" priority="186" operator="lessThan">
+    <cfRule type="cellIs" dxfId="611" priority="184" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="610" priority="185" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="609" priority="186" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H100:H108">
-    <cfRule type="cellIs" dxfId="584" priority="193" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="583" priority="194" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="582" priority="195" operator="lessThan">
+    <cfRule type="cellIs" dxfId="608" priority="193" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="607" priority="194" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="606" priority="195" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H112">
-    <cfRule type="cellIs" dxfId="581" priority="220" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="580" priority="221" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="579" priority="222" operator="lessThan">
+    <cfRule type="cellIs" dxfId="605" priority="220" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="604" priority="221" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="603" priority="222" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K15">
-    <cfRule type="cellIs" dxfId="578" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="577" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="576" priority="31" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="602" priority="33" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="601" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="600" priority="31" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K24">
-    <cfRule type="cellIs" dxfId="575" priority="42" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="574" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="573" priority="40" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="599" priority="42" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="598" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="597" priority="40" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K36">
-    <cfRule type="cellIs" dxfId="572" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="571" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="570" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="596" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="595" priority="51" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="594" priority="49" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:K53">
-    <cfRule type="cellIs" dxfId="569" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="568" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="567" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="593" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="592" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="591" priority="94" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K74">
-    <cfRule type="cellIs" dxfId="566" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="565" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="564" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="590" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="589" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="588" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K82:K91">
-    <cfRule type="cellIs" dxfId="563" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="562" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="561" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="587" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="586" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="585" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K98">
-    <cfRule type="cellIs" dxfId="560" priority="187" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="559" priority="188" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="558" priority="189" operator="lessThan">
+    <cfRule type="cellIs" dxfId="584" priority="187" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="583" priority="188" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="582" priority="189" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100:K108">
-    <cfRule type="cellIs" dxfId="557" priority="196" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="556" priority="197" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="555" priority="198" operator="lessThan">
+    <cfRule type="cellIs" dxfId="581" priority="196" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="580" priority="197" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="579" priority="198" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K111:K112">
-    <cfRule type="cellIs" dxfId="554" priority="223" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="553" priority="224" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="552" priority="225" operator="lessThan">
+    <cfRule type="cellIs" dxfId="578" priority="223" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="577" priority="224" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="576" priority="225" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44:N53">
-    <cfRule type="cellIs" dxfId="551" priority="99" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="550" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="549" priority="97" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="575" priority="99" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="574" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="573" priority="97" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:N60">
-    <cfRule type="cellIs" dxfId="548" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="547" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="546" priority="111" operator="lessThan">
+    <cfRule type="cellIs" dxfId="572" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="571" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="570" priority="111" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N62:N70">
-    <cfRule type="cellIs" dxfId="545" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="544" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="543" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="569" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="568" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="567" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N73:N74">
-    <cfRule type="cellIs" dxfId="542" priority="157" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="541" priority="158" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="540" priority="159" operator="lessThan">
+    <cfRule type="cellIs" dxfId="566" priority="157" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="565" priority="158" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="564" priority="159" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11943,7 +12854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V47"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -11955,75 +12866,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="41"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="45" t="s">
+      <c r="M3" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="39"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>107</v>
@@ -12044,16 +12955,16 @@
         <v>112</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>107</v>
@@ -14076,7 +14987,7 @@
     </row>
     <row r="45" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="18">
@@ -14225,650 +15136,650 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="539" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="538" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="537" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="563" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="562" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="561" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="536" priority="21" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="535" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="534" priority="20" operator="between">
+    <cfRule type="cellIs" dxfId="560" priority="21" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="559" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="558" priority="20" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="533" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="532" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="531" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="557" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="556" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="555" priority="39" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="530" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="529" priority="57" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="528" priority="55" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="554" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="553" priority="57" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="552" priority="55" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="527" priority="75" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="526" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="525" priority="73" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="551" priority="75" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="550" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="549" priority="73" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="524" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="523" priority="93" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="522" priority="91" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="548" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="547" priority="93" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="546" priority="91" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="521" priority="111" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="520" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="519" priority="109" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="545" priority="111" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="544" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="543" priority="109" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="518" priority="127" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="517" priority="129" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="516" priority="128" operator="between">
+    <cfRule type="cellIs" dxfId="542" priority="127" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="541" priority="129" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="540" priority="128" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="515" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="514" priority="165" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="513" priority="164" operator="between">
+    <cfRule type="cellIs" dxfId="539" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="538" priority="165" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="537" priority="164" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H7">
-    <cfRule type="cellIs" dxfId="512" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="511" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="510" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="536" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="535" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="534" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="509" priority="24" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="508" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="507" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="533" priority="24" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="532" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="531" priority="23" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:H16">
-    <cfRule type="cellIs" dxfId="506" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="505" priority="42" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="504" priority="40" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="530" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="529" priority="42" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="528" priority="40" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="503" priority="60" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="502" priority="59" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="501" priority="58" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="527" priority="60" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="526" priority="59" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="525" priority="58" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H25">
-    <cfRule type="cellIs" dxfId="500" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="499" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="498" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="524" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="523" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="522" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H30">
-    <cfRule type="cellIs" dxfId="497" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="496" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="495" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="521" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="520" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="519" priority="94" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H36">
-    <cfRule type="cellIs" dxfId="494" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="493" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="492" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="518" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="517" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="516" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:H45">
-    <cfRule type="cellIs" dxfId="491" priority="132" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="490" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="489" priority="130" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="515" priority="132" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="514" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="513" priority="130" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H47">
-    <cfRule type="cellIs" dxfId="488" priority="166" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="487" priority="167" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="486" priority="168" operator="lessThan">
+    <cfRule type="cellIs" dxfId="512" priority="166" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="511" priority="167" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="510" priority="168" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K7">
-    <cfRule type="cellIs" dxfId="485" priority="9" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="484" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="483" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="509" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="508" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="507" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11">
-    <cfRule type="cellIs" dxfId="482" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="481" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="480" priority="26" operator="between">
+    <cfRule type="cellIs" dxfId="506" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="505" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="504" priority="26" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K16">
-    <cfRule type="cellIs" dxfId="479" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="478" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="477" priority="43" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="503" priority="45" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="502" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="501" priority="43" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K19">
-    <cfRule type="cellIs" dxfId="476" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="475" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="474" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="500" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="499" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="498" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K25">
-    <cfRule type="cellIs" dxfId="473" priority="81" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="472" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="471" priority="79" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="497" priority="81" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="496" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="495" priority="79" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K30">
-    <cfRule type="cellIs" dxfId="470" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="469" priority="99" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="468" priority="98" operator="between">
+    <cfRule type="cellIs" dxfId="494" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="493" priority="99" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="492" priority="98" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32:K36">
-    <cfRule type="cellIs" dxfId="467" priority="117" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="466" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="465" priority="116" operator="between">
+    <cfRule type="cellIs" dxfId="491" priority="117" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="490" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="489" priority="116" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:K45">
-    <cfRule type="cellIs" dxfId="464" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="463" priority="135" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="462" priority="133" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="488" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="487" priority="135" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="486" priority="133" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="cellIs" dxfId="461" priority="169" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="460" priority="170" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="459" priority="171" operator="lessThan">
+    <cfRule type="cellIs" dxfId="485" priority="169" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="484" priority="170" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="483" priority="171" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P7">
-    <cfRule type="cellIs" dxfId="458" priority="12" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="457" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="456" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="482" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="481" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="480" priority="10" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P11">
-    <cfRule type="cellIs" dxfId="455" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="454" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="453" priority="29" operator="between">
+    <cfRule type="cellIs" dxfId="479" priority="30" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="478" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="477" priority="29" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P16">
-    <cfRule type="cellIs" dxfId="452" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="451" priority="47" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="450" priority="48" operator="lessThan">
+    <cfRule type="cellIs" dxfId="476" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="475" priority="47" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="474" priority="48" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:P19">
-    <cfRule type="cellIs" dxfId="449" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="448" priority="66" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="447" priority="64" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="473" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="472" priority="66" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="471" priority="64" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P25">
-    <cfRule type="cellIs" dxfId="446" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="445" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="444" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="470" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="469" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="468" priority="84" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P30">
-    <cfRule type="cellIs" dxfId="443" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="442" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="441" priority="101" operator="between">
+    <cfRule type="cellIs" dxfId="467" priority="102" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="466" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="465" priority="101" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32:P36">
-    <cfRule type="cellIs" dxfId="440" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="439" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="438" priority="119" operator="between">
+    <cfRule type="cellIs" dxfId="464" priority="120" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="463" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="462" priority="119" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38:P45">
-    <cfRule type="cellIs" dxfId="437" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="436" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="435" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="461" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="460" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="459" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="cellIs" dxfId="434" priority="172" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="433" priority="173" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="432" priority="174" operator="lessThan">
+    <cfRule type="cellIs" dxfId="458" priority="172" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="457" priority="173" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="456" priority="174" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S7">
-    <cfRule type="cellIs" dxfId="431" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="430" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="429" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="455" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="454" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="453" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S9:S11">
-    <cfRule type="cellIs" dxfId="428" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="427" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="426" priority="32" operator="between">
+    <cfRule type="cellIs" dxfId="452" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="451" priority="33" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="450" priority="32" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S16">
-    <cfRule type="cellIs" dxfId="425" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="424" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="423" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="449" priority="51" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="448" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="447" priority="49" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S19">
-    <cfRule type="cellIs" dxfId="422" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="421" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="420" priority="68" operator="between">
+    <cfRule type="cellIs" dxfId="446" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="445" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="444" priority="68" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S25">
-    <cfRule type="cellIs" dxfId="419" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="418" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="443" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="442" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="441" priority="87" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S30">
-    <cfRule type="cellIs" dxfId="416" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="414" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="440" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="439" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="438" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:S36">
-    <cfRule type="cellIs" dxfId="413" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="412" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="411" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="437" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="436" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="435" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S38:S45">
-    <cfRule type="cellIs" dxfId="410" priority="141" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="409" priority="139" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="408" priority="140" operator="between">
+    <cfRule type="cellIs" dxfId="434" priority="141" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="433" priority="139" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="432" priority="140" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47">
-    <cfRule type="cellIs" dxfId="407" priority="175" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="406" priority="176" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="405" priority="177" operator="lessThan">
+    <cfRule type="cellIs" dxfId="431" priority="175" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="430" priority="176" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="429" priority="177" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V7">
-    <cfRule type="cellIs" dxfId="404" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="403" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="428" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="427" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="426" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:V11">
-    <cfRule type="cellIs" dxfId="401" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="400" priority="36" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="34" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="425" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="424" priority="36" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="423" priority="34" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V16">
-    <cfRule type="cellIs" dxfId="398" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="397" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="396" priority="53" operator="between">
+    <cfRule type="cellIs" dxfId="422" priority="54" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="421" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="420" priority="53" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:V19">
-    <cfRule type="cellIs" dxfId="395" priority="72" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="394" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="393" priority="70" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="419" priority="72" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="418" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="417" priority="70" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V25">
-    <cfRule type="cellIs" dxfId="392" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="390" priority="89" operator="between">
+    <cfRule type="cellIs" dxfId="416" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="415" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="414" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V27:V30">
-    <cfRule type="cellIs" dxfId="389" priority="108" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="388" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="387" priority="106" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="413" priority="108" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="412" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="411" priority="106" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32:V36">
-    <cfRule type="cellIs" dxfId="386" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="385" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="125" operator="between">
+    <cfRule type="cellIs" dxfId="410" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="409" priority="126" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="408" priority="125" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V45">
-    <cfRule type="cellIs" dxfId="383" priority="142" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="382" priority="143" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="381" priority="144" operator="lessThan">
+    <cfRule type="cellIs" dxfId="407" priority="142" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="406" priority="143" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="405" priority="144" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="cellIs" dxfId="380" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="379" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="404" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="403" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="402" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14876,7 +15787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -14888,75 +15799,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="41"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="45" t="s">
+      <c r="M3" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="39"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>107</v>
@@ -14977,16 +15888,16 @@
         <v>112</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>107</v>
@@ -17035,7 +17946,7 @@
     </row>
     <row r="40" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="18">
@@ -17184,578 +18095,578 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="377" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="376" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="401" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="400" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="399" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="374" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="372" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="398" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="396" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="371" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="370" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="395" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="394" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="39" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="368" priority="55" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="57" operator="lessThan">
+    <cfRule type="cellIs" dxfId="392" priority="55" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="390" priority="57" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="365" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="363" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="389" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="387" priority="75" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="362" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="361" priority="93" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="360" priority="92" operator="between">
+    <cfRule type="cellIs" dxfId="386" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="385" priority="93" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="92" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E40">
-    <cfRule type="cellIs" dxfId="359" priority="111" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="358" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="357" priority="109" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="383" priority="111" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="382" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="381" priority="109" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="356" priority="147" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="355" priority="145" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="354" priority="146" operator="between">
+    <cfRule type="cellIs" dxfId="380" priority="147" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="379" priority="145" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="378" priority="146" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H8">
-    <cfRule type="cellIs" dxfId="353" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="352" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="351" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="377" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="376" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="375" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12">
-    <cfRule type="cellIs" dxfId="350" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="348" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="374" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="373" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="372" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H19">
-    <cfRule type="cellIs" dxfId="347" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="346" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="345" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="371" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="370" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="369" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H24">
-    <cfRule type="cellIs" dxfId="344" priority="58" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="343" priority="59" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="342" priority="60" operator="lessThan">
+    <cfRule type="cellIs" dxfId="368" priority="58" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="367" priority="59" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="366" priority="60" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H32">
-    <cfRule type="cellIs" dxfId="341" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="340" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="339" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="365" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="364" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="363" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H35">
-    <cfRule type="cellIs" dxfId="338" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="337" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="336" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="362" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="361" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="360" priority="94" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:H40">
-    <cfRule type="cellIs" dxfId="335" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="334" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="333" priority="113" operator="between">
+    <cfRule type="cellIs" dxfId="359" priority="114" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="358" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="357" priority="113" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="cellIs" dxfId="332" priority="148" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="149" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="330" priority="150" operator="lessThan">
+    <cfRule type="cellIs" dxfId="356" priority="148" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="355" priority="149" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="354" priority="150" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K8">
-    <cfRule type="cellIs" dxfId="329" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="328" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="327" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="353" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="352" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="351" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:K12">
-    <cfRule type="cellIs" dxfId="326" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="325" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="324" priority="27" operator="lessThan">
+    <cfRule type="cellIs" dxfId="350" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="349" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="348" priority="27" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14:K19">
-    <cfRule type="cellIs" dxfId="323" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="321" priority="45" operator="lessThan">
+    <cfRule type="cellIs" dxfId="347" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="346" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="345" priority="45" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K24">
-    <cfRule type="cellIs" dxfId="320" priority="63" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="62" operator="between">
+    <cfRule type="cellIs" dxfId="344" priority="63" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="343" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="342" priority="62" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K32">
-    <cfRule type="cellIs" dxfId="317" priority="79" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="81" operator="lessThan">
+    <cfRule type="cellIs" dxfId="341" priority="79" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="340" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="339" priority="81" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34:K35">
-    <cfRule type="cellIs" dxfId="314" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="313" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="338" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="337" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="336" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K40">
-    <cfRule type="cellIs" dxfId="311" priority="117" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="115" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="335" priority="117" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="334" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="333" priority="115" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="cellIs" dxfId="308" priority="153" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="306" priority="151" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="332" priority="153" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="331" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="330" priority="151" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P8">
-    <cfRule type="cellIs" dxfId="305" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="329" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="328" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="327" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P12">
-    <cfRule type="cellIs" dxfId="302" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="301" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="28" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="326" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="325" priority="30" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="324" priority="28" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P14:P19">
-    <cfRule type="cellIs" dxfId="299" priority="48" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="297" priority="47" operator="between">
+    <cfRule type="cellIs" dxfId="323" priority="48" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="322" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="321" priority="47" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P24">
-    <cfRule type="cellIs" dxfId="296" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="294" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="320" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="319" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="318" priority="66" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26:P32">
-    <cfRule type="cellIs" dxfId="293" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="84" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="82" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="317" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="316" priority="84" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="315" priority="82" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P34:P35">
-    <cfRule type="cellIs" dxfId="290" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="288" priority="100" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="314" priority="102" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="313" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="312" priority="100" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P40">
-    <cfRule type="cellIs" dxfId="287" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="118" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="311" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="310" priority="120" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="309" priority="118" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="cellIs" dxfId="284" priority="155" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="283" priority="154" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="282" priority="156" operator="lessThan">
+    <cfRule type="cellIs" dxfId="308" priority="155" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="307" priority="154" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="306" priority="156" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S8">
-    <cfRule type="cellIs" dxfId="281" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="305" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="304" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="303" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S12">
-    <cfRule type="cellIs" dxfId="278" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="276" priority="33" operator="lessThan">
+    <cfRule type="cellIs" dxfId="302" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="301" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="300" priority="33" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S14:S19">
-    <cfRule type="cellIs" dxfId="275" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="299" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="298" priority="51" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="297" priority="49" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S24">
-    <cfRule type="cellIs" dxfId="272" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="67" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="296" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="295" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="294" priority="67" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26:S32">
-    <cfRule type="cellIs" dxfId="269" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="87" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="86" operator="between">
+    <cfRule type="cellIs" dxfId="293" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="292" priority="87" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="291" priority="86" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S34:S35">
-    <cfRule type="cellIs" dxfId="266" priority="105" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="265" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="103" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="290" priority="105" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="289" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="288" priority="103" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S37:S40">
-    <cfRule type="cellIs" dxfId="263" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="287" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="286" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="285" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S42">
-    <cfRule type="cellIs" dxfId="260" priority="157" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="158" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="258" priority="159" operator="lessThan">
+    <cfRule type="cellIs" dxfId="284" priority="157" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="283" priority="158" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="282" priority="159" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V8">
-    <cfRule type="cellIs" dxfId="257" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="281" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="280" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="279" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:V12">
-    <cfRule type="cellIs" dxfId="254" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="278" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="277" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="276" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V14:V19">
-    <cfRule type="cellIs" dxfId="251" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="52" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="275" priority="54" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="274" priority="53" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="273" priority="52" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V24">
-    <cfRule type="cellIs" dxfId="248" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="246" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="272" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="271" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="270" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26:V32">
-    <cfRule type="cellIs" dxfId="245" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="88" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="269" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="268" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="267" priority="88" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V34:V35">
-    <cfRule type="cellIs" dxfId="242" priority="108" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="106" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="266" priority="108" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="265" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="264" priority="106" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V37:V40">
-    <cfRule type="cellIs" dxfId="239" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="124" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="263" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="262" priority="126" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="261" priority="124" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="cellIs" dxfId="236" priority="160" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="161" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="260" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="259" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="258" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17763,7 +18674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -17775,75 +18686,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="41"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="45" t="s">
+      <c r="M3" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="39"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>107</v>
@@ -17864,16 +18775,16 @@
         <v>112</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>107</v>
@@ -19194,7 +20105,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="18">
@@ -19343,434 +20254,434 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E11">
-    <cfRule type="cellIs" dxfId="233" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="257" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="256" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="255" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="230" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="254" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="253" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="252" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="227" priority="39" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="226" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="37" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="251" priority="39" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="250" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="249" priority="37" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="224" priority="57" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="55" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="56" operator="between">
+    <cfRule type="cellIs" dxfId="248" priority="57" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="247" priority="55" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="246" priority="56" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E28">
-    <cfRule type="cellIs" dxfId="221" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="75" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="74" operator="between">
+    <cfRule type="cellIs" dxfId="245" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="244" priority="75" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="243" priority="74" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="218" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="111" operator="lessThan">
+    <cfRule type="cellIs" dxfId="242" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="241" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="111" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H11">
-    <cfRule type="cellIs" dxfId="215" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="6" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="239" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="238" priority="6" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="237" priority="4" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:H16">
-    <cfRule type="cellIs" dxfId="212" priority="24" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="236" priority="24" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="235" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="234" priority="23" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="209" priority="42" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="40" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="233" priority="42" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="232" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="231" priority="40" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H23">
-    <cfRule type="cellIs" dxfId="206" priority="60" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="59" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="58" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="230" priority="60" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="229" priority="59" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="228" priority="58" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H28">
-    <cfRule type="cellIs" dxfId="203" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="227" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="226" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="225" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="cellIs" dxfId="200" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="113" operator="between">
+    <cfRule type="cellIs" dxfId="224" priority="114" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="222" priority="113" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K11">
-    <cfRule type="cellIs" dxfId="197" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="221" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="220" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="219" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K16">
-    <cfRule type="cellIs" dxfId="194" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="25" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="218" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="217" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="216" priority="25" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K19">
-    <cfRule type="cellIs" dxfId="191" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="44" operator="between">
+    <cfRule type="cellIs" dxfId="215" priority="45" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="214" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="44" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K23">
-    <cfRule type="cellIs" dxfId="188" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="212" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K28">
-    <cfRule type="cellIs" dxfId="185" priority="81" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="79" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="209" priority="81" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="208" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="207" priority="79" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="cellIs" dxfId="182" priority="117" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="115" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="206" priority="117" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="205" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="204" priority="115" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P11">
-    <cfRule type="cellIs" dxfId="179" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="203" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="202" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="201" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P16">
-    <cfRule type="cellIs" dxfId="176" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="200" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="199" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="198" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:P19">
-    <cfRule type="cellIs" dxfId="173" priority="48" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="47" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="46" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="197" priority="48" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="47" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="46" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P23">
-    <cfRule type="cellIs" dxfId="170" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="194" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="193" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="192" priority="66" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P25:P28">
-    <cfRule type="cellIs" dxfId="167" priority="84" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="83" operator="between">
+    <cfRule type="cellIs" dxfId="191" priority="84" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="190" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="189" priority="83" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30">
-    <cfRule type="cellIs" dxfId="164" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="118" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="188" priority="120" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="118" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S11">
-    <cfRule type="cellIs" dxfId="161" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="15" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="185" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="15" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="14" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S16">
-    <cfRule type="cellIs" dxfId="158" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="32" operator="between">
+    <cfRule type="cellIs" dxfId="182" priority="33" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="32" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S19">
-    <cfRule type="cellIs" dxfId="155" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="50" operator="between">
+    <cfRule type="cellIs" dxfId="179" priority="51" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="50" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S23">
-    <cfRule type="cellIs" dxfId="152" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="68" operator="between">
+    <cfRule type="cellIs" dxfId="176" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="68" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S25:S28">
-    <cfRule type="cellIs" dxfId="149" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="173" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="171" priority="87" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S30">
-    <cfRule type="cellIs" dxfId="146" priority="123" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="121" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="170" priority="123" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="168" priority="121" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V11">
-    <cfRule type="cellIs" dxfId="143" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="167" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="166" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="165" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V16">
-    <cfRule type="cellIs" dxfId="140" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="164" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:V19">
-    <cfRule type="cellIs" dxfId="137" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="54" operator="lessThan">
+    <cfRule type="cellIs" dxfId="161" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="160" priority="53" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="159" priority="54" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V23">
-    <cfRule type="cellIs" dxfId="134" priority="72" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="71" operator="between">
+    <cfRule type="cellIs" dxfId="158" priority="72" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="157" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="156" priority="71" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25:V28">
-    <cfRule type="cellIs" dxfId="131" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="88" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="155" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="154" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="88" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="cellIs" dxfId="128" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="152" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="151" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19778,7 +20689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:V41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -19790,75 +20701,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="41"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="45" t="s">
+      <c r="M3" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="39"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>107</v>
@@ -19879,16 +20790,16 @@
         <v>112</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
         <v>107</v>
@@ -21635,7 +22546,7 @@
     </row>
     <row r="39" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="18">
@@ -21784,506 +22695,506 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="125" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="149" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="122" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="146" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="144" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="119" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="39" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="37" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="143" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="39" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="37" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="116" priority="55" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="57" operator="lessThan">
+    <cfRule type="cellIs" dxfId="140" priority="55" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="57" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="113" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="137" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="75" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="110" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="134" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="107" priority="129" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="127" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="128" operator="between">
+    <cfRule type="cellIs" dxfId="131" priority="129" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="127" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="128" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H7">
-    <cfRule type="cellIs" dxfId="104" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="128" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="101" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="125" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:H20">
-    <cfRule type="cellIs" dxfId="98" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H28">
-    <cfRule type="cellIs" dxfId="95" priority="60" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="59" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="58" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="119" priority="60" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="59" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="58" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H32">
-    <cfRule type="cellIs" dxfId="92" priority="78" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="77" operator="between">
+    <cfRule type="cellIs" dxfId="116" priority="78" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="77" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H39">
-    <cfRule type="cellIs" dxfId="89" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="96" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="cellIs" dxfId="86" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="110" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K7">
-    <cfRule type="cellIs" dxfId="83" priority="9" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="107" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11">
-    <cfRule type="cellIs" dxfId="80" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="26" operator="between">
+    <cfRule type="cellIs" dxfId="104" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="26" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K20">
-    <cfRule type="cellIs" dxfId="77" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="43" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="101" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="45" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="43" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:K28">
-    <cfRule type="cellIs" dxfId="74" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="63" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="61" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="98" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="63" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="61" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:K32">
-    <cfRule type="cellIs" dxfId="71" priority="79" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="81" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="79" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="81" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34:K39">
-    <cfRule type="cellIs" dxfId="68" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="65" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P7">
-    <cfRule type="cellIs" dxfId="62" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="12" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="86" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="11" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P11">
-    <cfRule type="cellIs" dxfId="59" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="29" operator="between">
+    <cfRule type="cellIs" dxfId="83" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="30" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="29" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P20">
-    <cfRule type="cellIs" dxfId="56" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="47" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="48" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="47" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="48" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22:P28">
-    <cfRule type="cellIs" dxfId="53" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="66" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30:P32">
-    <cfRule type="cellIs" dxfId="50" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="74" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="84" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P34:P39">
-    <cfRule type="cellIs" dxfId="47" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="101" operator="between">
+    <cfRule type="cellIs" dxfId="71" priority="102" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="101" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P41">
-    <cfRule type="cellIs" dxfId="44" priority="138" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="137" operator="between">
+    <cfRule type="cellIs" dxfId="68" priority="138" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="137" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S7">
-    <cfRule type="cellIs" dxfId="41" priority="15" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="13" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="65" priority="15" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="13" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S9:S11">
-    <cfRule type="cellIs" dxfId="38" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="31" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="33" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="31" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S20">
-    <cfRule type="cellIs" dxfId="35" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="51" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S22:S28">
-    <cfRule type="cellIs" dxfId="32" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="67" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="56" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="67" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S30:S32">
-    <cfRule type="cellIs" dxfId="29" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="87" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S34:S39">
-    <cfRule type="cellIs" dxfId="26" priority="105" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="103" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="50" priority="105" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="103" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S41">
-    <cfRule type="cellIs" dxfId="23" priority="139" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="140" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="141" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="139" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="140" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="141" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V7">
-    <cfRule type="cellIs" dxfId="20" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="44" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="16" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:V11">
-    <cfRule type="cellIs" dxfId="17" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="36" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="34" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="41" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="36" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="34" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V20">
-    <cfRule type="cellIs" dxfId="14" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="52" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="38" priority="54" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="53" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="52" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22:V28">
-    <cfRule type="cellIs" dxfId="11" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30:V32">
-    <cfRule type="cellIs" dxfId="8" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="88" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="88" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V34:V39">
-    <cfRule type="cellIs" dxfId="5" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="cellIs" dxfId="2" priority="142" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="143" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="144" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="142" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="143" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="144" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BD6B75-302D-43BD-B47F-8D70CB435C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9442D1EA-C567-45FE-883C-9DFA65E58A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
-    <sheet name="武忠祥严选题" sheetId="7" r:id="rId2"/>
-    <sheet name="李林880专题" sheetId="2" r:id="rId3"/>
-    <sheet name="王道数据结构" sheetId="3" r:id="rId4"/>
-    <sheet name="王道计组" sheetId="4" r:id="rId5"/>
-    <sheet name="王道操作系统" sheetId="5" r:id="rId6"/>
-    <sheet name="王道计网" sheetId="6" r:id="rId7"/>
+    <sheet name="武忠祥高数严选题" sheetId="8" r:id="rId2"/>
+    <sheet name="李林880专题" sheetId="3" r:id="rId3"/>
+    <sheet name="王道数据结构" sheetId="4" r:id="rId4"/>
+    <sheet name="王道计组" sheetId="5" r:id="rId5"/>
+    <sheet name="王道操作系统" sheetId="6" r:id="rId6"/>
+    <sheet name="王道计网" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -39,38 +39,266 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="261">
+  <si>
+    <t>高等数学辅导讲义严选题 习题正确率记录</t>
+  </si>
+  <si>
+    <t>选择题</t>
+  </si>
+  <si>
+    <t>填空题</t>
+  </si>
+  <si>
+    <t>问答题</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>章节</t>
+  </si>
+  <si>
+    <t>总题数</t>
+  </si>
+  <si>
+    <t>正确数</t>
+  </si>
+  <si>
+    <t>正确率</t>
+  </si>
+  <si>
+    <t>第一章 函数 极限 连续</t>
+  </si>
+  <si>
+    <t>第二章 一元函数微分学</t>
+  </si>
+  <si>
+    <t>第三章 一元函数积分学</t>
+  </si>
+  <si>
+    <t>第四章 常微分方程</t>
+  </si>
+  <si>
+    <t>第五章 多元函数微分学</t>
+  </si>
+  <si>
+    <t>第六章 二重积分</t>
+  </si>
+  <si>
+    <t>第七章 无穷级数 (仅数学一、三)</t>
+  </si>
+  <si>
+    <t>第八章 向量代数与空间解析几何及多元微分学在几何上的应用 (仅数学一)</t>
+  </si>
+  <si>
+    <t>第九章 多元函数积分学及其应用 (仅数学一)</t>
+  </si>
+  <si>
+    <t>总  计</t>
+  </si>
+  <si>
+    <t>张宇1000题 习题册正确率记录</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>总题目</t>
+  </si>
+  <si>
+    <t>基础篇</t>
+  </si>
+  <si>
+    <t>高等数学</t>
+  </si>
+  <si>
+    <t>零基础</t>
+  </si>
+  <si>
+    <t>第1章 函数极限与连续</t>
+  </si>
+  <si>
+    <t>第2章 数列极限</t>
+  </si>
+  <si>
+    <t>第3章 一元函数微分学的概念</t>
+  </si>
+  <si>
+    <t>第4章 一元函数微分学的计算</t>
+  </si>
+  <si>
+    <t>第5章 一元函数微分学的应用(一) ——几何应用</t>
+  </si>
+  <si>
+    <t>第6章 一元函数微分学的应用(二) ——中值定理、微分等式与微分不等式</t>
+  </si>
+  <si>
+    <t>第7章 一元函数微分学的应用(三) ——物理应用</t>
+  </si>
+  <si>
+    <t>第8章 一元函数积分学的概念与性质</t>
+  </si>
+  <si>
+    <t>第9章 一元函数积分学的计算</t>
+  </si>
+  <si>
+    <t>第10章 一元函数积分学的应用(一) ——几何应用</t>
+  </si>
+  <si>
+    <t>第11章 一元函数积分学的应用(二) ——积分等式与积分不等式</t>
+  </si>
+  <si>
+    <t>第12章 一元函数积分学的应用(三) ——物理应用</t>
+  </si>
+  <si>
+    <t>第13章 多元函数微分学</t>
+  </si>
+  <si>
+    <t>第14章 二重积分</t>
+  </si>
+  <si>
+    <t>第15章 微分方程</t>
+  </si>
+  <si>
+    <t>第16章 无穷级数</t>
+  </si>
+  <si>
+    <t>第17章 多元函数积分学的预备知识</t>
+  </si>
+  <si>
+    <t>第18章 多元函数积分学</t>
+  </si>
+  <si>
+    <t>线性代数</t>
+  </si>
+  <si>
+    <t>第1章 行列式</t>
+  </si>
+  <si>
+    <t>第2章 矩阵</t>
+  </si>
+  <si>
+    <t>第3章 向量组</t>
+  </si>
+  <si>
+    <t>第4章 线性方程组</t>
+  </si>
+  <si>
+    <t>第5章 特征值与特征向量</t>
+  </si>
+  <si>
+    <t>第6章 二次型</t>
+  </si>
+  <si>
+    <t>概率论与数理统计</t>
+  </si>
+  <si>
+    <t>第1章 随机事件与概率</t>
+  </si>
+  <si>
+    <t>第2章 一维随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第3章 多维随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第4章 随机变量的数字特征</t>
+  </si>
+  <si>
+    <t>第5章 大数定律与中心极限定理</t>
+  </si>
+  <si>
+    <t>第6章 数理统计</t>
+  </si>
+  <si>
+    <t>基础篇合计</t>
+  </si>
+  <si>
+    <t>强化篇</t>
+  </si>
+  <si>
+    <t>第2章 余子式和代数余子式的计算</t>
+  </si>
+  <si>
+    <t>第3章 矩阵运算</t>
+  </si>
+  <si>
+    <t>第4章 矩阵的秩</t>
+  </si>
+  <si>
+    <t>第5章 线性方程组</t>
+  </si>
+  <si>
+    <t>第6章 向量组</t>
+  </si>
+  <si>
+    <t>第7章 特征值与特征向量</t>
+  </si>
+  <si>
+    <t>第8章 相似理论</t>
+  </si>
+  <si>
+    <t>第9章 二次型</t>
+  </si>
+  <si>
+    <t>第1章 随机事件和概率</t>
+  </si>
+  <si>
+    <t>第3章 一维随机变量函数的分布</t>
+  </si>
+  <si>
+    <t>第4章 多维随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第5章 多维随机变量函数的分布</t>
+  </si>
+  <si>
+    <t>第6章 数字特征</t>
+  </si>
+  <si>
+    <t>第7章 大数定律与中心极限定理</t>
+  </si>
+  <si>
+    <t>第8章 统计量及其分布</t>
+  </si>
+  <si>
+    <t>第9章 参数估计与假设检验</t>
+  </si>
+  <si>
+    <t>强化篇合计</t>
+  </si>
+  <si>
+    <t>综合篇</t>
+  </si>
+  <si>
+    <t>综合测试</t>
+  </si>
+  <si>
+    <t>测试卷一</t>
+  </si>
+  <si>
+    <t>测试卷二</t>
+  </si>
+  <si>
+    <t>测试卷三</t>
+  </si>
+  <si>
+    <t>测试卷四</t>
+  </si>
+  <si>
+    <t>综合篇合计</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
   <si>
     <t>李林880专题 （选择&amp;填空）习题正确率记录</t>
   </si>
   <si>
-    <t>基础篇</t>
-  </si>
-  <si>
-    <t>综合篇</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>章节</t>
-  </si>
-  <si>
     <t>时间</t>
   </si>
   <si>
-    <t>总题数</t>
-  </si>
-  <si>
-    <t>正确数</t>
-  </si>
-  <si>
-    <t>正确率</t>
-  </si>
-  <si>
-    <t>高等数学</t>
-  </si>
-  <si>
     <t>第一章 函数、极限、连续</t>
   </si>
   <si>
@@ -101,9 +329,6 @@
     <t>高等数学 合计</t>
   </si>
   <si>
-    <t>线性代数</t>
-  </si>
-  <si>
     <t>第十章 行列式</t>
   </si>
   <si>
@@ -125,9 +350,6 @@
     <t>线性代数 合计</t>
   </si>
   <si>
-    <t>概率论与数理统计</t>
-  </si>
-  <si>
     <t>第十六章 随机事件及其概率</t>
   </si>
   <si>
@@ -170,186 +392,6 @@
     <t>选填区</t>
   </si>
   <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>张宇1000题 习题册正确率记录</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>总题目</t>
-  </si>
-  <si>
-    <t>零基础</t>
-  </si>
-  <si>
-    <t>第1章 函数极限与连续</t>
-  </si>
-  <si>
-    <t>第2章 数列极限</t>
-  </si>
-  <si>
-    <t>第3章 一元函数微分学的概念</t>
-  </si>
-  <si>
-    <t>第4章 一元函数微分学的计算</t>
-  </si>
-  <si>
-    <t>第5章 一元函数微分学的应用(一) ——几何应用</t>
-  </si>
-  <si>
-    <t>第6章 一元函数微分学的应用(二) ——中值定理、微分等式与微分不等式</t>
-  </si>
-  <si>
-    <t>第7章 一元函数微分学的应用(三) ——物理应用</t>
-  </si>
-  <si>
-    <t>第8章 一元函数积分学的概念与性质</t>
-  </si>
-  <si>
-    <t>第9章 一元函数积分学的计算</t>
-  </si>
-  <si>
-    <t>第10章 一元函数积分学的应用(一) ——几何应用</t>
-  </si>
-  <si>
-    <t>第11章 一元函数积分学的应用(二) ——积分等式与积分不等式</t>
-  </si>
-  <si>
-    <t>第12章 一元函数积分学的应用(三) ——物理应用</t>
-  </si>
-  <si>
-    <t>第13章 多元函数微分学</t>
-  </si>
-  <si>
-    <t>第14章 二重积分</t>
-  </si>
-  <si>
-    <t>第15章 微分方程</t>
-  </si>
-  <si>
-    <t>第16章 无穷级数</t>
-  </si>
-  <si>
-    <t>第17章 多元函数积分学的预备知识</t>
-  </si>
-  <si>
-    <t>第18章 多元函数积分学</t>
-  </si>
-  <si>
-    <t>第1章 行列式</t>
-  </si>
-  <si>
-    <t>第2章 矩阵</t>
-  </si>
-  <si>
-    <t>第3章 向量组</t>
-  </si>
-  <si>
-    <t>第4章 线性方程组</t>
-  </si>
-  <si>
-    <t>第5章 特征值与特征向量</t>
-  </si>
-  <si>
-    <t>第6章 二次型</t>
-  </si>
-  <si>
-    <t>第1章 随机事件与概率</t>
-  </si>
-  <si>
-    <t>第2章 一维随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第3章 多维随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第4章 随机变量的数字特征</t>
-  </si>
-  <si>
-    <t>第5章 大数定律与中心极限定理</t>
-  </si>
-  <si>
-    <t>第6章 数理统计</t>
-  </si>
-  <si>
-    <t>基础篇合计</t>
-  </si>
-  <si>
-    <t>强化篇</t>
-  </si>
-  <si>
-    <t>第2章 余子式和代数余子式的计算</t>
-  </si>
-  <si>
-    <t>第3章 矩阵运算</t>
-  </si>
-  <si>
-    <t>第4章 矩阵的秩</t>
-  </si>
-  <si>
-    <t>第5章 线性方程组</t>
-  </si>
-  <si>
-    <t>第6章 向量组</t>
-  </si>
-  <si>
-    <t>第7章 特征值与特征向量</t>
-  </si>
-  <si>
-    <t>第8章 相似理论</t>
-  </si>
-  <si>
-    <t>第9章 二次型</t>
-  </si>
-  <si>
-    <t>第1章 随机事件和概率</t>
-  </si>
-  <si>
-    <t>第3章 一维随机变量函数的分布</t>
-  </si>
-  <si>
-    <t>第4章 多维随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第5章 多维随机变量函数的分布</t>
-  </si>
-  <si>
-    <t>第6章 数字特征</t>
-  </si>
-  <si>
-    <t>第7章 大数定律与中心极限定理</t>
-  </si>
-  <si>
-    <t>第8章 统计量及其分布</t>
-  </si>
-  <si>
-    <t>第9章 参数估计与假设检验</t>
-  </si>
-  <si>
-    <t>强化篇合计</t>
-  </si>
-  <si>
-    <t>综合测试</t>
-  </si>
-  <si>
-    <t>测试卷一</t>
-  </si>
-  <si>
-    <t>测试卷二</t>
-  </si>
-  <si>
-    <t>测试卷三</t>
-  </si>
-  <si>
-    <t>测试卷四</t>
-  </si>
-  <si>
-    <t>综合篇合计</t>
-  </si>
-  <si>
     <t>王道数据结构 课后习题正确率记录</t>
   </si>
   <si>
@@ -500,9 +542,6 @@
     <t>8.7 外部排序</t>
   </si>
   <si>
-    <t>总  计</t>
-  </si>
-  <si>
     <t>王道计算机组成原理 课后习题正确率记录</t>
   </si>
   <si>
@@ -783,45 +822,6 @@
   </si>
   <si>
     <t>6.5 万维网</t>
-  </si>
-  <si>
-    <t>高等数学辅导讲义严选题 习题正确率记录</t>
-  </si>
-  <si>
-    <t>选择题</t>
-  </si>
-  <si>
-    <t>填空题</t>
-  </si>
-  <si>
-    <t>问答题</t>
-  </si>
-  <si>
-    <t>第一章 函数 极限 连续</t>
-  </si>
-  <si>
-    <t>第二章 一元函数微分学</t>
-  </si>
-  <si>
-    <t>第三章 一元函数积分学</t>
-  </si>
-  <si>
-    <t>第四章 常微分方程</t>
-  </si>
-  <si>
-    <t>第五章 多元函数微分学</t>
-  </si>
-  <si>
-    <t>第六章 二重积分</t>
-  </si>
-  <si>
-    <t>第七章 无穷级数 (仅数学一、三)</t>
-  </si>
-  <si>
-    <t>第八章 向量代数与空间解析几何及多元微分学在几何上的应用 (仅数学一)</t>
-  </si>
-  <si>
-    <t>第九章 多元函数积分学及其应用 (仅数学一)</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1095,11 +1095,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1177,81 +1192,83 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7016,24 +7033,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
+      <c r="A1" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>7</v>
@@ -7043,17 +7060,17 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="A4" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -7062,7 +7079,7 @@
     </row>
     <row r="6" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B6" s="25">
         <v>514</v>
@@ -7080,7 +7097,7 @@
     </row>
     <row r="7" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B7" s="25">
         <v>515</v>
@@ -7098,7 +7115,7 @@
     </row>
     <row r="8" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B8" s="25">
         <v>516</v>
@@ -7116,7 +7133,7 @@
     </row>
     <row r="9" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B9" s="25">
         <v>517</v>
@@ -7134,7 +7151,7 @@
     </row>
     <row r="10" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="B10" s="25">
         <v>518</v>
@@ -7152,7 +7169,7 @@
     </row>
     <row r="11" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B11" s="25">
         <v>520</v>
@@ -7170,7 +7187,7 @@
     </row>
     <row r="12" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B12" s="25">
         <v>521</v>
@@ -7188,7 +7205,7 @@
     </row>
     <row r="13" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -7200,7 +7217,7 @@
     </row>
     <row r="14" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B14" s="25">
         <v>524</v>
@@ -7218,7 +7235,7 @@
     </row>
     <row r="15" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="B15" s="25">
         <v>526</v>
@@ -7236,7 +7253,7 @@
     </row>
     <row r="16" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B16" s="25">
         <v>527</v>
@@ -7254,7 +7271,7 @@
     </row>
     <row r="17" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -7266,7 +7283,7 @@
     </row>
     <row r="18" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
@@ -7278,7 +7295,7 @@
     </row>
     <row r="19" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -7290,7 +7307,7 @@
     </row>
     <row r="20" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
@@ -7302,7 +7319,7 @@
     </row>
     <row r="21" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -7314,7 +7331,7 @@
     </row>
     <row r="22" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
@@ -7326,7 +7343,7 @@
     </row>
     <row r="23" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -7338,7 +7355,7 @@
     </row>
     <row r="24" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -7350,7 +7367,7 @@
     </row>
     <row r="25" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -7359,7 +7376,7 @@
     </row>
     <row r="26" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B26" s="25">
         <v>522</v>
@@ -7377,7 +7394,7 @@
     </row>
     <row r="27" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B27" s="25">
         <v>523</v>
@@ -7395,7 +7412,7 @@
     </row>
     <row r="28" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B28" s="25">
         <v>525</v>
@@ -7413,7 +7430,7 @@
     </row>
     <row r="29" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B29" s="25">
         <v>528</v>
@@ -7431,7 +7448,7 @@
     </row>
     <row r="30" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
@@ -7443,7 +7460,7 @@
     </row>
     <row r="31" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -7455,7 +7472,7 @@
     </row>
     <row r="32" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -7464,7 +7481,7 @@
     </row>
     <row r="33" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -7476,7 +7493,7 @@
     </row>
     <row r="34" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
@@ -7488,7 +7505,7 @@
     </row>
     <row r="35" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -7500,7 +7517,7 @@
     </row>
     <row r="36" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
@@ -7512,7 +7529,7 @@
     </row>
     <row r="37" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -7524,7 +7541,7 @@
     </row>
     <row r="38" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
@@ -7536,7 +7553,7 @@
     </row>
     <row r="39" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B39" s="27"/>
       <c r="C39" s="27">
@@ -7554,17 +7571,17 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
+      <c r="A41" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
@@ -7573,7 +7590,7 @@
     </row>
     <row r="43" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -7585,7 +7602,7 @@
     </row>
     <row r="44" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="24" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
@@ -7597,7 +7614,7 @@
     </row>
     <row r="45" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="24" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -7609,7 +7626,7 @@
     </row>
     <row r="46" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="25"/>
@@ -7621,7 +7638,7 @@
     </row>
     <row r="47" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -7633,7 +7650,7 @@
     </row>
     <row r="48" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
@@ -7645,7 +7662,7 @@
     </row>
     <row r="49" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -7657,7 +7674,7 @@
     </row>
     <row r="50" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="24" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
@@ -7669,7 +7686,7 @@
     </row>
     <row r="51" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="24" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -7681,7 +7698,7 @@
     </row>
     <row r="52" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="25"/>
@@ -7693,7 +7710,7 @@
     </row>
     <row r="53" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -7705,7 +7722,7 @@
     </row>
     <row r="54" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="24" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="25"/>
@@ -7717,7 +7734,7 @@
     </row>
     <row r="55" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -7729,7 +7746,7 @@
     </row>
     <row r="56" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="25"/>
@@ -7741,7 +7758,7 @@
     </row>
     <row r="57" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -7753,7 +7770,7 @@
     </row>
     <row r="58" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -7765,7 +7782,7 @@
     </row>
     <row r="59" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -7777,7 +7794,7 @@
     </row>
     <row r="60" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="25"/>
@@ -7789,7 +7806,7 @@
     </row>
     <row r="61" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -7798,7 +7815,7 @@
     </row>
     <row r="62" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
@@ -7810,7 +7827,7 @@
     </row>
     <row r="63" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -7822,7 +7839,7 @@
     </row>
     <row r="64" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B64" s="25"/>
       <c r="C64" s="25"/>
@@ -7834,7 +7851,7 @@
     </row>
     <row r="65" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="24" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -7846,7 +7863,7 @@
     </row>
     <row r="66" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B66" s="25"/>
       <c r="C66" s="25"/>
@@ -7858,7 +7875,7 @@
     </row>
     <row r="67" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="24" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -7870,7 +7887,7 @@
     </row>
     <row r="68" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B68" s="25"/>
       <c r="C68" s="25"/>
@@ -7882,7 +7899,7 @@
     </row>
     <row r="69" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="24" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -7894,7 +7911,7 @@
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="B70" s="25"/>
       <c r="C70" s="25"/>
@@ -7906,7 +7923,7 @@
     </row>
     <row r="71" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B71" s="30"/>
       <c r="C71" s="30"/>
@@ -7915,7 +7932,7 @@
     </row>
     <row r="72" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B72" s="25"/>
       <c r="C72" s="25"/>
@@ -7927,7 +7944,7 @@
     </row>
     <row r="73" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="24" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -7939,7 +7956,7 @@
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B74" s="25"/>
       <c r="C74" s="25"/>
@@ -7951,7 +7968,7 @@
     </row>
     <row r="75" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -7963,7 +7980,7 @@
     </row>
     <row r="76" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B76" s="25"/>
       <c r="C76" s="25"/>
@@ -7975,7 +7992,7 @@
     </row>
     <row r="77" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -7987,7 +8004,7 @@
     </row>
     <row r="78" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B78" s="25"/>
       <c r="C78" s="25"/>
@@ -7999,7 +8016,7 @@
     </row>
     <row r="79" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="24" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -8011,7 +8028,7 @@
     </row>
     <row r="80" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B80" s="25"/>
       <c r="C80" s="25"/>
@@ -8023,7 +8040,7 @@
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B81" s="27"/>
       <c r="C81" s="27">
@@ -8041,17 +8058,17 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B83" s="40"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="41"/>
+      <c r="A83" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="42"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B84" s="30"/>
       <c r="C84" s="30"/>
@@ -8060,7 +8077,7 @@
     </row>
     <row r="85" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="24" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -8072,7 +8089,7 @@
     </row>
     <row r="86" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B86" s="25"/>
       <c r="C86" s="25"/>
@@ -8084,7 +8101,7 @@
     </row>
     <row r="87" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="24" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -8096,7 +8113,7 @@
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B88" s="25"/>
       <c r="C88" s="25"/>
@@ -8108,7 +8125,7 @@
     </row>
     <row r="89" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B89" s="27"/>
       <c r="C89" s="27">
@@ -8127,7 +8144,7 @@
     <row r="90" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="28" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B91" s="29"/>
       <c r="C91" s="29">
@@ -8252,531 +8269,548 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="13" width="9" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="14" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-    </row>
-    <row r="2" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+    </row>
+    <row r="2" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
-      <c r="B3" s="56" t="s">
-        <v>249</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="54" t="s">
-        <v>251</v>
-      </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="58" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="43"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="43"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="44"/>
-      <c r="M3" s="55"/>
-    </row>
-    <row r="4" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="43"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="43"/>
+      <c r="N3" s="58"/>
+    </row>
+    <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="E4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="F4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="G4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="I4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="J4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="K4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="L4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="M4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="N4" s="32" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>252</v>
+        <v>9</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
-      <c r="D5" s="34" t="str">
-        <f t="shared" ref="D5:D14" si="0">IF(AND(B5&lt;&gt;"",C5&lt;&gt;""),C5/B5,"")</f>
-        <v/>
-      </c>
-      <c r="E5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34" t="str">
+        <f t="shared" ref="E5:E14" si="0">IF(AND(C5&lt;&gt;"",D5&lt;&gt;""),D5/C5,"")</f>
+        <v/>
+      </c>
       <c r="F5" s="34"/>
-      <c r="G5" s="34" t="str">
-        <f t="shared" ref="G5:G14" si="1">IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),F5/E5,"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34" t="str">
+        <f t="shared" ref="H5:H14" si="1">IF(AND(F5&lt;&gt;"",G5&lt;&gt;""),G5/F5,"")</f>
+        <v/>
+      </c>
       <c r="I5" s="34"/>
-      <c r="J5" s="34" t="str">
-        <f t="shared" ref="J5:J14" si="2">IF(AND(H5&lt;&gt;"",I5&lt;&gt;""),I5/H5,"")</f>
-        <v/>
-      </c>
-      <c r="K5" s="34">
-        <f t="shared" ref="K5:K13" si="3">B5+E5+H5</f>
-        <v>0</v>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34" t="str">
+        <f t="shared" ref="K5:K14" si="2">IF(AND(I5&lt;&gt;"",J5&lt;&gt;""),J5/I5,"")</f>
+        <v/>
       </c>
       <c r="L5" s="34">
-        <f t="shared" ref="L5:L13" si="4">C5+F5+I5</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="34" t="e">
-        <f t="shared" ref="M5:M14" si="5">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),L5/K5,"")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="L5:L13" si="3">C5+F5+I5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="34">
+        <f t="shared" ref="M5:M13" si="4">D5+G5+J5</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="34" t="e">
+        <f t="shared" ref="N5:N14" si="5">IF(AND(L5&lt;&gt;"",M5&lt;&gt;""),M5/L5,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>253</v>
+        <v>10</v>
       </c>
       <c r="B6" s="34"/>
       <c r="C6" s="34"/>
-      <c r="D6" s="34" t="str">
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E6" s="34"/>
       <c r="F6" s="34"/>
-      <c r="G6" s="34" t="str">
+      <c r="G6" s="34"/>
+      <c r="H6" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H6" s="34"/>
       <c r="I6" s="34"/>
-      <c r="J6" s="34" t="str">
+      <c r="J6" s="34"/>
+      <c r="K6" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K6" s="34">
+      <c r="L6" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L6" s="34">
+      <c r="M6" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M6" s="34" t="e">
+      <c r="N6" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
-      <c r="D7" s="34" t="str">
+      <c r="D7" s="34"/>
+      <c r="E7" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E7" s="34"/>
       <c r="F7" s="34"/>
-      <c r="G7" s="34" t="str">
+      <c r="G7" s="34"/>
+      <c r="H7" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H7" s="34"/>
       <c r="I7" s="34"/>
-      <c r="J7" s="34" t="str">
+      <c r="J7" s="34"/>
+      <c r="K7" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K7" s="34">
+      <c r="L7" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L7" s="34">
+      <c r="M7" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M7" s="34" t="e">
+      <c r="N7" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
-      <c r="D8" s="34" t="str">
+      <c r="D8" s="34"/>
+      <c r="E8" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E8" s="34"/>
       <c r="F8" s="34"/>
-      <c r="G8" s="34" t="str">
+      <c r="G8" s="34"/>
+      <c r="H8" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H8" s="34"/>
       <c r="I8" s="34"/>
-      <c r="J8" s="34" t="str">
+      <c r="J8" s="34"/>
+      <c r="K8" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K8" s="34">
+      <c r="L8" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L8" s="34">
+      <c r="M8" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M8" s="34" t="e">
+      <c r="N8" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>256</v>
+        <v>13</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
-      <c r="D9" s="34" t="str">
+      <c r="D9" s="34"/>
+      <c r="E9" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E9" s="34"/>
       <c r="F9" s="34"/>
-      <c r="G9" s="34" t="str">
+      <c r="G9" s="34"/>
+      <c r="H9" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H9" s="34"/>
       <c r="I9" s="34"/>
-      <c r="J9" s="34" t="str">
+      <c r="J9" s="34"/>
+      <c r="K9" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K9" s="34">
+      <c r="L9" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L9" s="34">
+      <c r="M9" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="34" t="e">
+      <c r="N9" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>257</v>
+        <v>14</v>
       </c>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
-      <c r="D10" s="34" t="str">
+      <c r="D10" s="34"/>
+      <c r="E10" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E10" s="34"/>
       <c r="F10" s="34"/>
-      <c r="G10" s="34" t="str">
+      <c r="G10" s="34"/>
+      <c r="H10" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H10" s="34"/>
       <c r="I10" s="34"/>
-      <c r="J10" s="34" t="str">
+      <c r="J10" s="34"/>
+      <c r="K10" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K10" s="34">
+      <c r="L10" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="34">
+      <c r="M10" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="34" t="e">
+      <c r="N10" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>258</v>
+        <v>15</v>
       </c>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
-      <c r="D11" s="34" t="str">
+      <c r="D11" s="34"/>
+      <c r="E11" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E11" s="34"/>
       <c r="F11" s="34"/>
-      <c r="G11" s="34" t="str">
+      <c r="G11" s="34"/>
+      <c r="H11" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H11" s="34"/>
       <c r="I11" s="34"/>
-      <c r="J11" s="34" t="str">
+      <c r="J11" s="34"/>
+      <c r="K11" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K11" s="34">
+      <c r="L11" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="34">
+      <c r="M11" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="34" t="e">
+      <c r="N11" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
-      <c r="D12" s="34" t="str">
+      <c r="D12" s="34"/>
+      <c r="E12" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E12" s="34"/>
       <c r="F12" s="34"/>
-      <c r="G12" s="34" t="str">
+      <c r="G12" s="34"/>
+      <c r="H12" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H12" s="34"/>
       <c r="I12" s="34"/>
-      <c r="J12" s="34" t="str">
+      <c r="J12" s="34"/>
+      <c r="K12" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K12" s="34">
+      <c r="L12" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12" s="34">
+      <c r="M12" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="34" t="e">
+      <c r="N12" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
-      <c r="D13" s="34" t="str">
+      <c r="D13" s="34"/>
+      <c r="E13" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E13" s="34"/>
       <c r="F13" s="34"/>
-      <c r="G13" s="34" t="str">
+      <c r="G13" s="34"/>
+      <c r="H13" s="34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H13" s="34"/>
       <c r="I13" s="34"/>
-      <c r="J13" s="34" t="str">
+      <c r="J13" s="34"/>
+      <c r="K13" s="34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K13" s="34">
+      <c r="L13" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="34">
+      <c r="M13" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="34" t="e">
+      <c r="N13" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="36">
-        <f>SUM(B5:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="36">
+        <v>4</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37">
         <f>SUM(C5:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="36" t="e">
+      <c r="D14" s="37">
+        <f>SUM(D5:D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="37" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E14" s="36">
-        <f>SUM(E5:E13)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>SUM(F5:F13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="36" t="e">
+      <c r="G14" s="37">
+        <f>SUM(G5:G13)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="37" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="36">
-        <f>SUM(H5:H13)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="36">
+      <c r="I14" s="37">
         <f>SUM(I5:I13)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="36" t="e">
+      <c r="J14" s="37">
+        <f>SUM(J5:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="37" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K14" s="36">
-        <f>SUM(K5:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="36">
+      <c r="L14" s="37">
         <f>SUM(L5:L13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="36" t="e">
+      <c r="M14" s="37">
+        <f>SUM(M5:M13)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="37" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="B16" s="38">
-        <f>B14</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="38">
+    <row r="15" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40">
         <f>C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="38" t="e">
-        <f>IF(AND(B16&lt;&gt;"",C16&lt;&gt;""),C16/B16,"")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E16" s="38">
-        <f>E14</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="38">
+      <c r="D16" s="40">
+        <f>D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="40" t="e">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;""),D16/C16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="40">
         <f>F14</f>
         <v>0</v>
       </c>
-      <c r="G16" s="38" t="e">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),F16/E16,"")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H16" s="38">
-        <f>H14</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="38">
+      <c r="G16" s="40">
+        <f>G14</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="40" t="e">
+        <f>IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),G16/F16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="40">
         <f>I14</f>
         <v>0</v>
       </c>
-      <c r="J16" s="38" t="e">
-        <f>IF(AND(H16&lt;&gt;"",I16&lt;&gt;""),I16/H16,"")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="38">
-        <f>K14</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="38">
+      <c r="J16" s="40">
+        <f>J14</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="40" t="e">
+        <f>IF(AND(I16&lt;&gt;"",J16&lt;&gt;""),J16/I16,"")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L16" s="40">
         <f>L14</f>
         <v>0</v>
       </c>
-      <c r="M16" s="38" t="e">
-        <f>IF(AND(K16&lt;&gt;"",L16&lt;&gt;""),L16/K16,"")</f>
+      <c r="M16" s="40">
+        <f>M14</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="40" t="e">
+        <f>IF(AND(L16&lt;&gt;"",M16&lt;&gt;""),M16/L16,"")</f>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D5:D14">
+  <conditionalFormatting sqref="E5:E14">
     <cfRule type="cellIs" dxfId="23" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8788,7 +8822,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16">
+  <conditionalFormatting sqref="E16">
     <cfRule type="cellIs" dxfId="20" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8800,7 +8834,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G14">
+  <conditionalFormatting sqref="H5:H14">
     <cfRule type="cellIs" dxfId="17" priority="10" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8812,7 +8846,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
+  <conditionalFormatting sqref="H16">
     <cfRule type="cellIs" dxfId="14" priority="16" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8824,7 +8858,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J14">
+  <conditionalFormatting sqref="K5:K14">
     <cfRule type="cellIs" dxfId="11" priority="19" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8836,7 +8870,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
+  <conditionalFormatting sqref="K16">
     <cfRule type="cellIs" dxfId="8" priority="25" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8848,7 +8882,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M14">
+  <conditionalFormatting sqref="N5:N14">
     <cfRule type="cellIs" dxfId="5" priority="28" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8860,7 +8894,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M16">
+  <conditionalFormatting sqref="N16">
     <cfRule type="cellIs" dxfId="2" priority="34" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
@@ -8877,7 +8911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
@@ -8890,46 +8924,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
+      <c r="A1" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
     </row>
     <row r="2" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="41"/>
+      <c r="C3" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
@@ -8960,23 +8994,23 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="41"/>
+      <c r="A5" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4">
@@ -9014,7 +9048,7 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -9044,7 +9078,7 @@
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -9074,7 +9108,7 @@
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -9104,7 +9138,7 @@
     </row>
     <row r="10" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -9134,7 +9168,7 @@
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -9164,7 +9198,7 @@
     </row>
     <row r="12" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -9194,7 +9228,7 @@
     </row>
     <row r="13" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -9224,7 +9258,7 @@
     </row>
     <row r="14" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -9254,7 +9288,7 @@
     </row>
     <row r="15" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7">
@@ -9296,23 +9330,23 @@
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="41"/>
+      <c r="A17" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="42"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -9342,7 +9376,7 @@
     </row>
     <row r="19" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -9372,7 +9406,7 @@
     </row>
     <row r="20" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -9402,7 +9436,7 @@
     </row>
     <row r="21" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -9432,7 +9466,7 @@
     </row>
     <row r="22" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -9462,7 +9496,7 @@
     </row>
     <row r="23" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -9492,7 +9526,7 @@
     </row>
     <row r="24" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7">
@@ -9534,23 +9568,23 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="41"/>
+      <c r="A26" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="42"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -9580,7 +9614,7 @@
     </row>
     <row r="28" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -9610,7 +9644,7 @@
     </row>
     <row r="29" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -9640,7 +9674,7 @@
     </row>
     <row r="30" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -9670,7 +9704,7 @@
     </row>
     <row r="31" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -9700,7 +9734,7 @@
     </row>
     <row r="32" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -9730,7 +9764,7 @@
     </row>
     <row r="33" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -9760,7 +9794,7 @@
     </row>
     <row r="34" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -9790,7 +9824,7 @@
     </row>
     <row r="35" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="7">
@@ -9832,7 +9866,7 @@
     </row>
     <row r="36" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="10">
@@ -9873,54 +9907,54 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44"/>
-      <c r="N39" s="44"/>
+      <c r="A39" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
     </row>
     <row r="40" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="40"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="J41" s="40"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="40"/>
-      <c r="N41" s="41"/>
+      <c r="C41" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="41"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" s="41"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="J41" s="41"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="41"/>
+      <c r="N41" s="42"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -9960,26 +9994,26 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="40"/>
-      <c r="N43" s="41"/>
+      <c r="A43" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="41"/>
+      <c r="L43" s="41"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="42"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B44" s="4">
         <f t="shared" ref="B44:B52" si="13">B6</f>
@@ -10022,7 +10056,7 @@
     </row>
     <row r="45" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B45" s="4">
         <f t="shared" si="13"/>
@@ -10061,7 +10095,7 @@
     </row>
     <row r="46" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="B46" s="4">
         <f t="shared" si="13"/>
@@ -10100,7 +10134,7 @@
     </row>
     <row r="47" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="B47" s="4">
         <f t="shared" si="13"/>
@@ -10139,7 +10173,7 @@
     </row>
     <row r="48" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="B48" s="4">
         <f t="shared" si="13"/>
@@ -10178,7 +10212,7 @@
     </row>
     <row r="49" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="B49" s="4">
         <f t="shared" si="13"/>
@@ -10217,7 +10251,7 @@
     </row>
     <row r="50" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="B50" s="4">
         <f t="shared" si="13"/>
@@ -10256,7 +10290,7 @@
     </row>
     <row r="51" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" si="13"/>
@@ -10295,7 +10329,7 @@
     </row>
     <row r="52" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="B52" s="4">
         <f t="shared" si="13"/>
@@ -10334,7 +10368,7 @@
     </row>
     <row r="53" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="7">
@@ -10388,26 +10422,26 @@
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
-      <c r="N55" s="41"/>
+      <c r="A55" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="41"/>
+      <c r="M55" s="41"/>
+      <c r="N55" s="42"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B56" s="4">
         <f t="shared" ref="B56:B61" si="20">B18</f>
@@ -10446,7 +10480,7 @@
     </row>
     <row r="57" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="B57" s="4">
         <f t="shared" si="20"/>
@@ -10485,7 +10519,7 @@
     </row>
     <row r="58" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="B58" s="4">
         <f t="shared" si="20"/>
@@ -10524,7 +10558,7 @@
     </row>
     <row r="59" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B59" s="4">
         <f t="shared" si="20"/>
@@ -10563,7 +10597,7 @@
     </row>
     <row r="60" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B60" s="4">
         <f t="shared" si="20"/>
@@ -10602,7 +10636,7 @@
     </row>
     <row r="61" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="B61" s="4">
         <f t="shared" si="20"/>
@@ -10641,7 +10675,7 @@
     </row>
     <row r="62" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="7">
@@ -10695,26 +10729,26 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B64" s="40"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="40"/>
-      <c r="F64" s="40"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="40"/>
-      <c r="J64" s="40"/>
-      <c r="K64" s="40"/>
-      <c r="L64" s="40"/>
-      <c r="M64" s="40"/>
-      <c r="N64" s="41"/>
+      <c r="A64" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="41"/>
+      <c r="K64" s="41"/>
+      <c r="L64" s="41"/>
+      <c r="M64" s="41"/>
+      <c r="N64" s="42"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B65" s="4">
         <f t="shared" ref="B65:B72" si="26">B27</f>
@@ -10753,7 +10787,7 @@
     </row>
     <row r="66" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B66" s="4">
         <f t="shared" si="26"/>
@@ -10792,7 +10826,7 @@
     </row>
     <row r="67" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="B67" s="4">
         <f t="shared" si="26"/>
@@ -10831,7 +10865,7 @@
     </row>
     <row r="68" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="B68" s="4">
         <f t="shared" si="26"/>
@@ -10870,7 +10904,7 @@
     </row>
     <row r="69" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="B69" s="4">
         <f t="shared" si="26"/>
@@ -10909,7 +10943,7 @@
     </row>
     <row r="70" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B70" s="4">
         <f t="shared" si="26"/>
@@ -10948,7 +10982,7 @@
     </row>
     <row r="71" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="B71" s="4">
         <f t="shared" si="26"/>
@@ -10987,7 +11021,7 @@
     </row>
     <row r="72" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B72" s="4">
         <f t="shared" si="26"/>
@@ -11026,7 +11060,7 @@
     </row>
     <row r="73" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="7">
@@ -11080,7 +11114,7 @@
     </row>
     <row r="74" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="10">
@@ -11133,46 +11167,46 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="44"/>
-      <c r="C77" s="44"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="44"/>
-      <c r="G77" s="44"/>
-      <c r="H77" s="44"/>
-      <c r="I77" s="44"/>
-      <c r="J77" s="44"/>
-      <c r="K77" s="44"/>
+      <c r="A77" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B77" s="43"/>
+      <c r="C77" s="43"/>
+      <c r="D77" s="43"/>
+      <c r="E77" s="43"/>
+      <c r="F77" s="43"/>
+      <c r="G77" s="43"/>
+      <c r="H77" s="43"/>
+      <c r="I77" s="43"/>
+      <c r="J77" s="43"/>
+      <c r="K77" s="43"/>
     </row>
     <row r="78" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="D79" s="40"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="G79" s="40"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J79" s="40"/>
-      <c r="K79" s="41"/>
+      <c r="C79" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="41"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="G79" s="41"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="J79" s="41"/>
+      <c r="K79" s="42"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -11203,23 +11237,23 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" s="40"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="40"/>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="40"/>
-      <c r="H81" s="40"/>
-      <c r="I81" s="40"/>
-      <c r="J81" s="40"/>
-      <c r="K81" s="41"/>
+      <c r="A81" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="42"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B82" s="4">
         <f t="shared" ref="B82:B90" si="32">B6</f>
@@ -11264,7 +11298,7 @@
     </row>
     <row r="83" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B83" s="4">
         <f t="shared" si="32"/>
@@ -11309,7 +11343,7 @@
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="B84" s="4">
         <f t="shared" si="32"/>
@@ -11354,7 +11388,7 @@
     </row>
     <row r="85" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="B85" s="4">
         <f t="shared" si="32"/>
@@ -11399,7 +11433,7 @@
     </row>
     <row r="86" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="B86" s="4">
         <f t="shared" si="32"/>
@@ -11444,7 +11478,7 @@
     </row>
     <row r="87" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="B87" s="4">
         <f t="shared" si="32"/>
@@ -11489,7 +11523,7 @@
     </row>
     <row r="88" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="B88" s="4">
         <f t="shared" si="32"/>
@@ -11534,7 +11568,7 @@
     </row>
     <row r="89" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="B89" s="4">
         <f t="shared" si="32"/>
@@ -11579,7 +11613,7 @@
     </row>
     <row r="90" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="B90" s="4">
         <f t="shared" si="32"/>
@@ -11624,7 +11658,7 @@
     </row>
     <row r="91" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="7">
@@ -11666,23 +11700,23 @@
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B93" s="40"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="40"/>
-      <c r="E93" s="40"/>
-      <c r="F93" s="40"/>
-      <c r="G93" s="40"/>
-      <c r="H93" s="40"/>
-      <c r="I93" s="40"/>
-      <c r="J93" s="40"/>
-      <c r="K93" s="41"/>
+      <c r="A93" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" s="41"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="41"/>
+      <c r="E93" s="41"/>
+      <c r="F93" s="41"/>
+      <c r="G93" s="41"/>
+      <c r="H93" s="41"/>
+      <c r="I93" s="41"/>
+      <c r="J93" s="41"/>
+      <c r="K93" s="42"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B94" s="4">
         <f t="shared" ref="B94:B99" si="42">B18</f>
@@ -11727,7 +11761,7 @@
     </row>
     <row r="95" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="B95" s="4">
         <f t="shared" si="42"/>
@@ -11772,7 +11806,7 @@
     </row>
     <row r="96" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="B96" s="4">
         <f t="shared" si="42"/>
@@ -11817,7 +11851,7 @@
     </row>
     <row r="97" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B97" s="4">
         <f t="shared" si="42"/>
@@ -11862,7 +11896,7 @@
     </row>
     <row r="98" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B98" s="4">
         <f t="shared" si="42"/>
@@ -11907,7 +11941,7 @@
     </row>
     <row r="99" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="B99" s="4">
         <f t="shared" si="42"/>
@@ -11952,7 +11986,7 @@
     </row>
     <row r="100" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="7">
@@ -11994,23 +12028,23 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B102" s="40"/>
-      <c r="C102" s="40"/>
-      <c r="D102" s="40"/>
-      <c r="E102" s="40"/>
-      <c r="F102" s="40"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="40"/>
-      <c r="I102" s="40"/>
-      <c r="J102" s="40"/>
-      <c r="K102" s="41"/>
+      <c r="A102" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B102" s="41"/>
+      <c r="C102" s="41"/>
+      <c r="D102" s="41"/>
+      <c r="E102" s="41"/>
+      <c r="F102" s="41"/>
+      <c r="G102" s="41"/>
+      <c r="H102" s="41"/>
+      <c r="I102" s="41"/>
+      <c r="J102" s="41"/>
+      <c r="K102" s="42"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B103" s="4">
         <f t="shared" ref="B103:B110" si="49">B27</f>
@@ -12055,7 +12089,7 @@
     </row>
     <row r="104" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B104" s="4">
         <f t="shared" si="49"/>
@@ -12100,7 +12134,7 @@
     </row>
     <row r="105" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="B105" s="4">
         <f t="shared" si="49"/>
@@ -12145,7 +12179,7 @@
     </row>
     <row r="106" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="B106" s="4">
         <f t="shared" si="49"/>
@@ -12190,7 +12224,7 @@
     </row>
     <row r="107" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="B107" s="4">
         <f t="shared" si="49"/>
@@ -12235,7 +12269,7 @@
     </row>
     <row r="108" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B108" s="4">
         <f t="shared" si="49"/>
@@ -12280,7 +12314,7 @@
     </row>
     <row r="109" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="B109" s="4">
         <f t="shared" si="49"/>
@@ -12325,7 +12359,7 @@
     </row>
     <row r="110" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="B110" s="4">
         <f t="shared" si="49"/>
@@ -12370,7 +12404,7 @@
     </row>
     <row r="111" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="7">
@@ -12412,7 +12446,7 @@
     </row>
     <row r="112" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="B112" s="9"/>
       <c r="C112" s="10">
@@ -12455,6 +12489,7 @@
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
     <mergeCell ref="A5:K5"/>
@@ -12470,7 +12505,6 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="A93:K93"/>
     <mergeCell ref="F79:H79"/>
     <mergeCell ref="A39:N39"/>
@@ -12855,7 +12889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V47"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12866,69 +12900,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
+      <c r="A1" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="41"/>
+      <c r="A3" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
+      <c r="M3" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>7</v>
@@ -12937,28 +12971,28 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>7</v>
@@ -12967,27 +13001,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -13013,7 +13047,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -13069,7 +13103,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -13125,7 +13159,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -13151,7 +13185,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -13207,7 +13241,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -13263,7 +13297,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -13319,7 +13353,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -13345,7 +13379,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -13401,7 +13435,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -13457,7 +13491,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -13513,7 +13547,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -13569,7 +13603,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -13595,7 +13629,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -13651,7 +13685,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -13707,7 +13741,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -13733,7 +13767,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -13789,7 +13823,7 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -13845,7 +13879,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -13901,7 +13935,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -13957,7 +13991,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -14013,7 +14047,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -14039,7 +14073,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -14095,7 +14129,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -14151,7 +14185,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -14207,7 +14241,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -14263,7 +14297,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -14289,7 +14323,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -14345,7 +14379,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -14401,7 +14435,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -14457,7 +14491,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -14513,7 +14547,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -14569,7 +14603,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -14595,7 +14629,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -14651,7 +14685,7 @@
     </row>
     <row r="39" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -14707,7 +14741,7 @@
     </row>
     <row r="40" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -14763,7 +14797,7 @@
     </row>
     <row r="41" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -14819,7 +14853,7 @@
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -14875,7 +14909,7 @@
     </row>
     <row r="43" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -14931,7 +14965,7 @@
     </row>
     <row r="44" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -14987,7 +15021,7 @@
     </row>
     <row r="45" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="18">
@@ -15068,7 +15102,7 @@
     <row r="46" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="21">
@@ -15788,7 +15822,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15799,69 +15833,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
+      <c r="A1" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="41"/>
+      <c r="A3" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
+      <c r="M3" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>7</v>
@@ -15870,28 +15904,28 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>7</v>
@@ -15900,27 +15934,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -15946,7 +15980,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B6" s="15">
         <v>507</v>
@@ -16012,7 +16046,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B7" s="15">
         <v>507</v>
@@ -16078,7 +16112,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B8" s="15">
         <v>508</v>
@@ -16144,7 +16178,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -16170,7 +16204,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B10" s="15">
         <v>509</v>
@@ -16236,7 +16270,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B11" s="15">
         <v>510</v>
@@ -16302,7 +16336,7 @@
     </row>
     <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B12" s="15">
         <v>512</v>
@@ -16368,7 +16402,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -16394,7 +16428,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B14" s="15">
         <v>513</v>
@@ -16460,7 +16494,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B15" s="15">
         <v>514</v>
@@ -16526,7 +16560,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B16" s="15">
         <v>515</v>
@@ -16592,7 +16626,7 @@
     </row>
     <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B17" s="15">
         <v>516</v>
@@ -16658,7 +16692,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B18" s="15">
         <v>516</v>
@@ -16724,7 +16758,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B19" s="15">
         <v>517</v>
@@ -16790,7 +16824,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -16816,7 +16850,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B21" s="15">
         <v>518</v>
@@ -16882,7 +16916,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B22" s="15">
         <v>518</v>
@@ -16948,7 +16982,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B23" s="15">
         <v>519</v>
@@ -17010,7 +17044,7 @@
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B24" s="15">
         <v>520</v>
@@ -17076,7 +17110,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -17102,7 +17136,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B26" s="15">
         <v>521</v>
@@ -17168,7 +17202,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B27" s="15">
         <v>521</v>
@@ -17234,7 +17268,7 @@
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B28" s="15">
         <v>522</v>
@@ -17300,7 +17334,7 @@
     </row>
     <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B29" s="15">
         <v>523</v>
@@ -17366,7 +17400,7 @@
     </row>
     <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B30" s="15">
         <v>524</v>
@@ -17432,7 +17466,7 @@
     </row>
     <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B31" s="15">
         <v>525</v>
@@ -17498,7 +17532,7 @@
     </row>
     <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B32" s="15">
         <v>525</v>
@@ -17564,7 +17598,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -17590,7 +17624,7 @@
     </row>
     <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B34" s="15">
         <v>526</v>
@@ -17656,7 +17690,7 @@
     </row>
     <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B35" s="15">
         <v>526</v>
@@ -17722,7 +17756,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -17748,7 +17782,7 @@
     </row>
     <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B37" s="15">
         <v>526</v>
@@ -17814,7 +17848,7 @@
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B38" s="15">
         <v>527</v>
@@ -17880,7 +17914,7 @@
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B39" s="15">
         <v>528</v>
@@ -17946,7 +17980,7 @@
     </row>
     <row r="40" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="18">
@@ -18027,7 +18061,7 @@
     <row r="41" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="21">
@@ -18675,7 +18709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18686,69 +18720,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
+      <c r="A1" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="41"/>
+      <c r="A3" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
+      <c r="M3" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>7</v>
@@ -18757,28 +18791,28 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>7</v>
@@ -18787,27 +18821,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -18833,7 +18867,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B6" s="15">
         <v>530</v>
@@ -18899,7 +18933,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B7" s="15">
         <v>530</v>
@@ -18965,7 +18999,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B8" s="15">
         <v>530</v>
@@ -19031,7 +19065,7 @@
     </row>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B9" s="15">
         <v>531</v>
@@ -19097,7 +19131,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B10" s="15">
         <v>531</v>
@@ -19163,7 +19197,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B11" s="15">
         <v>531</v>
@@ -19229,7 +19263,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -19255,7 +19289,7 @@
     </row>
     <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B13" s="15">
         <v>601</v>
@@ -19321,7 +19355,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B14" s="15">
         <v>602</v>
@@ -19387,7 +19421,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B15" s="15">
         <v>606</v>
@@ -19453,7 +19487,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B16" s="15">
         <v>607</v>
@@ -19519,7 +19553,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -19545,7 +19579,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B18" s="15">
         <v>609</v>
@@ -19611,7 +19645,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B19" s="15">
         <v>610</v>
@@ -19677,7 +19711,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -19703,7 +19737,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B21" s="15">
         <v>611</v>
@@ -19769,7 +19803,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B22" s="15">
         <v>614</v>
@@ -19835,7 +19869,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B23" s="15">
         <v>614</v>
@@ -19901,7 +19935,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -19927,7 +19961,7 @@
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B25" s="15">
         <v>614</v>
@@ -19993,7 +20027,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -20049,7 +20083,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -20105,7 +20139,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="18">
@@ -20186,7 +20220,7 @@
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21">
@@ -20690,7 +20724,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:V41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20701,69 +20735,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
+      <c r="A1" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="41"/>
+      <c r="A3" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
+      <c r="M3" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>7</v>
@@ -20772,28 +20806,28 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>7</v>
@@ -20802,27 +20836,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -20848,7 +20882,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -20904,7 +20938,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -20960,7 +20994,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -20986,7 +21020,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -21042,7 +21076,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -21098,7 +21132,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -21154,7 +21188,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -21180,7 +21214,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -21236,7 +21270,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -21292,7 +21326,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -21348,7 +21382,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -21404,7 +21438,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -21460,7 +21494,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -21516,7 +21550,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -21572,7 +21606,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -21628,7 +21662,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -21654,7 +21688,7 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -21710,7 +21744,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -21766,7 +21800,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -21822,7 +21856,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -21878,7 +21912,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -21934,7 +21968,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -21990,7 +22024,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -22046,7 +22080,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -22072,7 +22106,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -22128,7 +22162,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -22184,7 +22218,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -22240,7 +22274,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -22266,7 +22300,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -22322,7 +22356,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -22378,7 +22412,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -22434,7 +22468,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -22490,7 +22524,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -22546,7 +22580,7 @@
     </row>
     <row r="39" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="18">
@@ -22627,7 +22661,7 @@
     <row r="40" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="21">

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3420FDE6-DE2C-4D73-BD64-FBC924493786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D604357E-BFC2-40AA-B49F-886213ED7CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="264">
   <si>
     <t>高等数学辅导讲义严选题 习题正确率记录</t>
   </si>
@@ -830,6 +830,10 @@
   </si>
   <si>
     <t>未完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等第二章 物理层后记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1286,16 +1290,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3208,6 +3212,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3256,6 +3268,38 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3264,6 +3308,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3280,6 +3332,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3288,6 +3356,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3304,6 +3380,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3312,6 +3404,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3320,6 +3420,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3336,6 +3460,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3344,6 +3476,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3352,6 +3492,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3376,6 +3524,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3384,6 +3540,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3392,6 +3556,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3408,6 +3580,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3424,6 +3604,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3440,6 +3628,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3448,6 +3644,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3456,6 +3660,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3472,6 +3700,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3488,6 +3724,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3504,6 +3748,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3512,6 +3764,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3520,6 +3780,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3536,6 +3812,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3544,6 +3828,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3560,6 +3868,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3568,6 +3884,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3576,6 +3900,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3584,6 +3916,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3600,6 +3940,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3608,6 +3956,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3616,6 +3972,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3624,6 +4004,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3632,6 +4020,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3664,6 +4076,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3712,6 +4132,38 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3720,6 +4172,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3728,6 +4188,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3736,6 +4220,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3760,6 +4260,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3784,6 +4292,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3808,6 +4324,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3816,6 +4340,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3824,6 +4356,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3832,6 +4372,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3840,6 +4404,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3848,6 +4428,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3864,6 +4468,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3880,6 +4492,38 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3888,6 +4532,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3912,6 +4572,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3920,6 +4604,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3928,6 +4620,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3952,6 +4660,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3960,6 +4692,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3968,6 +4716,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3976,6 +4748,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4008,6 +4788,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4016,6 +4804,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4024,6 +4820,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4032,6 +4836,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4040,6 +4852,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4080,6 +4900,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4096,6 +4924,38 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4120,6 +4980,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4128,6 +5012,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4144,6 +5036,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4160,6 +5068,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4192,6 +5108,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4200,6 +5132,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4216,6 +5164,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4224,6 +5196,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4232,6 +5228,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4264,6 +5276,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4280,6 +5308,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4288,6 +5324,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4312,6 +5356,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4320,6 +5388,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4328,6 +5420,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4344,6 +5444,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4352,6 +5460,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4360,6 +5484,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4368,6 +5500,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4376,6 +5516,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4450,1158 +5606,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8975,12 +8979,12 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="63" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="48"/>
       <c r="E3" s="49"/>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="61" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="48"/>
@@ -9027,7 +9031,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="60" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="48"/>
@@ -9363,7 +9367,7 @@
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="60" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="48"/>
@@ -9601,7 +9605,7 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="61" t="s">
+      <c r="A26" s="60" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="48"/>
@@ -9961,12 +9965,12 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="60" t="s">
+      <c r="C41" s="63" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="48"/>
       <c r="E41" s="49"/>
-      <c r="F41" s="63" t="s">
+      <c r="F41" s="61" t="s">
         <v>76</v>
       </c>
       <c r="G41" s="48"/>
@@ -10027,7 +10031,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="60" t="s">
         <v>23</v>
       </c>
       <c r="B43" s="48"/>
@@ -10455,7 +10459,7 @@
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="61" t="s">
+      <c r="A55" s="60" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="48"/>
@@ -10762,7 +10766,7 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="61" t="s">
+      <c r="A64" s="60" t="s">
         <v>50</v>
       </c>
       <c r="B64" s="48"/>
@@ -11218,12 +11222,12 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="60" t="s">
+      <c r="C79" s="63" t="s">
         <v>116</v>
       </c>
       <c r="D79" s="48"/>
       <c r="E79" s="49"/>
-      <c r="F79" s="63" t="s">
+      <c r="F79" s="61" t="s">
         <v>113</v>
       </c>
       <c r="G79" s="48"/>
@@ -11270,7 +11274,7 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="61" t="s">
+      <c r="A81" s="60" t="s">
         <v>23</v>
       </c>
       <c r="B81" s="48"/>
@@ -11733,7 +11737,7 @@
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="61" t="s">
+      <c r="A93" s="60" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="48"/>
@@ -12061,7 +12065,7 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="61" t="s">
+      <c r="A102" s="60" t="s">
         <v>50</v>
       </c>
       <c r="B102" s="48"/>
@@ -12521,12 +12525,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A81:K81"/>
@@ -12543,6 +12541,12 @@
     <mergeCell ref="C79:E79"/>
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
@@ -15516,650 +15520,650 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="395" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="394" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="393" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="539" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="538" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="537" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="392" priority="21" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="390" priority="20" operator="between">
+    <cfRule type="cellIs" dxfId="536" priority="21" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="535" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="534" priority="20" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="389" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="388" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="387" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="533" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="532" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="531" priority="39" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="386" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="385" priority="57" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="55" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="530" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="529" priority="57" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="528" priority="55" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="383" priority="75" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="382" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="381" priority="73" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="527" priority="75" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="526" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="525" priority="73" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="380" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="379" priority="93" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="91" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="524" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="523" priority="93" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="522" priority="91" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="377" priority="111" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="376" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="109" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="521" priority="111" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="520" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="519" priority="109" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="374" priority="127" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="129" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="372" priority="128" operator="between">
+    <cfRule type="cellIs" dxfId="518" priority="127" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="517" priority="129" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="516" priority="128" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="371" priority="163" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="370" priority="165" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="164" operator="between">
+    <cfRule type="cellIs" dxfId="515" priority="163" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="514" priority="165" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="513" priority="164" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H7">
-    <cfRule type="cellIs" dxfId="368" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="512" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="511" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="510" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="365" priority="24" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="363" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="509" priority="24" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="508" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="507" priority="23" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:H16">
-    <cfRule type="cellIs" dxfId="362" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="361" priority="42" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="360" priority="40" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="506" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="505" priority="42" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="504" priority="40" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="359" priority="60" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="358" priority="59" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="357" priority="58" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="503" priority="60" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="502" priority="59" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="501" priority="58" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H25">
-    <cfRule type="cellIs" dxfId="356" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="355" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="354" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="500" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="499" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="498" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H30">
-    <cfRule type="cellIs" dxfId="353" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="352" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="351" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="497" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="496" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="495" priority="94" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H36">
-    <cfRule type="cellIs" dxfId="350" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="348" priority="114" operator="lessThan">
+    <cfRule type="cellIs" dxfId="494" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="493" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="492" priority="114" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:H45">
-    <cfRule type="cellIs" dxfId="347" priority="132" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="346" priority="131" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="345" priority="130" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="491" priority="132" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="490" priority="131" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="489" priority="130" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H47">
-    <cfRule type="cellIs" dxfId="344" priority="166" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="343" priority="167" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="342" priority="168" operator="lessThan">
+    <cfRule type="cellIs" dxfId="488" priority="166" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="487" priority="167" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="486" priority="168" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K7">
-    <cfRule type="cellIs" dxfId="341" priority="9" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="340" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="339" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="485" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="484" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="483" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11">
-    <cfRule type="cellIs" dxfId="338" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="337" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="336" priority="26" operator="between">
+    <cfRule type="cellIs" dxfId="482" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="481" priority="27" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="480" priority="26" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K16">
-    <cfRule type="cellIs" dxfId="335" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="334" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="333" priority="43" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="479" priority="45" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="478" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="477" priority="43" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K19">
-    <cfRule type="cellIs" dxfId="332" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="330" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="476" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="475" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="474" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K25">
-    <cfRule type="cellIs" dxfId="329" priority="81" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="328" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="327" priority="79" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="473" priority="81" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="472" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="471" priority="79" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K30">
-    <cfRule type="cellIs" dxfId="326" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="325" priority="99" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="324" priority="98" operator="between">
+    <cfRule type="cellIs" dxfId="470" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="469" priority="99" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="468" priority="98" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32:K36">
-    <cfRule type="cellIs" dxfId="323" priority="117" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="321" priority="116" operator="between">
+    <cfRule type="cellIs" dxfId="467" priority="117" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="466" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="465" priority="116" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:K45">
-    <cfRule type="cellIs" dxfId="320" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="135" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="133" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="464" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="463" priority="135" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="462" priority="133" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="cellIs" dxfId="317" priority="169" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="170" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="171" operator="lessThan">
+    <cfRule type="cellIs" dxfId="461" priority="169" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="460" priority="170" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="459" priority="171" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P7">
-    <cfRule type="cellIs" dxfId="314" priority="12" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="313" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="458" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="457" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="456" priority="10" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P11">
-    <cfRule type="cellIs" dxfId="311" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="29" operator="between">
+    <cfRule type="cellIs" dxfId="455" priority="30" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="454" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="453" priority="29" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P16">
-    <cfRule type="cellIs" dxfId="308" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="47" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="306" priority="48" operator="lessThan">
+    <cfRule type="cellIs" dxfId="452" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="451" priority="47" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="450" priority="48" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:P19">
-    <cfRule type="cellIs" dxfId="305" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="66" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="64" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="449" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="448" priority="66" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="447" priority="64" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P25">
-    <cfRule type="cellIs" dxfId="302" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="301" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="446" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="445" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="444" priority="84" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P30">
-    <cfRule type="cellIs" dxfId="299" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="297" priority="101" operator="between">
+    <cfRule type="cellIs" dxfId="443" priority="102" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="442" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="441" priority="101" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32:P36">
-    <cfRule type="cellIs" dxfId="296" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="294" priority="119" operator="between">
+    <cfRule type="cellIs" dxfId="440" priority="120" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="439" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="438" priority="119" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38:P45">
-    <cfRule type="cellIs" dxfId="293" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="437" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="436" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="435" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P47">
-    <cfRule type="cellIs" dxfId="290" priority="172" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="173" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="288" priority="174" operator="lessThan">
+    <cfRule type="cellIs" dxfId="434" priority="172" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="433" priority="173" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="432" priority="174" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S7">
-    <cfRule type="cellIs" dxfId="287" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="431" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="430" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="429" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S9:S11">
-    <cfRule type="cellIs" dxfId="284" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="283" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="282" priority="32" operator="between">
+    <cfRule type="cellIs" dxfId="428" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="427" priority="33" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="426" priority="32" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S16">
-    <cfRule type="cellIs" dxfId="281" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="425" priority="51" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="424" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="423" priority="49" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S19">
-    <cfRule type="cellIs" dxfId="278" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="276" priority="68" operator="between">
+    <cfRule type="cellIs" dxfId="422" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="421" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="420" priority="68" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S25">
-    <cfRule type="cellIs" dxfId="275" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="419" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="418" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="417" priority="87" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S30">
-    <cfRule type="cellIs" dxfId="272" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="416" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="415" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="414" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:S36">
-    <cfRule type="cellIs" dxfId="269" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="413" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="412" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="411" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S38:S45">
-    <cfRule type="cellIs" dxfId="266" priority="141" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="265" priority="139" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="140" operator="between">
+    <cfRule type="cellIs" dxfId="410" priority="141" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="409" priority="139" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="408" priority="140" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47">
-    <cfRule type="cellIs" dxfId="263" priority="175" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="176" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="177" operator="lessThan">
+    <cfRule type="cellIs" dxfId="407" priority="175" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="406" priority="176" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="405" priority="177" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V7">
-    <cfRule type="cellIs" dxfId="260" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="258" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="404" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="403" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="402" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:V11">
-    <cfRule type="cellIs" dxfId="257" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="36" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="34" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="401" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="400" priority="36" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="399" priority="34" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V16">
-    <cfRule type="cellIs" dxfId="254" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="53" operator="between">
+    <cfRule type="cellIs" dxfId="398" priority="54" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="396" priority="53" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:V19">
-    <cfRule type="cellIs" dxfId="251" priority="72" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="70" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="395" priority="72" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="394" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="70" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V25">
-    <cfRule type="cellIs" dxfId="248" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="246" priority="89" operator="between">
+    <cfRule type="cellIs" dxfId="392" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="390" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V27:V30">
-    <cfRule type="cellIs" dxfId="245" priority="108" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="106" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="389" priority="108" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="387" priority="106" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32:V36">
-    <cfRule type="cellIs" dxfId="242" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="125" operator="between">
+    <cfRule type="cellIs" dxfId="386" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="385" priority="126" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="125" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V45">
-    <cfRule type="cellIs" dxfId="239" priority="142" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="143" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="144" operator="lessThan">
+    <cfRule type="cellIs" dxfId="383" priority="142" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="382" priority="143" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="381" priority="144" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="cellIs" dxfId="236" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="179" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="380" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="379" priority="179" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="378" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18480,578 +18484,578 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="539" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="538" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="537" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="377" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="376" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="375" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="536" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="535" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="534" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="374" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="373" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="372" priority="21" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="533" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="532" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="531" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="371" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="370" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="369" priority="39" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="530" priority="55" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="529" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="528" priority="57" operator="lessThan">
+    <cfRule type="cellIs" dxfId="368" priority="55" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="367" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="366" priority="57" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="527" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="526" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="525" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="365" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="364" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="363" priority="75" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="524" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="523" priority="93" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="522" priority="92" operator="between">
+    <cfRule type="cellIs" dxfId="362" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="361" priority="93" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="360" priority="92" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E40">
-    <cfRule type="cellIs" dxfId="521" priority="111" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="520" priority="110" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="519" priority="109" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="359" priority="111" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="358" priority="110" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="357" priority="109" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="518" priority="147" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="517" priority="145" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="516" priority="146" operator="between">
+    <cfRule type="cellIs" dxfId="356" priority="147" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="355" priority="145" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="354" priority="146" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H8">
-    <cfRule type="cellIs" dxfId="515" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="514" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="513" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="353" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="352" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="351" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H12">
-    <cfRule type="cellIs" dxfId="512" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="511" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="510" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="350" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="349" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="348" priority="24" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H19">
-    <cfRule type="cellIs" dxfId="509" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="508" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="507" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="347" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="346" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="345" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H24">
-    <cfRule type="cellIs" dxfId="506" priority="58" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="505" priority="59" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="504" priority="60" operator="lessThan">
+    <cfRule type="cellIs" dxfId="344" priority="58" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="343" priority="59" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="342" priority="60" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H32">
-    <cfRule type="cellIs" dxfId="503" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="502" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="501" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="341" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="340" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="339" priority="78" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H35">
-    <cfRule type="cellIs" dxfId="500" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="499" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="498" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="338" priority="96" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="337" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="336" priority="94" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:H40">
-    <cfRule type="cellIs" dxfId="497" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="496" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="495" priority="113" operator="between">
+    <cfRule type="cellIs" dxfId="335" priority="114" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="334" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="333" priority="113" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="cellIs" dxfId="494" priority="148" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="493" priority="149" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="492" priority="150" operator="lessThan">
+    <cfRule type="cellIs" dxfId="332" priority="148" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="331" priority="149" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="330" priority="150" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K8">
-    <cfRule type="cellIs" dxfId="491" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="490" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="489" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="329" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="328" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="327" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:K12">
-    <cfRule type="cellIs" dxfId="488" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="487" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="486" priority="27" operator="lessThan">
+    <cfRule type="cellIs" dxfId="326" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="325" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="324" priority="27" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14:K19">
-    <cfRule type="cellIs" dxfId="485" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="484" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="483" priority="45" operator="lessThan">
+    <cfRule type="cellIs" dxfId="323" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="322" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="321" priority="45" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K24">
-    <cfRule type="cellIs" dxfId="482" priority="63" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="481" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="480" priority="62" operator="between">
+    <cfRule type="cellIs" dxfId="320" priority="63" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="319" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="318" priority="62" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K32">
-    <cfRule type="cellIs" dxfId="479" priority="79" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="478" priority="80" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="477" priority="81" operator="lessThan">
+    <cfRule type="cellIs" dxfId="317" priority="79" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="316" priority="80" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="315" priority="81" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34:K35">
-    <cfRule type="cellIs" dxfId="476" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="475" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="474" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="314" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="313" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="312" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K40">
-    <cfRule type="cellIs" dxfId="473" priority="117" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="472" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="471" priority="115" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="311" priority="117" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="310" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="309" priority="115" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="cellIs" dxfId="470" priority="153" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="469" priority="152" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="468" priority="151" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="308" priority="153" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="307" priority="152" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="306" priority="151" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P8">
-    <cfRule type="cellIs" dxfId="467" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="466" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="465" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="305" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="304" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="303" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P12">
-    <cfRule type="cellIs" dxfId="464" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="463" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="462" priority="28" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="302" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="301" priority="30" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="300" priority="28" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P14:P19">
-    <cfRule type="cellIs" dxfId="461" priority="48" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="460" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="459" priority="47" operator="between">
+    <cfRule type="cellIs" dxfId="299" priority="48" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="298" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="297" priority="47" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P24">
-    <cfRule type="cellIs" dxfId="458" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="457" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="456" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="296" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="295" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="294" priority="66" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26:P32">
-    <cfRule type="cellIs" dxfId="455" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="454" priority="84" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="453" priority="82" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="293" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="292" priority="84" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="291" priority="82" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P34:P35">
-    <cfRule type="cellIs" dxfId="452" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="451" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="450" priority="100" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="290" priority="102" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="289" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="288" priority="100" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P40">
-    <cfRule type="cellIs" dxfId="449" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="448" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="447" priority="118" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="287" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="286" priority="120" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="285" priority="118" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="cellIs" dxfId="446" priority="155" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="445" priority="154" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="444" priority="156" operator="lessThan">
+    <cfRule type="cellIs" dxfId="284" priority="155" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="283" priority="154" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="282" priority="156" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S8">
-    <cfRule type="cellIs" dxfId="443" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="442" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="441" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="281" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="280" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="279" priority="15" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S12">
-    <cfRule type="cellIs" dxfId="440" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="439" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="438" priority="33" operator="lessThan">
+    <cfRule type="cellIs" dxfId="278" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="277" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="276" priority="33" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S14:S19">
-    <cfRule type="cellIs" dxfId="437" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="436" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="435" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="275" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="274" priority="51" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="273" priority="49" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S24">
-    <cfRule type="cellIs" dxfId="434" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="433" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="432" priority="67" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="272" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="271" priority="69" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="270" priority="67" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26:S32">
-    <cfRule type="cellIs" dxfId="431" priority="85" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="430" priority="87" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="429" priority="86" operator="between">
+    <cfRule type="cellIs" dxfId="269" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="268" priority="87" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="267" priority="86" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S34:S35">
-    <cfRule type="cellIs" dxfId="428" priority="105" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="427" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="426" priority="103" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="266" priority="105" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="265" priority="104" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="264" priority="103" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S37:S40">
-    <cfRule type="cellIs" dxfId="425" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="424" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="423" priority="123" operator="lessThan">
+    <cfRule type="cellIs" dxfId="263" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="262" priority="122" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="261" priority="123" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S42">
-    <cfRule type="cellIs" dxfId="422" priority="157" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="421" priority="158" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="420" priority="159" operator="lessThan">
+    <cfRule type="cellIs" dxfId="260" priority="157" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="259" priority="158" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="258" priority="159" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V8">
-    <cfRule type="cellIs" dxfId="419" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="418" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="257" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="256" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="255" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:V12">
-    <cfRule type="cellIs" dxfId="416" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="414" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="254" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="253" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="252" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V14:V19">
-    <cfRule type="cellIs" dxfId="413" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="412" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="411" priority="52" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="251" priority="54" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="250" priority="53" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="249" priority="52" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V24">
-    <cfRule type="cellIs" dxfId="410" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="409" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="408" priority="72" operator="lessThan">
+    <cfRule type="cellIs" dxfId="248" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="247" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="246" priority="72" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26:V32">
-    <cfRule type="cellIs" dxfId="407" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="406" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="405" priority="88" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="245" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="244" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="243" priority="88" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V34:V35">
-    <cfRule type="cellIs" dxfId="404" priority="108" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="403" priority="107" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="106" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="242" priority="108" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="241" priority="107" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="106" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V37:V40">
-    <cfRule type="cellIs" dxfId="401" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="400" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="124" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="239" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="238" priority="126" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="237" priority="124" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="cellIs" dxfId="398" priority="160" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="397" priority="161" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="396" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="236" priority="160" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="235" priority="161" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="234" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21107,7 +21111,7 @@
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="12" max="12" width="18.08984375" customWidth="1"/>
     <col min="13" max="22" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21261,14 +21265,20 @@
       <c r="A6" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+      <c r="B6" s="15">
+        <v>16</v>
+      </c>
+      <c r="C6" s="15">
+        <v>17</v>
+      </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="str">
         <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="15">
+        <v>5</v>
+      </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15" t="str">
         <f>IF(AND(F6&lt;&gt;"",G6&lt;&gt;""),G6/F6,"")</f>
@@ -21276,17 +21286,19 @@
       </c>
       <c r="I6" s="15">
         <f>C6-F6</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J6" s="15">
         <f>D6-G6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="15" t="e">
+      <c r="K6" s="15">
         <f>IF(AND(I6&lt;&gt;"",J6&lt;&gt;""),J6/I6,"")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L6" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>263</v>
+      </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
@@ -22962,39 +22974,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="18" t="e">
+      <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="18" t="e">
+      <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
         <v>0</v>
       </c>
-      <c r="K39" s="18" t="e">
+      <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23043,39 +23055,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
         <v>0</v>
       </c>
-      <c r="E41" s="21" t="e">
+      <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
         <v>0</v>
       </c>
-      <c r="H41" s="21" t="e">
+      <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
         <v>0</v>
       </c>
-      <c r="K41" s="21" t="e">
+      <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D604357E-BFC2-40AA-B49F-886213ED7CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D462556C-0851-423B-A4D8-B496C94096E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="263">
   <si>
     <t>高等数学辅导讲义严选题 习题正确率记录</t>
   </si>
@@ -830,10 +830,6 @@
   </si>
   <si>
     <t>未完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等第二章 物理层后记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8409,36 +8405,50 @@
       <c r="A5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34" t="str">
+      <c r="B5" s="34">
+        <v>618</v>
+      </c>
+      <c r="C5" s="34">
+        <v>18</v>
+      </c>
+      <c r="D5" s="34">
+        <v>14</v>
+      </c>
+      <c r="E5" s="34">
         <f t="shared" ref="E5:E14" si="0">IF(AND(C5&lt;&gt;"",D5&lt;&gt;""),D5/C5,"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="F5" s="34">
+        <v>8</v>
+      </c>
+      <c r="G5" s="34">
+        <v>8</v>
+      </c>
+      <c r="H5" s="34">
         <f t="shared" ref="H5:H14" si="1">IF(AND(F5&lt;&gt;"",G5&lt;&gt;""),G5/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34" t="str">
+        <v>1</v>
+      </c>
+      <c r="I5" s="34">
+        <v>23</v>
+      </c>
+      <c r="J5" s="34">
+        <v>21</v>
+      </c>
+      <c r="K5" s="34">
         <f t="shared" ref="K5:K14" si="2">IF(AND(I5&lt;&gt;"",J5&lt;&gt;""),J5/I5,"")</f>
-        <v/>
+        <v>0.91304347826086951</v>
       </c>
       <c r="L5" s="34">
         <f t="shared" ref="L5:L13" si="3">C5+F5+I5</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M5" s="34">
         <f t="shared" ref="M5:M13" si="4">D5+G5+J5</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="34" t="e">
+        <v>43</v>
+      </c>
+      <c r="N5" s="34">
         <f t="shared" ref="N5:N14" si="5">IF(AND(L5&lt;&gt;"",M5&lt;&gt;""),M5/L5,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.87755102040816324</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -8736,51 +8746,51 @@
       <c r="B14" s="36"/>
       <c r="C14" s="37">
         <f>SUM(C5:C13)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D14" s="37">
         <f>SUM(D5:D13)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="37" t="e">
+        <v>14</v>
+      </c>
+      <c r="E14" s="37">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F14" s="37">
         <f>SUM(F5:F13)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14" s="37">
         <f>SUM(G5:G13)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="37" t="e">
+        <v>8</v>
+      </c>
+      <c r="H14" s="37">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="I14" s="37">
         <f>SUM(I5:I13)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J14" s="37">
         <f>SUM(J5:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="37" t="e">
+        <v>21</v>
+      </c>
+      <c r="K14" s="37">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.91304347826086951</v>
       </c>
       <c r="L14" s="37">
         <f>SUM(L5:L13)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M14" s="37">
         <f>SUM(M5:M13)</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="37" t="e">
+        <v>43</v>
+      </c>
+      <c r="N14" s="37">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.87755102040816324</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8791,51 +8801,51 @@
       <c r="B16" s="39"/>
       <c r="C16" s="40">
         <f>C14</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D16" s="40">
         <f>D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="40" t="e">
+        <v>14</v>
+      </c>
+      <c r="E16" s="40">
         <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;""),D16/C16,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="F16" s="40">
         <f>F14</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" s="40">
         <f>G14</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="40" t="e">
+        <v>8</v>
+      </c>
+      <c r="H16" s="40">
         <f>IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),G16/F16,"")</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="I16" s="40">
         <f>I14</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J16" s="40">
         <f>J14</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="40" t="e">
+        <v>21</v>
+      </c>
+      <c r="K16" s="40">
         <f>IF(AND(I16&lt;&gt;"",J16&lt;&gt;""),J16/I16,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.91304347826086951</v>
       </c>
       <c r="L16" s="40">
         <f>L14</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M16" s="40">
         <f>M14</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="40" t="e">
+        <v>43</v>
+      </c>
+      <c r="N16" s="40">
         <f>IF(AND(L16&lt;&gt;"",M16&lt;&gt;""),M16/L16,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.87755102040816324</v>
       </c>
     </row>
   </sheetData>
@@ -9049,26 +9059,28 @@
       <c r="A6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4">
+        <v>618</v>
+      </c>
       <c r="C6" s="4">
         <v>15</v>
       </c>
       <c r="D6" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" ref="E6:E15" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
-        <v>0.8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F6" s="4">
         <v>22</v>
       </c>
       <c r="G6" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" ref="H6:H15" si="1">IF(AND(F6&lt;&gt;"",G6&lt;&gt;""),G6/F6,"")</f>
-        <v>0.63636363636363635</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" ref="I6:I14" si="2">C6+F6</f>
@@ -9076,11 +9088,11 @@
       </c>
       <c r="J6" s="4">
         <f t="shared" ref="J6:J14" si="3">D6+G6</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" ref="K6:K15" si="4">IF(AND(I6&lt;&gt;"",J6&lt;&gt;""),J6/I6,"")</f>
-        <v>0.70270270270270274</v>
+        <v>0.94594594594594594</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -9334,11 +9346,11 @@
       </c>
       <c r="D15" s="7">
         <f>SUM(D6:D14)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" s="7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F15" s="7">
         <f>SUM(F6:F14)</f>
@@ -9346,11 +9358,11 @@
       </c>
       <c r="G15" s="7">
         <f>SUM(G6:G14)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>0.63636363636363635</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="I15" s="7">
         <f>SUM(I6:I14)</f>
@@ -9358,11 +9370,11 @@
       </c>
       <c r="J15" s="7">
         <f>SUM(J6:J14)</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="4"/>
-        <v>0.70270270270270274</v>
+        <v>0.94594594594594594</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9912,11 +9924,11 @@
       </c>
       <c r="D36" s="10">
         <f>D15+D24+D35</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E36" s="10">
         <f t="shared" si="9"/>
-        <v>0.8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F36" s="10">
         <f>F15+F24+F35</f>
@@ -9924,11 +9936,11 @@
       </c>
       <c r="G36" s="10">
         <f>G15+G24+G35</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H36" s="10">
         <f t="shared" si="10"/>
-        <v>0.63636363636363635</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="I36" s="10">
         <f>I15+I24+I35</f>
@@ -9936,11 +9948,11 @@
       </c>
       <c r="J36" s="10">
         <f>J15+J24+J35</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="12"/>
-        <v>0.70270270270270274</v>
+        <v>0.94594594594594594</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10054,19 +10066,21 @@
       </c>
       <c r="B44" s="4">
         <f t="shared" ref="B44:B52" si="13">B6</f>
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="C44" s="4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D44" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E44" s="4">
         <f t="shared" ref="E44:E53" si="14">IF(AND(C44&lt;&gt;"",D44&lt;&gt;""),D44/C44,"")</f>
-        <v>0.625</v>
-      </c>
-      <c r="F44" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="F44" s="4">
+        <v>12</v>
+      </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="str">
         <f t="shared" ref="H44:H53" si="15">IF(AND(F44&lt;&gt;"",G44&lt;&gt;""),G44/F44,"")</f>
@@ -10080,15 +10094,15 @@
       </c>
       <c r="L44" s="4">
         <f t="shared" ref="L44:L52" si="17">C44+F44+I44</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M44" s="4">
         <f t="shared" ref="M44:M52" si="18">D44+G44+J44</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N44" s="4">
         <f t="shared" ref="N44:N53" si="19">IF(AND(L44&lt;&gt;"",M44&lt;&gt;""),M44/L44,"")</f>
-        <v>0.625</v>
+        <v>0.29411764705882354</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -10410,27 +10424,27 @@
       <c r="B53" s="6"/>
       <c r="C53" s="7">
         <f>SUM(C44:C52)</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D53" s="7">
         <f>SUM(D44:D52)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E53" s="7">
         <f t="shared" si="14"/>
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="F53" s="7">
         <f>SUM(F44:F52)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G53" s="7">
         <f>SUM(G44:G52)</f>
         <v>0</v>
       </c>
-      <c r="H53" s="7" t="e">
+      <c r="H53" s="7">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I53" s="7">
         <f>SUM(I44:I52)</f>
@@ -10446,15 +10460,15 @@
       </c>
       <c r="L53" s="7">
         <f>SUM(L44:L52)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M53" s="7">
         <f>SUM(M44:M52)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N53" s="7">
         <f t="shared" si="19"/>
-        <v>0.625</v>
+        <v>0.29411764705882354</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11156,27 +11170,27 @@
       <c r="B74" s="9"/>
       <c r="C74" s="10">
         <f>C53+C62+C73</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D74" s="10">
         <f>D53+D62+D73</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E74" s="10">
         <f t="shared" si="27"/>
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="F74" s="10">
         <f>F53+F62+F73</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G74" s="10">
         <f>G53+G62+G73</f>
         <v>0</v>
       </c>
-      <c r="H74" s="10" t="e">
+      <c r="H74" s="10">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I74" s="10">
         <f>I53+I62+I73</f>
@@ -11192,15 +11206,15 @@
       </c>
       <c r="L74" s="10">
         <f>L53+L62+L73</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M74" s="10">
         <f>M53+M62+M73</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N74" s="10">
         <f t="shared" si="31"/>
-        <v>0.625</v>
+        <v>0.29411764705882354</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11294,7 +11308,7 @@
       </c>
       <c r="B82" s="4">
         <f t="shared" ref="B82:B90" si="32">B6</f>
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="C82" s="4">
         <f t="shared" ref="C82:C90" si="33">I6</f>
@@ -11302,35 +11316,35 @@
       </c>
       <c r="D82" s="4">
         <f t="shared" ref="D82:D90" si="34">J6</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E82" s="4">
         <f t="shared" ref="E82:E91" si="35">IF(AND(C82&lt;&gt;"",D82&lt;&gt;""),D82/C82,"")</f>
-        <v>0.70270270270270274</v>
+        <v>0.94594594594594594</v>
       </c>
       <c r="F82" s="4">
         <f t="shared" ref="F82:F90" si="36">L44</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G82" s="4">
         <f t="shared" ref="G82:G90" si="37">M44</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H82" s="4">
         <f t="shared" ref="H82:H91" si="38">IF(AND(F82&lt;&gt;"",G82&lt;&gt;""),G82/F82,"")</f>
-        <v>0.625</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I82" s="4">
         <f t="shared" ref="I82:I90" si="39">C82+F82</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ref="J82:J90" si="40">D82+G82</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K82" s="4">
         <f t="shared" ref="K82:K91" si="41">IF(AND(I82&lt;&gt;"",J82&lt;&gt;""),J82/I82,"")</f>
-        <v>0.67924528301886788</v>
+        <v>0.7407407407407407</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -11704,35 +11718,35 @@
       </c>
       <c r="D91" s="7">
         <f>SUM(D82:D90)</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E91" s="7">
         <f t="shared" si="35"/>
-        <v>0.70270270270270274</v>
+        <v>0.94594594594594594</v>
       </c>
       <c r="F91" s="7">
         <f>SUM(F82:F90)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G91" s="7">
         <f>SUM(G82:G90)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H91" s="7">
         <f t="shared" si="38"/>
-        <v>0.625</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I91" s="7">
         <f>SUM(I82:I90)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J91" s="7">
         <f>SUM(J82:J90)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K91" s="7">
         <f t="shared" si="41"/>
-        <v>0.67924528301886788</v>
+        <v>0.7407407407407407</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12492,35 +12506,35 @@
       </c>
       <c r="D112" s="10">
         <f>D91+D100+D111</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E112" s="10">
         <f t="shared" si="51"/>
-        <v>0.70270270270270274</v>
+        <v>0.94594594594594594</v>
       </c>
       <c r="F112" s="10">
         <f>F91+F100+F111</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G112" s="10">
         <f>G91+G100+G111</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H112" s="10">
         <f t="shared" si="53"/>
-        <v>0.625</v>
+        <v>0.29411764705882354</v>
       </c>
       <c r="I112" s="10">
         <f>I91+I100+I111</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J112" s="10">
         <f>J91+J100+J111</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K112" s="10">
         <f t="shared" si="55"/>
-        <v>0.67924528301886788</v>
+        <v>0.7407407407407407</v>
       </c>
     </row>
   </sheetData>
@@ -21266,23 +21280,27 @@
         <v>227</v>
       </c>
       <c r="B6" s="15">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="C6" s="15">
         <v>17</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15" t="str">
+      <c r="D6" s="15">
+        <v>14</v>
+      </c>
+      <c r="E6" s="15">
         <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
-        <v/>
+        <v>0.82352941176470584</v>
       </c>
       <c r="F6" s="15">
         <v>5</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="str">
+      <c r="G6" s="15">
+        <v>4</v>
+      </c>
+      <c r="H6" s="15">
         <f>IF(AND(F6&lt;&gt;"",G6&lt;&gt;""),G6/F6,"")</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="I6" s="15">
         <f>C6-F6</f>
@@ -21290,15 +21308,13 @@
       </c>
       <c r="J6" s="15">
         <f>D6-G6</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K6" s="15">
         <f>IF(AND(I6&lt;&gt;"",J6&lt;&gt;""),J6/I6,"")</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>263</v>
-      </c>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L6" s="11"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
@@ -21329,30 +21345,40 @@
       <c r="A7" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="str">
+      <c r="B7" s="15">
+        <v>617</v>
+      </c>
+      <c r="C7" s="15">
+        <v>38</v>
+      </c>
+      <c r="D7" s="15">
+        <v>30</v>
+      </c>
+      <c r="E7" s="15">
         <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;""),D7/C7,"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15" t="str">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="F7" s="15">
+        <v>10</v>
+      </c>
+      <c r="G7" s="15">
+        <v>8</v>
+      </c>
+      <c r="H7" s="15">
         <f>IF(AND(F7&lt;&gt;"",G7&lt;&gt;""),G7/F7,"")</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="I7" s="15">
         <f>C7-F7</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J7" s="15">
         <f>D7-G7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="15" t="e">
+        <v>22</v>
+      </c>
+      <c r="K7" s="15">
         <f>IF(AND(I7&lt;&gt;"",J7&lt;&gt;""),J7/I7,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="L7" s="11"/>
       <c r="M7" s="15"/>
@@ -21411,30 +21437,40 @@
       <c r="A9" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="str">
+      <c r="B9" s="15">
+        <v>618</v>
+      </c>
+      <c r="C9" s="15">
+        <v>28</v>
+      </c>
+      <c r="D9" s="15">
+        <v>21</v>
+      </c>
+      <c r="E9" s="15">
         <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;""),D9/C9,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="F9" s="15">
+        <v>11</v>
+      </c>
+      <c r="G9" s="15">
+        <v>10</v>
+      </c>
+      <c r="H9" s="15">
         <f>IF(AND(F9&lt;&gt;"",G9&lt;&gt;""),G9/F9,"")</f>
-        <v/>
+        <v>0.90909090909090906</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" ref="I9:J11" si="0">C9-F9</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="15" t="e">
+        <v>11</v>
+      </c>
+      <c r="K9" s="15">
         <f>IF(AND(I9&lt;&gt;"",J9&lt;&gt;""),J9/I9,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="15"/>
@@ -21467,30 +21503,40 @@
       <c r="A10" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15" t="str">
+      <c r="B10" s="15">
+        <v>618</v>
+      </c>
+      <c r="C10" s="15">
+        <v>12</v>
+      </c>
+      <c r="D10" s="15">
+        <v>10</v>
+      </c>
+      <c r="E10" s="15">
         <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;""),D10/C10,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="str">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F10" s="15">
+        <v>2</v>
+      </c>
+      <c r="G10" s="15">
+        <v>2</v>
+      </c>
+      <c r="H10" s="15">
         <f>IF(AND(F10&lt;&gt;"",G10&lt;&gt;""),G10/F10,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="15" t="e">
+        <v>8</v>
+      </c>
+      <c r="K10" s="15">
         <f>IF(AND(I10&lt;&gt;"",J10&lt;&gt;""),J10/I10,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.8</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="15"/>
@@ -21523,30 +21569,40 @@
       <c r="A11" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15" t="str">
+      <c r="B11" s="15">
+        <v>618</v>
+      </c>
+      <c r="C11" s="15">
+        <v>9</v>
+      </c>
+      <c r="D11" s="15">
+        <v>9</v>
+      </c>
+      <c r="E11" s="15">
         <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;""),D11/C11,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15" t="str">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="e">
         <f>IF(AND(F11&lt;&gt;"",G11&lt;&gt;""),G11/F11,"")</f>
-        <v/>
+        <v>#DIV/0!</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="15" t="e">
+        <v>9</v>
+      </c>
+      <c r="K11" s="15">
         <f>IF(AND(I11&lt;&gt;"",J11&lt;&gt;""),J11/I11,"")</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="15"/>
@@ -22974,39 +23030,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.80769230769230771</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23055,39 +23111,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>0</v>
+        <v>0.80769230769230771</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>0</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D462556C-0851-423B-A4D8-B496C94096E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE981BE-AE38-4529-BEF8-9952F3A65384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
     <sheet name="武忠祥高数严选题" sheetId="8" r:id="rId2"/>
-    <sheet name="李林880专题" sheetId="3" r:id="rId3"/>
+    <sheet name="李林880" sheetId="3" r:id="rId3"/>
     <sheet name="王道数据结构" sheetId="4" r:id="rId4"/>
     <sheet name="王道计组" sheetId="5" r:id="rId5"/>
     <sheet name="王道操作系统" sheetId="6" r:id="rId6"/>
@@ -293,9 +293,6 @@
     <t>总计</t>
   </si>
   <si>
-    <t>李林880专题 （选择&amp;填空）习题正确率记录</t>
-  </si>
-  <si>
     <t>时间</t>
   </si>
   <si>
@@ -830,6 +827,10 @@
   </si>
   <si>
     <t>未完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李林880 （选择&amp;填空）习题正确率记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1249,16 +1250,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1283,22 +1293,13 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7066,7 +7067,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="55" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="46"/>
@@ -7093,7 +7094,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="54" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="48"/>
@@ -7604,7 +7605,7 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="54" t="s">
         <v>58</v>
       </c>
       <c r="B41" s="48"/>
@@ -8091,7 +8092,7 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="51" t="s">
+      <c r="A83" s="54" t="s">
         <v>76</v>
       </c>
       <c r="B83" s="48"/>
@@ -8315,7 +8316,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="46"/>
@@ -8336,26 +8337,26 @@
     <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="57" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="46"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="58" t="s">
+      <c r="E3" s="58"/>
+      <c r="F3" s="61" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="46"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="57" t="s">
+      <c r="H3" s="58"/>
+      <c r="I3" s="60" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="46"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="56" t="s">
+      <c r="K3" s="58"/>
+      <c r="L3" s="59" t="s">
         <v>4</v>
       </c>
       <c r="M3" s="46"/>
-      <c r="N3" s="55"/>
+      <c r="N3" s="58"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -8971,8 +8972,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
-        <v>84</v>
+      <c r="A1" s="65" t="s">
+        <v>262</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -8989,17 +8990,17 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="52" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="48"/>
       <c r="E3" s="49"/>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="50" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="48"/>
       <c r="H3" s="49"/>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="51" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="48"/>
@@ -9010,7 +9011,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
@@ -9041,7 +9042,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="47" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="48"/>
@@ -9057,7 +9058,7 @@
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="4">
         <v>618</v>
@@ -9097,7 +9098,7 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -9127,7 +9128,7 @@
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -9157,7 +9158,7 @@
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -9187,7 +9188,7 @@
     </row>
     <row r="10" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -9217,7 +9218,7 @@
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -9247,7 +9248,7 @@
     </row>
     <row r="12" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -9277,7 +9278,7 @@
     </row>
     <row r="13" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -9307,7 +9308,7 @@
     </row>
     <row r="14" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -9337,7 +9338,7 @@
     </row>
     <row r="15" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7">
@@ -9379,7 +9380,7 @@
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="48"/>
@@ -9395,7 +9396,7 @@
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -9425,7 +9426,7 @@
     </row>
     <row r="19" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -9455,7 +9456,7 @@
     </row>
     <row r="20" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -9485,7 +9486,7 @@
     </row>
     <row r="21" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -9515,7 +9516,7 @@
     </row>
     <row r="22" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -9545,7 +9546,7 @@
     </row>
     <row r="23" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -9575,7 +9576,7 @@
     </row>
     <row r="24" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7">
@@ -9617,7 +9618,7 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="48"/>
@@ -9633,7 +9634,7 @@
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -9663,7 +9664,7 @@
     </row>
     <row r="28" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -9693,7 +9694,7 @@
     </row>
     <row r="29" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -9723,7 +9724,7 @@
     </row>
     <row r="30" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -9753,7 +9754,7 @@
     </row>
     <row r="31" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -9783,7 +9784,7 @@
     </row>
     <row r="32" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -9813,7 +9814,7 @@
     </row>
     <row r="33" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -9843,7 +9844,7 @@
     </row>
     <row r="34" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -9873,7 +9874,7 @@
     </row>
     <row r="35" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="7">
@@ -9915,7 +9916,7 @@
     </row>
     <row r="36" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="10">
@@ -9956,8 +9957,8 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="59" t="s">
-        <v>113</v>
+      <c r="A39" s="45" t="s">
+        <v>112</v>
       </c>
       <c r="B39" s="46"/>
       <c r="C39" s="46"/>
@@ -9977,22 +9978,22 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="52" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="48"/>
       <c r="E41" s="49"/>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="50" t="s">
         <v>76</v>
       </c>
       <c r="G41" s="48"/>
       <c r="H41" s="49"/>
-      <c r="I41" s="64" t="s">
-        <v>114</v>
+      <c r="I41" s="53" t="s">
+        <v>113</v>
       </c>
       <c r="J41" s="48"/>
       <c r="K41" s="49"/>
-      <c r="L41" s="62" t="s">
+      <c r="L41" s="51" t="s">
         <v>4</v>
       </c>
       <c r="M41" s="48"/>
@@ -10003,7 +10004,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -10043,7 +10044,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="60" t="s">
+      <c r="A43" s="47" t="s">
         <v>23</v>
       </c>
       <c r="B43" s="48"/>
@@ -10062,7 +10063,7 @@
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="4">
         <f t="shared" ref="B44:B52" si="13">B6</f>
@@ -10081,33 +10082,39 @@
       <c r="F44" s="4">
         <v>12</v>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4" t="str">
+      <c r="G44" s="4">
+        <v>6</v>
+      </c>
+      <c r="H44" s="4">
         <f t="shared" ref="H44:H53" si="15">IF(AND(F44&lt;&gt;"",G44&lt;&gt;""),G44/F44,"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="I44" s="4">
+        <v>2</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
         <f t="shared" ref="K44:K53" si="16">IF(AND(I44&lt;&gt;"",J44&lt;&gt;""),J44/I44,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" ref="L44:L52" si="17">C44+F44+I44</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M44" s="4">
         <f t="shared" ref="M44:M52" si="18">D44+G44+J44</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N44" s="4">
         <f t="shared" ref="N44:N53" si="19">IF(AND(L44&lt;&gt;"",M44&lt;&gt;""),M44/L44,"")</f>
-        <v>0.29411764705882354</v>
+        <v>0.57894736842105265</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B45" s="4">
         <f t="shared" si="13"/>
@@ -10146,7 +10153,7 @@
     </row>
     <row r="46" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46" s="4">
         <f t="shared" si="13"/>
@@ -10185,7 +10192,7 @@
     </row>
     <row r="47" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B47" s="4">
         <f t="shared" si="13"/>
@@ -10224,7 +10231,7 @@
     </row>
     <row r="48" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B48" s="4">
         <f t="shared" si="13"/>
@@ -10263,7 +10270,7 @@
     </row>
     <row r="49" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B49" s="4">
         <f t="shared" si="13"/>
@@ -10302,7 +10309,7 @@
     </row>
     <row r="50" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B50" s="4">
         <f t="shared" si="13"/>
@@ -10341,7 +10348,7 @@
     </row>
     <row r="51" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" si="13"/>
@@ -10380,7 +10387,7 @@
     </row>
     <row r="52" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B52" s="4">
         <f t="shared" si="13"/>
@@ -10419,7 +10426,7 @@
     </row>
     <row r="53" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="7">
@@ -10440,40 +10447,40 @@
       </c>
       <c r="G53" s="7">
         <f>SUM(G44:G52)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H53" s="7">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I53" s="7">
         <f>SUM(I44:I52)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="7">
         <f>SUM(J44:J52)</f>
         <v>0</v>
       </c>
-      <c r="K53" s="7" t="e">
+      <c r="K53" s="7">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L53" s="7">
         <f>SUM(L44:L52)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M53" s="7">
         <f>SUM(M44:M52)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N53" s="7">
         <f t="shared" si="19"/>
-        <v>0.29411764705882354</v>
+        <v>0.57894736842105265</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="60" t="s">
+      <c r="A55" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="48"/>
@@ -10492,7 +10499,7 @@
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B56" s="4">
         <f t="shared" ref="B56:B61" si="20">B18</f>
@@ -10531,7 +10538,7 @@
     </row>
     <row r="57" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B57" s="4">
         <f t="shared" si="20"/>
@@ -10570,7 +10577,7 @@
     </row>
     <row r="58" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B58" s="4">
         <f t="shared" si="20"/>
@@ -10609,7 +10616,7 @@
     </row>
     <row r="59" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B59" s="4">
         <f t="shared" si="20"/>
@@ -10648,7 +10655,7 @@
     </row>
     <row r="60" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="4">
         <f t="shared" si="20"/>
@@ -10687,7 +10694,7 @@
     </row>
     <row r="61" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B61" s="4">
         <f t="shared" si="20"/>
@@ -10726,7 +10733,7 @@
     </row>
     <row r="62" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="7">
@@ -10780,7 +10787,7 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="60" t="s">
+      <c r="A64" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B64" s="48"/>
@@ -10799,7 +10806,7 @@
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" s="4">
         <f t="shared" ref="B65:B72" si="26">B27</f>
@@ -10838,7 +10845,7 @@
     </row>
     <row r="66" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" s="4">
         <f t="shared" si="26"/>
@@ -10877,7 +10884,7 @@
     </row>
     <row r="67" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B67" s="4">
         <f t="shared" si="26"/>
@@ -10916,7 +10923,7 @@
     </row>
     <row r="68" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B68" s="4">
         <f t="shared" si="26"/>
@@ -10955,7 +10962,7 @@
     </row>
     <row r="69" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B69" s="4">
         <f t="shared" si="26"/>
@@ -10994,7 +11001,7 @@
     </row>
     <row r="70" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70" s="4">
         <f t="shared" si="26"/>
@@ -11033,7 +11040,7 @@
     </row>
     <row r="71" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B71" s="4">
         <f t="shared" si="26"/>
@@ -11072,7 +11079,7 @@
     </row>
     <row r="72" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B72" s="4">
         <f t="shared" si="26"/>
@@ -11111,7 +11118,7 @@
     </row>
     <row r="73" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="7">
@@ -11165,7 +11172,7 @@
     </row>
     <row r="74" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="10">
@@ -11186,40 +11193,40 @@
       </c>
       <c r="G74" s="10">
         <f>G53+G62+G73</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H74" s="10">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I74" s="10">
         <f>I53+I62+I73</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="10">
         <f>J53+J62+J73</f>
         <v>0</v>
       </c>
-      <c r="K74" s="10" t="e">
+      <c r="K74" s="10">
         <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L74" s="10">
         <f>L53+L62+L73</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M74" s="10">
         <f>M53+M62+M73</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N74" s="10">
         <f t="shared" si="31"/>
-        <v>0.29411764705882354</v>
+        <v>0.57894736842105265</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="59" t="s">
-        <v>115</v>
+      <c r="A77" s="45" t="s">
+        <v>114</v>
       </c>
       <c r="B77" s="46"/>
       <c r="C77" s="46"/>
@@ -11236,17 +11243,17 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="63" t="s">
-        <v>116</v>
+      <c r="C79" s="52" t="s">
+        <v>115</v>
       </c>
       <c r="D79" s="48"/>
       <c r="E79" s="49"/>
-      <c r="F79" s="61" t="s">
-        <v>113</v>
+      <c r="F79" s="50" t="s">
+        <v>112</v>
       </c>
       <c r="G79" s="48"/>
       <c r="H79" s="49"/>
-      <c r="I79" s="62" t="s">
+      <c r="I79" s="51" t="s">
         <v>83</v>
       </c>
       <c r="J79" s="48"/>
@@ -11257,7 +11264,7 @@
         <v>5</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -11288,7 +11295,7 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="60" t="s">
+      <c r="A81" s="47" t="s">
         <v>23</v>
       </c>
       <c r="B81" s="48"/>
@@ -11304,7 +11311,7 @@
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" s="4">
         <f t="shared" ref="B82:B90" si="32">B6</f>
@@ -11324,32 +11331,32 @@
       </c>
       <c r="F82" s="4">
         <f t="shared" ref="F82:F90" si="36">L44</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G82" s="4">
         <f t="shared" ref="G82:G90" si="37">M44</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H82" s="4">
         <f t="shared" ref="H82:H91" si="38">IF(AND(F82&lt;&gt;"",G82&lt;&gt;""),G82/F82,"")</f>
-        <v>0.29411764705882354</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="I82" s="4">
         <f t="shared" ref="I82:I90" si="39">C82+F82</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ref="J82:J90" si="40">D82+G82</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K82" s="4">
         <f t="shared" ref="K82:K91" si="41">IF(AND(I82&lt;&gt;"",J82&lt;&gt;""),J82/I82,"")</f>
-        <v>0.7407407407407407</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83" s="4">
         <f t="shared" si="32"/>
@@ -11394,7 +11401,7 @@
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84" s="4">
         <f t="shared" si="32"/>
@@ -11439,7 +11446,7 @@
     </row>
     <row r="85" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85" s="4">
         <f t="shared" si="32"/>
@@ -11484,7 +11491,7 @@
     </row>
     <row r="86" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" s="4">
         <f t="shared" si="32"/>
@@ -11529,7 +11536,7 @@
     </row>
     <row r="87" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87" s="4">
         <f t="shared" si="32"/>
@@ -11574,7 +11581,7 @@
     </row>
     <row r="88" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" s="4">
         <f t="shared" si="32"/>
@@ -11619,7 +11626,7 @@
     </row>
     <row r="89" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" s="4">
         <f t="shared" si="32"/>
@@ -11664,7 +11671,7 @@
     </row>
     <row r="90" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90" s="4">
         <f t="shared" si="32"/>
@@ -11709,7 +11716,7 @@
     </row>
     <row r="91" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="7">
@@ -11726,32 +11733,32 @@
       </c>
       <c r="F91" s="7">
         <f>SUM(F82:F90)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G91" s="7">
         <f>SUM(G82:G90)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H91" s="7">
         <f t="shared" si="38"/>
-        <v>0.29411764705882354</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="I91" s="7">
         <f>SUM(I82:I90)</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J91" s="7">
         <f>SUM(J82:J90)</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K91" s="7">
         <f t="shared" si="41"/>
-        <v>0.7407407407407407</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="60" t="s">
+      <c r="A93" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B93" s="48"/>
@@ -11767,7 +11774,7 @@
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="4">
         <f t="shared" ref="B94:B99" si="42">B18</f>
@@ -11812,7 +11819,7 @@
     </row>
     <row r="95" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B95" s="4">
         <f t="shared" si="42"/>
@@ -11857,7 +11864,7 @@
     </row>
     <row r="96" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B96" s="4">
         <f t="shared" si="42"/>
@@ -11902,7 +11909,7 @@
     </row>
     <row r="97" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B97" s="4">
         <f t="shared" si="42"/>
@@ -11947,7 +11954,7 @@
     </row>
     <row r="98" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B98" s="4">
         <f t="shared" si="42"/>
@@ -11992,7 +11999,7 @@
     </row>
     <row r="99" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B99" s="4">
         <f t="shared" si="42"/>
@@ -12037,7 +12044,7 @@
     </row>
     <row r="100" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="7">
@@ -12079,7 +12086,7 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="60" t="s">
+      <c r="A102" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B102" s="48"/>
@@ -12095,7 +12102,7 @@
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="4">
         <f t="shared" ref="B103:B110" si="49">B27</f>
@@ -12140,7 +12147,7 @@
     </row>
     <row r="104" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="4">
         <f t="shared" si="49"/>
@@ -12185,7 +12192,7 @@
     </row>
     <row r="105" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="4">
         <f t="shared" si="49"/>
@@ -12230,7 +12237,7 @@
     </row>
     <row r="106" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" s="4">
         <f t="shared" si="49"/>
@@ -12275,7 +12282,7 @@
     </row>
     <row r="107" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="4">
         <f t="shared" si="49"/>
@@ -12320,7 +12327,7 @@
     </row>
     <row r="108" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="4">
         <f t="shared" si="49"/>
@@ -12365,7 +12372,7 @@
     </row>
     <row r="109" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="4">
         <f t="shared" si="49"/>
@@ -12410,7 +12417,7 @@
     </row>
     <row r="110" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="4">
         <f t="shared" si="49"/>
@@ -12455,7 +12462,7 @@
     </row>
     <row r="111" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="7">
@@ -12497,7 +12504,7 @@
     </row>
     <row r="112" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" s="9"/>
       <c r="C112" s="10">
@@ -12514,27 +12521,27 @@
       </c>
       <c r="F112" s="10">
         <f>F91+F100+F111</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G112" s="10">
         <f>G91+G100+G111</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H112" s="10">
         <f t="shared" si="53"/>
-        <v>0.29411764705882354</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="I112" s="10">
         <f>I91+I100+I111</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J112" s="10">
         <f>J91+J100+J111</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K112" s="10">
         <f t="shared" si="55"/>
-        <v>0.7407407407407407</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
   </sheetData>
@@ -12954,8 +12961,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>117</v>
+      <c r="A1" s="62" t="s">
+        <v>116</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -12981,8 +12988,8 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>118</v>
+      <c r="A3" s="64" t="s">
+        <v>117</v>
       </c>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
@@ -12995,8 +13002,8 @@
       <c r="J3" s="48"/>
       <c r="K3" s="49"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="47" t="s">
-        <v>119</v>
+      <c r="M3" s="63" t="s">
+        <v>118</v>
       </c>
       <c r="N3" s="48"/>
       <c r="O3" s="48"/>
@@ -13010,7 +13017,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -13025,22 +13032,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>20</v>
@@ -13055,27 +13062,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -13101,7 +13108,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="15">
         <v>415</v>
@@ -13167,7 +13174,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="15">
         <v>416</v>
@@ -13233,7 +13240,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -13259,7 +13266,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" s="15">
         <v>417</v>
@@ -13325,7 +13332,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" s="15">
         <v>418</v>
@@ -13391,7 +13398,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" s="15">
         <v>419</v>
@@ -13457,7 +13464,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -13483,7 +13490,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B13" s="15">
         <v>420</v>
@@ -13549,7 +13556,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14" s="15">
         <v>421</v>
@@ -13615,7 +13622,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B15" s="15">
         <v>422</v>
@@ -13681,7 +13688,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B16" s="15">
         <v>423</v>
@@ -13747,7 +13754,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -13773,7 +13780,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" s="15">
         <v>424</v>
@@ -13839,7 +13846,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B19" s="15">
         <v>424</v>
@@ -13905,7 +13912,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -13931,7 +13938,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="15">
         <v>425</v>
@@ -13997,7 +14004,7 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B22" s="15">
         <v>425</v>
@@ -14063,7 +14070,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B23" s="15">
         <v>426</v>
@@ -14129,7 +14136,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B24" s="15">
         <v>427</v>
@@ -14195,7 +14202,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B25" s="15">
         <v>428</v>
@@ -14261,7 +14268,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -14287,7 +14294,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B27" s="15">
         <v>429</v>
@@ -14353,7 +14360,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B28" s="15">
         <v>430</v>
@@ -14419,7 +14426,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B29" s="15">
         <v>501</v>
@@ -14485,7 +14492,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B30" s="15">
         <v>502</v>
@@ -14551,7 +14558,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -14577,7 +14584,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B32" s="15">
         <v>503</v>
@@ -14643,7 +14650,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" s="15">
         <v>503</v>
@@ -14709,7 +14716,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B34" s="15">
         <v>503</v>
@@ -14747,7 +14754,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="L34" s="43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
@@ -14777,7 +14784,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="15">
         <v>504</v>
@@ -14843,7 +14850,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B36" s="15">
         <v>504</v>
@@ -14909,7 +14916,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -14935,7 +14942,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B38" s="15">
         <v>505</v>
@@ -15001,7 +15008,7 @@
     </row>
     <row r="39" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B39" s="15">
         <v>505</v>
@@ -15067,7 +15074,7 @@
     </row>
     <row r="40" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B40" s="15">
         <v>505</v>
@@ -15133,7 +15140,7 @@
     </row>
     <row r="41" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B41" s="15">
         <v>505</v>
@@ -15199,7 +15206,7 @@
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B42" s="15">
         <v>506</v>
@@ -15265,7 +15272,7 @@
     </row>
     <row r="43" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B43" s="15">
         <v>506</v>
@@ -15295,7 +15302,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L43" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
@@ -15325,7 +15332,7 @@
     </row>
     <row r="44" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="15">
         <v>506</v>
@@ -15355,7 +15362,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L44" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
@@ -16201,7 +16208,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="65" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -16227,8 +16234,8 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>118</v>
+      <c r="A3" s="64" t="s">
+        <v>117</v>
       </c>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
@@ -16241,8 +16248,8 @@
       <c r="J3" s="48"/>
       <c r="K3" s="49"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="47" t="s">
-        <v>119</v>
+      <c r="M3" s="63" t="s">
+        <v>118</v>
       </c>
       <c r="N3" s="48"/>
       <c r="O3" s="48"/>
@@ -16256,7 +16263,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -16271,22 +16278,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>20</v>
@@ -16301,27 +16308,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -16347,7 +16354,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B6" s="15">
         <v>507</v>
@@ -16413,7 +16420,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="15">
         <v>507</v>
@@ -16479,7 +16486,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="15">
         <v>508</v>
@@ -16545,7 +16552,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -16571,7 +16578,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B10" s="15">
         <v>509</v>
@@ -16637,7 +16644,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B11" s="15">
         <v>510</v>
@@ -16703,7 +16710,7 @@
     </row>
     <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B12" s="15">
         <v>512</v>
@@ -16769,7 +16776,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -16795,7 +16802,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="15">
         <v>513</v>
@@ -16861,7 +16868,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B15" s="15">
         <v>514</v>
@@ -16927,7 +16934,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" s="15">
         <v>515</v>
@@ -16993,7 +17000,7 @@
     </row>
     <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" s="15">
         <v>516</v>
@@ -17059,7 +17066,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" s="15">
         <v>516</v>
@@ -17125,7 +17132,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B19" s="15">
         <v>517</v>
@@ -17191,7 +17198,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -17217,7 +17224,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" s="15">
         <v>518</v>
@@ -17283,7 +17290,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B22" s="15">
         <v>518</v>
@@ -17349,7 +17356,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B23" s="15">
         <v>519</v>
@@ -17383,7 +17390,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L23" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -17413,7 +17420,7 @@
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B24" s="15">
         <v>520</v>
@@ -17479,7 +17486,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -17505,7 +17512,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B26" s="15">
         <v>521</v>
@@ -17571,7 +17578,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B27" s="15">
         <v>521</v>
@@ -17637,7 +17644,7 @@
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B28" s="15">
         <v>522</v>
@@ -17703,7 +17710,7 @@
     </row>
     <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B29" s="15">
         <v>523</v>
@@ -17769,7 +17776,7 @@
     </row>
     <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B30" s="15">
         <v>524</v>
@@ -17835,7 +17842,7 @@
     </row>
     <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B31" s="15">
         <v>525</v>
@@ -17901,7 +17908,7 @@
     </row>
     <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B32" s="15">
         <v>525</v>
@@ -17967,7 +17974,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -17993,7 +18000,7 @@
     </row>
     <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B34" s="15">
         <v>526</v>
@@ -18059,7 +18066,7 @@
     </row>
     <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B35" s="15">
         <v>526</v>
@@ -18125,7 +18132,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -18151,7 +18158,7 @@
     </row>
     <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B37" s="15">
         <v>526</v>
@@ -18217,7 +18224,7 @@
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B38" s="15">
         <v>527</v>
@@ -18283,7 +18290,7 @@
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B39" s="15">
         <v>528</v>
@@ -19092,8 +19099,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>202</v>
+      <c r="A1" s="62" t="s">
+        <v>201</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -19119,8 +19126,8 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>118</v>
+      <c r="A3" s="64" t="s">
+        <v>117</v>
       </c>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
@@ -19133,8 +19140,8 @@
       <c r="J3" s="48"/>
       <c r="K3" s="49"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="47" t="s">
-        <v>119</v>
+      <c r="M3" s="63" t="s">
+        <v>118</v>
       </c>
       <c r="N3" s="48"/>
       <c r="O3" s="48"/>
@@ -19148,7 +19155,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -19163,22 +19170,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>20</v>
@@ -19193,27 +19200,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -19239,7 +19246,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B6" s="15">
         <v>530</v>
@@ -19305,7 +19312,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B7" s="15">
         <v>530</v>
@@ -19371,7 +19378,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B8" s="15">
         <v>530</v>
@@ -19437,7 +19444,7 @@
     </row>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B9" s="15">
         <v>531</v>
@@ -19503,7 +19510,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B10" s="15">
         <v>531</v>
@@ -19569,7 +19576,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B11" s="15">
         <v>531</v>
@@ -19635,7 +19642,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -19661,7 +19668,7 @@
     </row>
     <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="15">
         <v>601</v>
@@ -19727,7 +19734,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="15">
         <v>602</v>
@@ -19793,7 +19800,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="15">
         <v>606</v>
@@ -19859,7 +19866,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="15">
         <v>607</v>
@@ -19925,7 +19932,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -19951,7 +19958,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B18" s="15">
         <v>609</v>
@@ -20017,7 +20024,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" s="15">
         <v>610</v>
@@ -20083,7 +20090,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -20109,7 +20116,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B21" s="15">
         <v>611</v>
@@ -20175,7 +20182,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="15">
         <v>614</v>
@@ -20241,7 +20248,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B23" s="15">
         <v>614</v>
@@ -20307,7 +20314,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -20333,7 +20340,7 @@
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B25" s="15">
         <v>614</v>
@@ -20399,7 +20406,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B26" s="15">
         <v>615</v>
@@ -20465,7 +20472,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B27" s="15">
         <v>615</v>
@@ -21130,8 +21137,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>225</v>
+      <c r="A1" s="62" t="s">
+        <v>224</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -21157,8 +21164,8 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>118</v>
+      <c r="A3" s="64" t="s">
+        <v>117</v>
       </c>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
@@ -21171,8 +21178,8 @@
       <c r="J3" s="48"/>
       <c r="K3" s="49"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="47" t="s">
-        <v>119</v>
+      <c r="M3" s="63" t="s">
+        <v>118</v>
       </c>
       <c r="N3" s="48"/>
       <c r="O3" s="48"/>
@@ -21186,7 +21193,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
@@ -21201,22 +21208,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>20</v>
@@ -21231,27 +21238,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -21277,7 +21284,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" s="15">
         <v>616</v>
@@ -21343,7 +21350,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B7" s="15">
         <v>617</v>
@@ -21409,7 +21416,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -21435,7 +21442,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B9" s="15">
         <v>618</v>
@@ -21501,7 +21508,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B10" s="15">
         <v>618</v>
@@ -21567,7 +21574,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" s="15">
         <v>618</v>
@@ -21633,7 +21640,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -21659,7 +21666,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -21715,7 +21722,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -21771,7 +21778,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -21827,7 +21834,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -21883,7 +21890,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -21939,7 +21946,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -21995,7 +22002,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -22051,7 +22058,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -22107,7 +22114,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -22133,7 +22140,7 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -22189,7 +22196,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -22245,7 +22252,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -22301,7 +22308,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -22357,7 +22364,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -22413,7 +22420,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -22469,7 +22476,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -22525,7 +22532,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -22551,7 +22558,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -22607,7 +22614,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -22663,7 +22670,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -22719,7 +22726,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -22745,7 +22752,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -22801,7 +22808,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -22857,7 +22864,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -22913,7 +22920,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -22969,7 +22976,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FF6858-418B-46C2-B3EE-8E0957E38028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2502D9-047E-4C3A-A580-858D85DB98B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1436,14 +1436,14 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1469,16 +1469,16 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1487,7 +1487,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1507,6 +1507,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1531,6 +1539,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1579,6 +1603,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1611,6 +1643,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1619,6 +1659,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -1645,54 +1693,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9406,7 +9406,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="67" t="s">
         <v>127</v>
       </c>
       <c r="B1" s="55"/>
@@ -9429,12 +9429,12 @@
       </c>
       <c r="D3" s="59"/>
       <c r="E3" s="60"/>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="70" t="s">
         <v>106</v>
       </c>
       <c r="G3" s="59"/>
       <c r="H3" s="60"/>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="69" t="s">
         <v>47</v>
       </c>
       <c r="J3" s="59"/>
@@ -9476,7 +9476,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="68" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="59"/>
@@ -9814,7 +9814,7 @@
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="59"/>
@@ -10052,7 +10052,7 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="68" t="s">
         <v>80</v>
       </c>
       <c r="B26" s="59"/>
@@ -10391,7 +10391,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="73" t="s">
         <v>156</v>
       </c>
       <c r="B39" s="55"/>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="D41" s="59"/>
       <c r="E41" s="60"/>
-      <c r="F41" s="68" t="s">
+      <c r="F41" s="70" t="s">
         <v>106</v>
       </c>
       <c r="G41" s="59"/>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="J41" s="59"/>
       <c r="K41" s="60"/>
-      <c r="L41" s="70" t="s">
+      <c r="L41" s="69" t="s">
         <v>47</v>
       </c>
       <c r="M41" s="59"/>
@@ -10478,7 +10478,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="68" t="s">
         <v>53</v>
       </c>
       <c r="B43" s="59"/>
@@ -10914,7 +10914,7 @@
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B55" s="59"/>
@@ -11221,7 +11221,7 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="67" t="s">
+      <c r="A64" s="68" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="59"/>
@@ -11659,7 +11659,7 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="69" t="s">
+      <c r="A77" s="73" t="s">
         <v>158</v>
       </c>
       <c r="B77" s="55"/>
@@ -11682,12 +11682,12 @@
       </c>
       <c r="D79" s="59"/>
       <c r="E79" s="60"/>
-      <c r="F79" s="68" t="s">
+      <c r="F79" s="70" t="s">
         <v>156</v>
       </c>
       <c r="G79" s="59"/>
       <c r="H79" s="60"/>
-      <c r="I79" s="70" t="s">
+      <c r="I79" s="69" t="s">
         <v>113</v>
       </c>
       <c r="J79" s="59"/>
@@ -11729,7 +11729,7 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="67" t="s">
+      <c r="A81" s="68" t="s">
         <v>53</v>
       </c>
       <c r="B81" s="59"/>
@@ -12192,7 +12192,7 @@
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="67" t="s">
+      <c r="A93" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B93" s="59"/>
@@ -12520,7 +12520,7 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="67" t="s">
+      <c r="A102" s="68" t="s">
         <v>80</v>
       </c>
       <c r="B102" s="59"/>
@@ -12980,6 +12980,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
@@ -12996,12 +13002,6 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
@@ -16641,7 +16641,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="67" t="s">
         <v>212</v>
       </c>
       <c r="B1" s="55"/>
@@ -22300,7 +22300,9 @@
       <c r="A16" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="15"/>
+      <c r="B16" s="15">
+        <v>620</v>
+      </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15" t="str">
@@ -24154,6 +24156,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.39997558519241921"/>
+  </sheetPr>
   <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24169,7 +24174,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
@@ -24199,35 +24204,35 @@
     <row r="2" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="57" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="55"/>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
-      <c r="L3" s="56" t="s">
+      <c r="L3" s="57" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
-      <c r="Q3" s="56" t="s">
+      <c r="Q3" s="57" t="s">
         <v>4</v>
       </c>
       <c r="R3" s="55"/>
       <c r="S3" s="55"/>
       <c r="T3" s="55"/>
       <c r="U3" s="55"/>
-      <c r="V3" s="54" t="s">
+      <c r="V3" s="56" t="s">
         <v>5</v>
       </c>
       <c r="W3" s="55"/>
@@ -25491,11 +25496,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K21">
-    <cfRule type="cellIs" dxfId="23" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="21" priority="12" operator="lessThan">
@@ -25530,24 +25535,24 @@
     <cfRule type="cellIs" dxfId="14" priority="25" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="13" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="27" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U21">
-    <cfRule type="cellIs" dxfId="11" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="11" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="30" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U23">
@@ -25575,15 +25580,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X23">
-    <cfRule type="cellIs" dxfId="2" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="2" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="45" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2502D9-047E-4C3A-A580-858D85DB98B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642F5922-017B-4145-AD3E-47993928C4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -1436,21 +1436,21 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1490,13 +1490,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7528,13 +7528,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
@@ -8039,13 +8039,13 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
+      <c r="A41" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
@@ -8526,13 +8526,13 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="59"/>
-      <c r="C83" s="59"/>
-      <c r="D83" s="59"/>
-      <c r="E83" s="60"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="58"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
@@ -8774,23 +8774,23 @@
       <c r="C3" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="60"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -9427,18 +9427,18 @@
       <c r="C3" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -9479,16 +9479,16 @@
       <c r="A5" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -9817,16 +9817,16 @@
       <c r="A17" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -10055,16 +10055,16 @@
       <c r="A26" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="60"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="58"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -10415,23 +10415,23 @@
       <c r="C41" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
       <c r="F41" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="G41" s="59"/>
-      <c r="H41" s="60"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="58"/>
       <c r="I41" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="J41" s="59"/>
-      <c r="K41" s="60"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="58"/>
       <c r="L41" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="59"/>
-      <c r="N41" s="60"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -10481,19 +10481,19 @@
       <c r="A43" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="60"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
@@ -10917,19 +10917,19 @@
       <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
-      <c r="M55" s="59"/>
-      <c r="N55" s="60"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
@@ -11224,19 +11224,19 @@
       <c r="A64" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="59"/>
-      <c r="C64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
-      <c r="M64" s="59"/>
-      <c r="N64" s="60"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
+      <c r="N64" s="58"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -11680,18 +11680,18 @@
       <c r="C79" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="59"/>
-      <c r="E79" s="60"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="58"/>
       <c r="F79" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="G79" s="59"/>
-      <c r="H79" s="60"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="58"/>
       <c r="I79" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="J79" s="59"/>
-      <c r="K79" s="60"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="58"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
@@ -11732,16 +11732,16 @@
       <c r="A81" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="59"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
-      <c r="E81" s="59"/>
-      <c r="F81" s="59"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="59"/>
-      <c r="J81" s="59"/>
-      <c r="K81" s="60"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="57"/>
+      <c r="I81" s="57"/>
+      <c r="J81" s="57"/>
+      <c r="K81" s="58"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
@@ -12195,16 +12195,16 @@
       <c r="A93" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B93" s="59"/>
-      <c r="C93" s="59"/>
-      <c r="D93" s="59"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="60"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="58"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
@@ -12523,16 +12523,16 @@
       <c r="A102" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B102" s="59"/>
-      <c r="C102" s="59"/>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
-      <c r="F102" s="59"/>
-      <c r="G102" s="59"/>
-      <c r="H102" s="59"/>
-      <c r="I102" s="59"/>
-      <c r="J102" s="59"/>
-      <c r="K102" s="60"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="58"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
@@ -13395,7 +13395,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>160</v>
       </c>
       <c r="B1" s="55"/>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -16668,32 +16668,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -19533,7 +19533,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>248</v>
       </c>
       <c r="B1" s="55"/>
@@ -19560,32 +19560,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -21571,7 +21571,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>271</v>
       </c>
       <c r="B1" s="55"/>
@@ -21598,32 +21598,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -22303,29 +22303,37 @@
       <c r="B16" s="15">
         <v>620</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15" t="str">
+      <c r="C16" s="15">
+        <v>31</v>
+      </c>
+      <c r="D16" s="15">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15" t="str">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="F16" s="15">
+        <v>10</v>
+      </c>
+      <c r="G16" s="15">
+        <v>8</v>
+      </c>
+      <c r="H16" s="15">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="15" t="e">
+        <v>20</v>
+      </c>
+      <c r="K16" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" s="15"/>
@@ -22424,7 +22432,7 @@
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(F18&lt;&gt;"",G18&lt;&gt;""),G18/F18,"")</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -22432,7 +22440,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="4"/>
+        <f>D18-G18</f>
         <v>0</v>
       </c>
       <c r="K18" s="15" t="e">
@@ -22480,7 +22488,7 @@
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(AND(F19&lt;&gt;"",G19&lt;&gt;""),G19/F19,"")</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -22488,7 +22496,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="4"/>
+        <f>D19-G19</f>
         <v>0</v>
       </c>
       <c r="K19" s="15" t="e">
@@ -23503,39 +23511,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>0.8</v>
+        <v>0.82119205298013243</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>0.87096774193548387</v>
+        <v>0.85365853658536583</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>0.7752808988764045</v>
+        <v>0.80909090909090908</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23584,39 +23592,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>0.8</v>
+        <v>0.82119205298013243</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>0.87096774193548387</v>
+        <v>0.85365853658536583</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>0.7752808988764045</v>
+        <v>0.80909090909090908</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
@@ -24174,7 +24182,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
@@ -24204,35 +24212,35 @@
     <row r="2" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="76" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="76" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="55"/>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="76" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
-      <c r="Q3" s="57" t="s">
+      <c r="Q3" s="76" t="s">
         <v>4</v>
       </c>
       <c r="R3" s="55"/>
       <c r="S3" s="55"/>
       <c r="T3" s="55"/>
       <c r="U3" s="55"/>
-      <c r="V3" s="56" t="s">
+      <c r="V3" s="75" t="s">
         <v>5</v>
       </c>
       <c r="W3" s="55"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642F5922-017B-4145-AD3E-47993928C4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52CDD89-50C7-4D31-BE25-350CD2E630F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1469,25 +1469,25 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9406,7 +9406,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="72" t="s">
         <v>127</v>
       </c>
       <c r="B1" s="55"/>
@@ -9424,17 +9424,17 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="67" t="s">
         <v>52</v>
       </c>
       <c r="D3" s="57"/>
       <c r="E3" s="58"/>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="69" t="s">
         <v>106</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="58"/>
-      <c r="I3" s="69" t="s">
+      <c r="I3" s="71" t="s">
         <v>47</v>
       </c>
       <c r="J3" s="57"/>
@@ -10391,7 +10391,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="70" t="s">
         <v>156</v>
       </c>
       <c r="B39" s="55"/>
@@ -10412,22 +10412,22 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="72" t="s">
+      <c r="C41" s="67" t="s">
         <v>52</v>
       </c>
       <c r="D41" s="57"/>
       <c r="E41" s="58"/>
-      <c r="F41" s="70" t="s">
+      <c r="F41" s="69" t="s">
         <v>106</v>
       </c>
       <c r="G41" s="57"/>
       <c r="H41" s="58"/>
-      <c r="I41" s="71" t="s">
+      <c r="I41" s="73" t="s">
         <v>157</v>
       </c>
       <c r="J41" s="57"/>
       <c r="K41" s="58"/>
-      <c r="L41" s="69" t="s">
+      <c r="L41" s="71" t="s">
         <v>47</v>
       </c>
       <c r="M41" s="57"/>
@@ -11659,7 +11659,7 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="70" t="s">
         <v>158</v>
       </c>
       <c r="B77" s="55"/>
@@ -11677,17 +11677,17 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="72" t="s">
+      <c r="C79" s="67" t="s">
         <v>159</v>
       </c>
       <c r="D79" s="57"/>
       <c r="E79" s="58"/>
-      <c r="F79" s="70" t="s">
+      <c r="F79" s="69" t="s">
         <v>156</v>
       </c>
       <c r="G79" s="57"/>
       <c r="H79" s="58"/>
-      <c r="I79" s="69" t="s">
+      <c r="I79" s="71" t="s">
         <v>113</v>
       </c>
       <c r="J79" s="57"/>
@@ -12980,12 +12980,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
@@ -13002,6 +12996,12 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
@@ -16641,7 +16641,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="72" t="s">
         <v>212</v>
       </c>
       <c r="B1" s="55"/>
@@ -22366,30 +22366,40 @@
       <c r="A17" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15" t="str">
+      <c r="B17" s="15">
+        <v>621</v>
+      </c>
+      <c r="C17" s="15">
+        <v>21</v>
+      </c>
+      <c r="D17" s="15">
+        <v>21</v>
+      </c>
+      <c r="E17" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15" t="str">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15">
+        <v>2</v>
+      </c>
+      <c r="G17" s="15">
+        <v>2</v>
+      </c>
+      <c r="H17" s="15">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="15" t="e">
+        <v>19</v>
+      </c>
+      <c r="K17" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" s="15"/>
@@ -23511,39 +23521,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>0.82119205298013243</v>
+        <v>0.84302325581395354</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>0.85365853658536583</v>
+        <v>0.86046511627906974</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>0.80909090909090908</v>
+        <v>0.83720930232558144</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23592,39 +23602,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>0.82119205298013243</v>
+        <v>0.84302325581395354</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>0.85365853658536583</v>
+        <v>0.86046511627906974</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>0.80909090909090908</v>
+        <v>0.83720930232558144</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52CDD89-50C7-4D31-BE25-350CD2E630F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6856F19-2CF2-4B49-A2A4-1DCD57165205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -1436,21 +1436,21 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1490,13 +1490,13 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7528,13 +7528,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
@@ -8039,13 +8039,13 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
@@ -8526,13 +8526,13 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="60" t="s">
+      <c r="A83" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="57"/>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="58"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="60"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
@@ -8774,23 +8774,23 @@
       <c r="C3" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="60"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -9427,18 +9427,18 @@
       <c r="C3" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -9479,16 +9479,16 @@
       <c r="A5" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -9817,16 +9817,16 @@
       <c r="A17" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="58"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -10055,16 +10055,16 @@
       <c r="A26" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="58"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="60"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -10415,23 +10415,23 @@
       <c r="C41" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
       <c r="F41" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G41" s="57"/>
-      <c r="H41" s="58"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="60"/>
       <c r="I41" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="J41" s="57"/>
-      <c r="K41" s="58"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="60"/>
       <c r="L41" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="57"/>
-      <c r="N41" s="58"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="60"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -10481,19 +10481,19 @@
       <c r="A43" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="57"/>
-      <c r="N43" s="58"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="59"/>
+      <c r="K43" s="59"/>
+      <c r="L43" s="59"/>
+      <c r="M43" s="59"/>
+      <c r="N43" s="60"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
@@ -10917,19 +10917,19 @@
       <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="57"/>
-      <c r="C55" s="57"/>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="57"/>
-      <c r="L55" s="57"/>
-      <c r="M55" s="57"/>
-      <c r="N55" s="58"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="59"/>
+      <c r="K55" s="59"/>
+      <c r="L55" s="59"/>
+      <c r="M55" s="59"/>
+      <c r="N55" s="60"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
@@ -11224,19 +11224,19 @@
       <c r="A64" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="57"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
-      <c r="K64" s="57"/>
-      <c r="L64" s="57"/>
-      <c r="M64" s="57"/>
-      <c r="N64" s="58"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="59"/>
+      <c r="L64" s="59"/>
+      <c r="M64" s="59"/>
+      <c r="N64" s="60"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -11680,18 +11680,18 @@
       <c r="C79" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="57"/>
-      <c r="E79" s="58"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="60"/>
       <c r="F79" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="G79" s="57"/>
-      <c r="H79" s="58"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="60"/>
       <c r="I79" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="J79" s="57"/>
-      <c r="K79" s="58"/>
+      <c r="J79" s="59"/>
+      <c r="K79" s="60"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
@@ -11732,16 +11732,16 @@
       <c r="A81" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="57"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
-      <c r="K81" s="58"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="60"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
@@ -12195,16 +12195,16 @@
       <c r="A93" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B93" s="57"/>
-      <c r="C93" s="57"/>
-      <c r="D93" s="57"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="58"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="59"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="59"/>
+      <c r="F93" s="59"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="59"/>
+      <c r="J93" s="59"/>
+      <c r="K93" s="60"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
@@ -12523,16 +12523,16 @@
       <c r="A102" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B102" s="57"/>
-      <c r="C102" s="57"/>
-      <c r="D102" s="57"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="57"/>
-      <c r="I102" s="57"/>
-      <c r="J102" s="57"/>
-      <c r="K102" s="58"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="59"/>
+      <c r="D102" s="59"/>
+      <c r="E102" s="59"/>
+      <c r="F102" s="59"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="59"/>
+      <c r="I102" s="59"/>
+      <c r="J102" s="59"/>
+      <c r="K102" s="60"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
@@ -13395,7 +13395,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>160</v>
       </c>
       <c r="B1" s="55"/>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -16668,32 +16668,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -19533,7 +19533,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>248</v>
       </c>
       <c r="B1" s="55"/>
@@ -19560,32 +19560,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -21571,7 +21571,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>271</v>
       </c>
       <c r="B1" s="55"/>
@@ -21598,32 +21598,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -22432,7 +22432,9 @@
       <c r="A18" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="15">
+        <v>622</v>
+      </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="str">
@@ -24192,7 +24194,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
@@ -24222,35 +24224,35 @@
     <row r="2" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="57" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="55"/>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="57" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
-      <c r="Q3" s="76" t="s">
+      <c r="Q3" s="57" t="s">
         <v>4</v>
       </c>
       <c r="R3" s="55"/>
       <c r="S3" s="55"/>
       <c r="T3" s="55"/>
       <c r="U3" s="55"/>
-      <c r="V3" s="75" t="s">
+      <c r="V3" s="56" t="s">
         <v>5</v>
       </c>
       <c r="W3" s="55"/>
@@ -24682,15 +24684,21 @@
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
+      <c r="Q9" s="48">
+        <v>6.21</v>
+      </c>
+      <c r="R9" s="48">
+        <v>20</v>
+      </c>
       <c r="S9" s="48">
         <v>5</v>
       </c>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48" t="str">
+      <c r="T9" s="48">
+        <v>2</v>
+      </c>
+      <c r="U9" s="48">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="V9" s="48">
         <f t="shared" si="4"/>
@@ -24698,11 +24706,11 @@
       </c>
       <c r="W9" s="48">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X9" s="48">
         <f t="shared" si="6"/>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -25386,11 +25394,11 @@
       </c>
       <c r="T21" s="46">
         <f>SUM(T5:T20)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U21" s="46">
         <f t="shared" si="3"/>
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="V21" s="46">
         <f>SUM(V5:V20)</f>
@@ -25398,11 +25406,11 @@
       </c>
       <c r="W21" s="46">
         <f>SUM(W5:W20)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X21" s="46">
         <f t="shared" si="6"/>
-        <v>5.6250000000000001E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -25460,11 +25468,11 @@
       </c>
       <c r="T23" s="53">
         <f>T21</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U23" s="53">
         <f>IF(AND(S23&lt;&gt;"",T23&lt;&gt;""),T23/S23,"")</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="V23" s="53">
         <f>V21</f>
@@ -25472,11 +25480,11 @@
       </c>
       <c r="W23" s="53">
         <f>W21</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X23" s="53">
         <f>IF(AND(V23&lt;&gt;"",W23&lt;&gt;""),W23/V23,"")</f>
-        <v>5.6250000000000001E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
   </sheetData>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6856F19-2CF2-4B49-A2A4-1DCD57165205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998E818E-94EC-4F71-AF87-7EFB1337A1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -1436,21 +1436,21 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1490,13 +1490,13 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7528,13 +7528,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
@@ -8039,13 +8039,13 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
+      <c r="A41" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
@@ -8526,13 +8526,13 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="59"/>
-      <c r="C83" s="59"/>
-      <c r="D83" s="59"/>
-      <c r="E83" s="60"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="58"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
@@ -8774,23 +8774,23 @@
       <c r="C3" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="60"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -9427,18 +9427,18 @@
       <c r="C3" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -9479,16 +9479,16 @@
       <c r="A5" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -9817,16 +9817,16 @@
       <c r="A17" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -10055,16 +10055,16 @@
       <c r="A26" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="60"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="58"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -10415,23 +10415,23 @@
       <c r="C41" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
       <c r="F41" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G41" s="59"/>
-      <c r="H41" s="60"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="58"/>
       <c r="I41" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="J41" s="59"/>
-      <c r="K41" s="60"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="58"/>
       <c r="L41" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="59"/>
-      <c r="N41" s="60"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -10481,19 +10481,19 @@
       <c r="A43" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="60"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
@@ -10917,19 +10917,19 @@
       <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
-      <c r="M55" s="59"/>
-      <c r="N55" s="60"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
@@ -11224,19 +11224,19 @@
       <c r="A64" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="59"/>
-      <c r="C64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
-      <c r="M64" s="59"/>
-      <c r="N64" s="60"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
+      <c r="N64" s="58"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -11680,18 +11680,18 @@
       <c r="C79" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="59"/>
-      <c r="E79" s="60"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="58"/>
       <c r="F79" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="G79" s="59"/>
-      <c r="H79" s="60"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="58"/>
       <c r="I79" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="J79" s="59"/>
-      <c r="K79" s="60"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="58"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
@@ -11732,16 +11732,16 @@
       <c r="A81" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="59"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
-      <c r="E81" s="59"/>
-      <c r="F81" s="59"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="59"/>
-      <c r="J81" s="59"/>
-      <c r="K81" s="60"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="57"/>
+      <c r="I81" s="57"/>
+      <c r="J81" s="57"/>
+      <c r="K81" s="58"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
@@ -12195,16 +12195,16 @@
       <c r="A93" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B93" s="59"/>
-      <c r="C93" s="59"/>
-      <c r="D93" s="59"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="60"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="58"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
@@ -12523,16 +12523,16 @@
       <c r="A102" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B102" s="59"/>
-      <c r="C102" s="59"/>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
-      <c r="F102" s="59"/>
-      <c r="G102" s="59"/>
-      <c r="H102" s="59"/>
-      <c r="I102" s="59"/>
-      <c r="J102" s="59"/>
-      <c r="K102" s="60"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="58"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
@@ -13395,7 +13395,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>160</v>
       </c>
       <c r="B1" s="55"/>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -16668,32 +16668,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -19533,7 +19533,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>248</v>
       </c>
       <c r="B1" s="55"/>
@@ -19560,32 +19560,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -21571,7 +21571,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>271</v>
       </c>
       <c r="B1" s="55"/>
@@ -21598,32 +21598,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -22435,29 +22435,37 @@
       <c r="B18" s="15">
         <v>622</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15" t="str">
+      <c r="C18" s="15">
+        <v>49</v>
+      </c>
+      <c r="D18" s="15">
+        <v>36</v>
+      </c>
+      <c r="E18" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15" t="str">
+        <v>0.73469387755102045</v>
+      </c>
+      <c r="F18" s="15">
+        <v>13</v>
+      </c>
+      <c r="G18" s="15">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
         <f>IF(AND(F18&lt;&gt;"",G18&lt;&gt;""),G18/F18,"")</f>
-        <v/>
+        <v>0.84615384615384615</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J18" s="15">
         <f>D18-G18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="15" t="e">
+        <v>25</v>
+      </c>
+      <c r="K18" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="15"/>
@@ -22490,30 +22498,40 @@
       <c r="A19" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15" t="str">
+      <c r="B19" s="15">
+        <v>623</v>
+      </c>
+      <c r="C19" s="15">
+        <v>12</v>
+      </c>
+      <c r="D19" s="15">
+        <v>11</v>
+      </c>
+      <c r="E19" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15" t="str">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0</v>
+      </c>
+      <c r="H19" s="15" t="e">
         <f>IF(AND(F19&lt;&gt;"",G19&lt;&gt;""),G19/F19,"")</f>
-        <v/>
+        <v>#DIV/0!</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J19" s="15">
         <f>D19-G19</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="15" t="e">
+        <v>11</v>
+      </c>
+      <c r="K19" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="L19" s="11"/>
       <c r="M19" s="15"/>
@@ -22546,30 +22564,40 @@
       <c r="A20" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15" t="str">
+      <c r="B20" s="15">
+        <v>623</v>
+      </c>
+      <c r="C20" s="15">
+        <v>23</v>
+      </c>
+      <c r="D20" s="15">
+        <v>17</v>
+      </c>
+      <c r="E20" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15" t="str">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="F20" s="15">
+        <v>5</v>
+      </c>
+      <c r="G20" s="15">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="15" t="e">
+        <v>15</v>
+      </c>
+      <c r="K20" s="15">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L20" s="11"/>
       <c r="M20" s="15"/>
@@ -23523,39 +23551,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
-        <v>145</v>
+        <v>209</v>
       </c>
       <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>0.84302325581395354</v>
+        <v>0.81640625</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>0.86046511627906974</v>
+        <v>0.81967213114754101</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>0.83720930232558144</v>
+        <v>0.81538461538461537</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23604,39 +23632,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
-        <v>145</v>
+        <v>209</v>
       </c>
       <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>0.84302325581395354</v>
+        <v>0.81640625</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>0.86046511627906974</v>
+        <v>0.81967213114754101</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>0.83720930232558144</v>
+        <v>0.81538461538461537</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
@@ -24194,7 +24222,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
@@ -24224,35 +24252,35 @@
     <row r="2" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="76" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="76" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="55"/>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="76" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
-      <c r="Q3" s="57" t="s">
+      <c r="Q3" s="76" t="s">
         <v>4</v>
       </c>
       <c r="R3" s="55"/>
       <c r="S3" s="55"/>
       <c r="T3" s="55"/>
       <c r="U3" s="55"/>
-      <c r="V3" s="56" t="s">
+      <c r="V3" s="75" t="s">
         <v>5</v>
       </c>
       <c r="W3" s="55"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998E818E-94EC-4F71-AF87-7EFB1337A1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25E65FD-ACCF-4829-BF0F-671B52A6811B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -390,581 +390,582 @@
     <t>选择题</t>
   </si>
   <si>
+    <t>问答题</t>
+  </si>
+  <si>
+    <t>第一章 函数 极限 连续</t>
+  </si>
+  <si>
+    <t>第二章 一元函数微分学</t>
+  </si>
+  <si>
+    <t>第三章 一元函数积分学</t>
+  </si>
+  <si>
+    <t>第四章 常微分方程</t>
+  </si>
+  <si>
+    <t>第五章 多元函数微分学</t>
+  </si>
+  <si>
+    <t>第六章 二重积分</t>
+  </si>
+  <si>
+    <t>第七章 无穷级数 (仅数学一、三)</t>
+  </si>
+  <si>
+    <t>第八章 向量代数与空间解析几何及多元微分学在几何上的应用 (仅数学一)</t>
+  </si>
+  <si>
+    <t>第九章 多元函数积分学及其应用 (仅数学一)</t>
+  </si>
+  <si>
+    <t>李林880 （选择&amp;填空）习题正确率记录</t>
+  </si>
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>第一章 函数、极限、连续</t>
+  </si>
+  <si>
+    <t>第二章 一元函数微分学及其应用</t>
+  </si>
+  <si>
+    <t>第三章 一元函数积分学及其应用</t>
+  </si>
+  <si>
+    <t>第四章 空间解析几何</t>
+  </si>
+  <si>
+    <t>第五章 多元函数微分学及其应用</t>
+  </si>
+  <si>
+    <t>第六章 重积分及其应用</t>
+  </si>
+  <si>
+    <t>第七章 微分方程及其应用</t>
+  </si>
+  <si>
+    <t>第八章 无穷级数</t>
+  </si>
+  <si>
+    <t>第九章 曲线积分与曲面积分</t>
+  </si>
+  <si>
+    <t>高等数学 合计</t>
+  </si>
+  <si>
+    <t>第十章 行列式</t>
+  </si>
+  <si>
+    <t>第十一章 矩阵</t>
+  </si>
+  <si>
+    <t>第十二章 向量</t>
+  </si>
+  <si>
+    <t>第十三章 线性方程组</t>
+  </si>
+  <si>
+    <t>第十四章 相似矩阵</t>
+  </si>
+  <si>
+    <t>第十五章 二次型</t>
+  </si>
+  <si>
+    <t>线性代数 合计</t>
+  </si>
+  <si>
+    <t>第十六章 随机事件及其概率</t>
+  </si>
+  <si>
+    <t>第十七章 随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第十八章 多维随机变量及其分布</t>
+  </si>
+  <si>
+    <t>第十九章 随机变量的数字特征</t>
+  </si>
+  <si>
+    <t>第二十章 大数定律与中心极限定理</t>
+  </si>
+  <si>
+    <t>第二十一章 数理统计的基本概念</t>
+  </si>
+  <si>
+    <t>第二十二章 参数估计</t>
+  </si>
+  <si>
+    <t>第二十三章 假设检验</t>
+  </si>
+  <si>
+    <t>概率论与数理统计 合计</t>
+  </si>
+  <si>
+    <t>总 计</t>
+  </si>
+  <si>
+    <t>解答区</t>
+  </si>
+  <si>
+    <t>扩展篇</t>
+  </si>
+  <si>
+    <t>选填+解答总计区</t>
+  </si>
+  <si>
+    <t>选填区</t>
+  </si>
+  <si>
+    <t>王道数据结构 课后习题正确率记录</t>
+  </si>
+  <si>
+    <t>一 刷</t>
+  </si>
+  <si>
+    <t>二 刷</t>
+  </si>
+  <si>
+    <t>小节</t>
+  </si>
+  <si>
+    <t>真题总</t>
+  </si>
+  <si>
+    <t>真题正</t>
+  </si>
+  <si>
+    <t>真题率</t>
+  </si>
+  <si>
+    <t>自编总</t>
+  </si>
+  <si>
+    <t>自编正</t>
+  </si>
+  <si>
+    <t>自编率</t>
+  </si>
+  <si>
+    <t>第1章 绪论</t>
+  </si>
+  <si>
+    <t>1.1 数据结构的基本概念</t>
+  </si>
+  <si>
+    <t>1.2 算法和算法评价</t>
+  </si>
+  <si>
+    <t>第2章 线性表</t>
+  </si>
+  <si>
+    <t>2.1 线性表的定义和基本操作</t>
+  </si>
+  <si>
+    <t>2.2 线性表的顺序表示</t>
+  </si>
+  <si>
+    <t>2.3 线性表的链式表示</t>
+  </si>
+  <si>
+    <t>第3章 栈、队列和数组</t>
+  </si>
+  <si>
+    <t>3.1 栈</t>
+  </si>
+  <si>
+    <t>3.2 队列</t>
+  </si>
+  <si>
+    <t>3.3 栈和队列的应用</t>
+  </si>
+  <si>
+    <t>3.4 数组和特殊矩阵</t>
+  </si>
+  <si>
+    <t>第4章 串</t>
+  </si>
+  <si>
+    <t>4.1 串的定义和实现</t>
+  </si>
+  <si>
+    <t>4.2 串的模式匹配</t>
+  </si>
+  <si>
+    <t>第5章 树与二叉树</t>
+  </si>
+  <si>
+    <t>5.1 树的基本概念</t>
+  </si>
+  <si>
+    <t>5.2 二叉树的概念</t>
+  </si>
+  <si>
+    <t>5.3 二叉树的遍历和线索二叉树</t>
+  </si>
+  <si>
+    <t>5.4 树、森林</t>
+  </si>
+  <si>
+    <t>5.5 树与二叉树的应用</t>
+  </si>
+  <si>
+    <t>第6章 图</t>
+  </si>
+  <si>
+    <t>6.1 图的基本概念</t>
+  </si>
+  <si>
+    <t>6.2 图的存储及基本操作</t>
+  </si>
+  <si>
+    <t>6.3 图的遍历</t>
+  </si>
+  <si>
+    <t>6.4 图的应用</t>
+  </si>
+  <si>
+    <t>第7章 查找</t>
+  </si>
+  <si>
+    <t>7.1 查找的基本概念</t>
+  </si>
+  <si>
+    <t>7.2 顺序查找和折半查找</t>
+  </si>
+  <si>
+    <t>7.3 树形查找</t>
+  </si>
+  <si>
+    <t>未包含红黑树</t>
+  </si>
+  <si>
+    <t>7.4 B树和B+树</t>
+  </si>
+  <si>
+    <t>7.5 散列(Hash)表</t>
+  </si>
+  <si>
+    <t>第8章 排序</t>
+  </si>
+  <si>
+    <t>8.1 排序的基本概念</t>
+  </si>
+  <si>
+    <t>8.2 插入排序</t>
+  </si>
+  <si>
+    <t>8.3 交换排序</t>
+  </si>
+  <si>
+    <t>8.4 选择排序</t>
+  </si>
+  <si>
+    <t>8.5 归并排序、基数排序和计数排序</t>
+  </si>
+  <si>
+    <t>8.6 各种内部排序算法的比较及应用</t>
+  </si>
+  <si>
+    <t>未完成</t>
+  </si>
+  <si>
+    <t>8.7 外部排序</t>
+  </si>
+  <si>
+    <t>王道计算机组成原理 课后习题正确率记录</t>
+  </si>
+  <si>
+    <t>第1章 计算机系统概述</t>
+  </si>
+  <si>
+    <t>1.1 计算机发展历程</t>
+  </si>
+  <si>
+    <t>1.2 计算机系统层次结构</t>
+  </si>
+  <si>
+    <t>1.3 计算机的性能指标</t>
+  </si>
+  <si>
+    <t>第2章 数据的表示和运算</t>
+  </si>
+  <si>
+    <t>2.1 数制与编码</t>
+  </si>
+  <si>
+    <t>2.2 运算方法和运算电路</t>
+  </si>
+  <si>
+    <t>2.3 浮点数的表示与运算</t>
+  </si>
+  <si>
+    <t>第3章 存储系统</t>
+  </si>
+  <si>
+    <t>3.1 存储器概述</t>
+  </si>
+  <si>
+    <t>3.2 主存储器</t>
+  </si>
+  <si>
+    <t>3.3 主存储器与CPU的连接</t>
+  </si>
+  <si>
+    <t>3.4 外部存储器</t>
+  </si>
+  <si>
+    <t>3.5 高速缓冲存储器</t>
+  </si>
+  <si>
+    <t>3.6 虚拟存储器</t>
+  </si>
+  <si>
+    <t>第4章 指令系统</t>
+  </si>
+  <si>
+    <t>4.1 指令系统</t>
+  </si>
+  <si>
+    <t>4.2 寻址方式</t>
+  </si>
+  <si>
+    <t>4.3 程序的机器级代码表示</t>
+  </si>
+  <si>
+    <t>4.4 CISC和RISC的基本概念</t>
+  </si>
+  <si>
+    <t>第5章 中央处理器</t>
+  </si>
+  <si>
+    <t>5.1 CPU的功能和基本结构</t>
+  </si>
+  <si>
+    <t>5.2 指令执行过程</t>
+  </si>
+  <si>
+    <t>5.3 数据通路的功能和基本结构</t>
+  </si>
+  <si>
+    <t>5.4 控制器的功能和工作原理</t>
+  </si>
+  <si>
+    <t>5.5 异常和中断机制</t>
+  </si>
+  <si>
+    <t>5.6 指令流水线</t>
+  </si>
+  <si>
+    <t>5.7 多处理器的基本概念</t>
+  </si>
+  <si>
+    <t>第6章 总线</t>
+  </si>
+  <si>
+    <t>6.1 总线概述</t>
+  </si>
+  <si>
+    <t>6.2 总线事务和定时</t>
+  </si>
+  <si>
+    <t>第7章 输入/输出系统</t>
+  </si>
+  <si>
+    <t>7.1 I/O系统基本概念</t>
+  </si>
+  <si>
+    <t>7.2 I/O接口</t>
+  </si>
+  <si>
+    <t>7.3 I/O方式</t>
+  </si>
+  <si>
+    <t>王道操作系统 课后习题正确率记录</t>
+  </si>
+  <si>
+    <t>1.1 操作系统的基本概念</t>
+  </si>
+  <si>
+    <t>1.2 操作系统发展历程</t>
+  </si>
+  <si>
+    <t>1.3 操作系统的运行环境</t>
+  </si>
+  <si>
+    <t>1.4 操作系统结构</t>
+  </si>
+  <si>
+    <t>1.5 操作系统引导</t>
+  </si>
+  <si>
+    <t>1.6 虚拟机</t>
+  </si>
+  <si>
+    <t>第2章 进程与线程</t>
+  </si>
+  <si>
+    <t>2.1 进程与线程简介</t>
+  </si>
+  <si>
+    <t>2.2 CPU调度</t>
+  </si>
+  <si>
+    <t>2.3 同步与互斥</t>
+  </si>
+  <si>
+    <t>2.4 死锁</t>
+  </si>
+  <si>
+    <t>第3章 内存管理</t>
+  </si>
+  <si>
+    <t>3.1 内存管理概念</t>
+  </si>
+  <si>
+    <t>3.2 虚拟内存管理</t>
+  </si>
+  <si>
+    <t>第4章 文件管理</t>
+  </si>
+  <si>
+    <t>4.1 文件系统基础</t>
+  </si>
+  <si>
+    <t>4.2 目录与文件</t>
+  </si>
+  <si>
+    <t>4.3 文件系统</t>
+  </si>
+  <si>
+    <t>第5章 输入/输出管理</t>
+  </si>
+  <si>
+    <t>5.1 I/O管理概述</t>
+  </si>
+  <si>
+    <t>5.2 设备独立性软件</t>
+  </si>
+  <si>
+    <t>5.3 磁盘和固态硬盘</t>
+  </si>
+  <si>
+    <t>王道计算机网络 课后习题正确率记录</t>
+  </si>
+  <si>
+    <t>第1章 计算机网络体系结构</t>
+  </si>
+  <si>
+    <t>1.1 计算机网络概述</t>
+  </si>
+  <si>
+    <t>1.2 计算机网络体系结构与参考模型</t>
+  </si>
+  <si>
+    <t>第2章 物理层</t>
+  </si>
+  <si>
+    <t>2.1 通信基础</t>
+  </si>
+  <si>
+    <t>2.2 传输介质</t>
+  </si>
+  <si>
+    <t>2.3 物理层设备</t>
+  </si>
+  <si>
+    <t>第3章 数据链路层</t>
+  </si>
+  <si>
+    <t>3.1 数据链路层的功能</t>
+  </si>
+  <si>
+    <t>3.2 组帧</t>
+  </si>
+  <si>
+    <t>3.3 差错控制</t>
+  </si>
+  <si>
+    <t>3.4 流量控制与可靠传输机制</t>
+  </si>
+  <si>
+    <t>3.5 介质访问控制</t>
+  </si>
+  <si>
+    <t>3.6 局域网</t>
+  </si>
+  <si>
+    <t>3.7 广域网</t>
+  </si>
+  <si>
+    <t>3.8 数据链路层设备</t>
+  </si>
+  <si>
+    <t>第4章 网络层</t>
+  </si>
+  <si>
+    <t>4.1 网络层的功能</t>
+  </si>
+  <si>
+    <t>4.2 IPv4</t>
+  </si>
+  <si>
+    <t>4.3 IPv6</t>
+  </si>
+  <si>
+    <t>4.4 路由算法与路由协议</t>
+  </si>
+  <si>
+    <t>4.5 IP多播</t>
+  </si>
+  <si>
+    <t>4.6 移动IP</t>
+  </si>
+  <si>
+    <t>4.7 网络层设备</t>
+  </si>
+  <si>
+    <t>第5章 传输层</t>
+  </si>
+  <si>
+    <t>5.1 传输层提供的服务</t>
+  </si>
+  <si>
+    <t>5.2 UDP</t>
+  </si>
+  <si>
+    <t>5.3 TCP</t>
+  </si>
+  <si>
+    <t>第6章 应用层</t>
+  </si>
+  <si>
+    <t>6.1 网络应用模型</t>
+  </si>
+  <si>
+    <t>6.2 域名系统</t>
+  </si>
+  <si>
+    <t>6.3 文件传输协议</t>
+  </si>
+  <si>
+    <t>6.4 电子邮件</t>
+  </si>
+  <si>
+    <t>6.5 万维网</t>
+  </si>
+  <si>
     <t>填空题</t>
-  </si>
-  <si>
-    <t>问答题</t>
-  </si>
-  <si>
-    <t>第一章 函数 极限 连续</t>
-  </si>
-  <si>
-    <t>第二章 一元函数微分学</t>
-  </si>
-  <si>
-    <t>第三章 一元函数积分学</t>
-  </si>
-  <si>
-    <t>第四章 常微分方程</t>
-  </si>
-  <si>
-    <t>第五章 多元函数微分学</t>
-  </si>
-  <si>
-    <t>第六章 二重积分</t>
-  </si>
-  <si>
-    <t>第七章 无穷级数 (仅数学一、三)</t>
-  </si>
-  <si>
-    <t>第八章 向量代数与空间解析几何及多元微分学在几何上的应用 (仅数学一)</t>
-  </si>
-  <si>
-    <t>第九章 多元函数积分学及其应用 (仅数学一)</t>
-  </si>
-  <si>
-    <t>李林880 （选择&amp;填空）习题正确率记录</t>
-  </si>
-  <si>
-    <t>时间</t>
-  </si>
-  <si>
-    <t>第一章 函数、极限、连续</t>
-  </si>
-  <si>
-    <t>第二章 一元函数微分学及其应用</t>
-  </si>
-  <si>
-    <t>第三章 一元函数积分学及其应用</t>
-  </si>
-  <si>
-    <t>第四章 空间解析几何</t>
-  </si>
-  <si>
-    <t>第五章 多元函数微分学及其应用</t>
-  </si>
-  <si>
-    <t>第六章 重积分及其应用</t>
-  </si>
-  <si>
-    <t>第七章 微分方程及其应用</t>
-  </si>
-  <si>
-    <t>第八章 无穷级数</t>
-  </si>
-  <si>
-    <t>第九章 曲线积分与曲面积分</t>
-  </si>
-  <si>
-    <t>高等数学 合计</t>
-  </si>
-  <si>
-    <t>第十章 行列式</t>
-  </si>
-  <si>
-    <t>第十一章 矩阵</t>
-  </si>
-  <si>
-    <t>第十二章 向量</t>
-  </si>
-  <si>
-    <t>第十三章 线性方程组</t>
-  </si>
-  <si>
-    <t>第十四章 相似矩阵</t>
-  </si>
-  <si>
-    <t>第十五章 二次型</t>
-  </si>
-  <si>
-    <t>线性代数 合计</t>
-  </si>
-  <si>
-    <t>第十六章 随机事件及其概率</t>
-  </si>
-  <si>
-    <t>第十七章 随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第十八章 多维随机变量及其分布</t>
-  </si>
-  <si>
-    <t>第十九章 随机变量的数字特征</t>
-  </si>
-  <si>
-    <t>第二十章 大数定律与中心极限定理</t>
-  </si>
-  <si>
-    <t>第二十一章 数理统计的基本概念</t>
-  </si>
-  <si>
-    <t>第二十二章 参数估计</t>
-  </si>
-  <si>
-    <t>第二十三章 假设检验</t>
-  </si>
-  <si>
-    <t>概率论与数理统计 合计</t>
-  </si>
-  <si>
-    <t>总 计</t>
-  </si>
-  <si>
-    <t>解答区</t>
-  </si>
-  <si>
-    <t>扩展篇</t>
-  </si>
-  <si>
-    <t>选填+解答总计区</t>
-  </si>
-  <si>
-    <t>选填区</t>
-  </si>
-  <si>
-    <t>王道数据结构 课后习题正确率记录</t>
-  </si>
-  <si>
-    <t>一 刷</t>
-  </si>
-  <si>
-    <t>二 刷</t>
-  </si>
-  <si>
-    <t>小节</t>
-  </si>
-  <si>
-    <t>真题总</t>
-  </si>
-  <si>
-    <t>真题正</t>
-  </si>
-  <si>
-    <t>真题率</t>
-  </si>
-  <si>
-    <t>自编总</t>
-  </si>
-  <si>
-    <t>自编正</t>
-  </si>
-  <si>
-    <t>自编率</t>
-  </si>
-  <si>
-    <t>第1章 绪论</t>
-  </si>
-  <si>
-    <t>1.1 数据结构的基本概念</t>
-  </si>
-  <si>
-    <t>1.2 算法和算法评价</t>
-  </si>
-  <si>
-    <t>第2章 线性表</t>
-  </si>
-  <si>
-    <t>2.1 线性表的定义和基本操作</t>
-  </si>
-  <si>
-    <t>2.2 线性表的顺序表示</t>
-  </si>
-  <si>
-    <t>2.3 线性表的链式表示</t>
-  </si>
-  <si>
-    <t>第3章 栈、队列和数组</t>
-  </si>
-  <si>
-    <t>3.1 栈</t>
-  </si>
-  <si>
-    <t>3.2 队列</t>
-  </si>
-  <si>
-    <t>3.3 栈和队列的应用</t>
-  </si>
-  <si>
-    <t>3.4 数组和特殊矩阵</t>
-  </si>
-  <si>
-    <t>第4章 串</t>
-  </si>
-  <si>
-    <t>4.1 串的定义和实现</t>
-  </si>
-  <si>
-    <t>4.2 串的模式匹配</t>
-  </si>
-  <si>
-    <t>第5章 树与二叉树</t>
-  </si>
-  <si>
-    <t>5.1 树的基本概念</t>
-  </si>
-  <si>
-    <t>5.2 二叉树的概念</t>
-  </si>
-  <si>
-    <t>5.3 二叉树的遍历和线索二叉树</t>
-  </si>
-  <si>
-    <t>5.4 树、森林</t>
-  </si>
-  <si>
-    <t>5.5 树与二叉树的应用</t>
-  </si>
-  <si>
-    <t>第6章 图</t>
-  </si>
-  <si>
-    <t>6.1 图的基本概念</t>
-  </si>
-  <si>
-    <t>6.2 图的存储及基本操作</t>
-  </si>
-  <si>
-    <t>6.3 图的遍历</t>
-  </si>
-  <si>
-    <t>6.4 图的应用</t>
-  </si>
-  <si>
-    <t>第7章 查找</t>
-  </si>
-  <si>
-    <t>7.1 查找的基本概念</t>
-  </si>
-  <si>
-    <t>7.2 顺序查找和折半查找</t>
-  </si>
-  <si>
-    <t>7.3 树形查找</t>
-  </si>
-  <si>
-    <t>未包含红黑树</t>
-  </si>
-  <si>
-    <t>7.4 B树和B+树</t>
-  </si>
-  <si>
-    <t>7.5 散列(Hash)表</t>
-  </si>
-  <si>
-    <t>第8章 排序</t>
-  </si>
-  <si>
-    <t>8.1 排序的基本概念</t>
-  </si>
-  <si>
-    <t>8.2 插入排序</t>
-  </si>
-  <si>
-    <t>8.3 交换排序</t>
-  </si>
-  <si>
-    <t>8.4 选择排序</t>
-  </si>
-  <si>
-    <t>8.5 归并排序、基数排序和计数排序</t>
-  </si>
-  <si>
-    <t>8.6 各种内部排序算法的比较及应用</t>
-  </si>
-  <si>
-    <t>未完成</t>
-  </si>
-  <si>
-    <t>8.7 外部排序</t>
-  </si>
-  <si>
-    <t>王道计算机组成原理 课后习题正确率记录</t>
-  </si>
-  <si>
-    <t>第1章 计算机系统概述</t>
-  </si>
-  <si>
-    <t>1.1 计算机发展历程</t>
-  </si>
-  <si>
-    <t>1.2 计算机系统层次结构</t>
-  </si>
-  <si>
-    <t>1.3 计算机的性能指标</t>
-  </si>
-  <si>
-    <t>第2章 数据的表示和运算</t>
-  </si>
-  <si>
-    <t>2.1 数制与编码</t>
-  </si>
-  <si>
-    <t>2.2 运算方法和运算电路</t>
-  </si>
-  <si>
-    <t>2.3 浮点数的表示与运算</t>
-  </si>
-  <si>
-    <t>第3章 存储系统</t>
-  </si>
-  <si>
-    <t>3.1 存储器概述</t>
-  </si>
-  <si>
-    <t>3.2 主存储器</t>
-  </si>
-  <si>
-    <t>3.3 主存储器与CPU的连接</t>
-  </si>
-  <si>
-    <t>3.4 外部存储器</t>
-  </si>
-  <si>
-    <t>3.5 高速缓冲存储器</t>
-  </si>
-  <si>
-    <t>3.6 虚拟存储器</t>
-  </si>
-  <si>
-    <t>第4章 指令系统</t>
-  </si>
-  <si>
-    <t>4.1 指令系统</t>
-  </si>
-  <si>
-    <t>4.2 寻址方式</t>
-  </si>
-  <si>
-    <t>4.3 程序的机器级代码表示</t>
-  </si>
-  <si>
-    <t>4.4 CISC和RISC的基本概念</t>
-  </si>
-  <si>
-    <t>第5章 中央处理器</t>
-  </si>
-  <si>
-    <t>5.1 CPU的功能和基本结构</t>
-  </si>
-  <si>
-    <t>5.2 指令执行过程</t>
-  </si>
-  <si>
-    <t>5.3 数据通路的功能和基本结构</t>
-  </si>
-  <si>
-    <t>5.4 控制器的功能和工作原理</t>
-  </si>
-  <si>
-    <t>5.5 异常和中断机制</t>
-  </si>
-  <si>
-    <t>5.6 指令流水线</t>
-  </si>
-  <si>
-    <t>5.7 多处理器的基本概念</t>
-  </si>
-  <si>
-    <t>第6章 总线</t>
-  </si>
-  <si>
-    <t>6.1 总线概述</t>
-  </si>
-  <si>
-    <t>6.2 总线事务和定时</t>
-  </si>
-  <si>
-    <t>第7章 输入/输出系统</t>
-  </si>
-  <si>
-    <t>7.1 I/O系统基本概念</t>
-  </si>
-  <si>
-    <t>7.2 I/O接口</t>
-  </si>
-  <si>
-    <t>7.3 I/O方式</t>
-  </si>
-  <si>
-    <t>王道操作系统 课后习题正确率记录</t>
-  </si>
-  <si>
-    <t>1.1 操作系统的基本概念</t>
-  </si>
-  <si>
-    <t>1.2 操作系统发展历程</t>
-  </si>
-  <si>
-    <t>1.3 操作系统的运行环境</t>
-  </si>
-  <si>
-    <t>1.4 操作系统结构</t>
-  </si>
-  <si>
-    <t>1.5 操作系统引导</t>
-  </si>
-  <si>
-    <t>1.6 虚拟机</t>
-  </si>
-  <si>
-    <t>第2章 进程与线程</t>
-  </si>
-  <si>
-    <t>2.1 进程与线程简介</t>
-  </si>
-  <si>
-    <t>2.2 CPU调度</t>
-  </si>
-  <si>
-    <t>2.3 同步与互斥</t>
-  </si>
-  <si>
-    <t>2.4 死锁</t>
-  </si>
-  <si>
-    <t>第3章 内存管理</t>
-  </si>
-  <si>
-    <t>3.1 内存管理概念</t>
-  </si>
-  <si>
-    <t>3.2 虚拟内存管理</t>
-  </si>
-  <si>
-    <t>第4章 文件管理</t>
-  </si>
-  <si>
-    <t>4.1 文件系统基础</t>
-  </si>
-  <si>
-    <t>4.2 目录与文件</t>
-  </si>
-  <si>
-    <t>4.3 文件系统</t>
-  </si>
-  <si>
-    <t>第5章 输入/输出管理</t>
-  </si>
-  <si>
-    <t>5.1 I/O管理概述</t>
-  </si>
-  <si>
-    <t>5.2 设备独立性软件</t>
-  </si>
-  <si>
-    <t>5.3 磁盘和固态硬盘</t>
-  </si>
-  <si>
-    <t>王道计算机网络 课后习题正确率记录</t>
-  </si>
-  <si>
-    <t>第1章 计算机网络体系结构</t>
-  </si>
-  <si>
-    <t>1.1 计算机网络概述</t>
-  </si>
-  <si>
-    <t>1.2 计算机网络体系结构与参考模型</t>
-  </si>
-  <si>
-    <t>第2章 物理层</t>
-  </si>
-  <si>
-    <t>2.1 通信基础</t>
-  </si>
-  <si>
-    <t>2.2 传输介质</t>
-  </si>
-  <si>
-    <t>2.3 物理层设备</t>
-  </si>
-  <si>
-    <t>第3章 数据链路层</t>
-  </si>
-  <si>
-    <t>3.1 数据链路层的功能</t>
-  </si>
-  <si>
-    <t>3.2 组帧</t>
-  </si>
-  <si>
-    <t>3.3 差错控制</t>
-  </si>
-  <si>
-    <t>3.4 流量控制与可靠传输机制</t>
-  </si>
-  <si>
-    <t>3.5 介质访问控制</t>
-  </si>
-  <si>
-    <t>3.6 局域网</t>
-  </si>
-  <si>
-    <t>3.7 广域网</t>
-  </si>
-  <si>
-    <t>3.8 数据链路层设备</t>
-  </si>
-  <si>
-    <t>第4章 网络层</t>
-  </si>
-  <si>
-    <t>4.1 网络层的功能</t>
-  </si>
-  <si>
-    <t>4.2 IPv4</t>
-  </si>
-  <si>
-    <t>4.3 IPv6</t>
-  </si>
-  <si>
-    <t>4.4 路由算法与路由协议</t>
-  </si>
-  <si>
-    <t>4.5 IP多播</t>
-  </si>
-  <si>
-    <t>4.6 移动IP</t>
-  </si>
-  <si>
-    <t>4.7 网络层设备</t>
-  </si>
-  <si>
-    <t>第5章 传输层</t>
-  </si>
-  <si>
-    <t>5.1 传输层提供的服务</t>
-  </si>
-  <si>
-    <t>5.2 UDP</t>
-  </si>
-  <si>
-    <t>5.3 TCP</t>
-  </si>
-  <si>
-    <t>第6章 应用层</t>
-  </si>
-  <si>
-    <t>6.1 网络应用模型</t>
-  </si>
-  <si>
-    <t>6.2 域名系统</t>
-  </si>
-  <si>
-    <t>6.3 文件传输协议</t>
-  </si>
-  <si>
-    <t>6.4 电子邮件</t>
-  </si>
-  <si>
-    <t>6.5 万维网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1110,6 +1111,13 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1466,28 +1474,28 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -8777,12 +8785,12 @@
       <c r="D3" s="57"/>
       <c r="E3" s="58"/>
       <c r="F3" s="66" t="s">
-        <v>116</v>
+        <v>305</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="58"/>
       <c r="I3" s="65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
@@ -8838,7 +8846,7 @@
     </row>
     <row r="5" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B5" s="34">
         <v>618</v>
@@ -8888,43 +8896,57 @@
     </row>
     <row r="6" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34" t="str">
+        <v>118</v>
+      </c>
+      <c r="B6" s="34">
+        <v>624</v>
+      </c>
+      <c r="C6" s="34">
+        <v>17</v>
+      </c>
+      <c r="D6" s="34">
+        <v>14</v>
+      </c>
+      <c r="E6" s="34">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34" t="str">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="F6" s="34">
+        <v>11</v>
+      </c>
+      <c r="G6" s="34">
+        <v>10</v>
+      </c>
+      <c r="H6" s="34">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34" t="str">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="I6" s="34">
+        <v>26</v>
+      </c>
+      <c r="J6" s="34">
+        <v>15</v>
+      </c>
+      <c r="K6" s="34">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.57692307692307687</v>
       </c>
       <c r="L6" s="34">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M6" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="34" t="e">
+        <v>39</v>
+      </c>
+      <c r="N6" s="34">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
@@ -8960,7 +8982,7 @@
     </row>
     <row r="8" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -8996,7 +9018,7 @@
     </row>
     <row r="9" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -9032,7 +9054,7 @@
     </row>
     <row r="10" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -9068,7 +9090,7 @@
     </row>
     <row r="11" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -9104,7 +9126,7 @@
     </row>
     <row r="12" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -9140,7 +9162,7 @@
     </row>
     <row r="13" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -9181,51 +9203,51 @@
       <c r="B14" s="36"/>
       <c r="C14" s="37">
         <f>SUM(C5:C13)</f>
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D14" s="37">
         <f>SUM(D5:D13)</f>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E14" s="37">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="F14" s="37">
         <f>SUM(F5:F13)</f>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G14" s="37">
         <f>SUM(G5:G13)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H14" s="37">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="I14" s="37">
         <f>SUM(I5:I13)</f>
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J14" s="37">
         <f>SUM(J5:J13)</f>
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K14" s="37">
         <f t="shared" si="2"/>
-        <v>0.91304347826086951</v>
+        <v>0.73469387755102045</v>
       </c>
       <c r="L14" s="37">
         <f>SUM(L5:L13)</f>
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="M14" s="37">
         <f>SUM(M5:M13)</f>
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="N14" s="37">
         <f t="shared" si="5"/>
-        <v>0.87755102040816324</v>
+        <v>0.79611650485436891</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9236,51 +9258,51 @@
       <c r="B16" s="39"/>
       <c r="C16" s="40">
         <f>C14</f>
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D16" s="40">
         <f>D14</f>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="40">
         <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;""),D16/C16,"")</f>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="F16" s="40">
         <f>F14</f>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G16" s="40">
         <f>G14</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H16" s="40">
         <f>IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),G16/F16,"")</f>
-        <v>1</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="I16" s="40">
         <f>I14</f>
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J16" s="40">
         <f>J14</f>
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K16" s="40">
         <f>IF(AND(I16&lt;&gt;"",J16&lt;&gt;""),J16/I16,"")</f>
-        <v>0.91304347826086951</v>
+        <v>0.73469387755102045</v>
       </c>
       <c r="L16" s="40">
         <f>L14</f>
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="M16" s="40">
         <f>M14</f>
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="N16" s="40">
         <f>IF(AND(L16&lt;&gt;"",M16&lt;&gt;""),M16/L16,"")</f>
-        <v>0.87755102040816324</v>
+        <v>0.79611650485436891</v>
       </c>
     </row>
   </sheetData>
@@ -9406,8 +9428,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>127</v>
+      <c r="A1" s="67" t="s">
+        <v>126</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -9424,17 +9446,17 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="72" t="s">
         <v>52</v>
       </c>
       <c r="D3" s="57"/>
       <c r="E3" s="58"/>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="70" t="s">
         <v>106</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="58"/>
-      <c r="I3" s="71" t="s">
+      <c r="I3" s="69" t="s">
         <v>47</v>
       </c>
       <c r="J3" s="57"/>
@@ -9445,7 +9467,7 @@
         <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -9492,7 +9514,7 @@
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="4">
         <v>618</v>
@@ -9532,7 +9554,7 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -9562,7 +9584,7 @@
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -9592,7 +9614,7 @@
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -9622,7 +9644,7 @@
     </row>
     <row r="10" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -9652,7 +9674,7 @@
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -9682,7 +9704,7 @@
     </row>
     <row r="12" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -9712,7 +9734,7 @@
     </row>
     <row r="13" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -9742,7 +9764,7 @@
     </row>
     <row r="14" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -9772,7 +9794,7 @@
     </row>
     <row r="15" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7">
@@ -9830,7 +9852,7 @@
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -9860,7 +9882,7 @@
     </row>
     <row r="19" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -9890,7 +9912,7 @@
     </row>
     <row r="20" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -9920,7 +9942,7 @@
     </row>
     <row r="21" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -9950,7 +9972,7 @@
     </row>
     <row r="22" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -9980,7 +10002,7 @@
     </row>
     <row r="23" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -10010,7 +10032,7 @@
     </row>
     <row r="24" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7">
@@ -10068,7 +10090,7 @@
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -10098,7 +10120,7 @@
     </row>
     <row r="28" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -10128,7 +10150,7 @@
     </row>
     <row r="29" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -10158,7 +10180,7 @@
     </row>
     <row r="30" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -10188,7 +10210,7 @@
     </row>
     <row r="31" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -10218,7 +10240,7 @@
     </row>
     <row r="32" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -10248,7 +10270,7 @@
     </row>
     <row r="33" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -10278,7 +10300,7 @@
     </row>
     <row r="34" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -10308,7 +10330,7 @@
     </row>
     <row r="35" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="7">
@@ -10350,7 +10372,7 @@
     </row>
     <row r="36" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="10">
@@ -10391,8 +10413,8 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="70" t="s">
-        <v>156</v>
+      <c r="A39" s="73" t="s">
+        <v>155</v>
       </c>
       <c r="B39" s="55"/>
       <c r="C39" s="55"/>
@@ -10412,22 +10434,22 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="67" t="s">
+      <c r="C41" s="72" t="s">
         <v>52</v>
       </c>
       <c r="D41" s="57"/>
       <c r="E41" s="58"/>
-      <c r="F41" s="69" t="s">
+      <c r="F41" s="70" t="s">
         <v>106</v>
       </c>
       <c r="G41" s="57"/>
       <c r="H41" s="58"/>
-      <c r="I41" s="73" t="s">
-        <v>157</v>
+      <c r="I41" s="71" t="s">
+        <v>156</v>
       </c>
       <c r="J41" s="57"/>
       <c r="K41" s="58"/>
-      <c r="L41" s="71" t="s">
+      <c r="L41" s="69" t="s">
         <v>47</v>
       </c>
       <c r="M41" s="57"/>
@@ -10438,7 +10460,7 @@
         <v>50</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
@@ -10497,7 +10519,7 @@
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B44" s="4">
         <f t="shared" ref="B44:B52" si="13">B6</f>
@@ -10548,7 +10570,7 @@
     </row>
     <row r="45" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B45" s="4">
         <f t="shared" si="13"/>
@@ -10587,7 +10609,7 @@
     </row>
     <row r="46" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B46" s="4">
         <f t="shared" si="13"/>
@@ -10626,7 +10648,7 @@
     </row>
     <row r="47" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B47" s="4">
         <f t="shared" si="13"/>
@@ -10665,7 +10687,7 @@
     </row>
     <row r="48" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B48" s="4">
         <f t="shared" si="13"/>
@@ -10704,7 +10726,7 @@
     </row>
     <row r="49" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="4">
         <f t="shared" si="13"/>
@@ -10743,7 +10765,7 @@
     </row>
     <row r="50" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B50" s="4">
         <f t="shared" si="13"/>
@@ -10782,7 +10804,7 @@
     </row>
     <row r="51" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B51" s="4">
         <f t="shared" si="13"/>
@@ -10821,7 +10843,7 @@
     </row>
     <row r="52" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B52" s="4">
         <f t="shared" si="13"/>
@@ -10860,7 +10882,7 @@
     </row>
     <row r="53" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="7">
@@ -10933,7 +10955,7 @@
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B56" s="4">
         <f t="shared" ref="B56:B61" si="20">B18</f>
@@ -10972,7 +10994,7 @@
     </row>
     <row r="57" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B57" s="4">
         <f t="shared" si="20"/>
@@ -11011,7 +11033,7 @@
     </row>
     <row r="58" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B58" s="4">
         <f t="shared" si="20"/>
@@ -11050,7 +11072,7 @@
     </row>
     <row r="59" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B59" s="4">
         <f t="shared" si="20"/>
@@ -11089,7 +11111,7 @@
     </row>
     <row r="60" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B60" s="4">
         <f t="shared" si="20"/>
@@ -11128,7 +11150,7 @@
     </row>
     <row r="61" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B61" s="4">
         <f t="shared" si="20"/>
@@ -11167,7 +11189,7 @@
     </row>
     <row r="62" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="7">
@@ -11240,7 +11262,7 @@
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B65" s="4">
         <f t="shared" ref="B65:B72" si="26">B27</f>
@@ -11279,7 +11301,7 @@
     </row>
     <row r="66" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B66" s="4">
         <f t="shared" si="26"/>
@@ -11318,7 +11340,7 @@
     </row>
     <row r="67" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B67" s="4">
         <f t="shared" si="26"/>
@@ -11357,7 +11379,7 @@
     </row>
     <row r="68" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B68" s="4">
         <f t="shared" si="26"/>
@@ -11396,7 +11418,7 @@
     </row>
     <row r="69" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B69" s="4">
         <f t="shared" si="26"/>
@@ -11435,7 +11457,7 @@
     </row>
     <row r="70" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B70" s="4">
         <f t="shared" si="26"/>
@@ -11474,7 +11496,7 @@
     </row>
     <row r="71" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B71" s="4">
         <f t="shared" si="26"/>
@@ -11513,7 +11535,7 @@
     </row>
     <row r="72" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B72" s="4">
         <f t="shared" si="26"/>
@@ -11552,7 +11574,7 @@
     </row>
     <row r="73" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="7">
@@ -11606,7 +11628,7 @@
     </row>
     <row r="74" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="10">
@@ -11659,8 +11681,8 @@
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="70" t="s">
-        <v>158</v>
+      <c r="A77" s="73" t="s">
+        <v>157</v>
       </c>
       <c r="B77" s="55"/>
       <c r="C77" s="55"/>
@@ -11677,17 +11699,17 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="67" t="s">
-        <v>159</v>
+      <c r="C79" s="72" t="s">
+        <v>158</v>
       </c>
       <c r="D79" s="57"/>
       <c r="E79" s="58"/>
-      <c r="F79" s="69" t="s">
-        <v>156</v>
+      <c r="F79" s="70" t="s">
+        <v>155</v>
       </c>
       <c r="G79" s="57"/>
       <c r="H79" s="58"/>
-      <c r="I79" s="71" t="s">
+      <c r="I79" s="69" t="s">
         <v>113</v>
       </c>
       <c r="J79" s="57"/>
@@ -11698,7 +11720,7 @@
         <v>50</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
@@ -11745,7 +11767,7 @@
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B82" s="4">
         <f t="shared" ref="B82:B90" si="32">B6</f>
@@ -11790,7 +11812,7 @@
     </row>
     <row r="83" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B83" s="4">
         <f t="shared" si="32"/>
@@ -11835,7 +11857,7 @@
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" s="4">
         <f t="shared" si="32"/>
@@ -11880,7 +11902,7 @@
     </row>
     <row r="85" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" s="4">
         <f t="shared" si="32"/>
@@ -11925,7 +11947,7 @@
     </row>
     <row r="86" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B86" s="4">
         <f t="shared" si="32"/>
@@ -11970,7 +11992,7 @@
     </row>
     <row r="87" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B87" s="4">
         <f t="shared" si="32"/>
@@ -12015,7 +12037,7 @@
     </row>
     <row r="88" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B88" s="4">
         <f t="shared" si="32"/>
@@ -12060,7 +12082,7 @@
     </row>
     <row r="89" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B89" s="4">
         <f t="shared" si="32"/>
@@ -12105,7 +12127,7 @@
     </row>
     <row r="90" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B90" s="4">
         <f t="shared" si="32"/>
@@ -12150,7 +12172,7 @@
     </row>
     <row r="91" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="7">
@@ -12208,7 +12230,7 @@
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B94" s="4">
         <f t="shared" ref="B94:B99" si="42">B18</f>
@@ -12253,7 +12275,7 @@
     </row>
     <row r="95" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B95" s="4">
         <f t="shared" si="42"/>
@@ -12298,7 +12320,7 @@
     </row>
     <row r="96" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B96" s="4">
         <f t="shared" si="42"/>
@@ -12343,7 +12365,7 @@
     </row>
     <row r="97" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B97" s="4">
         <f t="shared" si="42"/>
@@ -12388,7 +12410,7 @@
     </row>
     <row r="98" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" s="4">
         <f t="shared" si="42"/>
@@ -12433,7 +12455,7 @@
     </row>
     <row r="99" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B99" s="4">
         <f t="shared" si="42"/>
@@ -12478,7 +12500,7 @@
     </row>
     <row r="100" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="7">
@@ -12536,7 +12558,7 @@
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B103" s="4">
         <f t="shared" ref="B103:B110" si="49">B27</f>
@@ -12581,7 +12603,7 @@
     </row>
     <row r="104" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B104" s="4">
         <f t="shared" si="49"/>
@@ -12626,7 +12648,7 @@
     </row>
     <row r="105" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B105" s="4">
         <f t="shared" si="49"/>
@@ -12671,7 +12693,7 @@
     </row>
     <row r="106" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B106" s="4">
         <f t="shared" si="49"/>
@@ -12716,7 +12738,7 @@
     </row>
     <row r="107" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B107" s="4">
         <f t="shared" si="49"/>
@@ -12761,7 +12783,7 @@
     </row>
     <row r="108" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B108" s="4">
         <f t="shared" si="49"/>
@@ -12806,7 +12828,7 @@
     </row>
     <row r="109" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B109" s="4">
         <f t="shared" si="49"/>
@@ -12851,7 +12873,7 @@
     </row>
     <row r="110" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B110" s="4">
         <f t="shared" si="49"/>
@@ -12896,7 +12918,7 @@
     </row>
     <row r="111" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="7">
@@ -12938,7 +12960,7 @@
     </row>
     <row r="112" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B112" s="9"/>
       <c r="C112" s="10">
@@ -12980,6 +13002,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
@@ -12996,12 +13024,6 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
@@ -13396,7 +13418,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -13423,7 +13445,7 @@
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -13437,7 +13459,7 @@
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
       <c r="M3" s="56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N3" s="57"/>
       <c r="O3" s="57"/>
@@ -13451,7 +13473,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>7</v>
@@ -13466,22 +13488,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>169</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>7</v>
@@ -13496,27 +13518,27 @@
         <v>11</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -13542,7 +13564,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" s="15">
         <v>415</v>
@@ -13608,7 +13630,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" s="15">
         <v>416</v>
@@ -13674,7 +13696,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -13700,7 +13722,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="15">
         <v>417</v>
@@ -13766,7 +13788,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" s="15">
         <v>418</v>
@@ -13832,7 +13854,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" s="15">
         <v>419</v>
@@ -13898,7 +13920,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -13924,7 +13946,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B13" s="15">
         <v>420</v>
@@ -13990,7 +14012,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" s="15">
         <v>421</v>
@@ -14056,7 +14078,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" s="15">
         <v>422</v>
@@ -14122,7 +14144,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B16" s="15">
         <v>423</v>
@@ -14188,7 +14210,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -14214,7 +14236,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" s="15">
         <v>424</v>
@@ -14280,7 +14302,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B19" s="15">
         <v>424</v>
@@ -14346,7 +14368,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -14372,7 +14394,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B21" s="15">
         <v>425</v>
@@ -14438,7 +14460,7 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B22" s="15">
         <v>425</v>
@@ -14504,7 +14526,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B23" s="15">
         <v>426</v>
@@ -14570,7 +14592,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B24" s="15">
         <v>427</v>
@@ -14636,7 +14658,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B25" s="15">
         <v>428</v>
@@ -14702,7 +14724,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -14728,7 +14750,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B27" s="15">
         <v>429</v>
@@ -14794,7 +14816,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B28" s="15">
         <v>430</v>
@@ -14860,7 +14882,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B29" s="15">
         <v>501</v>
@@ -14926,7 +14948,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B30" s="15">
         <v>502</v>
@@ -14992,7 +15014,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -15018,7 +15040,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B32" s="15">
         <v>503</v>
@@ -15084,7 +15106,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B33" s="15">
         <v>503</v>
@@ -15150,7 +15172,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B34" s="15">
         <v>503</v>
@@ -15188,7 +15210,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="L34" s="43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
@@ -15218,7 +15240,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B35" s="15">
         <v>504</v>
@@ -15284,7 +15306,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B36" s="15">
         <v>504</v>
@@ -15350,7 +15372,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -15376,7 +15398,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B38" s="15">
         <v>505</v>
@@ -15442,7 +15464,7 @@
     </row>
     <row r="39" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B39" s="15">
         <v>505</v>
@@ -15508,7 +15530,7 @@
     </row>
     <row r="40" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B40" s="15">
         <v>505</v>
@@ -15574,7 +15596,7 @@
     </row>
     <row r="41" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B41" s="15">
         <v>505</v>
@@ -15640,7 +15662,7 @@
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B42" s="15">
         <v>506</v>
@@ -15706,7 +15728,7 @@
     </row>
     <row r="43" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B43" s="15">
         <v>506</v>
@@ -15736,7 +15758,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L43" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
@@ -15766,7 +15788,7 @@
     </row>
     <row r="44" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" s="15">
         <v>506</v>
@@ -15796,7 +15818,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L44" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
@@ -16641,8 +16663,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>212</v>
+      <c r="A1" s="67" t="s">
+        <v>211</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -16669,7 +16691,7 @@
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -16683,7 +16705,7 @@
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
       <c r="M3" s="56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N3" s="57"/>
       <c r="O3" s="57"/>
@@ -16697,7 +16719,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>7</v>
@@ -16712,22 +16734,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>169</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>7</v>
@@ -16742,27 +16764,27 @@
         <v>11</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -16788,7 +16810,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" s="15">
         <v>507</v>
@@ -16854,7 +16876,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="15">
         <v>507</v>
@@ -16920,7 +16942,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" s="15">
         <v>508</v>
@@ -16986,7 +17008,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -17012,7 +17034,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="15">
         <v>509</v>
@@ -17078,7 +17100,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="15">
         <v>510</v>
@@ -17144,7 +17166,7 @@
     </row>
     <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B12" s="15">
         <v>512</v>
@@ -17210,7 +17232,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -17236,7 +17258,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B14" s="15">
         <v>513</v>
@@ -17302,7 +17324,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B15" s="15">
         <v>514</v>
@@ -17368,7 +17390,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B16" s="15">
         <v>515</v>
@@ -17434,7 +17456,7 @@
     </row>
     <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B17" s="15">
         <v>516</v>
@@ -17500,7 +17522,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B18" s="15">
         <v>516</v>
@@ -17566,7 +17588,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B19" s="15">
         <v>517</v>
@@ -17632,7 +17654,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -17658,7 +17680,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" s="15">
         <v>518</v>
@@ -17724,7 +17746,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" s="15">
         <v>518</v>
@@ -17790,7 +17812,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" s="15">
         <v>519</v>
@@ -17824,7 +17846,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L23" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -17854,7 +17876,7 @@
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" s="15">
         <v>520</v>
@@ -17920,7 +17942,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -17946,7 +17968,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B26" s="15">
         <v>521</v>
@@ -18012,7 +18034,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B27" s="15">
         <v>521</v>
@@ -18078,7 +18100,7 @@
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B28" s="15">
         <v>522</v>
@@ -18144,7 +18166,7 @@
     </row>
     <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B29" s="15">
         <v>523</v>
@@ -18210,7 +18232,7 @@
     </row>
     <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B30" s="15">
         <v>524</v>
@@ -18276,7 +18298,7 @@
     </row>
     <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31" s="15">
         <v>525</v>
@@ -18342,7 +18364,7 @@
     </row>
     <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B32" s="15">
         <v>525</v>
@@ -18408,7 +18430,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -18434,7 +18456,7 @@
     </row>
     <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B34" s="15">
         <v>526</v>
@@ -18500,7 +18522,7 @@
     </row>
     <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B35" s="15">
         <v>526</v>
@@ -18566,7 +18588,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -18592,7 +18614,7 @@
     </row>
     <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B37" s="15">
         <v>526</v>
@@ -18658,7 +18680,7 @@
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B38" s="15">
         <v>527</v>
@@ -18724,7 +18746,7 @@
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B39" s="15">
         <v>528</v>
@@ -19534,7 +19556,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -19561,7 +19583,7 @@
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -19575,7 +19597,7 @@
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
       <c r="M3" s="56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N3" s="57"/>
       <c r="O3" s="57"/>
@@ -19589,7 +19611,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>7</v>
@@ -19604,22 +19626,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>169</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>7</v>
@@ -19634,27 +19656,27 @@
         <v>11</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -19680,7 +19702,7 @@
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B6" s="15">
         <v>530</v>
@@ -19746,7 +19768,7 @@
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B7" s="15">
         <v>530</v>
@@ -19812,7 +19834,7 @@
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B8" s="15">
         <v>530</v>
@@ -19878,7 +19900,7 @@
     </row>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" s="15">
         <v>531</v>
@@ -19944,7 +19966,7 @@
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B10" s="15">
         <v>531</v>
@@ -20010,7 +20032,7 @@
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B11" s="15">
         <v>531</v>
@@ -20076,7 +20098,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -20102,7 +20124,7 @@
     </row>
     <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B13" s="15">
         <v>601</v>
@@ -20168,7 +20190,7 @@
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B14" s="15">
         <v>602</v>
@@ -20234,7 +20256,7 @@
     </row>
     <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B15" s="15">
         <v>606</v>
@@ -20300,7 +20322,7 @@
     </row>
     <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B16" s="15">
         <v>607</v>
@@ -20366,7 +20388,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -20392,7 +20414,7 @@
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B18" s="15">
         <v>609</v>
@@ -20458,7 +20480,7 @@
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B19" s="15">
         <v>610</v>
@@ -20524,7 +20546,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -20550,7 +20572,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B21" s="15">
         <v>611</v>
@@ -20616,7 +20638,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B22" s="15">
         <v>614</v>
@@ -20682,7 +20704,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B23" s="15">
         <v>614</v>
@@ -20748,7 +20770,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -20774,7 +20796,7 @@
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B25" s="15">
         <v>614</v>
@@ -20840,7 +20862,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" s="15">
         <v>615</v>
@@ -20906,7 +20928,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B27" s="15">
         <v>615</v>
@@ -21572,7 +21594,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -21599,7 +21621,7 @@
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -21613,7 +21635,7 @@
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
       <c r="M3" s="56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N3" s="57"/>
       <c r="O3" s="57"/>
@@ -21627,7 +21649,7 @@
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>7</v>
@@ -21642,22 +21664,22 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>169</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>7</v>
@@ -21672,27 +21694,27 @@
         <v>11</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -21718,7 +21740,7 @@
     </row>
     <row r="6" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B6" s="15">
         <v>616</v>
@@ -21784,7 +21806,7 @@
     </row>
     <row r="7" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B7" s="15">
         <v>617</v>
@@ -21850,7 +21872,7 @@
     </row>
     <row r="8" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -21876,7 +21898,7 @@
     </row>
     <row r="9" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B9" s="15">
         <v>618</v>
@@ -21942,7 +21964,7 @@
     </row>
     <row r="10" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B10" s="15">
         <v>618</v>
@@ -22008,7 +22030,7 @@
     </row>
     <row r="11" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B11" s="15">
         <v>618</v>
@@ -22074,7 +22096,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -22100,7 +22122,7 @@
     </row>
     <row r="13" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B13" s="15">
         <v>619</v>
@@ -22166,7 +22188,7 @@
     </row>
     <row r="14" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B14" s="15">
         <v>619</v>
@@ -22232,7 +22254,7 @@
     </row>
     <row r="15" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B15" s="15">
         <v>619</v>
@@ -22298,7 +22320,7 @@
     </row>
     <row r="16" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B16" s="15">
         <v>620</v>
@@ -22364,7 +22386,7 @@
     </row>
     <row r="17" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B17" s="15">
         <v>621</v>
@@ -22430,7 +22452,7 @@
     </row>
     <row r="18" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B18" s="15">
         <v>622</v>
@@ -22496,7 +22518,7 @@
     </row>
     <row r="19" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B19" s="15">
         <v>623</v>
@@ -22562,7 +22584,7 @@
     </row>
     <row r="20" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B20" s="15">
         <v>623</v>
@@ -22628,7 +22650,7 @@
     </row>
     <row r="21" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -22654,32 +22676,42 @@
     </row>
     <row r="22" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15" t="str">
+        <v>288</v>
+      </c>
+      <c r="B22" s="15">
+        <v>624</v>
+      </c>
+      <c r="C22" s="15">
+        <v>21</v>
+      </c>
+      <c r="D22" s="15">
+        <v>16</v>
+      </c>
+      <c r="E22" s="15">
         <f t="shared" ref="E22:E28" si="10">IF(AND(C22&lt;&gt;"",D22&lt;&gt;""),D22/C22,"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15" t="str">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="F22" s="15">
+        <v>3</v>
+      </c>
+      <c r="G22" s="15">
+        <v>3</v>
+      </c>
+      <c r="H22" s="15">
         <f t="shared" ref="H22:H28" si="11">IF(AND(F22&lt;&gt;"",G22&lt;&gt;""),G22/F22,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" ref="I22:J28" si="12">C22-F22</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="15" t="e">
+        <v>13</v>
+      </c>
+      <c r="K22" s="15">
         <f t="shared" ref="K22:K28" si="13">IF(AND(I22&lt;&gt;"",J22&lt;&gt;""),J22/I22,"")</f>
-        <v>#DIV/0!</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" s="15"/>
@@ -22710,7 +22742,7 @@
     </row>
     <row r="23" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -22766,7 +22798,7 @@
     </row>
     <row r="24" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -22822,7 +22854,7 @@
     </row>
     <row r="25" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -22878,7 +22910,7 @@
     </row>
     <row r="26" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -22934,7 +22966,7 @@
     </row>
     <row r="27" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -22990,7 +23022,7 @@
     </row>
     <row r="28" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -23046,7 +23078,7 @@
     </row>
     <row r="29" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -23072,7 +23104,7 @@
     </row>
     <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -23128,7 +23160,7 @@
     </row>
     <row r="31" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -23184,7 +23216,7 @@
     </row>
     <row r="32" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -23240,7 +23272,7 @@
     </row>
     <row r="33" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -23266,7 +23298,7 @@
     </row>
     <row r="34" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -23322,7 +23354,7 @@
     </row>
     <row r="35" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -23378,7 +23410,7 @@
     </row>
     <row r="36" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -23434,7 +23466,7 @@
     </row>
     <row r="37" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -23490,7 +23522,7 @@
     </row>
     <row r="38" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -23551,39 +23583,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>0.81640625</v>
+        <v>0.81227436823104693</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>0.81967213114754101</v>
+        <v>0.828125</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>0.81538461538461537</v>
+        <v>0.80751173708920188</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23632,39 +23664,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>0.81640625</v>
+        <v>0.81227436823104693</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>0.81967213114754101</v>
+        <v>0.828125</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>0.81538461538461537</v>
+        <v>0.80751173708920188</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
@@ -24745,25 +24777,37 @@
       <c r="A10" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
+      <c r="B10" s="48">
+        <v>6.23</v>
+      </c>
+      <c r="C10" s="48">
+        <v>17</v>
+      </c>
       <c r="D10" s="48">
         <v>5</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48" t="str">
+      <c r="E10" s="48">
+        <v>2</v>
+      </c>
+      <c r="F10" s="48">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="48">
+        <v>6.25</v>
+      </c>
+      <c r="H10" s="48">
+        <v>28</v>
+      </c>
       <c r="I10" s="48">
         <v>5</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48" t="str">
+      <c r="J10" s="48">
+        <v>3</v>
+      </c>
+      <c r="K10" s="48">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="L10" s="48"/>
       <c r="M10" s="48"/>
@@ -24791,11 +24835,11 @@
       </c>
       <c r="W10" s="48">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X10" s="48">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -25380,11 +25424,11 @@
       </c>
       <c r="E21" s="46">
         <f>SUM(E5:E20)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" si="0"/>
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G21" s="50"/>
       <c r="H21" s="50"/>
@@ -25394,11 +25438,11 @@
       </c>
       <c r="J21" s="46">
         <f>SUM(J5:J20)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K21" s="46">
         <f t="shared" si="1"/>
-        <v>7.4999999999999997E-2</v>
+        <v>0.1125</v>
       </c>
       <c r="L21" s="50"/>
       <c r="M21" s="50"/>
@@ -25434,11 +25478,11 @@
       </c>
       <c r="W21" s="46">
         <f>SUM(W5:W20)</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X21" s="46">
         <f t="shared" si="6"/>
-        <v>6.25E-2</v>
+        <v>7.8125E-2</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -25454,11 +25498,11 @@
       </c>
       <c r="E23" s="53">
         <f>E21</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="53">
         <f>IF(AND(D23&lt;&gt;"",E23&lt;&gt;""),E23/D23,"")</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G23" s="52"/>
       <c r="H23" s="52"/>
@@ -25468,11 +25512,11 @@
       </c>
       <c r="J23" s="53">
         <f>J21</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K23" s="53">
         <f>IF(AND(I23&lt;&gt;"",J23&lt;&gt;""),J23/I23,"")</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0.1125</v>
       </c>
       <c r="L23" s="52"/>
       <c r="M23" s="52"/>
@@ -25508,11 +25552,11 @@
       </c>
       <c r="W23" s="53">
         <f>W21</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X23" s="53">
         <f>IF(AND(V23&lt;&gt;"",W23&lt;&gt;""),W23/V23,"")</f>
-        <v>6.25E-2</v>
+        <v>7.8125E-2</v>
       </c>
     </row>
   </sheetData>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25E65FD-ACCF-4829-BF0F-671B52A6811B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51BA39C-AB44-49E9-BC00-759574EEF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -1444,21 +1444,21 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1477,34 +1477,34 @@
     <xf numFmtId="0" fontId="24" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7536,13 +7536,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
@@ -8047,13 +8047,13 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
@@ -8534,13 +8534,13 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="60" t="s">
+      <c r="A83" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="57"/>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="58"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="60"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
@@ -8782,23 +8782,23 @@
       <c r="C3" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="66" t="s">
         <v>305</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="60"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -9428,7 +9428,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="72" t="s">
         <v>126</v>
       </c>
       <c r="B1" s="55"/>
@@ -9446,21 +9446,21 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="70" t="s">
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="69" t="s">
+      <c r="G3" s="59"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -9501,16 +9501,16 @@
       <c r="A5" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -9839,16 +9839,16 @@
       <c r="A17" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="58"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -10077,16 +10077,16 @@
       <c r="A26" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="58"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="60"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -10413,7 +10413,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="70" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="55"/>
@@ -10434,26 +10434,26 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="72" t="s">
+      <c r="C41" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="70" t="s">
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G41" s="57"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="71" t="s">
+      <c r="G41" s="59"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="J41" s="57"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="69" t="s">
+      <c r="J41" s="59"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="57"/>
-      <c r="N41" s="58"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="60"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -10503,19 +10503,19 @@
       <c r="A43" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="57"/>
-      <c r="N43" s="58"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="59"/>
+      <c r="K43" s="59"/>
+      <c r="L43" s="59"/>
+      <c r="M43" s="59"/>
+      <c r="N43" s="60"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
@@ -10573,22 +10573,31 @@
         <v>129</v>
       </c>
       <c r="B45" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4" t="str">
+        <v>625</v>
+      </c>
+      <c r="C45" s="4">
+        <v>17</v>
+      </c>
+      <c r="D45" s="4">
+        <v>16</v>
+      </c>
+      <c r="E45" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4" t="str">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="F45" s="4">
+        <v>17</v>
+      </c>
+      <c r="G45" s="4">
+        <v>13</v>
+      </c>
+      <c r="H45" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="I45" s="4"/>
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="I45" s="4">
+        <v>19</v>
+      </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="str">
         <f t="shared" si="16"/>
@@ -10596,15 +10605,15 @@
       </c>
       <c r="L45" s="4">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M45" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N45" s="4" t="e">
+        <v>29</v>
+      </c>
+      <c r="N45" s="4">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>0.54716981132075471</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -10887,31 +10896,31 @@
       <c r="B53" s="6"/>
       <c r="C53" s="7">
         <f>SUM(C44:C52)</f>
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D53" s="7">
         <f>SUM(D44:D52)</f>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E53" s="7">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="F53" s="7">
         <f>SUM(F44:F52)</f>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G53" s="7">
         <f>SUM(G44:G52)</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H53" s="7">
         <f t="shared" si="15"/>
-        <v>0.5</v>
+        <v>0.65517241379310343</v>
       </c>
       <c r="I53" s="7">
         <f>SUM(I44:I52)</f>
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J53" s="7">
         <f>SUM(J44:J52)</f>
@@ -10923,15 +10932,15 @@
       </c>
       <c r="L53" s="7">
         <f>SUM(L44:L52)</f>
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="M53" s="7">
         <f>SUM(M44:M52)</f>
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="N53" s="7">
         <f t="shared" si="19"/>
-        <v>0.57894736842105265</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10939,19 +10948,19 @@
       <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="57"/>
-      <c r="C55" s="57"/>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="57"/>
-      <c r="L55" s="57"/>
-      <c r="M55" s="57"/>
-      <c r="N55" s="58"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="59"/>
+      <c r="K55" s="59"/>
+      <c r="L55" s="59"/>
+      <c r="M55" s="59"/>
+      <c r="N55" s="60"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
@@ -11246,19 +11255,19 @@
       <c r="A64" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="57"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
-      <c r="K64" s="57"/>
-      <c r="L64" s="57"/>
-      <c r="M64" s="57"/>
-      <c r="N64" s="58"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="59"/>
+      <c r="L64" s="59"/>
+      <c r="M64" s="59"/>
+      <c r="N64" s="60"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -11633,31 +11642,31 @@
       <c r="B74" s="9"/>
       <c r="C74" s="10">
         <f>C53+C62+C73</f>
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D74" s="10">
         <f>D53+D62+D73</f>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E74" s="10">
         <f t="shared" si="27"/>
-        <v>1</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="F74" s="10">
         <f>F53+F62+F73</f>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G74" s="10">
         <f>G53+G62+G73</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H74" s="10">
         <f t="shared" si="28"/>
-        <v>0.5</v>
+        <v>0.65517241379310343</v>
       </c>
       <c r="I74" s="10">
         <f>I53+I62+I73</f>
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J74" s="10">
         <f>J53+J62+J73</f>
@@ -11669,19 +11678,19 @@
       </c>
       <c r="L74" s="10">
         <f>L53+L62+L73</f>
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="M74" s="10">
         <f>M53+M62+M73</f>
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="N74" s="10">
         <f t="shared" si="31"/>
-        <v>0.57894736842105265</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="70" t="s">
         <v>157</v>
       </c>
       <c r="B77" s="55"/>
@@ -11699,21 +11708,21 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="72" t="s">
+      <c r="C79" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="57"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="70" t="s">
+      <c r="D79" s="59"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="G79" s="57"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="69" t="s">
+      <c r="G79" s="59"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="J79" s="57"/>
-      <c r="K79" s="58"/>
+      <c r="J79" s="59"/>
+      <c r="K79" s="60"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
@@ -11754,16 +11763,16 @@
       <c r="A81" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="57"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
-      <c r="K81" s="58"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="60"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
@@ -11832,27 +11841,27 @@
       </c>
       <c r="F83" s="4">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G83" s="4">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="4" t="e">
+        <v>29</v>
+      </c>
+      <c r="H83" s="4">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>0.54716981132075471</v>
       </c>
       <c r="I83" s="4">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="4" t="e">
+        <v>29</v>
+      </c>
+      <c r="K83" s="4">
         <f t="shared" si="41"/>
-        <v>#DIV/0!</v>
+        <v>0.54716981132075471</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -12189,27 +12198,27 @@
       </c>
       <c r="F91" s="7">
         <f>SUM(F82:F90)</f>
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="G91" s="7">
         <f>SUM(G82:G90)</f>
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H91" s="7">
         <f t="shared" si="38"/>
-        <v>0.57894736842105265</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I91" s="7">
         <f>SUM(I82:I90)</f>
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="J91" s="7">
         <f>SUM(J82:J90)</f>
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="K91" s="7">
         <f t="shared" si="41"/>
-        <v>0.8214285714285714</v>
+        <v>0.68807339449541283</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12217,16 +12226,16 @@
       <c r="A93" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B93" s="57"/>
-      <c r="C93" s="57"/>
-      <c r="D93" s="57"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="58"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="59"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="59"/>
+      <c r="F93" s="59"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="59"/>
+      <c r="J93" s="59"/>
+      <c r="K93" s="60"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
@@ -12545,16 +12554,16 @@
       <c r="A102" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B102" s="57"/>
-      <c r="C102" s="57"/>
-      <c r="D102" s="57"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="57"/>
-      <c r="I102" s="57"/>
-      <c r="J102" s="57"/>
-      <c r="K102" s="58"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="59"/>
+      <c r="D102" s="59"/>
+      <c r="E102" s="59"/>
+      <c r="F102" s="59"/>
+      <c r="G102" s="59"/>
+      <c r="H102" s="59"/>
+      <c r="I102" s="59"/>
+      <c r="J102" s="59"/>
+      <c r="K102" s="60"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
@@ -12977,37 +12986,31 @@
       </c>
       <c r="F112" s="10">
         <f>F91+F100+F111</f>
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="G112" s="10">
         <f>G91+G100+G111</f>
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H112" s="10">
         <f t="shared" si="53"/>
-        <v>0.57894736842105265</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I112" s="10">
         <f>I91+I100+I111</f>
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="J112" s="10">
         <f>J91+J100+J111</f>
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="K112" s="10">
         <f t="shared" si="55"/>
-        <v>0.8214285714285714</v>
+        <v>0.68807339449541283</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
@@ -13024,6 +13027,12 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
@@ -13417,7 +13426,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>159</v>
       </c>
       <c r="B1" s="55"/>
@@ -13444,32 +13453,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -16663,7 +16672,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="72" t="s">
         <v>211</v>
       </c>
       <c r="B1" s="55"/>
@@ -16690,32 +16699,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -19555,7 +19564,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>247</v>
       </c>
       <c r="B1" s="55"/>
@@ -19582,32 +19591,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -21593,7 +21602,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>270</v>
       </c>
       <c r="B1" s="55"/>
@@ -21620,32 +21629,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="58"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -24254,7 +24263,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
@@ -24284,35 +24293,35 @@
     <row r="2" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="57" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="55"/>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="57" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
-      <c r="Q3" s="76" t="s">
+      <c r="Q3" s="57" t="s">
         <v>4</v>
       </c>
       <c r="R3" s="55"/>
       <c r="S3" s="55"/>
       <c r="T3" s="55"/>
       <c r="U3" s="55"/>
-      <c r="V3" s="75" t="s">
+      <c r="V3" s="56" t="s">
         <v>5</v>
       </c>
       <c r="W3" s="55"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51BA39C-AB44-49E9-BC00-759574EEF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749A5A13-8345-44CF-A973-40EF18BAA05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1444,21 +1444,33 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1477,27 +1489,6 @@
     <xf numFmtId="0" fontId="24" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1505,6 +1496,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7509,7 +7509,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="65" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="55"/>
@@ -7536,13 +7536,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
     </row>
     <row r="5" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
@@ -8047,13 +8047,13 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
+      <c r="A41" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
     </row>
     <row r="42" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
@@ -8534,13 +8534,13 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="59"/>
-      <c r="C83" s="59"/>
-      <c r="D83" s="59"/>
-      <c r="E83" s="60"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="58"/>
     </row>
     <row r="84" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
@@ -8758,7 +8758,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="55"/>
@@ -8779,26 +8779,26 @@
     <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="66" t="s">
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="70" t="s">
         <v>305</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="65" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="64" t="s">
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="60"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
     </row>
     <row r="4" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
@@ -9428,7 +9428,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="54" t="s">
         <v>126</v>
       </c>
       <c r="B1" s="55"/>
@@ -9446,21 +9446,21 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="69" t="s">
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="71" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -9498,19 +9498,19 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -9556,12 +9556,18 @@
       <c r="A7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="str">
+      <c r="B7" s="4">
+        <v>626</v>
+      </c>
+      <c r="C7" s="4">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0.8529411764705882</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -9571,15 +9577,15 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="e">
+        <v>29</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.8529411764705882</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -9799,15 +9805,15 @@
       <c r="B15" s="6"/>
       <c r="C15" s="7">
         <f>SUM(C6:C14)</f>
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D15" s="7">
         <f>SUM(D6:D14)</f>
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E15" s="7">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
+        <v>0.87755102040816324</v>
       </c>
       <c r="F15" s="7">
         <f>SUM(F6:F14)</f>
@@ -9823,32 +9829,32 @@
       </c>
       <c r="I15" s="7">
         <f>SUM(I6:I14)</f>
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="J15" s="7">
         <f>SUM(J6:J14)</f>
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="4"/>
-        <v>0.94594594594594594</v>
+        <v>0.90140845070422537</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -10074,19 +10080,19 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="60"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="58"/>
     </row>
     <row r="27" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -10377,15 +10383,15 @@
       <c r="B36" s="9"/>
       <c r="C36" s="10">
         <f>C15+C24+C35</f>
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="D36" s="10">
         <f>D15+D24+D35</f>
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E36" s="10">
         <f t="shared" si="9"/>
-        <v>0.93333333333333335</v>
+        <v>0.87755102040816324</v>
       </c>
       <c r="F36" s="10">
         <f>F15+F24+F35</f>
@@ -10401,19 +10407,19 @@
       </c>
       <c r="I36" s="10">
         <f>I15+I24+I35</f>
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="J36" s="10">
         <f>J15+J24+J35</f>
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="12"/>
-        <v>0.94594594594594594</v>
+        <v>0.90140845070422537</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="63" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="55"/>
@@ -10434,26 +10440,26 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="67" t="s">
+      <c r="C41" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="59"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="69" t="s">
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="G41" s="59"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="73" t="s">
+      <c r="G41" s="57"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="J41" s="59"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="71" t="s">
+      <c r="J41" s="57"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="59"/>
-      <c r="N41" s="60"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
@@ -10500,22 +10506,22 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="60"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
     </row>
     <row r="44" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
@@ -10576,28 +10582,22 @@
         <v>625</v>
       </c>
       <c r="C45" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D45" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E45" s="4">
         <f t="shared" si="14"/>
-        <v>0.94117647058823528</v>
-      </c>
-      <c r="F45" s="4">
-        <v>17</v>
-      </c>
-      <c r="G45" s="4">
-        <v>13</v>
-      </c>
-      <c r="H45" s="4">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4" t="str">
         <f t="shared" si="15"/>
-        <v>0.76470588235294112</v>
-      </c>
-      <c r="I45" s="4">
-        <v>19</v>
-      </c>
+        <v/>
+      </c>
+      <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="str">
         <f t="shared" si="16"/>
@@ -10605,15 +10605,15 @@
       </c>
       <c r="L45" s="4">
         <f t="shared" si="17"/>
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="M45" s="4">
         <f t="shared" si="18"/>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="N45" s="4">
         <f t="shared" si="19"/>
-        <v>0.54716981132075471</v>
+        <v>0.63157894736842102</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -10896,31 +10896,31 @@
       <c r="B53" s="6"/>
       <c r="C53" s="7">
         <f>SUM(C44:C52)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D53" s="7">
         <f>SUM(D44:D52)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E53" s="7">
         <f t="shared" si="14"/>
-        <v>0.95454545454545459</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F53" s="7">
         <f>SUM(F44:F52)</f>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G53" s="7">
         <f>SUM(G44:G52)</f>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H53" s="7">
         <f t="shared" si="15"/>
-        <v>0.65517241379310343</v>
+        <v>0.5</v>
       </c>
       <c r="I53" s="7">
         <f>SUM(I44:I52)</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J53" s="7">
         <f>SUM(J44:J52)</f>
@@ -10932,35 +10932,35 @@
       </c>
       <c r="L53" s="7">
         <f>SUM(L44:L52)</f>
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M53" s="7">
         <f>SUM(M44:M52)</f>
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N53" s="7">
         <f t="shared" si="19"/>
-        <v>0.55555555555555558</v>
+        <v>0.60526315789473684</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="68" t="s">
+      <c r="A55" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
-      <c r="M55" s="59"/>
-      <c r="N55" s="60"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
     </row>
     <row r="56" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
@@ -11252,22 +11252,22 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="68" t="s">
+      <c r="A64" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="59"/>
-      <c r="C64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
-      <c r="M64" s="59"/>
-      <c r="N64" s="60"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
+      <c r="N64" s="58"/>
     </row>
     <row r="65" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -11642,31 +11642,31 @@
       <c r="B74" s="9"/>
       <c r="C74" s="10">
         <f>C53+C62+C73</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D74" s="10">
         <f>D53+D62+D73</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E74" s="10">
         <f t="shared" si="27"/>
-        <v>0.95454545454545459</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F74" s="10">
         <f>F53+F62+F73</f>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G74" s="10">
         <f>G53+G62+G73</f>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H74" s="10">
         <f t="shared" si="28"/>
-        <v>0.65517241379310343</v>
+        <v>0.5</v>
       </c>
       <c r="I74" s="10">
         <f>I53+I62+I73</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J74" s="10">
         <f>J53+J62+J73</f>
@@ -11678,19 +11678,19 @@
       </c>
       <c r="L74" s="10">
         <f>L53+L62+L73</f>
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="M74" s="10">
         <f>M53+M62+M73</f>
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N74" s="10">
         <f t="shared" si="31"/>
-        <v>0.55555555555555558</v>
+        <v>0.60526315789473684</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="70" t="s">
+      <c r="A77" s="63" t="s">
         <v>157</v>
       </c>
       <c r="B77" s="55"/>
@@ -11708,21 +11708,21 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="67" t="s">
+      <c r="C79" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="59"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="69" t="s">
+      <c r="D79" s="57"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="G79" s="59"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="71" t="s">
+      <c r="G79" s="57"/>
+      <c r="H79" s="58"/>
+      <c r="I79" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="J79" s="59"/>
-      <c r="K79" s="60"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="58"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
@@ -11760,19 +11760,19 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="68" t="s">
+      <c r="A81" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B81" s="59"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
-      <c r="E81" s="59"/>
-      <c r="F81" s="59"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="59"/>
-      <c r="J81" s="59"/>
-      <c r="K81" s="60"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="57"/>
+      <c r="I81" s="57"/>
+      <c r="J81" s="57"/>
+      <c r="K81" s="58"/>
     </row>
     <row r="82" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
@@ -11825,31 +11825,31 @@
       </c>
       <c r="B83" s="4">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="C83" s="4">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D83" s="4">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="E83" s="4" t="e">
+        <v>29</v>
+      </c>
+      <c r="E83" s="4">
         <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="F83" s="4">
         <f t="shared" si="36"/>
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G83" s="4">
         <f t="shared" si="37"/>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H83" s="4">
         <f t="shared" si="38"/>
-        <v>0.54716981132075471</v>
+        <v>0.63157894736842102</v>
       </c>
       <c r="I83" s="4">
         <f t="shared" si="39"/>
@@ -11857,11 +11857,11 @@
       </c>
       <c r="J83" s="4">
         <f t="shared" si="40"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K83" s="4">
         <f t="shared" si="41"/>
-        <v>0.54716981132075471</v>
+        <v>0.77358490566037741</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -12186,27 +12186,27 @@
       <c r="B91" s="6"/>
       <c r="C91" s="7">
         <f>SUM(C82:C90)</f>
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D91" s="7">
         <f>SUM(D82:D90)</f>
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E91" s="7">
         <f t="shared" si="35"/>
-        <v>0.94594594594594594</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="F91" s="7">
         <f>SUM(F82:F90)</f>
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G91" s="7">
         <f>SUM(G82:G90)</f>
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H91" s="7">
         <f t="shared" si="38"/>
-        <v>0.55555555555555558</v>
+        <v>0.60526315789473684</v>
       </c>
       <c r="I91" s="7">
         <f>SUM(I82:I90)</f>
@@ -12214,28 +12214,28 @@
       </c>
       <c r="J91" s="7">
         <f>SUM(J82:J90)</f>
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K91" s="7">
         <f t="shared" si="41"/>
-        <v>0.68807339449541283</v>
+        <v>0.79816513761467889</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="68" t="s">
+      <c r="A93" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B93" s="59"/>
-      <c r="C93" s="59"/>
-      <c r="D93" s="59"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="60"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="58"/>
     </row>
     <row r="94" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
@@ -12551,19 +12551,19 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="68" t="s">
+      <c r="A102" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B102" s="59"/>
-      <c r="C102" s="59"/>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
-      <c r="F102" s="59"/>
-      <c r="G102" s="59"/>
-      <c r="H102" s="59"/>
-      <c r="I102" s="59"/>
-      <c r="J102" s="59"/>
-      <c r="K102" s="60"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="58"/>
     </row>
     <row r="103" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
@@ -12974,27 +12974,27 @@
       <c r="B112" s="9"/>
       <c r="C112" s="10">
         <f>C91+C100+C111</f>
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D112" s="10">
         <f>D91+D100+D111</f>
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E112" s="10">
         <f t="shared" si="51"/>
-        <v>0.94594594594594594</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="F112" s="10">
         <f>F91+F100+F111</f>
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="G112" s="10">
         <f>G91+G100+G111</f>
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H112" s="10">
         <f t="shared" si="53"/>
-        <v>0.55555555555555558</v>
+        <v>0.60526315789473684</v>
       </c>
       <c r="I112" s="10">
         <f>I91+I100+I111</f>
@@ -13002,15 +13002,21 @@
       </c>
       <c r="J112" s="10">
         <f>J91+J100+J111</f>
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K112" s="10">
         <f t="shared" si="55"/>
-        <v>0.68807339449541283</v>
+        <v>0.79816513761467889</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
@@ -13027,12 +13033,6 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
@@ -13426,7 +13426,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>159</v>
       </c>
       <c r="B1" s="55"/>
@@ -13453,32 +13453,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -16672,7 +16672,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="54" t="s">
         <v>211</v>
       </c>
       <c r="B1" s="55"/>
@@ -16699,32 +16699,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -19564,7 +19564,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>247</v>
       </c>
       <c r="B1" s="55"/>
@@ -19591,32 +19591,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -21602,7 +21602,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>270</v>
       </c>
       <c r="B1" s="55"/>
@@ -21629,32 +21629,32 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="75" t="s">
+      <c r="M3" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-      <c r="V3" s="60"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -24263,7 +24263,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="55"/>
@@ -24293,35 +24293,35 @@
     <row r="2" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="76" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
       <c r="F3" s="55"/>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="76" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="55"/>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="55"/>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="76" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
       <c r="P3" s="55"/>
-      <c r="Q3" s="57" t="s">
+      <c r="Q3" s="76" t="s">
         <v>4</v>
       </c>
       <c r="R3" s="55"/>
       <c r="S3" s="55"/>
       <c r="T3" s="55"/>
       <c r="U3" s="55"/>
-      <c r="V3" s="56" t="s">
+      <c r="V3" s="75" t="s">
         <v>5</v>
       </c>
       <c r="W3" s="55"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749A5A13-8345-44CF-A973-40EF18BAA05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DC31A0-3D86-498A-AB94-C94A56218CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -9569,23 +9569,27 @@
         <f t="shared" si="0"/>
         <v>0.8529411764705882</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="str">
+      <c r="F7" s="4">
+        <v>35</v>
+      </c>
+      <c r="G7" s="4">
+        <v>30</v>
+      </c>
+      <c r="H7" s="4">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="4"/>
-        <v>0.8529411764705882</v>
+        <v>0.85507246376811596</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -9817,27 +9821,27 @@
       </c>
       <c r="F15" s="7">
         <f>SUM(F6:F14)</f>
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="G15" s="7">
         <f>SUM(G6:G14)</f>
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>0.95454545454545459</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="I15" s="7">
         <f>SUM(I6:I14)</f>
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="J15" s="7">
         <f>SUM(J6:J14)</f>
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="4"/>
-        <v>0.90140845070422537</v>
+        <v>0.8867924528301887</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10395,27 +10399,27 @@
       </c>
       <c r="F36" s="10">
         <f>F15+F24+F35</f>
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="G36" s="10">
         <f>G15+G24+G35</f>
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H36" s="10">
         <f t="shared" si="10"/>
-        <v>0.95454545454545459</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="I36" s="10">
         <f>I15+I24+I35</f>
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="J36" s="10">
         <f>J15+J24+J35</f>
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="12"/>
-        <v>0.90140845070422537</v>
+        <v>0.8867924528301887</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11829,15 +11833,15 @@
       </c>
       <c r="C83" s="4">
         <f t="shared" si="33"/>
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D83" s="4">
         <f t="shared" si="34"/>
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E83" s="4">
         <f t="shared" si="35"/>
-        <v>0.8529411764705882</v>
+        <v>0.85507246376811596</v>
       </c>
       <c r="F83" s="4">
         <f t="shared" si="36"/>
@@ -11853,15 +11857,15 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" si="39"/>
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" si="40"/>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="K83" s="4">
         <f t="shared" si="41"/>
-        <v>0.77358490566037741</v>
+        <v>0.80681818181818177</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -12186,15 +12190,15 @@
       <c r="B91" s="6"/>
       <c r="C91" s="7">
         <f>SUM(C82:C90)</f>
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="D91" s="7">
         <f>SUM(D82:D90)</f>
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="E91" s="7">
         <f t="shared" si="35"/>
-        <v>0.90140845070422537</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="F91" s="7">
         <f>SUM(F82:F90)</f>
@@ -12210,15 +12214,15 @@
       </c>
       <c r="I91" s="7">
         <f>SUM(I82:I90)</f>
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="J91" s="7">
         <f>SUM(J82:J90)</f>
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="K91" s="7">
         <f t="shared" si="41"/>
-        <v>0.79816513761467889</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12974,15 +12978,15 @@
       <c r="B112" s="9"/>
       <c r="C112" s="10">
         <f>C91+C100+C111</f>
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="D112" s="10">
         <f>D91+D100+D111</f>
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="E112" s="10">
         <f t="shared" si="51"/>
-        <v>0.90140845070422537</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="F112" s="10">
         <f>F91+F100+F111</f>
@@ -12998,15 +13002,15 @@
       </c>
       <c r="I112" s="10">
         <f>I91+I100+I111</f>
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="J112" s="10">
         <f>J91+J100+J111</f>
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="K112" s="10">
         <f t="shared" si="55"/>
-        <v>0.79816513761467889</v>
+        <v>0.8125</v>
       </c>
     </row>
   </sheetData>
@@ -22753,30 +22757,40 @@
       <c r="A23" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15" t="str">
+      <c r="B23" s="15">
+        <v>627</v>
+      </c>
+      <c r="C23" s="15">
+        <v>72</v>
+      </c>
+      <c r="D23" s="15">
+        <v>56</v>
+      </c>
+      <c r="E23" s="15">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="F23" s="15">
+        <v>23</v>
+      </c>
+      <c r="G23" s="15">
+        <v>18</v>
+      </c>
+      <c r="H23" s="15">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.78260869565217395</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="15" t="e">
+        <v>38</v>
+      </c>
+      <c r="K23" s="15">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0.77551020408163263</v>
       </c>
       <c r="L23" s="11"/>
       <c r="M23" s="15"/>
@@ -23592,39 +23606,39 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18">
         <f>SUM(C5:C38)</f>
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(D5:D38)</f>
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="E39" s="18">
         <f t="shared" si="20"/>
-        <v>0.81227436823104693</v>
+        <v>0.80515759312320911</v>
       </c>
       <c r="F39" s="18">
         <f>SUM(F5:F38)</f>
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G39" s="18">
         <f>SUM(G5:G38)</f>
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H39" s="18">
         <f t="shared" si="21"/>
-        <v>0.828125</v>
+        <v>0.81609195402298851</v>
       </c>
       <c r="I39" s="18">
         <f>SUM(I5:I38)</f>
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="J39" s="18">
         <f>SUM(J5:J38)</f>
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="K39" s="18">
         <f t="shared" si="23"/>
-        <v>0.80751173708920188</v>
+        <v>0.80152671755725191</v>
       </c>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -23673,39 +23687,39 @@
       <c r="B41" s="20"/>
       <c r="C41" s="21">
         <f>C39+N39</f>
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="D41" s="21">
         <f>D39+O39</f>
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="E41" s="21">
         <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;""),D41/C41,"")</f>
-        <v>0.81227436823104693</v>
+        <v>0.80515759312320911</v>
       </c>
       <c r="F41" s="21">
         <f>F39+Q39</f>
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G41" s="21">
         <f>G39+R39</f>
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H41" s="21">
         <f>IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41/F41,"")</f>
-        <v>0.828125</v>
+        <v>0.81609195402298851</v>
       </c>
       <c r="I41" s="21">
         <f>I39+T39</f>
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="J41" s="21">
         <f>J39+U39</f>
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="K41" s="21">
         <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41/I41,"")</f>
-        <v>0.80751173708920188</v>
+        <v>0.80152671755725191</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DC31A0-3D86-498A-AB94-C94A56218CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440D2737-C0B1-4A91-9A05-A2BA44677AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -1444,28 +1444,16 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1489,13 +1477,25 @@
     <xf numFmtId="0" fontId="24" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1803,6 +1803,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -1811,6 +1827,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1819,6 +1843,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1827,6 +1859,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1851,6 +1899,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -1859,6 +1923,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1867,6 +1939,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1875,6 +1955,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -1907,6 +1995,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1915,6 +2011,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1923,6 +2027,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1947,6 +2067,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -1955,6 +2091,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1963,6 +2107,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1971,6 +2123,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1995,6 +2163,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2003,6 +2187,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2011,6 +2203,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2019,6 +2219,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2027,6 +2243,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2035,6 +2259,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2051,6 +2283,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2059,6 +2299,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2067,6 +2315,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2075,6 +2331,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2083,6 +2347,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2139,6 +2411,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2211,6 +2499,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2219,6 +2515,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2227,6 +2531,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2235,6 +2547,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2243,6 +2563,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2251,6 +2579,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2331,6 +2667,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2379,6 +2731,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2403,6 +2771,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2411,6 +2787,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2419,6 +2803,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2427,6 +2819,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2475,6 +2883,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2499,6 +2915,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2507,6 +2931,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2515,6 +2947,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2523,6 +2963,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2595,6 +3051,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2619,6 +3083,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2627,6 +3107,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2635,6 +3123,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2643,6 +3139,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2691,6 +3195,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2715,6 +3235,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2787,6 +3315,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2795,6 +3339,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2803,6 +3355,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2835,6 +3395,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2867,6 +3443,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2875,6 +3459,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2883,6 +3475,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2891,6 +3491,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2899,6 +3507,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2915,6 +3531,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2923,6 +3547,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2931,6 +3563,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2955,6 +3603,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3035,6 +3691,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3043,6 +3707,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3051,6 +3723,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3059,6 +3747,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3067,6 +3763,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3099,6 +3803,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3123,6 +3843,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3131,6 +3867,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3139,6 +3883,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3147,6 +3899,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3195,6 +3963,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3203,6 +3987,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3211,6 +4003,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3219,6 +4019,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3227,6 +4035,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3235,6 +4051,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3243,6 +4067,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3267,6 +4107,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3291,6 +4139,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3315,6 +4171,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3339,6 +4203,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3363,6 +4235,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3387,6 +4275,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3395,6 +4299,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3403,6 +4315,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3411,6 +4331,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3419,6 +4347,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3427,6 +4363,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3459,6 +4403,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3483,6 +4435,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3507,6 +4467,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3515,6 +4483,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3523,6 +4499,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3531,6 +4515,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3555,6 +4547,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3563,6 +4563,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3571,6 +4579,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3579,6 +4595,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3651,6 +4683,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3683,6 +4731,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3691,6 +4747,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3699,6 +4763,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3707,6 +4779,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3715,6 +4795,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3723,6 +4811,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3747,6 +4851,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3755,6 +4875,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3763,6 +4891,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3771,6 +4907,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3779,6 +4931,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3787,6 +4947,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3795,6 +4963,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3803,6 +4987,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3811,6 +5003,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3867,6 +5067,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3875,6 +5091,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3883,6 +5107,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3899,6 +5131,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3907,6 +5147,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3915,6 +5163,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3963,6 +5227,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4019,6 +5291,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4027,6 +5307,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4067,6 +5355,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4075,6 +5371,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4083,6 +5387,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4107,6 +5419,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4131,6 +5451,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4155,6 +5483,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4179,6 +5515,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4203,6 +5547,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4211,6 +5571,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4219,6 +5587,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4227,6 +5603,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4235,6 +5619,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4243,6 +5635,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4251,6 +5651,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4259,6 +5675,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4267,6 +5691,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4275,6 +5707,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4299,6 +5739,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4323,6 +5771,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4419,6 +5883,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4443,6 +5915,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4451,6 +5931,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4459,6 +5947,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4467,6 +5963,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4587,6 +6099,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4611,6 +6131,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4619,6 +6147,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4627,6 +6163,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4643,6 +6187,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4651,6 +6203,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4827,6 +6387,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4835,6 +6403,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4843,6 +6419,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4851,6 +6435,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4859,6 +6459,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4867,6 +6475,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4883,6 +6499,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4891,6 +6515,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4899,6 +6531,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4907,6 +6555,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4915,6 +6571,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4947,6 +6611,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -4971,6 +6643,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -4979,6 +6667,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4987,6 +6683,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -5019,6 +6723,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -5043,6 +6755,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -5051,6 +6779,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -5059,6 +6795,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -5067,1752 +6811,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7509,7 +7509,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="61" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="55"/>
@@ -7536,7 +7536,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="60" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="57"/>
@@ -8047,7 +8047,7 @@
     </row>
     <row r="40" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="64" t="s">
+      <c r="A41" s="60" t="s">
         <v>88</v>
       </c>
       <c r="B41" s="57"/>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="82" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="64" t="s">
+      <c r="A83" s="60" t="s">
         <v>106</v>
       </c>
       <c r="B83" s="57"/>
@@ -8758,7 +8758,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="55"/>
@@ -8779,22 +8779,22 @@
     <row r="3" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="63" t="s">
         <v>115</v>
       </c>
       <c r="D3" s="57"/>
       <c r="E3" s="58"/>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="66" t="s">
         <v>305</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="58"/>
-      <c r="I3" s="69" t="s">
+      <c r="I3" s="65" t="s">
         <v>116</v>
       </c>
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
-      <c r="L3" s="68" t="s">
+      <c r="L3" s="64" t="s">
         <v>47</v>
       </c>
       <c r="M3" s="57"/>
@@ -9428,7 +9428,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="72" t="s">
         <v>126</v>
       </c>
       <c r="B1" s="55"/>
@@ -9446,17 +9446,17 @@
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="67" t="s">
         <v>52</v>
       </c>
       <c r="D3" s="57"/>
       <c r="E3" s="58"/>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="69" t="s">
         <v>106</v>
       </c>
       <c r="G3" s="57"/>
       <c r="H3" s="58"/>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="71" t="s">
         <v>47</v>
       </c>
       <c r="J3" s="57"/>
@@ -9498,7 +9498,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="68" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="57"/>
@@ -9846,7 +9846,7 @@
     </row>
     <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="57"/>
@@ -10084,7 +10084,7 @@
     </row>
     <row r="25" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="68" t="s">
         <v>80</v>
       </c>
       <c r="B26" s="57"/>
@@ -10423,7 +10423,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="70" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="55"/>
@@ -10444,22 +10444,22 @@
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="62" t="s">
+      <c r="C41" s="67" t="s">
         <v>52</v>
       </c>
       <c r="D41" s="57"/>
       <c r="E41" s="58"/>
-      <c r="F41" s="60" t="s">
+      <c r="F41" s="69" t="s">
         <v>106</v>
       </c>
       <c r="G41" s="57"/>
       <c r="H41" s="58"/>
-      <c r="I41" s="61" t="s">
+      <c r="I41" s="73" t="s">
         <v>156</v>
       </c>
       <c r="J41" s="57"/>
       <c r="K41" s="58"/>
-      <c r="L41" s="59" t="s">
+      <c r="L41" s="71" t="s">
         <v>47</v>
       </c>
       <c r="M41" s="57"/>
@@ -10510,7 +10510,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="68" t="s">
         <v>53</v>
       </c>
       <c r="B43" s="57"/>
@@ -10595,25 +10595,33 @@
         <f t="shared" si="14"/>
         <v>0.63157894736842102</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4" t="str">
+      <c r="F45" s="4">
+        <v>16</v>
+      </c>
+      <c r="G45" s="4">
+        <v>11</v>
+      </c>
+      <c r="H45" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4" t="str">
+        <v>0.6875</v>
+      </c>
+      <c r="I45" s="4">
+        <v>3</v>
+      </c>
+      <c r="J45" s="4">
+        <v>1</v>
+      </c>
+      <c r="K45" s="4">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="17"/>
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M45" s="4">
         <f t="shared" si="18"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N45" s="4">
         <f t="shared" si="19"/>
@@ -10832,7 +10840,7 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f>IF(AND(F51&lt;&gt;"",G51&lt;&gt;""),G51/F51,"")</f>
         <v/>
       </c>
       <c r="I51" s="4"/>
@@ -10846,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="4">
-        <f t="shared" si="18"/>
+        <f>D51+G51+J51</f>
         <v>0</v>
       </c>
       <c r="N51" s="4" t="e">
@@ -10912,44 +10920,44 @@
       </c>
       <c r="F53" s="7">
         <f>SUM(F44:F52)</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G53" s="7">
         <f>SUM(G44:G52)</f>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H53" s="7">
         <f t="shared" si="15"/>
-        <v>0.5</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="I53" s="7">
         <f>SUM(I44:I52)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J53" s="7">
         <f>SUM(J44:J52)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L53" s="7">
         <f>SUM(L44:L52)</f>
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M53" s="7">
         <f>SUM(M44:M52)</f>
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N53" s="7">
         <f t="shared" si="19"/>
-        <v>0.60526315789473684</v>
+        <v>0.61403508771929827</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
+      <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B55" s="57"/>
@@ -11256,7 +11264,7 @@
     </row>
     <row r="63" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="56" t="s">
+      <c r="A64" s="68" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="57"/>
@@ -11658,43 +11666,43 @@
       </c>
       <c r="F74" s="10">
         <f>F53+F62+F73</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G74" s="10">
         <f>G53+G62+G73</f>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H74" s="10">
         <f t="shared" si="28"/>
-        <v>0.5</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="I74" s="10">
         <f>I53+I62+I73</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" s="10">
         <f>J53+J62+J73</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L74" s="10">
         <f>L53+L62+L73</f>
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M74" s="10">
         <f>M53+M62+M73</f>
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N74" s="10">
         <f t="shared" si="31"/>
-        <v>0.60526315789473684</v>
+        <v>0.61403508771929827</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="63" t="s">
+      <c r="A77" s="70" t="s">
         <v>157</v>
       </c>
       <c r="B77" s="55"/>
@@ -11712,17 +11720,17 @@
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="62" t="s">
+      <c r="C79" s="67" t="s">
         <v>158</v>
       </c>
       <c r="D79" s="57"/>
       <c r="E79" s="58"/>
-      <c r="F79" s="60" t="s">
+      <c r="F79" s="69" t="s">
         <v>155</v>
       </c>
       <c r="G79" s="57"/>
       <c r="H79" s="58"/>
-      <c r="I79" s="59" t="s">
+      <c r="I79" s="71" t="s">
         <v>113</v>
       </c>
       <c r="J79" s="57"/>
@@ -11764,7 +11772,7 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="56" t="s">
+      <c r="A81" s="68" t="s">
         <v>53</v>
       </c>
       <c r="B81" s="57"/>
@@ -11845,11 +11853,11 @@
       </c>
       <c r="F83" s="4">
         <f t="shared" si="36"/>
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G83" s="4">
         <f t="shared" si="37"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H83" s="4">
         <f t="shared" si="38"/>
@@ -11857,15 +11865,15 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" si="39"/>
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" si="40"/>
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K83" s="4">
         <f t="shared" si="41"/>
-        <v>0.80681818181818177</v>
+        <v>0.77570093457943923</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
@@ -12202,32 +12210,32 @@
       </c>
       <c r="F91" s="7">
         <f>SUM(F82:F90)</f>
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G91" s="7">
         <f>SUM(G82:G90)</f>
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H91" s="7">
         <f t="shared" si="38"/>
-        <v>0.60526315789473684</v>
+        <v>0.61403508771929827</v>
       </c>
       <c r="I91" s="7">
         <f>SUM(I82:I90)</f>
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J91" s="7">
         <f>SUM(J82:J90)</f>
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K91" s="7">
         <f t="shared" si="41"/>
-        <v>0.8125</v>
+        <v>0.79141104294478526</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="56" t="s">
+      <c r="A93" s="68" t="s">
         <v>73</v>
       </c>
       <c r="B93" s="57"/>
@@ -12555,7 +12563,7 @@
     </row>
     <row r="101" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="56" t="s">
+      <c r="A102" s="68" t="s">
         <v>80</v>
       </c>
       <c r="B102" s="57"/>
@@ -12990,37 +12998,31 @@
       </c>
       <c r="F112" s="10">
         <f>F91+F100+F111</f>
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G112" s="10">
         <f>G91+G100+G111</f>
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H112" s="10">
         <f t="shared" si="53"/>
-        <v>0.60526315789473684</v>
+        <v>0.61403508771929827</v>
       </c>
       <c r="I112" s="10">
         <f>I91+I100+I111</f>
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J112" s="10">
         <f>J91+J100+J111</f>
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K112" s="10">
         <f t="shared" si="55"/>
-        <v>0.8125</v>
+        <v>0.79141104294478526</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="L41:N41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A55:N55"/>
@@ -13037,18 +13039,24 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="A43:N43"/>
     <mergeCell ref="A77:K77"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="L41:N41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E6:E15">
-    <cfRule type="cellIs" dxfId="662" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="661" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="660" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="662" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="661" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="660" priority="27" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E24">
@@ -13064,39 +13072,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E36">
-    <cfRule type="cellIs" dxfId="656" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="655" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="654" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="656" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="655" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="654" priority="45" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E44:E53">
-    <cfRule type="cellIs" dxfId="653" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="652" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="651" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="653" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="652" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="651" priority="90" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E55:E74">
-    <cfRule type="cellIs" dxfId="650" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="649" priority="3" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="648" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="650" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="649" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="648" priority="3" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E82:E91">
@@ -13112,11 +13120,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93:E98">
-    <cfRule type="cellIs" dxfId="644" priority="182" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="643" priority="181" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="644" priority="181" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="643" priority="182" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="642" priority="183" operator="lessThan">
@@ -13124,15 +13132,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E100:E108">
-    <cfRule type="cellIs" dxfId="641" priority="192" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="641" priority="190" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="640" priority="191" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="639" priority="190" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="639" priority="192" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E112">
@@ -13160,15 +13168,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H24">
-    <cfRule type="cellIs" dxfId="632" priority="39" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="631" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="630" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="632" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="631" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="630" priority="39" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H36">
@@ -13196,23 +13204,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H55:H74">
-    <cfRule type="cellIs" dxfId="623" priority="9" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="623" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="622" priority="8" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="621" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="621" priority="9" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82:H91">
-    <cfRule type="cellIs" dxfId="620" priority="176" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="619" priority="175" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="620" priority="175" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="619" priority="176" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="618" priority="177" operator="lessThan">
@@ -13256,59 +13264,59 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K15">
-    <cfRule type="cellIs" dxfId="608" priority="33" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="608" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="607" priority="32" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="606" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="606" priority="33" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K24">
-    <cfRule type="cellIs" dxfId="605" priority="42" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="605" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="604" priority="41" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="603" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="603" priority="42" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K36">
-    <cfRule type="cellIs" dxfId="602" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="601" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="600" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="602" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="601" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="600" priority="51" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:K53">
-    <cfRule type="cellIs" dxfId="599" priority="96" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="599" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="598" priority="95" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="597" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="597" priority="96" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55:K74">
-    <cfRule type="cellIs" dxfId="596" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="595" priority="13" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="596" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="595" priority="14" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="594" priority="15" operator="lessThan">
@@ -13364,15 +13372,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N44:N53">
-    <cfRule type="cellIs" dxfId="581" priority="99" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="581" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="580" priority="98" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="579" priority="97" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="579" priority="99" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:N60">
@@ -13430,7 +13438,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="54" t="s">
         <v>159</v>
       </c>
       <c r="B1" s="55"/>
@@ -13457,7 +13465,7 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="59" t="s">
         <v>160</v>
       </c>
       <c r="B3" s="57"/>
@@ -13471,7 +13479,7 @@
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="72" t="s">
+      <c r="M3" s="56" t="s">
         <v>161</v>
       </c>
       <c r="N3" s="57"/>
@@ -16022,15 +16030,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="566" priority="21" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="565" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="564" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="566" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="565" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="564" priority="21" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
@@ -16046,83 +16054,83 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="560" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="559" priority="57" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="558" priority="55" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="560" priority="55" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="559" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="558" priority="57" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="557" priority="75" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="557" priority="73" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="556" priority="74" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="555" priority="73" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="555" priority="75" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="554" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="553" priority="93" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="552" priority="91" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="554" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="553" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="552" priority="93" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="551" priority="111" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="551" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="550" priority="110" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="549" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="549" priority="111" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
     <cfRule type="cellIs" dxfId="548" priority="127" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="547" priority="129" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="546" priority="128" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="547" priority="128" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="546" priority="129" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
     <cfRule type="cellIs" dxfId="545" priority="163" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="544" priority="165" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="543" priority="164" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="544" priority="164" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="543" priority="165" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H7">
-    <cfRule type="cellIs" dxfId="542" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="541" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="542" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="541" priority="5" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="540" priority="6" operator="lessThan">
@@ -16130,39 +16138,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="539" priority="24" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="538" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="537" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="539" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="538" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="537" priority="24" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:H16">
-    <cfRule type="cellIs" dxfId="536" priority="41" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="535" priority="42" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="534" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="536" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="535" priority="41" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="534" priority="42" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="533" priority="60" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="533" priority="58" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="532" priority="59" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="531" priority="58" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="531" priority="60" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H25">
@@ -16178,23 +16186,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H30">
-    <cfRule type="cellIs" dxfId="527" priority="95" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="526" priority="96" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="525" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="527" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="526" priority="95" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="525" priority="96" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:H36">
-    <cfRule type="cellIs" dxfId="524" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="523" priority="112" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="524" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="523" priority="113" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="522" priority="114" operator="lessThan">
@@ -16202,15 +16210,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:H45">
-    <cfRule type="cellIs" dxfId="521" priority="132" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="521" priority="130" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="520" priority="131" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="519" priority="130" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="519" priority="132" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H47">
@@ -16226,39 +16234,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K7">
-    <cfRule type="cellIs" dxfId="515" priority="9" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="515" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="514" priority="8" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="513" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="513" priority="9" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11">
     <cfRule type="cellIs" dxfId="512" priority="25" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="511" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="510" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="511" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="510" priority="27" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K16">
-    <cfRule type="cellIs" dxfId="509" priority="45" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="509" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="508" priority="44" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="507" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="507" priority="45" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K19">
@@ -16274,51 +16282,51 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K25">
-    <cfRule type="cellIs" dxfId="503" priority="81" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="503" priority="79" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="502" priority="80" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="501" priority="79" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="501" priority="81" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K30">
     <cfRule type="cellIs" dxfId="500" priority="97" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="499" priority="99" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="498" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="499" priority="98" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="498" priority="99" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32:K36">
-    <cfRule type="cellIs" dxfId="497" priority="117" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="496" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="495" priority="116" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="497" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="496" priority="116" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="495" priority="117" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:K45">
-    <cfRule type="cellIs" dxfId="494" priority="134" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="493" priority="135" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="492" priority="133" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="494" priority="133" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="493" priority="134" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="492" priority="135" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
@@ -16334,27 +16342,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P7">
-    <cfRule type="cellIs" dxfId="488" priority="12" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="488" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="487" priority="11" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="486" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="486" priority="12" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P11">
-    <cfRule type="cellIs" dxfId="485" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="484" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="483" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="485" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="484" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="483" priority="30" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P16">
@@ -16370,15 +16378,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:P19">
-    <cfRule type="cellIs" dxfId="479" priority="65" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="478" priority="66" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="477" priority="64" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="479" priority="64" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="478" priority="65" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="477" priority="66" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P25">
@@ -16394,27 +16402,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P30">
-    <cfRule type="cellIs" dxfId="473" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="472" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="471" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="473" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="472" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="471" priority="102" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P32:P36">
-    <cfRule type="cellIs" dxfId="470" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="469" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="468" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="470" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="469" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="468" priority="120" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38:P45">
@@ -16442,11 +16450,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S7">
-    <cfRule type="cellIs" dxfId="461" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="460" priority="13" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="461" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="460" priority="14" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="459" priority="15" operator="lessThan">
@@ -16457,44 +16465,44 @@
     <cfRule type="cellIs" dxfId="458" priority="31" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="457" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="456" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="457" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="456" priority="33" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S16">
-    <cfRule type="cellIs" dxfId="455" priority="51" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="455" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="454" priority="50" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="453" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="453" priority="51" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S19">
     <cfRule type="cellIs" dxfId="452" priority="67" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="451" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="450" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="451" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="450" priority="69" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S25">
-    <cfRule type="cellIs" dxfId="449" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="448" priority="85" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="449" priority="85" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="448" priority="86" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="447" priority="87" operator="lessThan">
@@ -16502,11 +16510,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S30">
-    <cfRule type="cellIs" dxfId="446" priority="104" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="445" priority="103" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="446" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="445" priority="104" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="444" priority="105" operator="lessThan">
@@ -16514,11 +16522,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:S36">
-    <cfRule type="cellIs" dxfId="443" priority="122" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="442" priority="121" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="443" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="442" priority="122" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="441" priority="123" operator="lessThan">
@@ -16526,15 +16534,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S38:S45">
-    <cfRule type="cellIs" dxfId="440" priority="141" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="439" priority="139" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="438" priority="140" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="440" priority="139" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="439" priority="140" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="438" priority="141" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47">
@@ -16553,84 +16561,84 @@
     <cfRule type="cellIs" dxfId="434" priority="16" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="433" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="432" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="433" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="432" priority="18" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:V11">
-    <cfRule type="cellIs" dxfId="431" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="430" priority="36" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="429" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="431" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="430" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="429" priority="36" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V16">
-    <cfRule type="cellIs" dxfId="428" priority="54" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="427" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="426" priority="53" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="428" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="427" priority="53" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="426" priority="54" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:V19">
-    <cfRule type="cellIs" dxfId="425" priority="72" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="425" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="424" priority="71" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="423" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="423" priority="72" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V25">
     <cfRule type="cellIs" dxfId="422" priority="88" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="421" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="420" priority="89" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="421" priority="89" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="420" priority="90" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V27:V30">
-    <cfRule type="cellIs" dxfId="419" priority="108" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="419" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="418" priority="107" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="417" priority="108" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32:V36">
     <cfRule type="cellIs" dxfId="416" priority="124" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="414" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="415" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="414" priority="126" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V45">
@@ -16676,7 +16684,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="72" t="s">
         <v>211</v>
       </c>
       <c r="B1" s="55"/>
@@ -16703,7 +16711,7 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="59" t="s">
         <v>160</v>
       </c>
       <c r="B3" s="57"/>
@@ -16717,7 +16725,7 @@
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="72" t="s">
+      <c r="M3" s="56" t="s">
         <v>161</v>
       </c>
       <c r="N3" s="57"/>
@@ -19037,36 +19045,36 @@
     <cfRule type="cellIs" dxfId="392" priority="91" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="93" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="390" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="391" priority="92" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="390" priority="93" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E40">
-    <cfRule type="cellIs" dxfId="389" priority="111" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="389" priority="109" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="388" priority="110" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="387" priority="109" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="387" priority="111" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="386" priority="147" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="385" priority="145" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="146" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="386" priority="145" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="385" priority="146" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="147" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H8">
@@ -19130,27 +19138,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H35">
-    <cfRule type="cellIs" dxfId="368" priority="96" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="368" priority="94" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="367" priority="95" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="94" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="366" priority="96" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:H40">
-    <cfRule type="cellIs" dxfId="365" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="363" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="365" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="364" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="363" priority="114" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
@@ -19202,15 +19210,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K24">
-    <cfRule type="cellIs" dxfId="350" priority="63" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="348" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="350" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="349" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="348" priority="63" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K32">
@@ -19226,11 +19234,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34:K35">
-    <cfRule type="cellIs" dxfId="344" priority="98" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="343" priority="97" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="344" priority="97" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="343" priority="98" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="342" priority="99" operator="lessThan">
@@ -19238,27 +19246,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:K40">
-    <cfRule type="cellIs" dxfId="341" priority="117" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="341" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="340" priority="116" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="339" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="339" priority="117" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="cellIs" dxfId="338" priority="153" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="338" priority="151" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="337" priority="152" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="336" priority="151" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="336" priority="153" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P8">
@@ -19274,27 +19282,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P12">
-    <cfRule type="cellIs" dxfId="332" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="330" priority="28" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="332" priority="28" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="331" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="330" priority="30" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P14:P19">
-    <cfRule type="cellIs" dxfId="329" priority="48" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="328" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="327" priority="47" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="329" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="328" priority="47" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="327" priority="48" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P24">
@@ -19310,47 +19318,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26:P32">
-    <cfRule type="cellIs" dxfId="323" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="84" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="321" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="323" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="322" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="321" priority="84" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P34:P35">
-    <cfRule type="cellIs" dxfId="320" priority="102" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="320" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="319" priority="101" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="318" priority="102" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P40">
-    <cfRule type="cellIs" dxfId="317" priority="119" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="120" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="317" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="316" priority="119" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="315" priority="120" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="cellIs" dxfId="314" priority="155" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="313" priority="154" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="314" priority="154" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="313" priority="155" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="312" priority="156" operator="lessThan">
@@ -19382,51 +19390,51 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S14:S19">
-    <cfRule type="cellIs" dxfId="305" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="305" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="304" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="303" priority="51" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S24">
-    <cfRule type="cellIs" dxfId="302" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="301" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="302" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="301" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="300" priority="69" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S26:S32">
     <cfRule type="cellIs" dxfId="299" priority="85" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="87" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="297" priority="86" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="298" priority="86" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="297" priority="87" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S34:S35">
-    <cfRule type="cellIs" dxfId="296" priority="105" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="296" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="295" priority="104" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="294" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="294" priority="105" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S37:S40">
@@ -19457,20 +19465,20 @@
     <cfRule type="cellIs" dxfId="287" priority="16" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="286" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="285" priority="18" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:V12">
-    <cfRule type="cellIs" dxfId="284" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="283" priority="34" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="284" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="283" priority="35" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="282" priority="36" operator="lessThan">
@@ -19478,15 +19486,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V14:V19">
-    <cfRule type="cellIs" dxfId="281" priority="54" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="281" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="280" priority="53" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="279" priority="54" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V24">
@@ -19502,39 +19510,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26:V32">
-    <cfRule type="cellIs" dxfId="275" priority="90" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="275" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="274" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="273" priority="90" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V34:V35">
-    <cfRule type="cellIs" dxfId="272" priority="108" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="272" priority="106" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="271" priority="107" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="106" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="270" priority="108" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V37:V40">
-    <cfRule type="cellIs" dxfId="269" priority="125" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="124" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="269" priority="124" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="268" priority="125" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="267" priority="126" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
@@ -19568,7 +19576,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="54" t="s">
         <v>247</v>
       </c>
       <c r="B1" s="55"/>
@@ -19595,7 +19603,7 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="59" t="s">
         <v>160</v>
       </c>
       <c r="B3" s="57"/>
@@ -19609,7 +19617,7 @@
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="72" t="s">
+      <c r="M3" s="56" t="s">
         <v>161</v>
       </c>
       <c r="N3" s="57"/>
@@ -21180,39 +21188,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="257" priority="39" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="257" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="256" priority="38" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="255" priority="39" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="254" priority="57" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="55" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="56" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="254" priority="55" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="253" priority="56" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="252" priority="57" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E28">
     <cfRule type="cellIs" dxfId="251" priority="73" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="75" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="74" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="250" priority="74" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="249" priority="75" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
@@ -21228,51 +21236,51 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H11">
-    <cfRule type="cellIs" dxfId="245" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="6" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="245" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="244" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="243" priority="6" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:H16">
-    <cfRule type="cellIs" dxfId="242" priority="24" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="242" priority="22" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="241" priority="23" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="240" priority="24" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" dxfId="239" priority="42" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="239" priority="40" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="238" priority="41" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="40" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="237" priority="42" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:H23">
-    <cfRule type="cellIs" dxfId="236" priority="60" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="236" priority="58" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="235" priority="59" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="58" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="234" priority="60" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H28">
@@ -21288,15 +21296,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="cellIs" dxfId="230" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="113" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="230" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="229" priority="113" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="228" priority="114" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K11">
@@ -21312,27 +21320,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K16">
-    <cfRule type="cellIs" dxfId="224" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="224" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="222" priority="27" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:K19">
-    <cfRule type="cellIs" dxfId="221" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="221" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="220" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="219" priority="45" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K23">
@@ -21348,27 +21356,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K28">
-    <cfRule type="cellIs" dxfId="215" priority="81" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="215" priority="79" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="214" priority="80" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="79" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="213" priority="81" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="cellIs" dxfId="212" priority="117" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="212" priority="115" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="211" priority="116" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="115" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="210" priority="117" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:P11">
@@ -21396,15 +21404,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:P19">
-    <cfRule type="cellIs" dxfId="203" priority="48" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="203" priority="46" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="202" priority="47" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="46" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="201" priority="48" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P21:P23">
@@ -21420,75 +21428,75 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P25:P28">
-    <cfRule type="cellIs" dxfId="197" priority="84" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="82" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="83" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="197" priority="82" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="196" priority="83" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="195" priority="84" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30">
-    <cfRule type="cellIs" dxfId="194" priority="120" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="194" priority="118" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="193" priority="119" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="118" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="192" priority="120" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S11">
     <cfRule type="cellIs" dxfId="191" priority="13" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="15" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="14" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="190" priority="14" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="189" priority="15" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S16">
-    <cfRule type="cellIs" dxfId="188" priority="33" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="32" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="188" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="187" priority="32" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="33" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S19">
-    <cfRule type="cellIs" dxfId="185" priority="51" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="49" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="185" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="184" priority="50" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="183" priority="51" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S21:S23">
-    <cfRule type="cellIs" dxfId="182" priority="69" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="68" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="182" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="181" priority="68" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="69" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S25:S28">
@@ -21504,23 +21512,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S30">
-    <cfRule type="cellIs" dxfId="176" priority="123" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="176" priority="121" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="175" priority="122" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="121" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="174" priority="123" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V11">
-    <cfRule type="cellIs" dxfId="173" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="173" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="172" priority="17" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="171" priority="18" operator="lessThan">
@@ -21528,11 +21536,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V16">
-    <cfRule type="cellIs" dxfId="170" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="34" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="170" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="169" priority="35" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="168" priority="36" operator="lessThan">
@@ -21552,27 +21560,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V21:V23">
-    <cfRule type="cellIs" dxfId="164" priority="72" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="70" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="71" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="164" priority="70" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="163" priority="71" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="162" priority="72" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25:V28">
-    <cfRule type="cellIs" dxfId="161" priority="90" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="161" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="160" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="159" priority="90" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
@@ -21606,7 +21614,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="54" t="s">
         <v>270</v>
       </c>
       <c r="B1" s="55"/>
@@ -21633,7 +21641,7 @@
     </row>
     <row r="2" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="59" t="s">
         <v>160</v>
       </c>
       <c r="B3" s="57"/>
@@ -21647,7 +21655,7 @@
       <c r="J3" s="57"/>
       <c r="K3" s="58"/>
       <c r="L3" s="11"/>
-      <c r="M3" s="72" t="s">
+      <c r="M3" s="56" t="s">
         <v>161</v>
       </c>
       <c r="N3" s="57"/>
@@ -23774,15 +23782,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="149" priority="38" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="39" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="149" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="148" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="147" priority="39" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
@@ -23810,11 +23818,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="140" priority="92" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="91" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="140" priority="91" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="92" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="138" priority="93" operator="lessThan">
@@ -23822,15 +23830,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="137" priority="129" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="127" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="128" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="137" priority="127" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="128" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="129" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H7">
@@ -23870,27 +23878,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H28">
-    <cfRule type="cellIs" dxfId="125" priority="60" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="125" priority="58" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="124" priority="59" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="58" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="123" priority="60" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:H32">
-    <cfRule type="cellIs" dxfId="122" priority="78" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="77" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="122" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="77" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="78" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H39">
@@ -23918,51 +23926,51 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K7">
-    <cfRule type="cellIs" dxfId="113" priority="9" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="113" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="112" priority="8" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="111" priority="9" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K11">
-    <cfRule type="cellIs" dxfId="110" priority="27" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="25" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="26" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="110" priority="25" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="26" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="27" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:K20">
-    <cfRule type="cellIs" dxfId="107" priority="44" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="45" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="43" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="107" priority="43" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="44" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="45" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:K28">
-    <cfRule type="cellIs" dxfId="104" priority="62" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="63" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="104" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="62" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="63" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:K32">
@@ -24005,24 +24013,24 @@
     <cfRule type="cellIs" dxfId="92" priority="10" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="12" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="91" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="12" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:P11">
     <cfRule type="cellIs" dxfId="89" priority="28" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="30" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="29" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="88" priority="29" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="30" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P20">
@@ -24062,59 +24070,59 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P34:P39">
-    <cfRule type="cellIs" dxfId="77" priority="102" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="100" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="101" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="77" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="102" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P41">
-    <cfRule type="cellIs" dxfId="74" priority="138" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="136" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="137" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="74" priority="136" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="137" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="138" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:S7">
-    <cfRule type="cellIs" dxfId="71" priority="15" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="71" priority="13" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="70" priority="14" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="13" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="69" priority="15" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S9:S11">
-    <cfRule type="cellIs" dxfId="68" priority="33" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="68" priority="31" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="67" priority="32" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="31" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="66" priority="33" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:S20">
-    <cfRule type="cellIs" dxfId="65" priority="50" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="65" priority="49" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="50" operator="between">
+      <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="63" priority="51" operator="lessThan">
@@ -24122,15 +24130,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S22:S28">
-    <cfRule type="cellIs" dxfId="62" priority="69" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="62" priority="67" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="61" priority="68" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="67" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="60" priority="69" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S30:S32">
@@ -24146,15 +24154,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S34:S39">
-    <cfRule type="cellIs" dxfId="56" priority="105" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="56" priority="103" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="55" priority="104" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="103" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="54" priority="105" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S41">
@@ -24170,39 +24178,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V7">
-    <cfRule type="cellIs" dxfId="50" priority="18" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="50" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="49" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="48" priority="18" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9:V11">
-    <cfRule type="cellIs" dxfId="47" priority="35" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="36" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="34" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="47" priority="34" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="35" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="36" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:V20">
-    <cfRule type="cellIs" dxfId="44" priority="54" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="44" priority="52" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="43" priority="53" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="52" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="42" priority="54" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22:V28">
@@ -24218,15 +24226,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30:V32">
-    <cfRule type="cellIs" dxfId="38" priority="90" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="38" priority="88" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="37" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="88" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="36" priority="90" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V34:V39">

--- a/习题册.xlsx
+++ b/习题册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440D2737-C0B1-4A91-9A05-A2BA44677AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E182BC50-5042-42CD-A249-C0DE6A84CCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="张宇1000题" sheetId="1" r:id="rId1"/>
@@ -1803,6 +1803,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1811,6 +1827,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1827,6 +1851,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1835,6 +1875,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1851,6 +1907,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1859,6 +1923,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1875,6 +1947,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1883,6 +1971,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1899,6 +1995,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1907,6 +2019,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1923,6 +2051,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1931,6 +2067,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -1939,6 +2083,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -1979,6 +2139,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2043,6 +2211,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2051,6 +2227,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2059,6 +2243,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2139,6 +2331,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2179,6 +2379,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2195,6 +2403,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2203,6 +2419,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2235,6 +2475,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2243,6 +2499,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2251,6 +2515,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2307,6 +2595,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2315,6 +2619,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2323,6 +2643,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2355,6 +2691,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2371,6 +2715,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2427,6 +2787,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2459,6 +2835,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2483,6 +2867,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2491,6 +2883,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2499,6 +2899,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2507,6 +2931,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2523,6 +2955,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2587,6 +3035,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2595,6 +3051,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2627,6 +3099,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2643,6 +3123,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2651,6 +3147,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2691,6 +3195,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2699,6 +3219,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2707,6 +3235,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2715,6 +3267,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2723,6 +3291,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2731,6 +3315,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2739,6 +3339,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2747,6 +3363,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2763,6 +3387,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2771,6 +3411,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2779,6 +3427,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2795,6 +3459,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2803,6 +3483,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2811,6 +3507,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2819,6 +3523,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2843,6 +3555,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2851,6 +3571,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2907,6 +3651,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2931,6 +3683,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2939,6 +3699,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2947,6 +3715,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -2955,6 +3747,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2963,6 +3771,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -2971,6 +3795,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3027,6 +3867,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3043,6 +3899,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3051,6 +3915,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3091,6 +3963,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3131,6 +4019,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3171,6 +4067,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3179,6 +4083,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3187,6 +4107,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3195,6 +4131,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3203,6 +4155,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3211,6 +4179,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3219,6 +4203,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3227,6 +4227,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3235,6 +4243,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3243,6 +4267,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3267,6 +4299,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3275,6 +4323,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3363,6 +4419,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3371,6 +4443,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3379,6 +4459,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3483,6 +4587,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3491,6 +4611,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3499,6 +4627,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3675,6 +4827,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3683,6 +4843,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3691,6 +4867,30 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3699,6 +4899,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3731,6 +4947,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3739,6 +4971,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3771,6 +5019,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -3779,6 +5043,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFEB9C"/>
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
@@ -3787,6 +5067,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
@@ -3795,6 +5083,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF